--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -556,10 +556,10 @@
         <v>320</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>8640000</v>
+        <v>8646939.759036161</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1624,10 +1624,10 @@
         <v>23</v>
       </c>
       <c r="N31" t="n">
-        <v>14857.623272727</v>
+        <v>14857.623287671</v>
       </c>
       <c r="O31" t="n">
-        <v>341725.335272721</v>
+        <v>341725.335616433</v>
       </c>
       <c r="P31" t="n">
         <v>34900</v>
@@ -4075,10 +4075,10 @@
         <v>1235</v>
       </c>
       <c r="N87" t="n">
-        <v>10600</v>
+        <v>10603.665283541</v>
       </c>
       <c r="O87" t="n">
-        <v>13091000</v>
+        <v>13095526.62517313</v>
       </c>
       <c r="P87" t="n">
         <v>17200</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.723754458</v>
+        <v>3474452.723357589</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.795543168</v>
+        <v>863221.925017416</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -6751,10 +6751,10 @@
         <v>1930</v>
       </c>
       <c r="N146" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O146" t="n">
-        <v>8436360.534186831</v>
+        <v>8437509.745538689</v>
       </c>
       <c r="P146" t="n">
         <v>8900</v>
@@ -8770,10 +8770,10 @@
         <v>1422</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1943880809</v>
+        <v>1550.1943922358</v>
       </c>
       <c r="O190" t="n">
-        <v>2204376.41985104</v>
+        <v>2204376.425759308</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5165803524</v>
+        <v>2403.5166025127</v>
       </c>
       <c r="O192" t="n">
-        <v>418211.8849813176</v>
+        <v>418211.8888372098</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -11700,10 +11700,10 @@
         <v>522</v>
       </c>
       <c r="N256" t="n">
-        <v>1561.0035960591</v>
+        <v>1561.003634439</v>
       </c>
       <c r="O256" t="n">
-        <v>814843.8771428502</v>
+        <v>814843.897177158</v>
       </c>
       <c r="P256" t="n">
         <v>2900</v>
@@ -18159,10 +18159,10 @@
         <v>1248</v>
       </c>
       <c r="N396" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O396" t="n">
-        <v>1892016.36599639</v>
+        <v>1892016.365524647</v>
       </c>
       <c r="P396" t="n">
         <v>2300</v>
@@ -18343,10 +18343,10 @@
         <v>168</v>
       </c>
       <c r="N400" t="n">
-        <v>2079.3834819145</v>
+        <v>2079.3834145441</v>
       </c>
       <c r="O400" t="n">
-        <v>349336.424961636</v>
+        <v>349336.4136434088</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -19485,22 +19485,22 @@
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M425" t="n">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="N425" t="n">
         <v>9736</v>
       </c>
       <c r="O425" t="n">
-        <v>7009920</v>
+        <v>6893088</v>
       </c>
       <c r="P425" t="n">
         <v>15900</v>
       </c>
       <c r="Q425" t="n">
-        <v>11448000</v>
+        <v>11257200</v>
       </c>
     </row>
     <row r="426">
@@ -20604,10 +20604,10 @@
         <v>306</v>
       </c>
       <c r="N449" t="n">
-        <v>1690.8700092894</v>
+        <v>1690.870009298</v>
       </c>
       <c r="O449" t="n">
-        <v>517406.2228425564</v>
+        <v>517406.222845188</v>
       </c>
       <c r="P449" t="n">
         <v>3000</v>
@@ -20937,10 +20937,10 @@
         <v>140</v>
       </c>
       <c r="N456" t="n">
-        <v>3907.5003375527</v>
+        <v>3907.5003418803</v>
       </c>
       <c r="O456" t="n">
-        <v>547050.047257378</v>
+        <v>547050.047863242</v>
       </c>
       <c r="P456" t="n">
         <v>3900</v>
@@ -22272,10 +22272,10 @@
         <v>18602</v>
       </c>
       <c r="N485" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O485" t="n">
-        <v>13091991.56374795</v>
+        <v>13093338.64969666</v>
       </c>
       <c r="P485" t="n">
         <v>900</v>
@@ -26412,10 +26412,10 @@
         <v>62</v>
       </c>
       <c r="N572" t="n">
-        <v>8919.16</v>
+        <v>8975.6103797468</v>
       </c>
       <c r="O572" t="n">
-        <v>552987.92</v>
+        <v>556487.8435443016</v>
       </c>
       <c r="P572" t="n">
         <v>10000</v>
@@ -27375,10 +27375,10 @@
         <v>95</v>
       </c>
       <c r="N592" t="n">
-        <v>315.02726865672</v>
+        <v>315.02740121581</v>
       </c>
       <c r="O592" t="n">
-        <v>29927.5905223884</v>
+        <v>29927.60311550195</v>
       </c>
       <c r="P592" t="n">
         <v>2200</v>
@@ -28415,22 +28415,22 @@
         <v>0</v>
       </c>
       <c r="L616" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M616" t="n">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="N616" t="n">
         <v>22951.704717477</v>
       </c>
       <c r="O616" t="n">
-        <v>7734724.489789749</v>
+        <v>7459304.033180025</v>
       </c>
       <c r="P616" t="n">
         <v>37900</v>
       </c>
       <c r="Q616" t="n">
-        <v>12772300</v>
+        <v>12317500</v>
       </c>
     </row>
     <row r="617">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -2005,10 +2005,10 @@
         <v>46</v>
       </c>
       <c r="N40" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O40" t="n">
-        <v>6505176.692541161</v>
+        <v>6526717.01271518</v>
       </c>
       <c r="P40" t="n">
         <v>251900</v>
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O86" t="n">
-        <v>1719781.921054654</v>
+        <v>1719781.917096083</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4433,22 +4433,22 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M95" t="n">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="N95" t="n">
-        <v>8214</v>
+        <v>8701.9603960396</v>
       </c>
       <c r="O95" t="n">
-        <v>2349204</v>
+        <v>2279913.623762375</v>
       </c>
       <c r="P95" t="n">
         <v>7900</v>
       </c>
       <c r="Q95" t="n">
-        <v>2259400</v>
+        <v>2069800</v>
       </c>
     </row>
     <row r="96">
@@ -8160,22 +8160,22 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M177" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N177" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O177" t="n">
-        <v>1394803.8</v>
+        <v>1362272.842505952</v>
       </c>
       <c r="P177" t="n">
         <v>19900</v>
       </c>
       <c r="Q177" t="n">
-        <v>2328300</v>
+        <v>2268600</v>
       </c>
     </row>
     <row r="178">
@@ -8632,10 +8632,10 @@
         <v>556</v>
       </c>
       <c r="N187" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O187" t="n">
-        <v>906793.874427314</v>
+        <v>906793.8783232061</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O192" t="n">
-        <v>418211.943120912</v>
+        <v>418211.9447247917</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -11163,10 +11163,10 @@
         <v>1280</v>
       </c>
       <c r="N244" t="n">
-        <v>4814.2679274047</v>
+        <v>4814.2679269747</v>
       </c>
       <c r="O244" t="n">
-        <v>6162262.947078016</v>
+        <v>6162262.946527615</v>
       </c>
       <c r="P244" t="n">
         <v>9900</v>
@@ -11561,22 +11561,22 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M253" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N253" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O253" t="n">
-        <v>882683.8799999999</v>
+        <v>853941.4601227</v>
       </c>
       <c r="P253" t="n">
         <v>26900</v>
       </c>
       <c r="Q253" t="n">
-        <v>1398800</v>
+        <v>1345000</v>
       </c>
     </row>
     <row r="254">
@@ -11878,22 +11878,22 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M260" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="N260" t="n">
-        <v>9627.34</v>
+        <v>11147.446315789</v>
       </c>
       <c r="O260" t="n">
-        <v>673913.8</v>
+        <v>512782.530526294</v>
       </c>
       <c r="P260" t="n">
         <v>15900</v>
       </c>
       <c r="Q260" t="n">
-        <v>1113000</v>
+        <v>731400</v>
       </c>
     </row>
     <row r="261">
@@ -12486,22 +12486,22 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M273" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="N273" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O273" t="n">
-        <v>2772000</v>
+        <v>2718765.895249705</v>
       </c>
       <c r="P273" t="n">
         <v>13900</v>
       </c>
       <c r="Q273" t="n">
-        <v>5004000</v>
+        <v>4837200</v>
       </c>
     </row>
     <row r="274">
@@ -12860,10 +12860,10 @@
         <v>81</v>
       </c>
       <c r="N281" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O281" t="n">
-        <v>422671.8170805777</v>
+        <v>422671.8172053015</v>
       </c>
       <c r="P281" t="n">
         <v>8500</v>
@@ -18113,10 +18113,10 @@
         <v>1248</v>
       </c>
       <c r="N395" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O395" t="n">
-        <v>1892016.362056579</v>
+        <v>1892016.361740586</v>
       </c>
       <c r="P395" t="n">
         <v>2300</v>
@@ -22226,10 +22226,10 @@
         <v>18602</v>
       </c>
       <c r="N484" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O484" t="n">
-        <v>13091991.40415972</v>
+        <v>13091991.38928742</v>
       </c>
       <c r="P484" t="n">
         <v>900</v>
@@ -27830,22 +27830,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M603" t="n">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="N603" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O603" t="n">
-        <v>2147782.5</v>
+        <v>2062512.872141393</v>
       </c>
       <c r="P603" t="n">
         <v>5100</v>
       </c>
       <c r="Q603" t="n">
-        <v>3442500</v>
+        <v>3238500</v>
       </c>
     </row>
     <row r="604">
@@ -28693,22 +28693,22 @@
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M622" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N622" t="n">
-        <v>3504.16</v>
+        <v>5649.5640816327</v>
       </c>
       <c r="O622" t="n">
-        <v>210249.6</v>
+        <v>169486.922448981</v>
       </c>
       <c r="P622" t="n">
         <v>3900</v>
       </c>
       <c r="Q622" t="n">
-        <v>234000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="623">
@@ -28877,22 +28877,22 @@
         <v>0</v>
       </c>
       <c r="L626" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M626" t="n">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="N626" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O626" t="n">
-        <v>712720.9</v>
+        <v>698860.3050000001</v>
       </c>
       <c r="P626" t="n">
         <v>3500</v>
       </c>
       <c r="Q626" t="n">
-        <v>1277500</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="627">
@@ -29761,22 +29761,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M645" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="N645" t="n">
-        <v>751.45</v>
+        <v>1093.0181818182</v>
       </c>
       <c r="O645" t="n">
-        <v>23294.95</v>
+        <v>1093.0181818182</v>
       </c>
       <c r="P645" t="n">
         <v>2500</v>
       </c>
       <c r="Q645" t="n">
-        <v>77500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="646">
@@ -30005,10 +30005,10 @@
         <v>95</v>
       </c>
       <c r="N650" t="n">
-        <v>4171.6685988024</v>
+        <v>4171.6685954382</v>
       </c>
       <c r="O650" t="n">
-        <v>396308.516886228</v>
+        <v>396308.516566629</v>
       </c>
       <c r="P650" t="n">
         <v>5000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="N34" t="n">
-        <v>16486.40779661</v>
+        <v>16486.407586207</v>
       </c>
       <c r="O34" t="n">
-        <v>395673.78711864</v>
+        <v>395673.7820689679</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
@@ -1802,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>13712.841538462</v>
+        <v>13712.84</v>
       </c>
       <c r="O35" t="n">
-        <v>13712.841538462</v>
+        <v>13712.84</v>
       </c>
       <c r="P35" t="n">
         <v>22600</v>
@@ -2005,10 +2005,10 @@
         <v>46</v>
       </c>
       <c r="N40" t="n">
-        <v>141885.15245033</v>
+        <v>141416.88463576</v>
       </c>
       <c r="O40" t="n">
-        <v>6526717.01271518</v>
+        <v>6505176.69324496</v>
       </c>
       <c r="P40" t="n">
         <v>251900</v>
@@ -2875,10 +2875,10 @@
         <v>228</v>
       </c>
       <c r="N60" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.3101659125</v>
       </c>
       <c r="O60" t="n">
-        <v>1125706.717714278</v>
+        <v>1125706.71782805</v>
       </c>
       <c r="P60" t="n">
         <v>7500</v>
@@ -3096,10 +3096,10 @@
         <v>1271</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.0632479443</v>
+        <v>1098.0633365079</v>
       </c>
       <c r="O65" t="n">
-        <v>1395638.388137205</v>
+        <v>1395638.500701541</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2551307749</v>
+        <v>2582.2550693069</v>
       </c>
       <c r="O86" t="n">
-        <v>1719781.917096083</v>
+        <v>1719781.876158396</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.895979825</v>
+        <v>5216.8959750483</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.72256345</v>
+        <v>3474452.719382168</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4427,22 +4427,22 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>262</v>
       </c>
       <c r="N95" t="n">
-        <v>8701.9603960396</v>
+        <v>8214</v>
       </c>
       <c r="O95" t="n">
-        <v>2279913.623762375</v>
+        <v>2152068</v>
       </c>
       <c r="P95" t="n">
         <v>7900</v>
@@ -5172,10 +5172,10 @@
         <v>309</v>
       </c>
       <c r="N111" t="n">
-        <v>4890.9300509879</v>
+        <v>4890.9300510856</v>
       </c>
       <c r="O111" t="n">
-        <v>1511297.385755261</v>
+        <v>1511297.38578545</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N113" t="n">
         <v>5888</v>
       </c>
       <c r="O113" t="n">
-        <v>783104</v>
+        <v>759552</v>
       </c>
       <c r="P113" t="n">
         <v>9500</v>
       </c>
       <c r="Q113" t="n">
-        <v>1263500</v>
+        <v>1225500</v>
       </c>
     </row>
     <row r="114">
@@ -5351,10 +5351,10 @@
         <v>309</v>
       </c>
       <c r="N115" t="n">
-        <v>2267.0481103035</v>
+        <v>2267.0481062554</v>
       </c>
       <c r="O115" t="n">
-        <v>700517.8660837815</v>
+        <v>700517.8648329186</v>
       </c>
       <c r="P115" t="n">
         <v>3900</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5486,19 +5486,19 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N118" t="n">
         <v>8012</v>
       </c>
       <c r="O118" t="n">
-        <v>1954928</v>
+        <v>1938904</v>
       </c>
       <c r="P118" t="n">
         <v>13200</v>
       </c>
       <c r="Q118" t="n">
-        <v>3220800</v>
+        <v>3194400</v>
       </c>
     </row>
     <row r="119">
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2532489451</v>
+        <v>3594.2532155477</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.7797468241</v>
+        <v>862620.771731448</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -5712,10 +5712,10 @@
         <v>108</v>
       </c>
       <c r="N123" t="n">
-        <v>3240.8500492611</v>
+        <v>3240.8500493827</v>
       </c>
       <c r="O123" t="n">
-        <v>350011.8053201988</v>
+        <v>350011.8053333316</v>
       </c>
       <c r="P123" t="n">
         <v>5200</v>
@@ -6261,10 +6261,10 @@
         <v>320</v>
       </c>
       <c r="N135" t="n">
-        <v>12422.462939145</v>
+        <v>12422.462940415</v>
       </c>
       <c r="O135" t="n">
-        <v>3975188.1405264</v>
+        <v>3975188.1409328</v>
       </c>
       <c r="P135" t="n">
         <v>19900</v>
@@ -6394,10 +6394,10 @@
         <v>2520</v>
       </c>
       <c r="N138" t="n">
-        <v>3472.0232664284</v>
+        <v>3472.2761671707</v>
       </c>
       <c r="O138" t="n">
-        <v>8749498.631399568</v>
+        <v>8750135.941270163</v>
       </c>
       <c r="P138" t="n">
         <v>5900</v>
@@ -6623,10 +6623,10 @@
         <v>210</v>
       </c>
       <c r="N143" t="n">
-        <v>3041.6600139179</v>
+        <v>3041.660013947</v>
       </c>
       <c r="O143" t="n">
-        <v>638748.602922759</v>
+        <v>638748.60292887</v>
       </c>
       <c r="P143" t="n">
         <v>5500</v>
@@ -6751,10 +6751,10 @@
         <v>1930</v>
       </c>
       <c r="N146" t="n">
-        <v>4371.1712622683</v>
+        <v>4371.1712623543</v>
       </c>
       <c r="O146" t="n">
-        <v>8436360.53617782</v>
+        <v>8436360.536343798</v>
       </c>
       <c r="P146" t="n">
         <v>8900</v>
@@ -6841,10 +6841,10 @@
         <v>181</v>
       </c>
       <c r="N148" t="n">
-        <v>1592.5654664342</v>
+        <v>1592.5654585153</v>
       </c>
       <c r="O148" t="n">
-        <v>288254.3494245902</v>
+        <v>288254.3479912693</v>
       </c>
       <c r="P148" t="n">
         <v>3900</v>
@@ -7831,10 +7831,10 @@
         <v>71</v>
       </c>
       <c r="N170" t="n">
-        <v>2021.7211300122</v>
+        <v>2021.7211313869</v>
       </c>
       <c r="O170" t="n">
-        <v>143542.2002308662</v>
+        <v>143542.2003284699</v>
       </c>
       <c r="P170" t="n">
         <v>2400</v>
@@ -8154,22 +8154,22 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>114</v>
       </c>
       <c r="N177" t="n">
-        <v>11949.761776368</v>
+        <v>11921.4</v>
       </c>
       <c r="O177" t="n">
-        <v>1362272.842505952</v>
+        <v>1359039.6</v>
       </c>
       <c r="P177" t="n">
         <v>19900</v>
@@ -8632,10 +8632,10 @@
         <v>556</v>
       </c>
       <c r="N187" t="n">
-        <v>1630.9242415885</v>
+        <v>1630.9242710358</v>
       </c>
       <c r="O187" t="n">
-        <v>906793.8783232061</v>
+        <v>906793.8946959048</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8724,10 +8724,10 @@
         <v>192</v>
       </c>
       <c r="N189" t="n">
-        <v>1690.5851822323</v>
+        <v>1690.5835202864</v>
       </c>
       <c r="O189" t="n">
-        <v>324592.3549886016</v>
+        <v>324592.0358949888</v>
       </c>
       <c r="P189" t="n">
         <v>2900</v>
@@ -8770,10 +8770,10 @@
         <v>1422</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.19440684</v>
+        <v>1550.1944427152</v>
       </c>
       <c r="O190" t="n">
-        <v>2204376.44652648</v>
+        <v>2204376.497541015</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8816,10 +8816,10 @@
         <v>22</v>
       </c>
       <c r="N191" t="n">
-        <v>1579.3856972112</v>
+        <v>1579.38564</v>
       </c>
       <c r="O191" t="n">
-        <v>34746.4853386464</v>
+        <v>34746.48408</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5169237057</v>
+        <v>2403.5172431982</v>
       </c>
       <c r="O192" t="n">
-        <v>418211.9447247917</v>
+        <v>418212.0003164868</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -10153,19 +10153,19 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N221" t="n">
         <v>2610</v>
       </c>
       <c r="O221" t="n">
-        <v>234900</v>
+        <v>227070</v>
       </c>
       <c r="P221" t="n">
         <v>3200</v>
       </c>
       <c r="Q221" t="n">
-        <v>288000</v>
+        <v>278400</v>
       </c>
     </row>
     <row r="222">
@@ -10717,10 +10717,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>3731.0244107744</v>
+        <v>3731.024440678</v>
       </c>
       <c r="O234" t="n">
-        <v>44772.2929292928</v>
+        <v>44772.293288136</v>
       </c>
       <c r="P234" t="n">
         <v>5200</v>
@@ -10809,10 +10809,10 @@
         <v>960</v>
       </c>
       <c r="N236" t="n">
-        <v>6207.9842244133</v>
+        <v>6207.9882238578</v>
       </c>
       <c r="O236" t="n">
-        <v>5959664.855436767</v>
+        <v>5959668.694903488</v>
       </c>
       <c r="P236" t="n">
         <v>9900</v>
@@ -10904,10 +10904,10 @@
         <v>113</v>
       </c>
       <c r="N238" t="n">
-        <v>4285.1961725395</v>
+        <v>4285.1962026862</v>
       </c>
       <c r="O238" t="n">
-        <v>484227.1674969635</v>
+        <v>484227.1709035406</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
@@ -11296,10 +11296,10 @@
         <v>17</v>
       </c>
       <c r="N247" t="n">
-        <v>13513.643333333</v>
+        <v>13513.643445378</v>
       </c>
       <c r="O247" t="n">
-        <v>229731.936666661</v>
+        <v>229731.938571426</v>
       </c>
       <c r="P247" t="n">
         <v>21900</v>
@@ -11555,22 +11555,22 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
         <v>50</v>
       </c>
       <c r="N253" t="n">
-        <v>17078.829202454</v>
+        <v>16974.69</v>
       </c>
       <c r="O253" t="n">
-        <v>853941.4601227</v>
+        <v>848734.4999999999</v>
       </c>
       <c r="P253" t="n">
         <v>26900</v>
@@ -11872,22 +11872,22 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
         <v>46</v>
       </c>
       <c r="N260" t="n">
-        <v>11147.446315789</v>
+        <v>9627.34</v>
       </c>
       <c r="O260" t="n">
-        <v>512782.530526294</v>
+        <v>442857.64</v>
       </c>
       <c r="P260" t="n">
         <v>15900</v>
@@ -12480,22 +12480,22 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
         <v>348</v>
       </c>
       <c r="N273" t="n">
-        <v>7812.5456760049</v>
+        <v>7700</v>
       </c>
       <c r="O273" t="n">
-        <v>2718765.895249705</v>
+        <v>2679600</v>
       </c>
       <c r="P273" t="n">
         <v>13900</v>
@@ -12538,10 +12538,10 @@
         <v>122</v>
       </c>
       <c r="N274" t="n">
-        <v>3113.8900281294</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O274" t="n">
-        <v>379894.5834317868</v>
+        <v>379894.583451197</v>
       </c>
       <c r="P274" t="n">
         <v>5000</v>
@@ -14896,10 +14896,10 @@
         <v>5</v>
       </c>
       <c r="N325" t="n">
-        <v>2252.2978962963</v>
+        <v>2252.2979080119</v>
       </c>
       <c r="O325" t="n">
-        <v>11261.4894814815</v>
+        <v>11261.4895400595</v>
       </c>
       <c r="P325" t="n">
         <v>3900</v>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15357,19 +15357,19 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N335" t="n">
         <v>32332</v>
       </c>
       <c r="O335" t="n">
-        <v>193992</v>
+        <v>161660</v>
       </c>
       <c r="P335" t="n">
         <v>55900</v>
       </c>
       <c r="Q335" t="n">
-        <v>335400</v>
+        <v>279500</v>
       </c>
     </row>
     <row r="336">
@@ -15866,10 +15866,10 @@
         <v>137</v>
       </c>
       <c r="N346" t="n">
-        <v>4907.82254</v>
+        <v>4907.8225450902</v>
       </c>
       <c r="O346" t="n">
-        <v>672371.68798</v>
+        <v>672371.6886773574</v>
       </c>
       <c r="P346" t="n">
         <v>8200</v>
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -16047,19 +16047,19 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="N350" t="n">
-        <v>3903.7388764045</v>
+        <v>3903.7389254766</v>
       </c>
       <c r="O350" t="n">
-        <v>1077431.929887642</v>
+        <v>936897.3421143839</v>
       </c>
       <c r="P350" t="n">
         <v>7500</v>
       </c>
       <c r="Q350" t="n">
-        <v>2070000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="351">
@@ -16493,7 +16493,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -16502,19 +16502,19 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="N360" t="n">
         <v>3898</v>
       </c>
       <c r="O360" t="n">
-        <v>611986</v>
+        <v>495046</v>
       </c>
       <c r="P360" t="n">
         <v>6900</v>
       </c>
       <c r="Q360" t="n">
-        <v>1083300</v>
+        <v>876300</v>
       </c>
     </row>
     <row r="361">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -17512,19 +17512,19 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N382" t="n">
         <v>3639.35</v>
       </c>
       <c r="O382" t="n">
-        <v>418525.25</v>
+        <v>407607.2</v>
       </c>
       <c r="P382" t="n">
         <v>7500</v>
       </c>
       <c r="Q382" t="n">
-        <v>862500</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="383">
@@ -18009,7 +18009,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
@@ -18018,19 +18018,19 @@
         <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N393" t="n">
         <v>15223.06</v>
       </c>
       <c r="O393" t="n">
-        <v>776376.0599999999</v>
+        <v>761153</v>
       </c>
       <c r="P393" t="n">
         <v>17500</v>
       </c>
       <c r="Q393" t="n">
-        <v>892500</v>
+        <v>875000</v>
       </c>
     </row>
     <row r="394">
@@ -18205,10 +18205,10 @@
         <v>48</v>
       </c>
       <c r="N397" t="n">
-        <v>2458.5126365879</v>
+        <v>2458.5126313933</v>
       </c>
       <c r="O397" t="n">
-        <v>118008.6065562192</v>
+        <v>118008.6063068784</v>
       </c>
       <c r="P397" t="n">
         <v>3500</v>
@@ -18297,10 +18297,10 @@
         <v>168</v>
       </c>
       <c r="N399" t="n">
-        <v>2079.3834072432</v>
+        <v>2079.3833876946</v>
       </c>
       <c r="O399" t="n">
-        <v>349336.4124168576</v>
+        <v>349336.4091326928</v>
       </c>
       <c r="P399" t="n">
         <v>2900</v>
@@ -18343,10 +18343,10 @@
         <v>48</v>
       </c>
       <c r="N400" t="n">
-        <v>1803.0163058036</v>
+        <v>1803.0164892802</v>
       </c>
       <c r="O400" t="n">
-        <v>86544.78267857281</v>
+        <v>86544.79148544959</v>
       </c>
       <c r="P400" t="n">
         <v>2500</v>
@@ -18435,10 +18435,10 @@
         <v>96</v>
       </c>
       <c r="N402" t="n">
-        <v>2108.7956032172</v>
+        <v>2108.7956591928</v>
       </c>
       <c r="O402" t="n">
-        <v>202444.3779088512</v>
+        <v>202444.3832825088</v>
       </c>
       <c r="P402" t="n">
         <v>2900</v>
@@ -18481,10 +18481,10 @@
         <v>144</v>
       </c>
       <c r="N403" t="n">
-        <v>2056.0823271375</v>
+        <v>2056.0823128492</v>
       </c>
       <c r="O403" t="n">
-        <v>296075.8551078</v>
+        <v>296075.8530502848</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
@@ -18527,10 +18527,10 @@
         <v>90</v>
       </c>
       <c r="N404" t="n">
-        <v>3224.5693668237</v>
+        <v>3224.5693815514</v>
       </c>
       <c r="O404" t="n">
-        <v>290211.243014133</v>
+        <v>290211.244339626</v>
       </c>
       <c r="P404" t="n">
         <v>4500</v>
@@ -20558,10 +20558,10 @@
         <v>306</v>
       </c>
       <c r="N448" t="n">
-        <v>1690.870009298</v>
+        <v>1690.8700093371</v>
       </c>
       <c r="O448" t="n">
-        <v>517406.222845188</v>
+        <v>517406.2228571526</v>
       </c>
       <c r="P448" t="n">
         <v>3000</v>
@@ -20984,10 +20984,10 @@
         <v>5817</v>
       </c>
       <c r="N457" t="n">
-        <v>711.33664937221</v>
+        <v>711.3366477489</v>
       </c>
       <c r="O457" t="n">
-        <v>4137845.289398145</v>
+        <v>4137845.279955351</v>
       </c>
       <c r="P457" t="n">
         <v>900</v>
@@ -21303,10 +21303,10 @@
         <v>52</v>
       </c>
       <c r="N464" t="n">
-        <v>4032.396796875</v>
+        <v>4032.3967885117</v>
       </c>
       <c r="O464" t="n">
-        <v>209684.6334375</v>
+        <v>209684.6330026084</v>
       </c>
       <c r="P464" t="n">
         <v>4200</v>
@@ -21714,7 +21714,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -21723,19 +21723,19 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="N473" t="n">
         <v>3259.1344047619</v>
       </c>
       <c r="O473" t="n">
-        <v>84737.49452380939</v>
+        <v>65182.688095238</v>
       </c>
       <c r="P473" t="n">
         <v>3600</v>
       </c>
       <c r="Q473" t="n">
-        <v>93600</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="474">
@@ -21775,10 +21775,10 @@
         <v>631</v>
       </c>
       <c r="N474" t="n">
-        <v>3110.8380493577</v>
+        <v>3110.8379516019</v>
       </c>
       <c r="O474" t="n">
-        <v>1962938.809144709</v>
+        <v>1962938.747460799</v>
       </c>
       <c r="P474" t="n">
         <v>4500</v>
@@ -22138,10 +22138,10 @@
         <v>240</v>
       </c>
       <c r="N482" t="n">
-        <v>3002.0210014306</v>
+        <v>3002.0210028653</v>
       </c>
       <c r="O482" t="n">
-        <v>720485.040343344</v>
+        <v>720485.040687672</v>
       </c>
       <c r="P482" t="n">
         <v>4500</v>
@@ -22226,10 +22226,10 @@
         <v>18602</v>
       </c>
       <c r="N484" t="n">
-        <v>703.79482793718</v>
+        <v>703.79482106458</v>
       </c>
       <c r="O484" t="n">
-        <v>13091991.38928742</v>
+        <v>13091991.26144332</v>
       </c>
       <c r="P484" t="n">
         <v>900</v>
@@ -24608,10 +24608,10 @@
         <v>94</v>
       </c>
       <c r="N534" t="n">
-        <v>3067.0906122449</v>
+        <v>3067.0906143345</v>
       </c>
       <c r="O534" t="n">
-        <v>288306.5175510206</v>
+        <v>288306.517747443</v>
       </c>
       <c r="P534" t="n">
         <v>7200</v>
@@ -25283,10 +25283,10 @@
         <v>2950</v>
       </c>
       <c r="N548" t="n">
-        <v>286.61333044868</v>
+        <v>286.61335546613</v>
       </c>
       <c r="O548" t="n">
-        <v>845509.3248236061</v>
+        <v>845509.3986250834</v>
       </c>
       <c r="P548" t="n">
         <v>350</v>
@@ -27824,22 +27824,22 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M603" t="n">
         <v>635</v>
       </c>
       <c r="N603" t="n">
-        <v>3248.0517671518</v>
+        <v>3181.9</v>
       </c>
       <c r="O603" t="n">
-        <v>2062512.872141393</v>
+        <v>2020506.5</v>
       </c>
       <c r="P603" t="n">
         <v>5100</v>
@@ -27921,10 +27921,10 @@
         <v>450</v>
       </c>
       <c r="N605" t="n">
-        <v>1794.287966004</v>
+        <v>1794.2879651247</v>
       </c>
       <c r="O605" t="n">
-        <v>807429.5847018</v>
+        <v>807429.5843061149</v>
       </c>
       <c r="P605" t="n">
         <v>1600</v>
@@ -27965,10 +27965,10 @@
         <v>44</v>
       </c>
       <c r="N606" t="n">
-        <v>2830.2251488095</v>
+        <v>2830.2251641791</v>
       </c>
       <c r="O606" t="n">
-        <v>124529.906547618</v>
+        <v>124529.9072238804</v>
       </c>
       <c r="P606" t="n">
         <v>2400</v>
@@ -28053,10 +28053,10 @@
         <v>190</v>
       </c>
       <c r="N608" t="n">
-        <v>2523.3377451257</v>
+        <v>2523.3377380952</v>
       </c>
       <c r="O608" t="n">
-        <v>479434.171573883</v>
+        <v>479434.1702380881</v>
       </c>
       <c r="P608" t="n">
         <v>2800</v>
@@ -28687,22 +28687,22 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M622" t="n">
         <v>30</v>
       </c>
       <c r="N622" t="n">
-        <v>5649.5640816327</v>
+        <v>3504.16</v>
       </c>
       <c r="O622" t="n">
-        <v>169486.922448981</v>
+        <v>105124.8</v>
       </c>
       <c r="P622" t="n">
         <v>3900</v>
@@ -28825,7 +28825,7 @@
         </is>
       </c>
       <c r="J625" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K625" t="n">
         <v>0</v>
@@ -28834,19 +28834,19 @@
         <v>0</v>
       </c>
       <c r="M625" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N625" t="n">
         <v>14576.2</v>
       </c>
       <c r="O625" t="n">
-        <v>116609.6</v>
+        <v>102033.4</v>
       </c>
       <c r="P625" t="n">
         <v>19000</v>
       </c>
       <c r="Q625" t="n">
-        <v>152000</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="626">
@@ -28871,22 +28871,22 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
       </c>
       <c r="L626" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M626" t="n">
         <v>351</v>
       </c>
       <c r="N626" t="n">
-        <v>1991.055</v>
+        <v>1952.66</v>
       </c>
       <c r="O626" t="n">
-        <v>698860.3050000001</v>
+        <v>685383.66</v>
       </c>
       <c r="P626" t="n">
         <v>3500</v>
@@ -29193,7 +29193,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -29202,19 +29202,19 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N633" t="n">
         <v>5280</v>
       </c>
       <c r="O633" t="n">
-        <v>337920</v>
+        <v>306240</v>
       </c>
       <c r="P633" t="n">
         <v>6900</v>
       </c>
       <c r="Q633" t="n">
-        <v>441600</v>
+        <v>400200</v>
       </c>
     </row>
     <row r="634">
@@ -29423,7 +29423,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -29432,19 +29432,19 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N638" t="n">
         <v>415.07</v>
       </c>
       <c r="O638" t="n">
-        <v>9961.68</v>
+        <v>7056.19</v>
       </c>
       <c r="P638" t="n">
         <v>2900</v>
       </c>
       <c r="Q638" t="n">
-        <v>69600</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="639">
@@ -29515,7 +29515,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -29524,19 +29524,19 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N640" t="n">
         <v>910.85</v>
       </c>
       <c r="O640" t="n">
-        <v>30968.9</v>
+        <v>28236.35</v>
       </c>
       <c r="P640" t="n">
         <v>7900</v>
       </c>
       <c r="Q640" t="n">
-        <v>268600</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="641">
@@ -29755,22 +29755,22 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M645" t="n">
         <v>1</v>
       </c>
       <c r="N645" t="n">
-        <v>1093.0181818182</v>
+        <v>751.45</v>
       </c>
       <c r="O645" t="n">
-        <v>1093.0181818182</v>
+        <v>751.45</v>
       </c>
       <c r="P645" t="n">
         <v>2500</v>
@@ -30005,10 +30005,10 @@
         <v>95</v>
       </c>
       <c r="N650" t="n">
-        <v>4171.6685954382</v>
+        <v>4171.6685869565</v>
       </c>
       <c r="O650" t="n">
-        <v>396308.516566629</v>
+        <v>396308.5157608675</v>
       </c>
       <c r="P650" t="n">
         <v>5000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -870,10 +870,10 @@
         <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>15970.739066667</v>
+        <v>15970.739014085</v>
       </c>
       <c r="O12" t="n">
-        <v>191648.868800004</v>
+        <v>191648.86816902</v>
       </c>
       <c r="P12" t="n">
         <v>26900</v>
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="N34" t="n">
-        <v>16486.407586207</v>
+        <v>16486.407256637</v>
       </c>
       <c r="O34" t="n">
-        <v>395673.7820689679</v>
+        <v>395673.774159288</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
@@ -1802,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>13712.84</v>
+        <v>13712.837142857</v>
       </c>
       <c r="O35" t="n">
-        <v>13712.84</v>
+        <v>13712.837142857</v>
       </c>
       <c r="P35" t="n">
         <v>22600</v>
@@ -3096,10 +3096,10 @@
         <v>1271</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.0633365079</v>
+        <v>1098.0633810433</v>
       </c>
       <c r="O65" t="n">
-        <v>1395638.500701541</v>
+        <v>1395638.557306034</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O93" t="n">
-        <v>10004112.26845537</v>
+        <v>10004112.27055763</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4947,10 +4947,10 @@
         <v>581</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O106" t="n">
-        <v>2205307.514424141</v>
+        <v>2205307.514424954</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -5351,10 +5351,10 @@
         <v>309</v>
       </c>
       <c r="N115" t="n">
-        <v>2267.0481062554</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O115" t="n">
-        <v>700517.8648329186</v>
+        <v>700517.8635766482</v>
       </c>
       <c r="P115" t="n">
         <v>3900</v>
@@ -6841,10 +6841,10 @@
         <v>181</v>
       </c>
       <c r="N148" t="n">
-        <v>1592.5654585153</v>
+        <v>1592.5654545455</v>
       </c>
       <c r="O148" t="n">
-        <v>288254.3479912693</v>
+        <v>288254.3472727355</v>
       </c>
       <c r="P148" t="n">
         <v>3900</v>
@@ -8770,10 +8770,10 @@
         <v>1422</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O190" t="n">
-        <v>2204376.497541015</v>
+        <v>2204376.520312354</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8816,10 +8816,10 @@
         <v>22</v>
       </c>
       <c r="N191" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O191" t="n">
-        <v>34746.48408</v>
+        <v>34746.4639148946</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O192" t="n">
-        <v>418212.0003164868</v>
+        <v>418212.0069949896</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -8903,10 +8903,10 @@
         <v>59</v>
       </c>
       <c r="N193" t="n">
-        <v>1232.8060309278</v>
+        <v>1232.8059585492</v>
       </c>
       <c r="O193" t="n">
-        <v>72735.55582474021</v>
+        <v>72735.5515544028</v>
       </c>
       <c r="P193" t="n">
         <v>2400</v>
@@ -10717,10 +10717,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>3731.024440678</v>
+        <v>3731.0244863014</v>
       </c>
       <c r="O234" t="n">
-        <v>44772.293288136</v>
+        <v>44772.2938356168</v>
       </c>
       <c r="P234" t="n">
         <v>5200</v>
@@ -15866,10 +15866,10 @@
         <v>137</v>
       </c>
       <c r="N346" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O346" t="n">
-        <v>672371.6886773574</v>
+        <v>672371.6914949542</v>
       </c>
       <c r="P346" t="n">
         <v>8200</v>
@@ -18113,10 +18113,10 @@
         <v>1248</v>
       </c>
       <c r="N395" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O395" t="n">
-        <v>1892016.361740586</v>
+        <v>1892016.361108099</v>
       </c>
       <c r="P395" t="n">
         <v>2300</v>
@@ -18343,10 +18343,10 @@
         <v>48</v>
       </c>
       <c r="N400" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O400" t="n">
-        <v>86544.79148544959</v>
+        <v>86544.79220260801</v>
       </c>
       <c r="P400" t="n">
         <v>2500</v>
@@ -18481,10 +18481,10 @@
         <v>144</v>
       </c>
       <c r="N403" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O403" t="n">
-        <v>296075.8530502848</v>
+        <v>296075.8472482224</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q661"/>
+  <dimension ref="A1:Q666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="N34" t="n">
-        <v>16486.407256637</v>
+        <v>16486.407142857</v>
       </c>
       <c r="O34" t="n">
-        <v>395673.774159288</v>
+        <v>395673.7714285679</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
@@ -2875,10 +2875,10 @@
         <v>228</v>
       </c>
       <c r="N60" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O60" t="n">
-        <v>1125706.717714278</v>
+        <v>1125706.717742664</v>
       </c>
       <c r="P60" t="n">
         <v>7500</v>
@@ -3460,10 +3460,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O73" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="P73" t="n">
         <v>25500</v>
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O86" t="n">
-        <v>1719781.863920512</v>
+        <v>1719781.858999771</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.712196561</v>
+        <v>3476523.612337979</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4860,10 +4860,10 @@
         <v>371</v>
       </c>
       <c r="N104" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O104" t="n">
-        <v>2414097</v>
+        <v>2416493.522501649</v>
       </c>
       <c r="P104" t="n">
         <v>9900</v>
@@ -5397,10 +5397,10 @@
         <v>609</v>
       </c>
       <c r="N116" t="n">
-        <v>7041</v>
+        <v>7062.9802289282</v>
       </c>
       <c r="O116" t="n">
-        <v>4287969</v>
+        <v>4301354.959417273</v>
       </c>
       <c r="P116" t="n">
         <v>11500</v>
@@ -5489,10 +5489,10 @@
         <v>242</v>
       </c>
       <c r="N118" t="n">
-        <v>8012</v>
+        <v>8051.1465798046</v>
       </c>
       <c r="O118" t="n">
-        <v>1938904</v>
+        <v>1948377.472312713</v>
       </c>
       <c r="P118" t="n">
         <v>13200</v>
@@ -5535,10 +5535,10 @@
         <v>281</v>
       </c>
       <c r="N119" t="n">
-        <v>8662</v>
+        <v>8680.102403343801</v>
       </c>
       <c r="O119" t="n">
-        <v>2434022</v>
+        <v>2439108.775339608</v>
       </c>
       <c r="P119" t="n">
         <v>14200</v>
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.7566333839</v>
+        <v>862620.755460384</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -5896,10 +5896,10 @@
         <v>305</v>
       </c>
       <c r="N127" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O127" t="n">
-        <v>4520825.542490895</v>
+        <v>4526352.224083276</v>
       </c>
       <c r="P127" t="n">
         <v>24900</v>
@@ -6169,10 +6169,10 @@
         <v>708</v>
       </c>
       <c r="N133" t="n">
-        <v>2665.4</v>
+        <v>2668.7380087664</v>
       </c>
       <c r="O133" t="n">
-        <v>1887103.2</v>
+        <v>1889466.510206611</v>
       </c>
       <c r="P133" t="n">
         <v>20900</v>
@@ -6394,10 +6394,10 @@
         <v>2520</v>
       </c>
       <c r="N138" t="n">
-        <v>3472.2761671707</v>
+        <v>3490.9933434692</v>
       </c>
       <c r="O138" t="n">
-        <v>8750135.941270163</v>
+        <v>8797303.225542385</v>
       </c>
       <c r="P138" t="n">
         <v>5900</v>
@@ -6841,10 +6841,10 @@
         <v>181</v>
       </c>
       <c r="N148" t="n">
-        <v>1592.5653777778</v>
+        <v>1592.5653736655</v>
       </c>
       <c r="O148" t="n">
-        <v>288254.3333777818</v>
+        <v>288254.3326334555</v>
       </c>
       <c r="P148" t="n">
         <v>3900</v>
@@ -7192,10 +7192,10 @@
         <v>37</v>
       </c>
       <c r="N156" t="n">
-        <v>6242.93</v>
+        <v>6260.7161253561</v>
       </c>
       <c r="O156" t="n">
-        <v>230988.41</v>
+        <v>231646.4966381757</v>
       </c>
       <c r="P156" t="n">
         <v>10400</v>
@@ -8586,10 +8586,10 @@
         <v>193</v>
       </c>
       <c r="N186" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O186" t="n">
-        <v>1911279</v>
+        <v>1914265.3734375</v>
       </c>
       <c r="P186" t="n">
         <v>15900</v>
@@ -8632,10 +8632,10 @@
         <v>556</v>
       </c>
       <c r="N187" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O187" t="n">
-        <v>906793.9220449332</v>
+        <v>906793.9267773827</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8770,10 +8770,10 @@
         <v>1422</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O190" t="n">
-        <v>2204376.594296881</v>
+        <v>2204376.607578503</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5178067661</v>
+        <v>2403.5178733813</v>
       </c>
       <c r="O192" t="n">
-        <v>418212.0983773014</v>
+        <v>418212.1099683462</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -11163,10 +11163,10 @@
         <v>1280</v>
       </c>
       <c r="N244" t="n">
-        <v>4814.2679269747</v>
+        <v>4817.516083662</v>
       </c>
       <c r="O244" t="n">
-        <v>6162262.946527615</v>
+        <v>6166420.587087359</v>
       </c>
       <c r="P244" t="n">
         <v>9900</v>
@@ -11250,10 +11250,10 @@
         <v>32</v>
       </c>
       <c r="N246" t="n">
-        <v>11562.038418079</v>
+        <v>11660.859259259</v>
       </c>
       <c r="O246" t="n">
-        <v>369985.229378528</v>
+        <v>373147.496296288</v>
       </c>
       <c r="P246" t="n">
         <v>18500</v>
@@ -11296,10 +11296,10 @@
         <v>17</v>
       </c>
       <c r="N247" t="n">
-        <v>13513.643445378</v>
+        <v>13744.645897436</v>
       </c>
       <c r="O247" t="n">
-        <v>229731.938571426</v>
+        <v>233658.980256412</v>
       </c>
       <c r="P247" t="n">
         <v>21900</v>
@@ -11608,10 +11608,10 @@
         <v>1328</v>
       </c>
       <c r="N254" t="n">
-        <v>4100.45</v>
+        <v>4114.8123467601</v>
       </c>
       <c r="O254" t="n">
-        <v>5445397.6</v>
+        <v>5464470.796497413</v>
       </c>
       <c r="P254" t="n">
         <v>26900</v>
@@ -11700,10 +11700,10 @@
         <v>522</v>
       </c>
       <c r="N256" t="n">
-        <v>1561.0038892883</v>
+        <v>1561.0040101523</v>
       </c>
       <c r="O256" t="n">
-        <v>814844.0302084925</v>
+        <v>814844.0932995006</v>
       </c>
       <c r="P256" t="n">
         <v>2900</v>
@@ -11838,10 +11838,10 @@
         <v>188</v>
       </c>
       <c r="N259" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O259" t="n">
-        <v>1498350.631839868</v>
+        <v>1501819.036080243</v>
       </c>
       <c r="P259" t="n">
         <v>12900</v>
@@ -11884,10 +11884,10 @@
         <v>46</v>
       </c>
       <c r="N260" t="n">
-        <v>9627.34</v>
+        <v>9794.2880924855</v>
       </c>
       <c r="O260" t="n">
-        <v>442857.64</v>
+        <v>450537.252254333</v>
       </c>
       <c r="P260" t="n">
         <v>15900</v>
@@ -13740,10 +13740,10 @@
         <v>146</v>
       </c>
       <c r="N300" t="n">
-        <v>22739</v>
+        <v>22855.411262799</v>
       </c>
       <c r="O300" t="n">
-        <v>3319894</v>
+        <v>3336890.044368654</v>
       </c>
       <c r="P300" t="n">
         <v>36900</v>
@@ -14528,10 +14528,10 @@
         <v>57</v>
       </c>
       <c r="N317" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O317" t="n">
-        <v>780159</v>
+        <v>786334.401055401</v>
       </c>
       <c r="P317" t="n">
         <v>21900</v>
@@ -14804,10 +14804,10 @@
         <v>416</v>
       </c>
       <c r="N323" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O323" t="n">
-        <v>3684994.56</v>
+        <v>3691032.235412329</v>
       </c>
       <c r="P323" t="n">
         <v>15500</v>
@@ -16050,10 +16050,10 @@
         <v>240</v>
       </c>
       <c r="N350" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O350" t="n">
-        <v>936897.3778165921</v>
+        <v>936897.3898423919</v>
       </c>
       <c r="P350" t="n">
         <v>7500</v>
@@ -16091,10 +16091,10 @@
         <v>14</v>
       </c>
       <c r="N351" t="n">
-        <v>20726</v>
+        <v>21127.148387097</v>
       </c>
       <c r="O351" t="n">
-        <v>290164</v>
+        <v>295780.077419358</v>
       </c>
       <c r="P351" t="n">
         <v>33900</v>
@@ -16137,10 +16137,10 @@
         <v>23</v>
       </c>
       <c r="N352" t="n">
-        <v>33000</v>
+        <v>33980.198019802</v>
       </c>
       <c r="O352" t="n">
-        <v>759000</v>
+        <v>781544.5544554461</v>
       </c>
       <c r="P352" t="n">
         <v>52900</v>
@@ -16275,10 +16275,10 @@
         <v>382</v>
       </c>
       <c r="N355" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O355" t="n">
-        <v>2616394.4</v>
+        <v>2618879.105033239</v>
       </c>
       <c r="P355" t="n">
         <v>11500</v>
@@ -18072,10 +18072,10 @@
         <v>1248</v>
       </c>
       <c r="N394" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O394" t="n">
-        <v>1892016.355551878</v>
+        <v>1892016.354435917</v>
       </c>
       <c r="P394" t="n">
         <v>2300</v>
@@ -18158,22 +18158,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M396" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N396" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O396" t="n">
-        <v>118008.6055567344</v>
+        <v>0</v>
       </c>
       <c r="P396" t="n">
         <v>3500</v>
       </c>
       <c r="Q396" t="n">
-        <v>168000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -18204,22 +18204,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M397" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N397" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O397" t="n">
-        <v>85012.291143696</v>
+        <v>0</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
       </c>
       <c r="Q397" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -18256,10 +18256,10 @@
         <v>168</v>
       </c>
       <c r="N398" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O398" t="n">
-        <v>349336.3987429848</v>
+        <v>349336.3979034048</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
@@ -18296,22 +18296,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M399" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N399" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O399" t="n">
-        <v>86544.7973166912</v>
+        <v>0</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
       </c>
       <c r="Q399" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -18342,22 +18342,22 @@
         <v>0</v>
       </c>
       <c r="L400" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M400" t="n">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="N400" t="n">
-        <v>3306.5944272446</v>
+        <v>3645.1535836177</v>
       </c>
       <c r="O400" t="n">
-        <v>515828.7306501576</v>
+        <v>349934.7440272992</v>
       </c>
       <c r="P400" t="n">
         <v>4900</v>
       </c>
       <c r="Q400" t="n">
-        <v>764400</v>
+        <v>470400</v>
       </c>
     </row>
     <row r="401">
@@ -18434,22 +18434,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M402" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="N402" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O402" t="n">
-        <v>296075.8439053632</v>
+        <v>201007.0037781984</v>
       </c>
       <c r="P402" t="n">
         <v>2900</v>
       </c>
       <c r="Q402" t="n">
-        <v>417600</v>
+        <v>278400</v>
       </c>
     </row>
     <row r="403">
@@ -18526,22 +18526,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M404" t="n">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="N404" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O404" t="n">
-        <v>596134.633888044</v>
+        <v>378283.19328</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
       </c>
       <c r="Q404" t="n">
-        <v>900000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="405">
@@ -18762,10 +18762,10 @@
         <v>224</v>
       </c>
       <c r="N409" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="O409" t="n">
-        <v>356671.2712871392</v>
+        <v>356671.283181808</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
@@ -19355,10 +19355,10 @@
         <v>600</v>
       </c>
       <c r="N422" t="n">
-        <v>13518</v>
+        <v>13559.454697519</v>
       </c>
       <c r="O422" t="n">
-        <v>8110800</v>
+        <v>8135672.8185114</v>
       </c>
       <c r="P422" t="n">
         <v>21900</v>
@@ -19404,10 +19404,10 @@
         <v>708</v>
       </c>
       <c r="N423" t="n">
-        <v>9736</v>
+        <v>9760.865567680499</v>
       </c>
       <c r="O423" t="n">
-        <v>6893088</v>
+        <v>6910692.821917794</v>
       </c>
       <c r="P423" t="n">
         <v>15900</v>
@@ -19453,10 +19453,10 @@
         <v>48</v>
       </c>
       <c r="N424" t="n">
-        <v>44470</v>
+        <v>45032.911392405</v>
       </c>
       <c r="O424" t="n">
-        <v>2134560</v>
+        <v>2161579.74683544</v>
       </c>
       <c r="P424" t="n">
         <v>71900</v>
@@ -19502,10 +19502,10 @@
         <v>925</v>
       </c>
       <c r="N425" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O425" t="n">
-        <v>4823875</v>
+        <v>4835686.642997055</v>
       </c>
       <c r="P425" t="n">
         <v>8900</v>
@@ -19636,10 +19636,10 @@
         <v>46</v>
       </c>
       <c r="N428" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="O428" t="n">
-        <v>709474.5600000001</v>
+        <v>719756.8000000119</v>
       </c>
       <c r="P428" t="n">
         <v>24900</v>
@@ -21734,10 +21734,10 @@
         <v>631</v>
       </c>
       <c r="N473" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O473" t="n">
-        <v>1962938.734482769</v>
+        <v>1962938.687392628</v>
       </c>
       <c r="P473" t="n">
         <v>4500</v>
@@ -22185,10 +22185,10 @@
         <v>18602</v>
       </c>
       <c r="N483" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O483" t="n">
-        <v>13091991.06966284</v>
+        <v>13091990.70895164</v>
       </c>
       <c r="P483" t="n">
         <v>900</v>
@@ -28323,10 +28323,10 @@
         <v>43</v>
       </c>
       <c r="N614" t="n">
-        <v>4985.4069767442</v>
+        <v>4985.4071856287</v>
       </c>
       <c r="O614" t="n">
-        <v>214372.5000000006</v>
+        <v>214372.5089820341</v>
       </c>
       <c r="P614" t="n">
         <v>7900</v>
@@ -28425,10 +28425,10 @@
         <v>289</v>
       </c>
       <c r="N616" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="O616" t="n">
-        <v>507865.6593317538</v>
+        <v>507865.6597607743</v>
       </c>
       <c r="P616" t="n">
         <v>2000</v>
@@ -28486,17 +28486,20 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>DPB087</t>
-        </is>
+          <t>CH-436</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
+          <t>GLOBO 18 PULGADAS CH-436</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -28505,44 +28508,44 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K618" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="N618" t="n">
-        <v>13520</v>
+        <v>1760</v>
       </c>
       <c r="O618" t="n">
-        <v>135200</v>
+        <v>880000</v>
       </c>
       <c r="P618" t="n">
-        <v>16900</v>
+        <v>2300</v>
       </c>
       <c r="Q618" t="n">
-        <v>169000</v>
+        <v>1150000</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>DV052</t>
+          <t>DPB087</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DV052</t>
+          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -28551,7 +28554,7 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>2200</v>
+        <v>10</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
@@ -28560,35 +28563,35 @@
         <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>2200</v>
+        <v>10</v>
       </c>
       <c r="N619" t="n">
-        <v>220.00227919632</v>
+        <v>13520</v>
       </c>
       <c r="O619" t="n">
-        <v>484005.014231904</v>
+        <v>135200</v>
       </c>
       <c r="P619" t="n">
-        <v>260</v>
+        <v>16900</v>
       </c>
       <c r="Q619" t="n">
-        <v>572000</v>
+        <v>169000</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>FG021</t>
+          <t>DV052</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
+          <t>PELOTA PISCINA DV052</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -28597,7 +28600,7 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>10</v>
+        <v>2200</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
@@ -28606,35 +28609,35 @@
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>10</v>
+        <v>2200</v>
       </c>
       <c r="N620" t="n">
-        <v>3504.16</v>
+        <v>220.00227919632</v>
       </c>
       <c r="O620" t="n">
-        <v>35041.6</v>
+        <v>484005.014231904</v>
       </c>
       <c r="P620" t="n">
-        <v>3900</v>
+        <v>260</v>
       </c>
       <c r="Q620" t="n">
-        <v>39000</v>
+        <v>572000</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG021</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -28643,7 +28646,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
@@ -28652,30 +28655,30 @@
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="N621" t="n">
-        <v>13493.858292683</v>
+        <v>3504.16</v>
       </c>
       <c r="O621" t="n">
-        <v>1025533.230243908</v>
+        <v>35041.6</v>
       </c>
       <c r="P621" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q621" t="n">
-        <v>1284400</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -28689,7 +28692,7 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>439</v>
+        <v>76</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
@@ -28698,35 +28701,35 @@
         <v>0</v>
       </c>
       <c r="M622" t="n">
-        <v>439</v>
+        <v>76</v>
       </c>
       <c r="N622" t="n">
-        <v>2644.9</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O622" t="n">
-        <v>1161111.1</v>
+        <v>1025533.230243908</v>
       </c>
       <c r="P622" t="n">
-        <v>3900</v>
+        <v>16900</v>
       </c>
       <c r="Q622" t="n">
-        <v>1712100</v>
+        <v>1284400</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>FG042</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>BURBUJERO PANDA BLISTER 43043</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -28735,7 +28738,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>7</v>
+        <v>439</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -28744,30 +28747,30 @@
         <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>7</v>
+        <v>439</v>
       </c>
       <c r="N623" t="n">
-        <v>14576.2</v>
+        <v>2644.9</v>
       </c>
       <c r="O623" t="n">
-        <v>102033.4</v>
+        <v>1161111.1</v>
       </c>
       <c r="P623" t="n">
-        <v>19000</v>
+        <v>3900</v>
       </c>
       <c r="Q623" t="n">
-        <v>133000</v>
+        <v>1712100</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG042</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>BURBUJERO PANDA BLISTER 43043</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -28781,7 +28784,7 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="K624" t="n">
         <v>0</v>
@@ -28790,35 +28793,35 @@
         <v>0</v>
       </c>
       <c r="M624" t="n">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="N624" t="n">
-        <v>1952.66</v>
+        <v>14576.2</v>
       </c>
       <c r="O624" t="n">
-        <v>685383.66</v>
+        <v>102033.4</v>
       </c>
       <c r="P624" t="n">
-        <v>3500</v>
+        <v>19000</v>
       </c>
       <c r="Q624" t="n">
-        <v>1228500</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>FG050</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -28827,7 +28830,7 @@
         </is>
       </c>
       <c r="J625" t="n">
-        <v>10</v>
+        <v>351</v>
       </c>
       <c r="K625" t="n">
         <v>0</v>
@@ -28836,35 +28839,35 @@
         <v>0</v>
       </c>
       <c r="M625" t="n">
-        <v>10</v>
+        <v>351</v>
       </c>
       <c r="N625" t="n">
-        <v>9708.190000000001</v>
+        <v>1952.66</v>
       </c>
       <c r="O625" t="n">
-        <v>97081.90000000001</v>
+        <v>685383.66</v>
       </c>
       <c r="P625" t="n">
-        <v>10200</v>
+        <v>3500</v>
       </c>
       <c r="Q625" t="n">
-        <v>102000</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>FG057</t>
+          <t>FG050</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>ABACO BOLSA 8022</t>
+          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -28873,7 +28876,7 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>232</v>
+        <v>10</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
@@ -28882,30 +28885,30 @@
         <v>0</v>
       </c>
       <c r="M626" t="n">
-        <v>232</v>
+        <v>10</v>
       </c>
       <c r="N626" t="n">
-        <v>2293.26</v>
+        <v>9708.190000000001</v>
       </c>
       <c r="O626" t="n">
-        <v>532036.3200000001</v>
+        <v>97081.90000000001</v>
       </c>
       <c r="P626" t="n">
-        <v>4800</v>
+        <v>10200</v>
       </c>
       <c r="Q626" t="n">
-        <v>1113600</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>FG083</t>
+          <t>FG057</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA RANA XZM5XS</t>
+          <t>ABACO BOLSA 8022</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -28919,7 +28922,7 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
@@ -28928,35 +28931,35 @@
         <v>0</v>
       </c>
       <c r="M627" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="N627" t="n">
-        <v>1952.41</v>
+        <v>2293.26</v>
       </c>
       <c r="O627" t="n">
-        <v>333862.11</v>
+        <v>532036.3200000001</v>
       </c>
       <c r="P627" t="n">
-        <v>2700</v>
+        <v>4800</v>
       </c>
       <c r="Q627" t="n">
-        <v>461700</v>
+        <v>1113600</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>FG092</t>
+          <t>FG083</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>BLISTER  TETERA SJ377-1</t>
+          <t>SONAJERO BOLSA RANA XZM5XS</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -28965,7 +28968,7 @@
         </is>
       </c>
       <c r="J628" t="n">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="K628" t="n">
         <v>0</v>
@@ -28974,30 +28977,30 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="N628" t="n">
-        <v>9855.0380769231</v>
+        <v>1952.41</v>
       </c>
       <c r="O628" t="n">
-        <v>9855.0380769231</v>
+        <v>333862.11</v>
       </c>
       <c r="P628" t="n">
-        <v>15500</v>
+        <v>2700</v>
       </c>
       <c r="Q628" t="n">
-        <v>15500</v>
+        <v>461700</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>FG097</t>
+          <t>FG092</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>MUÑECO ROBOT BLISTER 5090B</t>
+          <t>BLISTER  TETERA SJ377-1</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -29011,7 +29014,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -29020,35 +29023,35 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="N629" t="n">
-        <v>17986.24</v>
+        <v>9855.0380769231</v>
       </c>
       <c r="O629" t="n">
-        <v>1456885.44</v>
+        <v>9855.0380769231</v>
       </c>
       <c r="P629" t="n">
-        <v>18500</v>
+        <v>15500</v>
       </c>
       <c r="Q629" t="n">
-        <v>1498500</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>FG097</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>MUÑECO ROBOT BLISTER 5090B</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -29057,7 +29060,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -29066,30 +29069,30 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="N630" t="n">
-        <v>7480</v>
+        <v>17986.24</v>
       </c>
       <c r="O630" t="n">
-        <v>269280</v>
+        <v>1456885.44</v>
       </c>
       <c r="P630" t="n">
-        <v>9500</v>
+        <v>18500</v>
       </c>
       <c r="Q630" t="n">
-        <v>342000</v>
+        <v>1498500</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>J-1316</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -29103,7 +29106,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -29112,30 +29115,30 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="N631" t="n">
-        <v>5280</v>
+        <v>7480</v>
       </c>
       <c r="O631" t="n">
-        <v>306240</v>
+        <v>269280</v>
       </c>
       <c r="P631" t="n">
-        <v>6900</v>
+        <v>9500</v>
       </c>
       <c r="Q631" t="n">
-        <v>400200</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>J-1317</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -29149,7 +29152,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29158,30 +29161,30 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="N632" t="n">
         <v>5280</v>
       </c>
       <c r="O632" t="n">
-        <v>469920</v>
+        <v>306240</v>
       </c>
       <c r="P632" t="n">
         <v>6900</v>
       </c>
       <c r="Q632" t="n">
-        <v>614100</v>
+        <v>400200</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -29195,7 +29198,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -29204,30 +29207,33 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="N633" t="n">
-        <v>9240</v>
+        <v>5280</v>
       </c>
       <c r="O633" t="n">
-        <v>166320</v>
+        <v>469920</v>
       </c>
       <c r="P633" t="n">
-        <v>11500</v>
+        <v>6900</v>
       </c>
       <c r="Q633" t="n">
-        <v>207000</v>
+        <v>614100</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>J-718</t>
-        </is>
+          <t>J-1385</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>PELOTA NUBES J-1385</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -29241,39 +29247,42 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K634" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>130</v>
+        <v>1200</v>
       </c>
       <c r="N634" t="n">
-        <v>4576</v>
+        <v>1056</v>
       </c>
       <c r="O634" t="n">
-        <v>594880</v>
+        <v>1267200</v>
       </c>
       <c r="P634" t="n">
-        <v>5900</v>
+        <v>1400</v>
       </c>
       <c r="Q634" t="n">
-        <v>767000</v>
+        <v>1680000</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>J-719</t>
-        </is>
+          <t>J-1386</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -29287,39 +29296,42 @@
         </is>
       </c>
       <c r="J635" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="K635" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
       </c>
       <c r="M635" t="n">
-        <v>243</v>
+        <v>144</v>
       </c>
       <c r="N635" t="n">
-        <v>5280</v>
+        <v>7945.2229299363</v>
       </c>
       <c r="O635" t="n">
-        <v>1283040</v>
+        <v>1144112.101910827</v>
       </c>
       <c r="P635" t="n">
-        <v>6900</v>
+        <v>10500</v>
       </c>
       <c r="Q635" t="n">
-        <v>1676700</v>
+        <v>1512000</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>LY6807</t>
-        </is>
+          <t>J-1387</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>VARA LUZ OSO 37cm J-1387</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -29333,39 +29345,42 @@
         </is>
       </c>
       <c r="J636" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K636" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L636" t="n">
         <v>0</v>
       </c>
       <c r="M636" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="N636" t="n">
-        <v>415.07</v>
+        <v>7940</v>
       </c>
       <c r="O636" t="n">
-        <v>7056.19</v>
+        <v>571680</v>
       </c>
       <c r="P636" t="n">
-        <v>2900</v>
+        <v>10500</v>
       </c>
       <c r="Q636" t="n">
-        <v>49300</v>
+        <v>756000</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>MG09</t>
-        </is>
+          <t>J-1389</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>VARA LUZ PRINCESA 37cm J-1389</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -29379,44 +29394,44 @@
         </is>
       </c>
       <c r="J637" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K637" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L637" t="n">
         <v>0</v>
       </c>
       <c r="M637" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="N637" t="n">
-        <v>46491.75</v>
+        <v>7961.0362694301</v>
       </c>
       <c r="O637" t="n">
-        <v>2743013.25</v>
+        <v>573194.6113989672</v>
       </c>
       <c r="P637" t="n">
-        <v>52900</v>
+        <v>10500</v>
       </c>
       <c r="Q637" t="n">
-        <v>3121100</v>
+        <v>756000</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -29425,7 +29440,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -29434,35 +29449,35 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N638" t="n">
-        <v>910.85</v>
+        <v>9240</v>
       </c>
       <c r="O638" t="n">
-        <v>28236.35</v>
+        <v>166320</v>
       </c>
       <c r="P638" t="n">
-        <v>7900</v>
+        <v>11500</v>
       </c>
       <c r="Q638" t="n">
-        <v>244900</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -29471,7 +29486,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -29480,35 +29495,35 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="N639" t="n">
-        <v>1129.14</v>
+        <v>4576</v>
       </c>
       <c r="O639" t="n">
-        <v>13549.68</v>
+        <v>594880</v>
       </c>
       <c r="P639" t="n">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="Q639" t="n">
-        <v>82800</v>
+        <v>767000</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -29517,7 +29532,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>6</v>
+        <v>243</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -29526,40 +29541,35 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>6</v>
+        <v>243</v>
       </c>
       <c r="N640" t="n">
-        <v>11433.53</v>
+        <v>5280</v>
       </c>
       <c r="O640" t="n">
-        <v>68601.18000000001</v>
+        <v>1283040</v>
       </c>
       <c r="P640" t="n">
-        <v>15000</v>
+        <v>6900</v>
       </c>
       <c r="Q640" t="n">
-        <v>90000</v>
+        <v>1676700</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -29568,7 +29578,7 @@
         </is>
       </c>
       <c r="J641" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K641" t="n">
         <v>0</v>
@@ -29577,35 +29587,35 @@
         <v>0</v>
       </c>
       <c r="M641" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="N641" t="n">
-        <v>15452.21</v>
+        <v>415.07</v>
       </c>
       <c r="O641" t="n">
-        <v>61808.84</v>
+        <v>7056.19</v>
       </c>
       <c r="P641" t="n">
-        <v>36500</v>
+        <v>2900</v>
       </c>
       <c r="Q641" t="n">
-        <v>146000</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -29614,7 +29624,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -29623,40 +29633,35 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="N642" t="n">
-        <v>1319.3609463722</v>
+        <v>46491.75</v>
       </c>
       <c r="O642" t="n">
-        <v>216375.1952050408</v>
+        <v>2743013.25</v>
       </c>
       <c r="P642" t="n">
-        <v>3500</v>
+        <v>52900</v>
       </c>
       <c r="Q642" t="n">
-        <v>574000</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -29665,7 +29670,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -29674,35 +29679,35 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="N643" t="n">
-        <v>751.45</v>
+        <v>910.85</v>
       </c>
       <c r="O643" t="n">
-        <v>751.45</v>
+        <v>28236.35</v>
       </c>
       <c r="P643" t="n">
-        <v>2500</v>
+        <v>7900</v>
       </c>
       <c r="Q643" t="n">
-        <v>2500</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -29711,7 +29716,7 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -29720,35 +29725,35 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="N644" t="n">
-        <v>571.87</v>
+        <v>1129.14</v>
       </c>
       <c r="O644" t="n">
-        <v>76058.71000000001</v>
+        <v>13549.68</v>
       </c>
       <c r="P644" t="n">
-        <v>2500</v>
+        <v>6900</v>
       </c>
       <c r="Q644" t="n">
-        <v>332500</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -29757,7 +29762,7 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>680</v>
+        <v>6</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -29766,40 +29771,40 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>680</v>
+        <v>6</v>
       </c>
       <c r="N645" t="n">
-        <v>227.41614285714</v>
+        <v>11433.53</v>
       </c>
       <c r="O645" t="n">
-        <v>154642.9771428552</v>
+        <v>68601.18000000001</v>
       </c>
       <c r="P645" t="n">
-        <v>1200</v>
+        <v>15000</v>
       </c>
       <c r="Q645" t="n">
-        <v>816000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>MG40720</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>MG40720</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -29808,7 +29813,7 @@
         </is>
       </c>
       <c r="J646" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K646" t="n">
         <v>0</v>
@@ -29817,47 +29822,44 @@
         <v>0</v>
       </c>
       <c r="M646" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N646" t="n">
-        <v>9917.040000000001</v>
+        <v>15452.21</v>
       </c>
       <c r="O646" t="n">
-        <v>208257.84</v>
+        <v>61808.84</v>
       </c>
       <c r="P646" t="n">
-        <v>15900</v>
+        <v>36500</v>
       </c>
       <c r="Q646" t="n">
-        <v>333900</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B647" t="n">
-        <v>7700154271143</v>
+          <t>MG32315</t>
+        </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J647" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="K647" t="n">
         <v>0</v>
@@ -29866,35 +29868,40 @@
         <v>0</v>
       </c>
       <c r="M647" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N647" t="n">
-        <v>2539.5716984733</v>
+        <v>1319.3609463722</v>
       </c>
       <c r="O647" t="n">
-        <v>401252.3283587814</v>
+        <v>216375.1952050408</v>
       </c>
       <c r="P647" t="n">
-        <v>2900</v>
+        <v>3500</v>
       </c>
       <c r="Q647" t="n">
-        <v>458200</v>
+        <v>574000</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -29903,7 +29910,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -29912,30 +29919,30 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="N648" t="n">
-        <v>4171.6685783718</v>
+        <v>751.45</v>
       </c>
       <c r="O648" t="n">
-        <v>396308.514945321</v>
+        <v>751.45</v>
       </c>
       <c r="P648" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="Q648" t="n">
-        <v>475000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -29949,7 +29956,7 @@
         </is>
       </c>
       <c r="J649" t="n">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="K649" t="n">
         <v>0</v>
@@ -29958,35 +29965,35 @@
         <v>0</v>
       </c>
       <c r="M649" t="n">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="N649" t="n">
-        <v>7600</v>
+        <v>571.87</v>
       </c>
       <c r="O649" t="n">
-        <v>364800</v>
+        <v>76058.71000000001</v>
       </c>
       <c r="P649" t="n">
-        <v>9500</v>
+        <v>2500</v>
       </c>
       <c r="Q649" t="n">
-        <v>456000</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -29995,7 +30002,7 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>95</v>
+        <v>680</v>
       </c>
       <c r="K650" t="n">
         <v>0</v>
@@ -30004,30 +30011,35 @@
         <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>95</v>
+        <v>680</v>
       </c>
       <c r="N650" t="n">
-        <v>5520</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O650" t="n">
-        <v>524400</v>
+        <v>154642.9771428552</v>
       </c>
       <c r="P650" t="n">
-        <v>6900</v>
+        <v>1200</v>
       </c>
       <c r="Q650" t="n">
-        <v>655500</v>
+        <v>816000</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -30041,7 +30053,7 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
@@ -30050,44 +30062,47 @@
         <v>0</v>
       </c>
       <c r="M651" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="N651" t="n">
-        <v>1600</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O651" t="n">
-        <v>132800</v>
+        <v>208257.84</v>
       </c>
       <c r="P651" t="n">
-        <v>2000</v>
+        <v>15900</v>
       </c>
       <c r="Q651" t="n">
-        <v>166000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J652" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
@@ -30096,30 +30111,30 @@
         <v>0</v>
       </c>
       <c r="M652" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="N652" t="n">
-        <v>4091.4</v>
+        <v>2539.5716984733</v>
       </c>
       <c r="O652" t="n">
-        <v>4091.4</v>
+        <v>401252.3283587814</v>
       </c>
       <c r="P652" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q652" t="n">
-        <v>10000</v>
+        <v>458200</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -30133,7 +30148,7 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
@@ -30142,35 +30157,35 @@
         <v>0</v>
       </c>
       <c r="M653" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="N653" t="n">
-        <v>3661.88</v>
+        <v>4171.6685783718</v>
       </c>
       <c r="O653" t="n">
-        <v>10985.64</v>
+        <v>396308.514945321</v>
       </c>
       <c r="P653" t="n">
-        <v>38900</v>
+        <v>5000</v>
       </c>
       <c r="Q653" t="n">
-        <v>116700</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -30179,7 +30194,7 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
@@ -30188,35 +30203,35 @@
         <v>0</v>
       </c>
       <c r="M654" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="N654" t="n">
-        <v>2797.08</v>
+        <v>7600</v>
       </c>
       <c r="O654" t="n">
-        <v>13985.4</v>
+        <v>364800</v>
       </c>
       <c r="P654" t="n">
-        <v>30900</v>
+        <v>9500</v>
       </c>
       <c r="Q654" t="n">
-        <v>154500</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -30225,7 +30240,7 @@
         </is>
       </c>
       <c r="J655" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="K655" t="n">
         <v>0</v>
@@ -30234,35 +30249,35 @@
         <v>0</v>
       </c>
       <c r="M655" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="N655" t="n">
-        <v>3462.255</v>
+        <v>5520</v>
       </c>
       <c r="O655" t="n">
-        <v>38084.805</v>
+        <v>524400</v>
       </c>
       <c r="P655" t="n">
-        <v>42000</v>
+        <v>6900</v>
       </c>
       <c r="Q655" t="n">
-        <v>462000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -30271,7 +30286,7 @@
         </is>
       </c>
       <c r="J656" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="K656" t="n">
         <v>0</v>
@@ -30280,35 +30295,35 @@
         <v>0</v>
       </c>
       <c r="M656" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="N656" t="n">
-        <v>24882.58</v>
+        <v>1600</v>
       </c>
       <c r="O656" t="n">
-        <v>696712.24</v>
+        <v>132800</v>
       </c>
       <c r="P656" t="n">
-        <v>31500</v>
+        <v>2000</v>
       </c>
       <c r="Q656" t="n">
-        <v>882000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -30317,7 +30332,7 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
@@ -30326,35 +30341,35 @@
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N657" t="n">
-        <v>0.8</v>
+        <v>4091.4</v>
       </c>
       <c r="O657" t="n">
-        <v>15.2</v>
+        <v>4091.4</v>
       </c>
       <c r="P657" t="n">
-        <v>22900</v>
+        <v>10000</v>
       </c>
       <c r="Q657" t="n">
-        <v>435100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T040-LJ</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -30363,7 +30378,7 @@
         </is>
       </c>
       <c r="J658" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K658" t="n">
         <v>0</v>
@@ -30372,35 +30387,35 @@
         <v>0</v>
       </c>
       <c r="M658" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N658" t="n">
-        <v>5186.45</v>
+        <v>3661.88</v>
       </c>
       <c r="O658" t="n">
-        <v>82983.2</v>
+        <v>10985.64</v>
       </c>
       <c r="P658" t="n">
-        <v>7200</v>
+        <v>38900</v>
       </c>
       <c r="Q658" t="n">
-        <v>115200</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>T041-LJ</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -30409,7 +30424,7 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K659" t="n">
         <v>0</v>
@@ -30418,35 +30433,35 @@
         <v>0</v>
       </c>
       <c r="M659" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N659" t="n">
-        <v>47796.1625</v>
+        <v>2797.08</v>
       </c>
       <c r="O659" t="n">
-        <v>95592.325</v>
+        <v>13985.4</v>
       </c>
       <c r="P659" t="n">
-        <v>54000</v>
+        <v>30900</v>
       </c>
       <c r="Q659" t="n">
-        <v>108000</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -30455,7 +30470,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -30464,64 +30479,294 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="N660" t="n">
-        <v>8006.3731111111</v>
+        <v>3462.255</v>
       </c>
       <c r="O660" t="n">
-        <v>344274.0437777773</v>
+        <v>38084.805</v>
       </c>
       <c r="P660" t="n">
-        <v>10000</v>
+        <v>42000</v>
       </c>
       <c r="Q660" t="n">
-        <v>430000</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
+          <t>T062-LJ</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J661" t="n">
+        <v>28</v>
+      </c>
+      <c r="K661" t="n">
+        <v>0</v>
+      </c>
+      <c r="L661" t="n">
+        <v>0</v>
+      </c>
+      <c r="M661" t="n">
+        <v>28</v>
+      </c>
+      <c r="N661" t="n">
+        <v>24882.58</v>
+      </c>
+      <c r="O661" t="n">
+        <v>696712.24</v>
+      </c>
+      <c r="P661" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q661" t="n">
+        <v>882000</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>T119-LJ</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J662" t="n">
+        <v>19</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0</v>
+      </c>
+      <c r="L662" t="n">
+        <v>0</v>
+      </c>
+      <c r="M662" t="n">
+        <v>19</v>
+      </c>
+      <c r="N662" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O662" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="P662" t="n">
+        <v>22900</v>
+      </c>
+      <c r="Q662" t="n">
+        <v>435100</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>T166-LJ</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J663" t="n">
+        <v>16</v>
+      </c>
+      <c r="K663" t="n">
+        <v>0</v>
+      </c>
+      <c r="L663" t="n">
+        <v>0</v>
+      </c>
+      <c r="M663" t="n">
+        <v>16</v>
+      </c>
+      <c r="N663" t="n">
+        <v>5186.45</v>
+      </c>
+      <c r="O663" t="n">
+        <v>82983.2</v>
+      </c>
+      <c r="P663" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Q663" t="n">
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>TB028</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J664" t="n">
+        <v>2</v>
+      </c>
+      <c r="K664" t="n">
+        <v>0</v>
+      </c>
+      <c r="L664" t="n">
+        <v>0</v>
+      </c>
+      <c r="M664" t="n">
+        <v>2</v>
+      </c>
+      <c r="N664" t="n">
+        <v>47796.1625</v>
+      </c>
+      <c r="O664" t="n">
+        <v>95592.325</v>
+      </c>
+      <c r="P664" t="n">
+        <v>54000</v>
+      </c>
+      <c r="Q664" t="n">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>TB115</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J665" t="n">
+        <v>43</v>
+      </c>
+      <c r="K665" t="n">
+        <v>0</v>
+      </c>
+      <c r="L665" t="n">
+        <v>0</v>
+      </c>
+      <c r="M665" t="n">
+        <v>43</v>
+      </c>
+      <c r="N665" t="n">
+        <v>8006.3731111111</v>
+      </c>
+      <c r="O665" t="n">
+        <v>344274.0437777773</v>
+      </c>
+      <c r="P665" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q665" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
           <t>TB122</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr">
+      <c r="E666" t="inlineStr">
         <is>
           <t>PELUCHES</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J661" t="n">
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J666" t="n">
         <v>4</v>
       </c>
-      <c r="K661" t="n">
-        <v>0</v>
-      </c>
-      <c r="L661" t="n">
-        <v>0</v>
-      </c>
-      <c r="M661" t="n">
+      <c r="K666" t="n">
+        <v>0</v>
+      </c>
+      <c r="L666" t="n">
+        <v>0</v>
+      </c>
+      <c r="M666" t="n">
         <v>4</v>
       </c>
-      <c r="N661" t="n">
+      <c r="N666" t="n">
         <v>47920</v>
       </c>
-      <c r="O661" t="n">
+      <c r="O666" t="n">
         <v>191680</v>
       </c>
-      <c r="P661" t="n">
+      <c r="P666" t="n">
         <v>59900</v>
       </c>
-      <c r="Q661" t="n">
+      <c r="Q666" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -2357,10 +2357,10 @@
         <v>98</v>
       </c>
       <c r="N48" t="n">
-        <v>544.6367953668</v>
+        <v>538.40061776062</v>
       </c>
       <c r="O48" t="n">
-        <v>53374.4059459464</v>
+        <v>52763.26054054076</v>
       </c>
       <c r="P48" t="n">
         <v>6800</v>
@@ -2573,10 +2573,10 @@
         <v>49</v>
       </c>
       <c r="N53" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O53" t="n">
-        <v>129561.9505035961</v>
+        <v>125937.84</v>
       </c>
       <c r="P53" t="n">
         <v>4700</v>
@@ -2695,10 +2695,10 @@
         <v>26</v>
       </c>
       <c r="N56" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O56" t="n">
-        <v>69138.31065420501</v>
+        <v>66646.84</v>
       </c>
       <c r="P56" t="n">
         <v>4700</v>
@@ -2829,10 +2829,10 @@
         <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O59" t="n">
-        <v>32692.764753363</v>
+        <v>32258.79</v>
       </c>
       <c r="P59" t="n">
         <v>18400</v>
@@ -3501,10 +3501,10 @@
         <v>48</v>
       </c>
       <c r="N74" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O74" t="n">
-        <v>828624.3574798079</v>
+        <v>825955.6799999999</v>
       </c>
       <c r="P74" t="n">
         <v>20000</v>
@@ -5351,10 +5351,10 @@
         <v>309</v>
       </c>
       <c r="N115" t="n">
-        <v>2271.9151051954</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O115" t="n">
-        <v>702021.7675053786</v>
+        <v>700517.8635766482</v>
       </c>
       <c r="P115" t="n">
         <v>3900</v>
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.748387104</v>
+        <v>862620.744827592</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -6348,10 +6348,10 @@
         <v>154</v>
       </c>
       <c r="N137" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O137" t="n">
-        <v>418701.639409284</v>
+        <v>415197.86</v>
       </c>
       <c r="P137" t="n">
         <v>8200</v>
@@ -7192,10 +7192,10 @@
         <v>37</v>
       </c>
       <c r="N156" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O156" t="n">
-        <v>231646.4966381757</v>
+        <v>230988.41</v>
       </c>
       <c r="P156" t="n">
         <v>10400</v>
@@ -7787,10 +7787,10 @@
         <v>109</v>
       </c>
       <c r="N169" t="n">
-        <v>4752.0246648045</v>
+        <v>4635.49</v>
       </c>
       <c r="O169" t="n">
-        <v>517970.6884636905</v>
+        <v>505268.41</v>
       </c>
       <c r="P169" t="n">
         <v>7500</v>
@@ -8944,10 +8944,10 @@
         <v>11</v>
       </c>
       <c r="N194" t="n">
-        <v>11749.140699301</v>
+        <v>11507.72</v>
       </c>
       <c r="O194" t="n">
-        <v>129240.547692311</v>
+        <v>126584.92</v>
       </c>
       <c r="P194" t="n">
         <v>25800</v>
@@ -10156,10 +10156,10 @@
         <v>87</v>
       </c>
       <c r="N221" t="n">
-        <v>2633.2</v>
+        <v>2610</v>
       </c>
       <c r="O221" t="n">
-        <v>229088.4</v>
+        <v>227070</v>
       </c>
       <c r="P221" t="n">
         <v>3200</v>
@@ -11480,10 +11480,10 @@
         <v>92</v>
       </c>
       <c r="N251" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O251" t="n">
-        <v>2505468.735272744</v>
+        <v>2495386.364202036</v>
       </c>
       <c r="P251" t="n">
         <v>44500</v>
@@ -11700,10 +11700,10 @@
         <v>522</v>
       </c>
       <c r="N256" t="n">
-        <v>1561.0041954445</v>
+        <v>1561.004375</v>
       </c>
       <c r="O256" t="n">
-        <v>814844.190022029</v>
+        <v>814844.2837499999</v>
       </c>
       <c r="P256" t="n">
         <v>2900</v>
@@ -11838,10 +11838,10 @@
         <v>188</v>
       </c>
       <c r="N259" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O259" t="n">
-        <v>1501819.036080243</v>
+        <v>1498350.631913583</v>
       </c>
       <c r="P259" t="n">
         <v>12900</v>
@@ -11884,10 +11884,10 @@
         <v>46</v>
       </c>
       <c r="N260" t="n">
-        <v>9794.2880924855</v>
+        <v>9627.34</v>
       </c>
       <c r="O260" t="n">
-        <v>450537.252254333</v>
+        <v>442857.64</v>
       </c>
       <c r="P260" t="n">
         <v>15900</v>
@@ -12538,10 +12538,10 @@
         <v>122</v>
       </c>
       <c r="N274" t="n">
-        <v>3131.5075106082</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O274" t="n">
-        <v>382043.9162942004</v>
+        <v>379894.583451197</v>
       </c>
       <c r="P274" t="n">
         <v>5000</v>
@@ -12768,10 +12768,10 @@
         <v>144</v>
       </c>
       <c r="N279" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O279" t="n">
-        <v>361568.1995698896</v>
+        <v>359421.12</v>
       </c>
       <c r="P279" t="n">
         <v>4100</v>
@@ -13231,10 +13231,10 @@
         <v>36</v>
       </c>
       <c r="N289" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="O289" t="n">
-        <v>210930.48</v>
+        <v>208477.8</v>
       </c>
       <c r="P289" t="n">
         <v>9300</v>
@@ -13418,10 +13418,10 @@
         <v>34</v>
       </c>
       <c r="N293" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O293" t="n">
-        <v>318889.2921379308</v>
+        <v>312425.32</v>
       </c>
       <c r="P293" t="n">
         <v>12900</v>
@@ -13832,10 +13832,10 @@
         <v>129</v>
       </c>
       <c r="N302" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O302" t="n">
-        <v>2075995.032679695</v>
+        <v>2071482</v>
       </c>
       <c r="P302" t="n">
         <v>25900</v>
@@ -13878,10 +13878,10 @@
         <v>313</v>
       </c>
       <c r="N303" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O303" t="n">
-        <v>8005566.650615967</v>
+        <v>7992142</v>
       </c>
       <c r="P303" t="n">
         <v>40900</v>
@@ -14528,10 +14528,10 @@
         <v>57</v>
       </c>
       <c r="N317" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O317" t="n">
-        <v>786318.150000006</v>
+        <v>780159</v>
       </c>
       <c r="P317" t="n">
         <v>21900</v>
@@ -14850,10 +14850,10 @@
         <v>15</v>
       </c>
       <c r="N324" t="n">
-        <v>10485.899280576</v>
+        <v>10411</v>
       </c>
       <c r="O324" t="n">
-        <v>157288.48920864</v>
+        <v>156165</v>
       </c>
       <c r="P324" t="n">
         <v>16900</v>
@@ -15360,10 +15360,10 @@
         <v>5</v>
       </c>
       <c r="N335" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O335" t="n">
-        <v>162834.285714285</v>
+        <v>161660</v>
       </c>
       <c r="P335" t="n">
         <v>55900</v>
@@ -15820,10 +15820,10 @@
         <v>149</v>
       </c>
       <c r="N345" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O345" t="n">
-        <v>508464.7084560524</v>
+        <v>506060.62</v>
       </c>
       <c r="P345" t="n">
         <v>6500</v>
@@ -15958,10 +15958,10 @@
         <v>44</v>
       </c>
       <c r="N348" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O348" t="n">
-        <v>582263.3098591759</v>
+        <v>581240</v>
       </c>
       <c r="P348" t="n">
         <v>23900</v>
@@ -16275,10 +16275,10 @@
         <v>382</v>
       </c>
       <c r="N355" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O355" t="n">
-        <v>2628865.297998078</v>
+        <v>2616394.4</v>
       </c>
       <c r="P355" t="n">
         <v>11500</v>
@@ -16597,10 +16597,10 @@
         <v>524</v>
       </c>
       <c r="N362" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O362" t="n">
-        <v>4002978.176223761</v>
+        <v>4000740</v>
       </c>
       <c r="P362" t="n">
         <v>13900</v>
@@ -17428,10 +17428,10 @@
         <v>51</v>
       </c>
       <c r="N380" t="n">
-        <v>8721.3759213759</v>
+        <v>8700</v>
       </c>
       <c r="O380" t="n">
-        <v>444790.1719901709</v>
+        <v>443700</v>
       </c>
       <c r="P380" t="n">
         <v>14900</v>
@@ -17750,10 +17750,10 @@
         <v>16</v>
       </c>
       <c r="N387" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O387" t="n">
-        <v>350148.134831456</v>
+        <v>348192</v>
       </c>
       <c r="P387" t="n">
         <v>35900</v>
@@ -17796,10 +17796,10 @@
         <v>1126</v>
       </c>
       <c r="N388" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O388" t="n">
-        <v>4305390.863791915</v>
+        <v>4302446</v>
       </c>
       <c r="P388" t="n">
         <v>5900</v>
@@ -17934,10 +17934,10 @@
         <v>39</v>
       </c>
       <c r="N391" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O391" t="n">
-        <v>284517.9747081711</v>
+        <v>282867</v>
       </c>
       <c r="P391" t="n">
         <v>11900</v>
@@ -18981,10 +18981,10 @@
         <v>2800</v>
       </c>
       <c r="N414" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O414" t="n">
-        <v>5476191.87407208</v>
+        <v>5474663.91649464</v>
       </c>
       <c r="P414" t="n">
         <v>3000</v>
@@ -19027,10 +19027,10 @@
         <v>2800</v>
       </c>
       <c r="N415" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O415" t="n">
-        <v>3320281.12280704</v>
+        <v>3318894.78362568</v>
       </c>
       <c r="P415" t="n">
         <v>1900</v>
@@ -19686,10 +19686,10 @@
         <v>46</v>
       </c>
       <c r="N429" t="n">
-        <v>3256.3775316456</v>
+        <v>3026.5160126582</v>
       </c>
       <c r="O429" t="n">
-        <v>149793.3664556976</v>
+        <v>139219.7365822772</v>
       </c>
       <c r="P429" t="n">
         <v>7000</v>
@@ -19828,10 +19828,10 @@
         <v>348</v>
       </c>
       <c r="N432" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O432" t="n">
-        <v>535209.473916588</v>
+        <v>532596.5715453972</v>
       </c>
       <c r="P432" t="n">
         <v>2600</v>
@@ -21955,10 +21955,10 @@
         <v>18602</v>
       </c>
       <c r="N478" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O478" t="n">
-        <v>13091990.34046778</v>
+        <v>13108380.08373474</v>
       </c>
       <c r="P478" t="n">
         <v>900</v>
@@ -24579,10 +24579,10 @@
         <v>323</v>
       </c>
       <c r="N533" t="n">
-        <v>5370.6369361702</v>
+        <v>5347.88</v>
       </c>
       <c r="O533" t="n">
-        <v>1734715.730382974</v>
+        <v>1727365.24</v>
       </c>
       <c r="P533" t="n">
         <v>7900</v>
@@ -24628,10 +24628,10 @@
         <v>292</v>
       </c>
       <c r="N534" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O534" t="n">
-        <v>1341214.129271528</v>
+        <v>1336787.68</v>
       </c>
       <c r="P534" t="n">
         <v>7500</v>
@@ -25626,10 +25626,10 @@
         <v>40</v>
       </c>
       <c r="N555" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O555" t="n">
-        <v>436516.10638296</v>
+        <v>431921.2</v>
       </c>
       <c r="P555" t="n">
         <v>45000</v>
@@ -26043,10 +26043,10 @@
         <v>73</v>
       </c>
       <c r="N564" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O564" t="n">
-        <v>384870.8063604223</v>
+        <v>380833.7</v>
       </c>
       <c r="P564" t="n">
         <v>20500</v>
@@ -27516,10 +27516,10 @@
         <v>635</v>
       </c>
       <c r="N596" t="n">
-        <v>3186.7802147239</v>
+        <v>3181.9</v>
       </c>
       <c r="O596" t="n">
-        <v>2023605.436349676</v>
+        <v>2020506.5</v>
       </c>
       <c r="P596" t="n">
         <v>5100</v>
@@ -28052,10 +28052,10 @@
         <v>172</v>
       </c>
       <c r="N608" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O608" t="n">
-        <v>121724.1988923076</v>
+        <v>121350.8107076924</v>
       </c>
       <c r="P608" t="n">
         <v>1500</v>
@@ -28471,10 +28471,10 @@
         <v>439</v>
       </c>
       <c r="N617" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O617" t="n">
-        <v>1165771.077658867</v>
+        <v>1161111.1</v>
       </c>
       <c r="P617" t="n">
         <v>3900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q665"/>
+  <dimension ref="A1:Q662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.309157128</v>
+        <v>1811.3091666667</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.309157128</v>
+        <v>1811.3091666667</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464140994</v>
+        <v>3376.7464051196</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.83006387</v>
+        <v>2985043.822125726</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1312,10 +1312,10 @@
         <v>66</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.7035327103</v>
+        <v>2474.7035205993</v>
       </c>
       <c r="O23" t="n">
-        <v>163330.4331588798</v>
+        <v>163330.4323595538</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1585,10 +1585,10 @@
         <v>29</v>
       </c>
       <c r="N30" t="n">
-        <v>31409.32</v>
+        <v>31566.3666</v>
       </c>
       <c r="O30" t="n">
-        <v>910870.28</v>
+        <v>915424.6314000001</v>
       </c>
       <c r="P30" t="n">
         <v>45500</v>
@@ -1755,10 +1755,10 @@
         <v>24</v>
       </c>
       <c r="N34" t="n">
-        <v>16486.407142857</v>
+        <v>16486.406666667</v>
       </c>
       <c r="O34" t="n">
-        <v>395673.7714285679</v>
+        <v>395673.760000008</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
@@ -2829,10 +2829,10 @@
         <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>10752.93</v>
+        <v>10899.560863636</v>
       </c>
       <c r="O59" t="n">
-        <v>32258.79</v>
+        <v>32698.682590908</v>
       </c>
       <c r="P59" t="n">
         <v>18400</v>
@@ -3096,10 +3096,10 @@
         <v>1127</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.0638359274</v>
+        <v>1098.0646017403</v>
       </c>
       <c r="O65" t="n">
-        <v>1237517.94309018</v>
+        <v>1237518.806161318</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3139,19 +3139,19 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N66" t="n">
         <v>6295.2</v>
       </c>
       <c r="O66" t="n">
-        <v>289579.2</v>
+        <v>195151.2</v>
       </c>
       <c r="P66" t="n">
         <v>10500</v>
       </c>
       <c r="Q66" t="n">
-        <v>483000</v>
+        <v>325500</v>
       </c>
     </row>
     <row r="67">
@@ -3460,10 +3460,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>13593.35</v>
+        <v>13609.886922141</v>
       </c>
       <c r="O73" t="n">
-        <v>13593.35</v>
+        <v>13609.886922141</v>
       </c>
       <c r="P73" t="n">
         <v>25500</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3803,19 +3803,19 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="N81" t="n">
         <v>2850.95</v>
       </c>
       <c r="O81" t="n">
-        <v>655718.5</v>
+        <v>518872.9</v>
       </c>
       <c r="P81" t="n">
         <v>4900</v>
       </c>
       <c r="Q81" t="n">
-        <v>1127000</v>
+        <v>891800</v>
       </c>
     </row>
     <row r="82">
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.25501002</v>
+        <v>2583.5545646704</v>
       </c>
       <c r="O86" t="n">
-        <v>1719781.83667332</v>
+        <v>1720647.340070486</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.8959455416</v>
+        <v>5216.8959284856</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.699730705</v>
+        <v>3474452.68837141</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4213,19 +4213,19 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N90" t="n">
         <v>5503.85</v>
       </c>
       <c r="O90" t="n">
-        <v>792554.4</v>
+        <v>704492.8</v>
       </c>
       <c r="P90" t="n">
         <v>9500</v>
       </c>
       <c r="Q90" t="n">
-        <v>1368000</v>
+        <v>1216000</v>
       </c>
     </row>
     <row r="91">
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3158.8608386776</v>
+        <v>3160.7464443118</v>
       </c>
       <c r="O93" t="n">
-        <v>10004112.27609196</v>
+        <v>10010083.98913547</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4439,10 +4439,10 @@
         <v>262</v>
       </c>
       <c r="N95" t="n">
-        <v>8214</v>
+        <v>8252.563380281699</v>
       </c>
       <c r="O95" t="n">
-        <v>2152068</v>
+        <v>2162171.605633805</v>
       </c>
       <c r="P95" t="n">
         <v>7900</v>
@@ -4488,10 +4488,10 @@
         <v>144</v>
       </c>
       <c r="N96" t="n">
-        <v>3230.0664248705</v>
+        <v>3283.163260274</v>
       </c>
       <c r="O96" t="n">
-        <v>465129.565181352</v>
+        <v>472775.509479456</v>
       </c>
       <c r="P96" t="n">
         <v>6200</v>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4765,19 +4765,19 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="N102" t="n">
-        <v>8796</v>
+        <v>8820</v>
       </c>
       <c r="O102" t="n">
-        <v>343044</v>
+        <v>202860</v>
       </c>
       <c r="P102" t="n">
         <v>14900</v>
       </c>
       <c r="Q102" t="n">
-        <v>581100</v>
+        <v>342700</v>
       </c>
     </row>
     <row r="103">
@@ -4947,10 +4947,10 @@
         <v>581</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100076161</v>
+        <v>3795.7100076176</v>
       </c>
       <c r="O106" t="n">
-        <v>2205307.514424954</v>
+        <v>2205307.514425825</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -5031,19 +5031,19 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="N108" t="n">
         <v>2612.77</v>
       </c>
       <c r="O108" t="n">
-        <v>300468.55</v>
+        <v>206408.83</v>
       </c>
       <c r="P108" t="n">
         <v>4900</v>
       </c>
       <c r="Q108" t="n">
-        <v>563500</v>
+        <v>387100</v>
       </c>
     </row>
     <row r="109">
@@ -5172,10 +5172,10 @@
         <v>309</v>
       </c>
       <c r="N111" t="n">
-        <v>4890.9300513149</v>
+        <v>4890.9300530504</v>
       </c>
       <c r="O111" t="n">
-        <v>1511297.385856304</v>
+        <v>1511297.386392574</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2531034483</v>
+        <v>3594.2530785869</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.744827592</v>
+        <v>862620.7388608559</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1650</v>
+        <v>1506</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5986,19 +5986,19 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>1650</v>
+        <v>1506</v>
       </c>
       <c r="N129" t="n">
         <v>2090.85</v>
       </c>
       <c r="O129" t="n">
-        <v>3449902.5</v>
+        <v>3148820.1</v>
       </c>
       <c r="P129" t="n">
         <v>2900</v>
       </c>
       <c r="Q129" t="n">
-        <v>4785000</v>
+        <v>4367400</v>
       </c>
     </row>
     <row r="130">
@@ -6261,10 +6261,10 @@
         <v>320</v>
       </c>
       <c r="N135" t="n">
-        <v>12422.462946776</v>
+        <v>12422.462948052</v>
       </c>
       <c r="O135" t="n">
-        <v>3975188.14296832</v>
+        <v>3975188.14337664</v>
       </c>
       <c r="P135" t="n">
         <v>19900</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>2520</v>
+        <v>2376</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -6391,19 +6391,19 @@
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>2520</v>
+        <v>2376</v>
       </c>
       <c r="N138" t="n">
-        <v>3472.2761773616</v>
+        <v>3472.2761978447</v>
       </c>
       <c r="O138" t="n">
-        <v>8750135.966951232</v>
+        <v>8250128.246079007</v>
       </c>
       <c r="P138" t="n">
         <v>5900</v>
       </c>
       <c r="Q138" t="n">
-        <v>14868000</v>
+        <v>14018400</v>
       </c>
     </row>
     <row r="139">
@@ -6623,10 +6623,10 @@
         <v>207</v>
       </c>
       <c r="N143" t="n">
-        <v>3041.6600140449</v>
+        <v>3041.6600141844</v>
       </c>
       <c r="O143" t="n">
-        <v>629623.6229072943</v>
+        <v>629623.6229361708</v>
       </c>
       <c r="P143" t="n">
         <v>5500</v>
@@ -6751,10 +6751,10 @@
         <v>1930</v>
       </c>
       <c r="N146" t="n">
-        <v>4371.1712626125</v>
+        <v>4372.0654674395</v>
       </c>
       <c r="O146" t="n">
-        <v>8436360.536842125</v>
+        <v>8438086.352158235</v>
       </c>
       <c r="P146" t="n">
         <v>8900</v>
@@ -6841,10 +6841,10 @@
         <v>181</v>
       </c>
       <c r="N148" t="n">
-        <v>1592.565242452</v>
+        <v>1592.565202952</v>
       </c>
       <c r="O148" t="n">
-        <v>288254.308883812</v>
+        <v>288254.301734312</v>
       </c>
       <c r="P148" t="n">
         <v>3900</v>
@@ -7010,10 +7010,10 @@
         <v>54</v>
       </c>
       <c r="N152" t="n">
-        <v>5331.69</v>
+        <v>5371.5779551122</v>
       </c>
       <c r="O152" t="n">
-        <v>287911.26</v>
+        <v>290065.2095760588</v>
       </c>
       <c r="P152" t="n">
         <v>7900</v>
@@ -7331,10 +7331,10 @@
         <v>450</v>
       </c>
       <c r="N159" t="n">
-        <v>1532.629025031</v>
+        <v>1534.4227525419</v>
       </c>
       <c r="O159" t="n">
-        <v>689683.0612639501</v>
+        <v>690490.2386438551</v>
       </c>
       <c r="P159" t="n">
         <v>1200</v>
@@ -8115,10 +8115,10 @@
         <v>36</v>
       </c>
       <c r="N176" t="n">
-        <v>3761.6</v>
+        <v>3776.2176165803</v>
       </c>
       <c r="O176" t="n">
-        <v>135417.6</v>
+        <v>135943.8341968908</v>
       </c>
       <c r="P176" t="n">
         <v>6900</v>
@@ -8632,10 +8632,10 @@
         <v>556</v>
       </c>
       <c r="N187" t="n">
-        <v>1630.9244361119</v>
+        <v>1630.924511587</v>
       </c>
       <c r="O187" t="n">
-        <v>906793.9864782164</v>
+        <v>906794.0284423721</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8678,10 +8678,10 @@
         <v>5</v>
       </c>
       <c r="N188" t="n">
-        <v>1467.3132911392</v>
+        <v>1467.3113333333</v>
       </c>
       <c r="O188" t="n">
-        <v>7336.566455696</v>
+        <v>7336.5566666665</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8724,10 +8724,10 @@
         <v>192</v>
       </c>
       <c r="N189" t="n">
-        <v>1690.582398524</v>
+        <v>1690.5810573248</v>
       </c>
       <c r="O189" t="n">
-        <v>324591.820516608</v>
+        <v>324591.5630063616</v>
       </c>
       <c r="P189" t="n">
         <v>2900</v>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>1422</v>
+        <v>1294</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -8767,19 +8767,19 @@
         <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>1422</v>
+        <v>1294</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1945724495</v>
+        <v>1550.1946099379</v>
       </c>
       <c r="O190" t="n">
-        <v>2204376.682023189</v>
+        <v>2005951.825259642</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
       </c>
       <c r="Q190" t="n">
-        <v>3555000</v>
+        <v>3235000</v>
       </c>
     </row>
     <row r="191">
@@ -8816,10 +8816,10 @@
         <v>22</v>
       </c>
       <c r="N191" t="n">
-        <v>1579.3839013453</v>
+        <v>1579.3838288288</v>
       </c>
       <c r="O191" t="n">
-        <v>34746.4458295966</v>
+        <v>34746.4442342336</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5190521472</v>
+        <v>2403.5197991712</v>
       </c>
       <c r="O192" t="n">
-        <v>418212.3150736128</v>
+        <v>418212.4450557888</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -9486,10 +9486,10 @@
         <v>45</v>
       </c>
       <c r="N206" t="n">
-        <v>14118.32</v>
+        <v>14292.620246914</v>
       </c>
       <c r="O206" t="n">
-        <v>635324.4</v>
+        <v>643167.91111113</v>
       </c>
       <c r="P206" t="n">
         <v>17900</v>
@@ -9532,10 +9532,10 @@
         <v>22</v>
       </c>
       <c r="N207" t="n">
-        <v>8720</v>
+        <v>9446.666666666701</v>
       </c>
       <c r="O207" t="n">
-        <v>191840</v>
+        <v>207826.6666666674</v>
       </c>
       <c r="P207" t="n">
         <v>10900</v>
@@ -9622,10 +9622,10 @@
         <v>67</v>
       </c>
       <c r="N209" t="n">
-        <v>19120</v>
+        <v>19359</v>
       </c>
       <c r="O209" t="n">
-        <v>1281040</v>
+        <v>1297053</v>
       </c>
       <c r="P209" t="n">
         <v>23900</v>
@@ -10074,10 +10074,10 @@
         <v>18</v>
       </c>
       <c r="N219" t="n">
-        <v>7537.4722834646</v>
+        <v>7719.830483871</v>
       </c>
       <c r="O219" t="n">
-        <v>135674.5011023628</v>
+        <v>138956.948709678</v>
       </c>
       <c r="P219" t="n">
         <v>8900</v>
@@ -10238,10 +10238,10 @@
         <v>254</v>
       </c>
       <c r="N223" t="n">
-        <v>1969</v>
+        <v>1974.990872211</v>
       </c>
       <c r="O223" t="n">
-        <v>500126</v>
+        <v>501647.681541594</v>
       </c>
       <c r="P223" t="n">
         <v>1500</v>
@@ -10279,10 +10279,10 @@
         <v>148</v>
       </c>
       <c r="N224" t="n">
-        <v>8794.48</v>
+        <v>8799.4655328798</v>
       </c>
       <c r="O224" t="n">
-        <v>1301583.04</v>
+        <v>1302320.89886621</v>
       </c>
       <c r="P224" t="n">
         <v>14500</v>
@@ -10717,10 +10717,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>3731.0244863014</v>
+        <v>3731.0245172414</v>
       </c>
       <c r="O234" t="n">
-        <v>44772.2938356168</v>
+        <v>44772.2942068968</v>
       </c>
       <c r="P234" t="n">
         <v>5200</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10901,19 +10901,19 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="N238" t="n">
-        <v>4285.1962793572</v>
+        <v>4285.1963341646</v>
       </c>
       <c r="O238" t="n">
-        <v>484227.1795673636</v>
+        <v>381382.4737406494</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
       </c>
       <c r="Q238" t="n">
-        <v>779700</v>
+        <v>614100</v>
       </c>
     </row>
     <row r="239">
@@ -11163,10 +11163,10 @@
         <v>1280</v>
       </c>
       <c r="N244" t="n">
-        <v>4814.2679265446</v>
+        <v>4814.2679260066</v>
       </c>
       <c r="O244" t="n">
-        <v>6162262.945977088</v>
+        <v>6162262.945288448</v>
       </c>
       <c r="P244" t="n">
         <v>9900</v>
@@ -11296,10 +11296,10 @@
         <v>17</v>
       </c>
       <c r="N247" t="n">
-        <v>13513.643504274</v>
+        <v>13513.643534483</v>
       </c>
       <c r="O247" t="n">
-        <v>229731.939572658</v>
+        <v>229731.940086211</v>
       </c>
       <c r="P247" t="n">
         <v>21900</v>
@@ -11388,10 +11388,10 @@
         <v>16</v>
       </c>
       <c r="N249" t="n">
-        <v>22730.48</v>
+        <v>22761.155411606</v>
       </c>
       <c r="O249" t="n">
-        <v>363687.68</v>
+        <v>364178.486585696</v>
       </c>
       <c r="P249" t="n">
         <v>36900</v>
@@ -11608,10 +11608,10 @@
         <v>1328</v>
       </c>
       <c r="N254" t="n">
-        <v>4100.45</v>
+        <v>4102.8563673709</v>
       </c>
       <c r="O254" t="n">
-        <v>5445397.6</v>
+        <v>5448593.255868556</v>
       </c>
       <c r="P254" t="n">
         <v>26900</v>
@@ -11700,10 +11700,10 @@
         <v>522</v>
       </c>
       <c r="N256" t="n">
-        <v>1561.004375</v>
+        <v>1561.0050819672</v>
       </c>
       <c r="O256" t="n">
-        <v>814844.2837499999</v>
+        <v>814844.6527868784</v>
       </c>
       <c r="P256" t="n">
         <v>2900</v>
@@ -13418,10 +13418,10 @@
         <v>34</v>
       </c>
       <c r="N293" t="n">
-        <v>9188.98</v>
+        <v>9252.7923611111</v>
       </c>
       <c r="O293" t="n">
-        <v>312425.32</v>
+        <v>314594.9402777774</v>
       </c>
       <c r="P293" t="n">
         <v>12900</v>
@@ -13556,10 +13556,10 @@
         <v>768</v>
       </c>
       <c r="N296" t="n">
-        <v>1778.4728179471</v>
+        <v>1778.4728348758</v>
       </c>
       <c r="O296" t="n">
-        <v>1365867.124183373</v>
+        <v>1365867.137184614</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
@@ -13786,10 +13786,10 @@
         <v>289</v>
       </c>
       <c r="N301" t="n">
-        <v>18016</v>
+        <v>18023.2064</v>
       </c>
       <c r="O301" t="n">
-        <v>5206624</v>
+        <v>5208706.6496</v>
       </c>
       <c r="P301" t="n">
         <v>29900</v>
@@ -14666,10 +14666,10 @@
         <v>592</v>
       </c>
       <c r="N320" t="n">
-        <v>3938.66</v>
+        <v>3950.9108864697</v>
       </c>
       <c r="O320" t="n">
-        <v>2331686.72</v>
+        <v>2338939.244790062</v>
       </c>
       <c r="P320" t="n">
         <v>4500</v>
@@ -14850,10 +14850,10 @@
         <v>15</v>
       </c>
       <c r="N324" t="n">
-        <v>10411</v>
+        <v>10448.584837545</v>
       </c>
       <c r="O324" t="n">
-        <v>156165</v>
+        <v>156728.772563175</v>
       </c>
       <c r="P324" t="n">
         <v>16900</v>
@@ -14896,10 +14896,10 @@
         <v>5</v>
       </c>
       <c r="N325" t="n">
-        <v>2252.2979910045</v>
+        <v>2252.2981374046</v>
       </c>
       <c r="O325" t="n">
-        <v>11261.4899550225</v>
+        <v>11261.490687023</v>
       </c>
       <c r="P325" t="n">
         <v>3900</v>
@@ -15222,10 +15222,10 @@
         <v>324</v>
       </c>
       <c r="N332" t="n">
-        <v>2328.1186691895</v>
+        <v>2328.1186615921</v>
       </c>
       <c r="O332" t="n">
-        <v>754310.448817398</v>
+        <v>754310.4463558404</v>
       </c>
       <c r="P332" t="n">
         <v>4500</v>
@@ -15866,10 +15866,10 @@
         <v>137</v>
       </c>
       <c r="N346" t="n">
-        <v>4907.8226185567</v>
+        <v>4907.8226736842</v>
       </c>
       <c r="O346" t="n">
-        <v>672371.6987422679</v>
+        <v>672371.7062947354</v>
       </c>
       <c r="P346" t="n">
         <v>8200</v>
@@ -16050,10 +16050,10 @@
         <v>240</v>
       </c>
       <c r="N350" t="n">
-        <v>3903.7391411043</v>
+        <v>3903.7392422907</v>
       </c>
       <c r="O350" t="n">
-        <v>936897.393865032</v>
+        <v>936897.418149768</v>
       </c>
       <c r="P350" t="n">
         <v>7500</v>
@@ -17474,10 +17474,10 @@
         <v>112</v>
       </c>
       <c r="N381" t="n">
-        <v>3639.35</v>
+        <v>3652.664695122</v>
       </c>
       <c r="O381" t="n">
-        <v>407607.2</v>
+        <v>409098.445853664</v>
       </c>
       <c r="P381" t="n">
         <v>7500</v>
@@ -17980,10 +17980,10 @@
         <v>50</v>
       </c>
       <c r="N392" t="n">
-        <v>15223.06</v>
+        <v>15334.994264706</v>
       </c>
       <c r="O392" t="n">
-        <v>761153</v>
+        <v>766749.7132353</v>
       </c>
       <c r="P392" t="n">
         <v>17500</v>
@@ -18060,7 +18060,7 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>1248</v>
+        <v>1152</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
@@ -18069,19 +18069,19 @@
         <v>0</v>
       </c>
       <c r="M394" t="n">
-        <v>1248</v>
+        <v>1152</v>
       </c>
       <c r="N394" t="n">
-        <v>1516.0387429797</v>
+        <v>1516.0387397625</v>
       </c>
       <c r="O394" t="n">
-        <v>1892016.351238665</v>
+        <v>1746476.6282064</v>
       </c>
       <c r="P394" t="n">
         <v>2300</v>
       </c>
       <c r="Q394" t="n">
-        <v>2870400</v>
+        <v>2649600</v>
       </c>
     </row>
     <row r="395">
@@ -18256,10 +18256,10 @@
         <v>96</v>
       </c>
       <c r="N398" t="n">
-        <v>2056.0821341463</v>
+        <v>2056.0821161192</v>
       </c>
       <c r="O398" t="n">
-        <v>197383.8848780448</v>
+        <v>197383.8831474432</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
@@ -18532,10 +18532,10 @@
         <v>224</v>
       </c>
       <c r="N404" t="n">
-        <v>1592.2827128427</v>
+        <v>1592.2831886228</v>
       </c>
       <c r="O404" t="n">
-        <v>356671.3276767648</v>
+        <v>356671.4342515072</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -18660,19 +18660,19 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="N407" t="n">
-        <v>2060.1587279843</v>
+        <v>2060.1585714286</v>
       </c>
       <c r="O407" t="n">
-        <v>766379.0468101597</v>
+        <v>642769.4742857233</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
       </c>
       <c r="Q407" t="n">
-        <v>1078800</v>
+        <v>904800</v>
       </c>
     </row>
     <row r="408">
@@ -18709,10 +18709,10 @@
         <v>400</v>
       </c>
       <c r="N408" t="n">
-        <v>1259.2748510332</v>
+        <v>1259.274867406</v>
       </c>
       <c r="O408" t="n">
-        <v>503709.94041328</v>
+        <v>503709.9469624</v>
       </c>
       <c r="P408" t="n">
         <v>1900</v>
@@ -18796,10 +18796,10 @@
         <v>97</v>
       </c>
       <c r="N410" t="n">
-        <v>2842.2744067797</v>
+        <v>2842.2743909348</v>
       </c>
       <c r="O410" t="n">
-        <v>275700.6174576309</v>
+        <v>275700.6159206756</v>
       </c>
       <c r="P410" t="n">
         <v>4900</v>
@@ -18886,10 +18886,10 @@
         <v>516</v>
       </c>
       <c r="N412" t="n">
-        <v>692.15240898798</v>
+        <v>692.1524140338601</v>
       </c>
       <c r="O412" t="n">
-        <v>357150.6430377977</v>
+        <v>357150.6456414718</v>
       </c>
       <c r="P412" t="n">
         <v>1200</v>
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -19220,19 +19220,19 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N419" t="n">
         <v>44470</v>
       </c>
       <c r="O419" t="n">
-        <v>2134560</v>
+        <v>1867740</v>
       </c>
       <c r="P419" t="n">
         <v>71900</v>
       </c>
       <c r="Q419" t="n">
-        <v>3451200</v>
+        <v>3019800</v>
       </c>
     </row>
     <row r="420">
@@ -19260,7 +19260,7 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
@@ -19269,19 +19269,19 @@
         <v>0</v>
       </c>
       <c r="M420" t="n">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="N420" t="n">
         <v>5215</v>
       </c>
       <c r="O420" t="n">
-        <v>4823875</v>
+        <v>4667425</v>
       </c>
       <c r="P420" t="n">
         <v>8900</v>
       </c>
       <c r="Q420" t="n">
-        <v>8232500</v>
+        <v>7965500</v>
       </c>
     </row>
     <row r="421">
@@ -19579,7 +19579,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -19588,19 +19588,19 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N427" t="n">
         <v>2857.22</v>
       </c>
       <c r="O427" t="n">
-        <v>605730.64</v>
+        <v>602873.4199999999</v>
       </c>
       <c r="P427" t="n">
         <v>4900</v>
       </c>
       <c r="Q427" t="n">
-        <v>1038800</v>
+        <v>1033900</v>
       </c>
     </row>
     <row r="428">
@@ -19920,10 +19920,10 @@
         <v>243</v>
       </c>
       <c r="N434" t="n">
-        <v>3629.36</v>
+        <v>3650.5019029126</v>
       </c>
       <c r="O434" t="n">
-        <v>881934.48</v>
+        <v>887071.9624077618</v>
       </c>
       <c r="P434" t="n">
         <v>3900</v>
@@ -20197,10 +20197,10 @@
         <v>20</v>
       </c>
       <c r="N440" t="n">
-        <v>2357.74</v>
+        <v>2479.6920689655</v>
       </c>
       <c r="O440" t="n">
-        <v>47154.8</v>
+        <v>49593.84137931</v>
       </c>
       <c r="P440" t="n">
         <v>3000</v>
@@ -20287,10 +20287,10 @@
         <v>306</v>
       </c>
       <c r="N442" t="n">
-        <v>1690.8700093502</v>
+        <v>1690.8700093809</v>
       </c>
       <c r="O442" t="n">
-        <v>517406.2228611612</v>
+        <v>517406.2228705554</v>
       </c>
       <c r="P442" t="n">
         <v>3000</v>
@@ -20571,10 +20571,10 @@
         <v>9193</v>
       </c>
       <c r="N448" t="n">
-        <v>345.55838633169</v>
+        <v>345.63428985635</v>
       </c>
       <c r="O448" t="n">
-        <v>3176718.245547226</v>
+        <v>3177416.026649425</v>
       </c>
       <c r="P448" t="n">
         <v>600</v>
@@ -20713,10 +20713,10 @@
         <v>5817</v>
       </c>
       <c r="N451" t="n">
-        <v>711.3366477489</v>
+        <v>711.87861852814</v>
       </c>
       <c r="O451" t="n">
-        <v>4137845.279955351</v>
+        <v>4140997.92397819</v>
       </c>
       <c r="P451" t="n">
         <v>900</v>
@@ -21455,10 +21455,10 @@
         <v>20</v>
       </c>
       <c r="N467" t="n">
-        <v>3259.1344047619</v>
+        <v>3285.20748</v>
       </c>
       <c r="O467" t="n">
-        <v>65182.688095238</v>
+        <v>65704.1496</v>
       </c>
       <c r="P467" t="n">
         <v>3600</v>
@@ -21504,10 +21504,10 @@
         <v>631</v>
       </c>
       <c r="N468" t="n">
-        <v>3110.8373975045</v>
+        <v>3110.837275018</v>
       </c>
       <c r="O468" t="n">
-        <v>1962938.39782534</v>
+        <v>1962938.320536358</v>
       </c>
       <c r="P468" t="n">
         <v>4500</v>
@@ -21943,7 +21943,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>18602</v>
+        <v>18026</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -21952,19 +21952,19 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>18602</v>
+        <v>18026</v>
       </c>
       <c r="N478" t="n">
-        <v>704.67584580877</v>
+        <v>703.7947515264</v>
       </c>
       <c r="O478" t="n">
-        <v>13108380.08373474</v>
+        <v>12686604.19101489</v>
       </c>
       <c r="P478" t="n">
         <v>900</v>
       </c>
       <c r="Q478" t="n">
-        <v>16741800</v>
+        <v>16223400</v>
       </c>
     </row>
     <row r="479">
@@ -22462,10 +22462,10 @@
         <v>47</v>
       </c>
       <c r="N489" t="n">
-        <v>1595.4993541033</v>
+        <v>1595.4991666667</v>
       </c>
       <c r="O489" t="n">
-        <v>74988.4696428551</v>
+        <v>74988.4608333349</v>
       </c>
       <c r="P489" t="n">
         <v>2500</v>
@@ -22560,10 +22560,10 @@
         <v>296</v>
       </c>
       <c r="N491" t="n">
-        <v>6078.9925934066</v>
+        <v>6078.9925962596</v>
       </c>
       <c r="O491" t="n">
-        <v>1799381.807648354</v>
+        <v>1799381.808492842</v>
       </c>
       <c r="P491" t="n">
         <v>18500</v>
@@ -22888,7 +22888,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -22897,19 +22897,19 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="N498" t="n">
         <v>3057.26</v>
       </c>
       <c r="O498" t="n">
-        <v>990552.2400000001</v>
+        <v>843803.76</v>
       </c>
       <c r="P498" t="n">
         <v>4900</v>
       </c>
       <c r="Q498" t="n">
-        <v>1587600</v>
+        <v>1352400</v>
       </c>
     </row>
     <row r="499">
@@ -22949,10 +22949,10 @@
         <v>24</v>
       </c>
       <c r="N499" t="n">
-        <v>2832.1952307692</v>
+        <v>2832.1953125</v>
       </c>
       <c r="O499" t="n">
-        <v>67972.68553846079</v>
+        <v>67972.6875</v>
       </c>
       <c r="P499" t="n">
         <v>12900</v>
@@ -23575,10 +23575,10 @@
         <v>30</v>
       </c>
       <c r="N512" t="n">
-        <v>7230.04</v>
+        <v>7887.3163636364</v>
       </c>
       <c r="O512" t="n">
-        <v>216901.2</v>
+        <v>236619.490909092</v>
       </c>
       <c r="P512" t="n">
         <v>15900</v>
@@ -24010,10 +24010,10 @@
         <v>10</v>
       </c>
       <c r="N521" t="n">
-        <v>5430.86</v>
+        <v>5480.6844036697</v>
       </c>
       <c r="O521" t="n">
-        <v>54308.6</v>
+        <v>54806.844036697</v>
       </c>
       <c r="P521" t="n">
         <v>13900</v>
@@ -24108,10 +24108,10 @@
         <v>60</v>
       </c>
       <c r="N523" t="n">
-        <v>4568.55</v>
+        <v>4726.0862068966</v>
       </c>
       <c r="O523" t="n">
-        <v>274113</v>
+        <v>283565.172413796</v>
       </c>
       <c r="P523" t="n">
         <v>6900</v>
@@ -24481,10 +24481,10 @@
         <v>162</v>
       </c>
       <c r="N531" t="n">
-        <v>4190.77</v>
+        <v>4234.4238541667</v>
       </c>
       <c r="O531" t="n">
-        <v>678904.7400000001</v>
+        <v>685976.6643750054</v>
       </c>
       <c r="P531" t="n">
         <v>5900</v>
@@ -24530,10 +24530,10 @@
         <v>341</v>
       </c>
       <c r="N532" t="n">
-        <v>3499.72</v>
+        <v>3503.9263942308</v>
       </c>
       <c r="O532" t="n">
-        <v>1193404.52</v>
+        <v>1194838.900432703</v>
       </c>
       <c r="P532" t="n">
         <v>6900</v>
@@ -24579,10 +24579,10 @@
         <v>323</v>
       </c>
       <c r="N533" t="n">
-        <v>5347.88</v>
+        <v>5370.7341880342</v>
       </c>
       <c r="O533" t="n">
-        <v>1727365.24</v>
+        <v>1734747.142735047</v>
       </c>
       <c r="P533" t="n">
         <v>7900</v>
@@ -24628,10 +24628,10 @@
         <v>292</v>
       </c>
       <c r="N534" t="n">
-        <v>4578.04</v>
+        <v>4593.2494352159</v>
       </c>
       <c r="O534" t="n">
-        <v>1336787.68</v>
+        <v>1341228.835083043</v>
       </c>
       <c r="P534" t="n">
         <v>7500</v>
@@ -26332,10 +26332,10 @@
         <v>1085</v>
       </c>
       <c r="N570" t="n">
-        <v>7046.9398271765</v>
+        <v>7056.0857581657</v>
       </c>
       <c r="O570" t="n">
-        <v>7645929.712486503</v>
+        <v>7655853.047609785</v>
       </c>
       <c r="P570" t="n">
         <v>9900</v>
@@ -26522,10 +26522,10 @@
         <v>648</v>
       </c>
       <c r="N574" t="n">
-        <v>665.32396350735</v>
+        <v>665.32397155917</v>
       </c>
       <c r="O574" t="n">
-        <v>431129.9283527628</v>
+        <v>431129.9335703421</v>
       </c>
       <c r="P574" t="n">
         <v>2900</v>
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="J575" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="K575" t="n">
         <v>0</v>
@@ -26568,19 +26568,19 @@
         <v>0</v>
       </c>
       <c r="M575" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="N575" t="n">
         <v>1080.18</v>
       </c>
       <c r="O575" t="n">
-        <v>315412.56</v>
+        <v>302450.4</v>
       </c>
       <c r="P575" t="n">
         <v>4900</v>
       </c>
       <c r="Q575" t="n">
-        <v>1430800</v>
+        <v>1372000</v>
       </c>
     </row>
     <row r="576">
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="J578" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="K578" t="n">
         <v>0</v>
@@ -26715,19 +26715,19 @@
         <v>0</v>
       </c>
       <c r="M578" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N578" t="n">
         <v>4581.84</v>
       </c>
       <c r="O578" t="n">
-        <v>339056.16</v>
+        <v>229092</v>
       </c>
       <c r="P578" t="n">
         <v>7900</v>
       </c>
       <c r="Q578" t="n">
-        <v>584600</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="579">
@@ -27349,10 +27349,10 @@
         <v>90</v>
       </c>
       <c r="N592" t="n">
-        <v>2489.1752653486</v>
+        <v>2490.4710359188</v>
       </c>
       <c r="O592" t="n">
-        <v>224025.773881374</v>
+        <v>224142.393232692</v>
       </c>
       <c r="P592" t="n">
         <v>3000</v>
@@ -27431,10 +27431,10 @@
         <v>5</v>
       </c>
       <c r="N594" t="n">
-        <v>5497.1753043478</v>
+        <v>5497.1752906977</v>
       </c>
       <c r="O594" t="n">
-        <v>27485.876521739</v>
+        <v>27485.8764534885</v>
       </c>
       <c r="P594" t="n">
         <v>6500</v>
@@ -27601,10 +27601,10 @@
         <v>450</v>
       </c>
       <c r="N598" t="n">
-        <v>1794.2879648314</v>
+        <v>1796.1048285838</v>
       </c>
       <c r="O598" t="n">
-        <v>807429.58417413</v>
+        <v>808247.1728627101</v>
       </c>
       <c r="P598" t="n">
         <v>1600</v>
@@ -28006,10 +28006,10 @@
         <v>325</v>
       </c>
       <c r="N607" t="n">
-        <v>22951.704710526</v>
+        <v>22951.704689564</v>
       </c>
       <c r="O607" t="n">
-        <v>7459304.03092095</v>
+        <v>7459304.024108301</v>
       </c>
       <c r="P607" t="n">
         <v>37900</v>
@@ -28333,10 +28333,10 @@
         <v>2200</v>
       </c>
       <c r="N614" t="n">
-        <v>220.00227919632</v>
+        <v>220.00190038478</v>
       </c>
       <c r="O614" t="n">
-        <v>484005.014231904</v>
+        <v>484004.180846516</v>
       </c>
       <c r="P614" t="n">
         <v>260</v>
@@ -28793,10 +28793,10 @@
         <v>81</v>
       </c>
       <c r="N624" t="n">
-        <v>17986.24</v>
+        <v>18186.087111111</v>
       </c>
       <c r="O624" t="n">
-        <v>1456885.44</v>
+        <v>1473073.055999991</v>
       </c>
       <c r="P624" t="n">
         <v>18500</v>
@@ -28839,10 +28839,10 @@
         <v>36</v>
       </c>
       <c r="N625" t="n">
-        <v>7480</v>
+        <v>7496.4757709251</v>
       </c>
       <c r="O625" t="n">
-        <v>269280</v>
+        <v>269873.1277533036</v>
       </c>
       <c r="P625" t="n">
         <v>9500</v>
@@ -28931,10 +28931,10 @@
         <v>89</v>
       </c>
       <c r="N627" t="n">
-        <v>5280</v>
+        <v>5320.824742268</v>
       </c>
       <c r="O627" t="n">
-        <v>469920</v>
+        <v>473553.402061852</v>
       </c>
       <c r="P627" t="n">
         <v>6900</v>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="J628" t="n">
-        <v>708</v>
+        <v>180</v>
       </c>
       <c r="K628" t="n">
         <v>0</v>
@@ -28977,19 +28977,19 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>708</v>
+        <v>180</v>
       </c>
       <c r="N628" t="n">
         <v>1056</v>
       </c>
       <c r="O628" t="n">
-        <v>747648</v>
+        <v>190080</v>
       </c>
       <c r="P628" t="n">
         <v>1400</v>
       </c>
       <c r="Q628" t="n">
-        <v>991200</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="629">
@@ -29017,7 +29017,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -29026,33 +29026,30 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="N629" t="n">
         <v>7920</v>
       </c>
       <c r="O629" t="n">
-        <v>902880</v>
+        <v>712800</v>
       </c>
       <c r="P629" t="n">
         <v>10500</v>
       </c>
       <c r="Q629" t="n">
-        <v>1197000</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>J-1387</t>
-        </is>
-      </c>
-      <c r="B630" t="n">
-        <v>7700154271143</v>
+          <t>J-582</t>
+        </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>VARA LUZ OSO 37cm J-1387</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -29066,7 +29063,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -29075,33 +29072,30 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="N630" t="n">
-        <v>7920</v>
+        <v>9240</v>
       </c>
       <c r="O630" t="n">
-        <v>332640</v>
+        <v>166320</v>
       </c>
       <c r="P630" t="n">
-        <v>10500</v>
+        <v>11500</v>
       </c>
       <c r="Q630" t="n">
-        <v>441000</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>J-1389</t>
-        </is>
-      </c>
-      <c r="B631" t="n">
-        <v>7700154271143</v>
+          <t>J-718</t>
+        </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>VARA LUZ PRINCESA 37cm J-1389</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -29115,7 +29109,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -29124,30 +29118,30 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="N631" t="n">
-        <v>7920</v>
+        <v>4576</v>
       </c>
       <c r="O631" t="n">
-        <v>332640</v>
+        <v>594880</v>
       </c>
       <c r="P631" t="n">
-        <v>10500</v>
+        <v>5900</v>
       </c>
       <c r="Q631" t="n">
-        <v>441000</v>
+        <v>767000</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -29161,7 +29155,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29170,30 +29164,30 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="N632" t="n">
-        <v>9240</v>
+        <v>5280</v>
       </c>
       <c r="O632" t="n">
-        <v>166320</v>
+        <v>1283040</v>
       </c>
       <c r="P632" t="n">
-        <v>11500</v>
+        <v>6900</v>
       </c>
       <c r="Q632" t="n">
-        <v>207000</v>
+        <v>1676700</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -29207,7 +29201,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -29216,30 +29210,30 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="N633" t="n">
-        <v>4576</v>
+        <v>415.07</v>
       </c>
       <c r="O633" t="n">
-        <v>594880</v>
+        <v>7056.19</v>
       </c>
       <c r="P633" t="n">
-        <v>5900</v>
+        <v>2900</v>
       </c>
       <c r="Q633" t="n">
-        <v>767000</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -29253,7 +29247,7 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>243</v>
+        <v>59</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -29262,35 +29256,35 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>243</v>
+        <v>59</v>
       </c>
       <c r="N634" t="n">
-        <v>5280</v>
+        <v>46491.75</v>
       </c>
       <c r="O634" t="n">
-        <v>1283040</v>
+        <v>2743013.25</v>
       </c>
       <c r="P634" t="n">
-        <v>6900</v>
+        <v>52900</v>
       </c>
       <c r="Q634" t="n">
-        <v>1676700</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -29299,7 +29293,7 @@
         </is>
       </c>
       <c r="J635" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K635" t="n">
         <v>0</v>
@@ -29308,35 +29302,35 @@
         <v>0</v>
       </c>
       <c r="M635" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="N635" t="n">
-        <v>415.07</v>
+        <v>965.501</v>
       </c>
       <c r="O635" t="n">
-        <v>7056.19</v>
+        <v>29930.531</v>
       </c>
       <c r="P635" t="n">
-        <v>2900</v>
+        <v>7900</v>
       </c>
       <c r="Q635" t="n">
-        <v>49300</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -29345,7 +29339,7 @@
         </is>
       </c>
       <c r="J636" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="K636" t="n">
         <v>0</v>
@@ -29354,30 +29348,30 @@
         <v>0</v>
       </c>
       <c r="M636" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="N636" t="n">
-        <v>46491.75</v>
+        <v>1129.14</v>
       </c>
       <c r="O636" t="n">
-        <v>2743013.25</v>
+        <v>13549.68</v>
       </c>
       <c r="P636" t="n">
-        <v>52900</v>
+        <v>6900</v>
       </c>
       <c r="Q636" t="n">
-        <v>3121100</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -29391,7 +29385,7 @@
         </is>
       </c>
       <c r="J637" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K637" t="n">
         <v>0</v>
@@ -29400,35 +29394,40 @@
         <v>0</v>
       </c>
       <c r="M637" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N637" t="n">
-        <v>910.85</v>
+        <v>11433.53</v>
       </c>
       <c r="O637" t="n">
-        <v>28236.35</v>
+        <v>68601.18000000001</v>
       </c>
       <c r="P637" t="n">
-        <v>7900</v>
+        <v>15000</v>
       </c>
       <c r="Q637" t="n">
-        <v>244900</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -29437,7 +29436,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -29446,35 +29445,35 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N638" t="n">
-        <v>1129.14</v>
+        <v>15452.21</v>
       </c>
       <c r="O638" t="n">
-        <v>13549.68</v>
+        <v>61808.84</v>
       </c>
       <c r="P638" t="n">
-        <v>6900</v>
+        <v>36500</v>
       </c>
       <c r="Q638" t="n">
-        <v>82800</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -29483,7 +29482,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -29492,40 +29491,40 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="N639" t="n">
-        <v>11433.53</v>
+        <v>1319.3609646302</v>
       </c>
       <c r="O639" t="n">
-        <v>68601.18000000001</v>
+        <v>216375.1981993528</v>
       </c>
       <c r="P639" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="Q639" t="n">
-        <v>90000</v>
+        <v>574000</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -29534,7 +29533,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -29543,35 +29542,35 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N640" t="n">
-        <v>15452.21</v>
+        <v>751.45</v>
       </c>
       <c r="O640" t="n">
-        <v>61808.84</v>
+        <v>751.45</v>
       </c>
       <c r="P640" t="n">
-        <v>36500</v>
+        <v>2500</v>
       </c>
       <c r="Q640" t="n">
-        <v>146000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -29580,7 +29579,7 @@
         </is>
       </c>
       <c r="J641" t="n">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="K641" t="n">
         <v>0</v>
@@ -29589,40 +29588,35 @@
         <v>0</v>
       </c>
       <c r="M641" t="n">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="N641" t="n">
-        <v>1319.3609646302</v>
+        <v>571.87</v>
       </c>
       <c r="O641" t="n">
-        <v>216375.1981993528</v>
+        <v>76058.71000000001</v>
       </c>
       <c r="P641" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="Q641" t="n">
-        <v>574000</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -29631,7 +29625,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -29640,35 +29634,40 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="N642" t="n">
-        <v>751.45</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O642" t="n">
-        <v>751.45</v>
+        <v>154642.9771428552</v>
       </c>
       <c r="P642" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q642" t="n">
-        <v>2500</v>
+        <v>816000</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -29677,7 +29676,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -29686,44 +29685,47 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="N643" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O643" t="n">
-        <v>76058.71000000001</v>
+        <v>208257.84</v>
       </c>
       <c r="P643" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q643" t="n">
-        <v>332500</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>MG40334</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J644" t="n">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -29732,40 +29734,35 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="N644" t="n">
-        <v>227.41614285714</v>
+        <v>2547.0191593353</v>
       </c>
       <c r="O644" t="n">
-        <v>154642.9771428552</v>
+        <v>402429.0271749774</v>
       </c>
       <c r="P644" t="n">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="Q644" t="n">
-        <v>816000</v>
+        <v>458200</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -29774,7 +29771,7 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -29783,47 +29780,44 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="N645" t="n">
-        <v>9917.040000000001</v>
+        <v>4171.6685076531</v>
       </c>
       <c r="O645" t="n">
-        <v>208257.84</v>
+        <v>396308.5082270445</v>
       </c>
       <c r="P645" t="n">
-        <v>15900</v>
+        <v>5000</v>
       </c>
       <c r="Q645" t="n">
-        <v>333900</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B646" t="n">
-        <v>7700154271143</v>
+          <t>SEB010</t>
+        </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J646" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="K646" t="n">
         <v>0</v>
@@ -29832,35 +29826,35 @@
         <v>0</v>
       </c>
       <c r="M646" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="N646" t="n">
-        <v>2539.5717348928</v>
+        <v>7600</v>
       </c>
       <c r="O646" t="n">
-        <v>401252.3341130624</v>
+        <v>364800</v>
       </c>
       <c r="P646" t="n">
-        <v>2900</v>
+        <v>9500</v>
       </c>
       <c r="Q646" t="n">
-        <v>458200</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -29881,32 +29875,32 @@
         <v>95</v>
       </c>
       <c r="N647" t="n">
-        <v>4171.6685679315</v>
+        <v>5520</v>
       </c>
       <c r="O647" t="n">
-        <v>396308.5139534925</v>
+        <v>524400</v>
       </c>
       <c r="P647" t="n">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="Q647" t="n">
-        <v>475000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -29915,7 +29909,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -29924,30 +29918,30 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="N648" t="n">
-        <v>7600</v>
+        <v>1600</v>
       </c>
       <c r="O648" t="n">
-        <v>364800</v>
+        <v>132800</v>
       </c>
       <c r="P648" t="n">
-        <v>9500</v>
+        <v>2000</v>
       </c>
       <c r="Q648" t="n">
-        <v>456000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -29961,7 +29955,7 @@
         </is>
       </c>
       <c r="J649" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K649" t="n">
         <v>0</v>
@@ -29970,35 +29964,38 @@
         <v>0</v>
       </c>
       <c r="M649" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="N649" t="n">
-        <v>5520</v>
+        <v>4091.4</v>
       </c>
       <c r="O649" t="n">
-        <v>524400</v>
+        <v>4091.4</v>
       </c>
       <c r="P649" t="n">
-        <v>6900</v>
+        <v>10000</v>
       </c>
       <c r="Q649" t="n">
-        <v>655500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>SEB09</t>
-        </is>
+          <t>SLT3727</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>SQUISHIE HUELLA COLOR + TRANSPARENTE 40gr SLT3727</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -30007,7 +30004,7 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="K650" t="n">
         <v>0</v>
@@ -30016,35 +30013,38 @@
         <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="N650" t="n">
-        <v>1600</v>
+        <v>2210</v>
       </c>
       <c r="O650" t="n">
-        <v>132800</v>
+        <v>260780</v>
       </c>
       <c r="P650" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="Q650" t="n">
-        <v>166000</v>
+        <v>318600</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
-        </is>
+          <t>SLT3728</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -30053,7 +30053,7 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
@@ -30062,25 +30062,25 @@
         <v>0</v>
       </c>
       <c r="M651" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="N651" t="n">
-        <v>4091.4</v>
+        <v>2465</v>
       </c>
       <c r="O651" t="n">
-        <v>4091.4</v>
+        <v>788800</v>
       </c>
       <c r="P651" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="Q651" t="n">
-        <v>10000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>SLT3727</t>
+          <t>SLT3783</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>SQUISHIE HUELLA COLOR + TRANSPARENTE 40gr SLT3727</t>
+          <t>SQUISHIE TORTUGA MINI 10gr SLT3783</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -30102,7 +30102,7 @@
         </is>
       </c>
       <c r="J652" t="n">
-        <v>246</v>
+        <v>2647</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
@@ -30111,25 +30111,25 @@
         <v>0</v>
       </c>
       <c r="M652" t="n">
-        <v>246</v>
+        <v>2647</v>
       </c>
       <c r="N652" t="n">
-        <v>2210</v>
+        <v>425</v>
       </c>
       <c r="O652" t="n">
-        <v>543660</v>
+        <v>1124975</v>
       </c>
       <c r="P652" t="n">
-        <v>2700</v>
+        <v>500</v>
       </c>
       <c r="Q652" t="n">
-        <v>664200</v>
+        <v>1323500</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>SLT3728</t>
+          <t>SLT4037</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
+          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -30151,7 +30151,7 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
@@ -30160,33 +30160,30 @@
         <v>0</v>
       </c>
       <c r="M653" t="n">
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="N653" t="n">
-        <v>2465</v>
+        <v>1700</v>
       </c>
       <c r="O653" t="n">
-        <v>1183200</v>
+        <v>652800</v>
       </c>
       <c r="P653" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="Q653" t="n">
-        <v>1440000</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>SLT3781</t>
-        </is>
-      </c>
-      <c r="B654" t="n">
-        <v>7700154271143</v>
+          <t>T040-LJ</t>
+        </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>SQUISHIE HUELLA MINI 10gr SLT3781</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -30200,7 +30197,7 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>2801</v>
+        <v>3</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
@@ -30209,33 +30206,30 @@
         <v>0</v>
       </c>
       <c r="M654" t="n">
-        <v>2801</v>
+        <v>3</v>
       </c>
       <c r="N654" t="n">
-        <v>467</v>
+        <v>3661.88</v>
       </c>
       <c r="O654" t="n">
-        <v>1308067</v>
+        <v>10985.64</v>
       </c>
       <c r="P654" t="n">
-        <v>600</v>
+        <v>38900</v>
       </c>
       <c r="Q654" t="n">
-        <v>1680600</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>SLT3783</t>
-        </is>
-      </c>
-      <c r="B655" t="n">
-        <v>7700154271143</v>
+          <t>T041-LJ</t>
+        </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>SQUISHIE TORTUGA MINI 10gr SLT3783</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -30249,7 +30243,7 @@
         </is>
       </c>
       <c r="J655" t="n">
-        <v>2647</v>
+        <v>5</v>
       </c>
       <c r="K655" t="n">
         <v>0</v>
@@ -30258,33 +30252,30 @@
         <v>0</v>
       </c>
       <c r="M655" t="n">
-        <v>2647</v>
+        <v>5</v>
       </c>
       <c r="N655" t="n">
-        <v>425</v>
+        <v>2797.08</v>
       </c>
       <c r="O655" t="n">
-        <v>1124975</v>
+        <v>13985.4</v>
       </c>
       <c r="P655" t="n">
-        <v>500</v>
+        <v>30900</v>
       </c>
       <c r="Q655" t="n">
-        <v>1323500</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>SLT4037</t>
-        </is>
-      </c>
-      <c r="B656" t="n">
-        <v>7700154271143</v>
+          <t>T048-LJ</t>
+        </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -30298,7 +30289,7 @@
         </is>
       </c>
       <c r="J656" t="n">
-        <v>576</v>
+        <v>11</v>
       </c>
       <c r="K656" t="n">
         <v>0</v>
@@ -30307,30 +30298,30 @@
         <v>0</v>
       </c>
       <c r="M656" t="n">
-        <v>576</v>
+        <v>11</v>
       </c>
       <c r="N656" t="n">
-        <v>1700</v>
+        <v>3462.255</v>
       </c>
       <c r="O656" t="n">
-        <v>979200</v>
+        <v>38084.805</v>
       </c>
       <c r="P656" t="n">
-        <v>2000</v>
+        <v>42000</v>
       </c>
       <c r="Q656" t="n">
-        <v>1152000</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -30344,7 +30335,7 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
@@ -30353,30 +30344,30 @@
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="N657" t="n">
-        <v>3661.88</v>
+        <v>24882.58</v>
       </c>
       <c r="O657" t="n">
-        <v>10985.64</v>
+        <v>696712.24</v>
       </c>
       <c r="P657" t="n">
-        <v>38900</v>
+        <v>31500</v>
       </c>
       <c r="Q657" t="n">
-        <v>116700</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -30390,7 +30381,7 @@
         </is>
       </c>
       <c r="J658" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K658" t="n">
         <v>0</v>
@@ -30399,35 +30390,35 @@
         <v>0</v>
       </c>
       <c r="M658" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N658" t="n">
-        <v>2797.08</v>
+        <v>0.8</v>
       </c>
       <c r="O658" t="n">
-        <v>13985.4</v>
+        <v>15.2</v>
       </c>
       <c r="P658" t="n">
-        <v>30900</v>
+        <v>22900</v>
       </c>
       <c r="Q658" t="n">
-        <v>154500</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -30436,7 +30427,7 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K659" t="n">
         <v>0</v>
@@ -30445,35 +30436,35 @@
         <v>0</v>
       </c>
       <c r="M659" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N659" t="n">
-        <v>3462.255</v>
+        <v>5186.45</v>
       </c>
       <c r="O659" t="n">
-        <v>38084.805</v>
+        <v>82983.2</v>
       </c>
       <c r="P659" t="n">
-        <v>42000</v>
+        <v>7200</v>
       </c>
       <c r="Q659" t="n">
-        <v>462000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>TB028</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -30482,7 +30473,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -30491,35 +30482,35 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="N660" t="n">
-        <v>24882.58</v>
+        <v>47796.1625</v>
       </c>
       <c r="O660" t="n">
-        <v>696712.24</v>
+        <v>95592.325</v>
       </c>
       <c r="P660" t="n">
-        <v>31500</v>
+        <v>54000</v>
       </c>
       <c r="Q660" t="n">
-        <v>882000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>TB115</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -30528,7 +30519,7 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K661" t="n">
         <v>0</v>
@@ -30537,30 +30528,30 @@
         <v>0</v>
       </c>
       <c r="M661" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="N661" t="n">
-        <v>0.8</v>
+        <v>8006.3731111111</v>
       </c>
       <c r="O661" t="n">
-        <v>15.2</v>
+        <v>344274.0437777773</v>
       </c>
       <c r="P661" t="n">
-        <v>22900</v>
+        <v>10000</v>
       </c>
       <c r="Q661" t="n">
-        <v>435100</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>TB122</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -30574,7 +30565,7 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
@@ -30583,156 +30574,18 @@
         <v>0</v>
       </c>
       <c r="M662" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N662" t="n">
-        <v>5186.45</v>
+        <v>47920</v>
       </c>
       <c r="O662" t="n">
-        <v>82983.2</v>
+        <v>191680</v>
       </c>
       <c r="P662" t="n">
-        <v>7200</v>
+        <v>59900</v>
       </c>
       <c r="Q662" t="n">
-        <v>115200</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>TB028</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I663" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J663" t="n">
-        <v>2</v>
-      </c>
-      <c r="K663" t="n">
-        <v>0</v>
-      </c>
-      <c r="L663" t="n">
-        <v>0</v>
-      </c>
-      <c r="M663" t="n">
-        <v>2</v>
-      </c>
-      <c r="N663" t="n">
-        <v>47796.1625</v>
-      </c>
-      <c r="O663" t="n">
-        <v>95592.325</v>
-      </c>
-      <c r="P663" t="n">
-        <v>54000</v>
-      </c>
-      <c r="Q663" t="n">
-        <v>108000</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>TB115</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I664" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J664" t="n">
-        <v>43</v>
-      </c>
-      <c r="K664" t="n">
-        <v>0</v>
-      </c>
-      <c r="L664" t="n">
-        <v>0</v>
-      </c>
-      <c r="M664" t="n">
-        <v>43</v>
-      </c>
-      <c r="N664" t="n">
-        <v>8006.3731111111</v>
-      </c>
-      <c r="O664" t="n">
-        <v>344274.0437777773</v>
-      </c>
-      <c r="P664" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Q664" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>TB122</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>PELUCHE DRAGON 50CM DRAG-50</t>
-        </is>
-      </c>
-      <c r="E665" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I665" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J665" t="n">
-        <v>4</v>
-      </c>
-      <c r="K665" t="n">
-        <v>0</v>
-      </c>
-      <c r="L665" t="n">
-        <v>0</v>
-      </c>
-      <c r="M665" t="n">
-        <v>4</v>
-      </c>
-      <c r="N665" t="n">
-        <v>47920</v>
-      </c>
-      <c r="O665" t="n">
-        <v>191680</v>
-      </c>
-      <c r="P665" t="n">
-        <v>59900</v>
-      </c>
-      <c r="Q665" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -1585,10 +1585,10 @@
         <v>29</v>
       </c>
       <c r="N30" t="n">
-        <v>31566.3666</v>
+        <v>31409.32</v>
       </c>
       <c r="O30" t="n">
-        <v>915424.6314000001</v>
+        <v>910870.28</v>
       </c>
       <c r="P30" t="n">
         <v>45500</v>
@@ -2829,10 +2829,10 @@
         <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O59" t="n">
-        <v>32698.682590908</v>
+        <v>32258.79</v>
       </c>
       <c r="P59" t="n">
         <v>18400</v>
@@ -3460,10 +3460,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O73" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="P73" t="n">
         <v>25500</v>
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O86" t="n">
-        <v>1720647.340070486</v>
+        <v>1719781.821620521</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O93" t="n">
-        <v>10010083.98913547</v>
+        <v>10004112.27767736</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4439,10 +4439,10 @@
         <v>262</v>
       </c>
       <c r="N95" t="n">
-        <v>8252.563380281699</v>
+        <v>8214</v>
       </c>
       <c r="O95" t="n">
-        <v>2162171.605633805</v>
+        <v>2152068</v>
       </c>
       <c r="P95" t="n">
         <v>7900</v>
@@ -4488,10 +4488,10 @@
         <v>144</v>
       </c>
       <c r="N96" t="n">
-        <v>3283.163260274</v>
+        <v>3230.0662191781</v>
       </c>
       <c r="O96" t="n">
-        <v>472775.509479456</v>
+        <v>465129.5355616464</v>
       </c>
       <c r="P96" t="n">
         <v>6200</v>
@@ -4768,10 +4768,10 @@
         <v>23</v>
       </c>
       <c r="N102" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O102" t="n">
-        <v>202860</v>
+        <v>202308</v>
       </c>
       <c r="P102" t="n">
         <v>14900</v>
@@ -6751,10 +6751,10 @@
         <v>1930</v>
       </c>
       <c r="N146" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O146" t="n">
-        <v>8438086.352158235</v>
+        <v>8436360.537340645</v>
       </c>
       <c r="P146" t="n">
         <v>8900</v>
@@ -7010,10 +7010,10 @@
         <v>54</v>
       </c>
       <c r="N152" t="n">
-        <v>5371.5779551122</v>
+        <v>5331.69</v>
       </c>
       <c r="O152" t="n">
-        <v>290065.2095760588</v>
+        <v>287911.26</v>
       </c>
       <c r="P152" t="n">
         <v>7900</v>
@@ -7331,10 +7331,10 @@
         <v>450</v>
       </c>
       <c r="N159" t="n">
-        <v>1534.4227525419</v>
+        <v>1532.6290227489</v>
       </c>
       <c r="O159" t="n">
-        <v>690490.2386438551</v>
+        <v>689683.060237005</v>
       </c>
       <c r="P159" t="n">
         <v>1200</v>
@@ -8115,10 +8115,10 @@
         <v>36</v>
       </c>
       <c r="N176" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O176" t="n">
-        <v>135943.8341968908</v>
+        <v>135417.6</v>
       </c>
       <c r="P176" t="n">
         <v>6900</v>
@@ -9486,10 +9486,10 @@
         <v>45</v>
       </c>
       <c r="N206" t="n">
-        <v>14292.620246914</v>
+        <v>14118.32</v>
       </c>
       <c r="O206" t="n">
-        <v>643167.91111113</v>
+        <v>635324.4</v>
       </c>
       <c r="P206" t="n">
         <v>17900</v>
@@ -9532,10 +9532,10 @@
         <v>22</v>
       </c>
       <c r="N207" t="n">
-        <v>9446.666666666701</v>
+        <v>8720</v>
       </c>
       <c r="O207" t="n">
-        <v>207826.6666666674</v>
+        <v>191840</v>
       </c>
       <c r="P207" t="n">
         <v>10900</v>
@@ -9622,10 +9622,10 @@
         <v>67</v>
       </c>
       <c r="N209" t="n">
-        <v>19359</v>
+        <v>19120</v>
       </c>
       <c r="O209" t="n">
-        <v>1297053</v>
+        <v>1281040</v>
       </c>
       <c r="P209" t="n">
         <v>23900</v>
@@ -10074,10 +10074,10 @@
         <v>18</v>
       </c>
       <c r="N219" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="O219" t="n">
-        <v>138956.948709678</v>
+        <v>135674.5020967746</v>
       </c>
       <c r="P219" t="n">
         <v>8900</v>
@@ -10238,10 +10238,10 @@
         <v>254</v>
       </c>
       <c r="N223" t="n">
-        <v>1974.990872211</v>
+        <v>1969</v>
       </c>
       <c r="O223" t="n">
-        <v>501647.681541594</v>
+        <v>500126</v>
       </c>
       <c r="P223" t="n">
         <v>1500</v>
@@ -10279,10 +10279,10 @@
         <v>148</v>
       </c>
       <c r="N224" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O224" t="n">
-        <v>1302320.89886621</v>
+        <v>1301583.04</v>
       </c>
       <c r="P224" t="n">
         <v>14500</v>
@@ -11388,10 +11388,10 @@
         <v>16</v>
       </c>
       <c r="N249" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O249" t="n">
-        <v>364178.486585696</v>
+        <v>363687.68</v>
       </c>
       <c r="P249" t="n">
         <v>36900</v>
@@ -11608,10 +11608,10 @@
         <v>1328</v>
       </c>
       <c r="N254" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O254" t="n">
-        <v>5448593.255868556</v>
+        <v>5445397.6</v>
       </c>
       <c r="P254" t="n">
         <v>26900</v>
@@ -13418,10 +13418,10 @@
         <v>34</v>
       </c>
       <c r="N293" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O293" t="n">
-        <v>314594.9402777774</v>
+        <v>312425.32</v>
       </c>
       <c r="P293" t="n">
         <v>12900</v>
@@ -13786,10 +13786,10 @@
         <v>289</v>
       </c>
       <c r="N301" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O301" t="n">
-        <v>5208706.6496</v>
+        <v>5206624</v>
       </c>
       <c r="P301" t="n">
         <v>29900</v>
@@ -14666,10 +14666,10 @@
         <v>592</v>
       </c>
       <c r="N320" t="n">
-        <v>3950.9108864697</v>
+        <v>3938.66</v>
       </c>
       <c r="O320" t="n">
-        <v>2338939.244790062</v>
+        <v>2331686.72</v>
       </c>
       <c r="P320" t="n">
         <v>4500</v>
@@ -14850,10 +14850,10 @@
         <v>15</v>
       </c>
       <c r="N324" t="n">
-        <v>10448.584837545</v>
+        <v>10411</v>
       </c>
       <c r="O324" t="n">
-        <v>156728.772563175</v>
+        <v>156165</v>
       </c>
       <c r="P324" t="n">
         <v>16900</v>
@@ -17474,10 +17474,10 @@
         <v>112</v>
       </c>
       <c r="N381" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O381" t="n">
-        <v>409098.445853664</v>
+        <v>407607.2</v>
       </c>
       <c r="P381" t="n">
         <v>7500</v>
@@ -17980,10 +17980,10 @@
         <v>50</v>
       </c>
       <c r="N392" t="n">
-        <v>15334.994264706</v>
+        <v>15223.06</v>
       </c>
       <c r="O392" t="n">
-        <v>766749.7132353</v>
+        <v>761153</v>
       </c>
       <c r="P392" t="n">
         <v>17500</v>
@@ -19920,10 +19920,10 @@
         <v>243</v>
       </c>
       <c r="N434" t="n">
-        <v>3650.5019029126</v>
+        <v>3629.36</v>
       </c>
       <c r="O434" t="n">
-        <v>887071.9624077618</v>
+        <v>881934.48</v>
       </c>
       <c r="P434" t="n">
         <v>3900</v>
@@ -20197,10 +20197,10 @@
         <v>20</v>
       </c>
       <c r="N440" t="n">
-        <v>2479.6920689655</v>
+        <v>2357.74</v>
       </c>
       <c r="O440" t="n">
-        <v>49593.84137931</v>
+        <v>47154.8</v>
       </c>
       <c r="P440" t="n">
         <v>3000</v>
@@ -20571,10 +20571,10 @@
         <v>9193</v>
       </c>
       <c r="N448" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O448" t="n">
-        <v>3177416.026649425</v>
+        <v>3176718.242288767</v>
       </c>
       <c r="P448" t="n">
         <v>600</v>
@@ -20713,10 +20713,10 @@
         <v>5817</v>
       </c>
       <c r="N451" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O451" t="n">
-        <v>4140997.92397819</v>
+        <v>4137845.265098209</v>
       </c>
       <c r="P451" t="n">
         <v>900</v>
@@ -21455,10 +21455,10 @@
         <v>20</v>
       </c>
       <c r="N467" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="O467" t="n">
-        <v>65704.1496</v>
+        <v>65182.6888</v>
       </c>
       <c r="P467" t="n">
         <v>3600</v>
@@ -23575,10 +23575,10 @@
         <v>30</v>
       </c>
       <c r="N512" t="n">
-        <v>7887.3163636364</v>
+        <v>7230.04</v>
       </c>
       <c r="O512" t="n">
-        <v>236619.490909092</v>
+        <v>216901.2</v>
       </c>
       <c r="P512" t="n">
         <v>15900</v>
@@ -24010,10 +24010,10 @@
         <v>10</v>
       </c>
       <c r="N521" t="n">
-        <v>5480.6844036697</v>
+        <v>5430.86</v>
       </c>
       <c r="O521" t="n">
-        <v>54806.844036697</v>
+        <v>54308.6</v>
       </c>
       <c r="P521" t="n">
         <v>13900</v>
@@ -24108,10 +24108,10 @@
         <v>60</v>
       </c>
       <c r="N523" t="n">
-        <v>4726.0862068966</v>
+        <v>4568.55</v>
       </c>
       <c r="O523" t="n">
-        <v>283565.172413796</v>
+        <v>274113</v>
       </c>
       <c r="P523" t="n">
         <v>6900</v>
@@ -24481,10 +24481,10 @@
         <v>162</v>
       </c>
       <c r="N531" t="n">
-        <v>4234.4238541667</v>
+        <v>4190.77</v>
       </c>
       <c r="O531" t="n">
-        <v>685976.6643750054</v>
+        <v>678904.7400000001</v>
       </c>
       <c r="P531" t="n">
         <v>5900</v>
@@ -24530,10 +24530,10 @@
         <v>341</v>
       </c>
       <c r="N532" t="n">
-        <v>3503.9263942308</v>
+        <v>3499.72</v>
       </c>
       <c r="O532" t="n">
-        <v>1194838.900432703</v>
+        <v>1193404.52</v>
       </c>
       <c r="P532" t="n">
         <v>6900</v>
@@ -24579,10 +24579,10 @@
         <v>323</v>
       </c>
       <c r="N533" t="n">
-        <v>5370.7341880342</v>
+        <v>5347.88</v>
       </c>
       <c r="O533" t="n">
-        <v>1734747.142735047</v>
+        <v>1727365.24</v>
       </c>
       <c r="P533" t="n">
         <v>7900</v>
@@ -24628,10 +24628,10 @@
         <v>292</v>
       </c>
       <c r="N534" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O534" t="n">
-        <v>1341228.835083043</v>
+        <v>1336787.68</v>
       </c>
       <c r="P534" t="n">
         <v>7500</v>
@@ -26332,10 +26332,10 @@
         <v>1085</v>
       </c>
       <c r="N570" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O570" t="n">
-        <v>7655853.047609785</v>
+        <v>7645929.712243137</v>
       </c>
       <c r="P570" t="n">
         <v>9900</v>
@@ -27349,10 +27349,10 @@
         <v>90</v>
       </c>
       <c r="N592" t="n">
-        <v>2490.4710359188</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O592" t="n">
-        <v>224142.393232692</v>
+        <v>224025.773659551</v>
       </c>
       <c r="P592" t="n">
         <v>3000</v>
@@ -27601,10 +27601,10 @@
         <v>450</v>
       </c>
       <c r="N598" t="n">
-        <v>1796.1048285838</v>
+        <v>1794.2879574714</v>
       </c>
       <c r="O598" t="n">
-        <v>808247.1728627101</v>
+        <v>807429.58086213</v>
       </c>
       <c r="P598" t="n">
         <v>1600</v>
@@ -28793,10 +28793,10 @@
         <v>81</v>
       </c>
       <c r="N624" t="n">
-        <v>18186.087111111</v>
+        <v>17986.24</v>
       </c>
       <c r="O624" t="n">
-        <v>1473073.055999991</v>
+        <v>1456885.44</v>
       </c>
       <c r="P624" t="n">
         <v>18500</v>
@@ -28839,10 +28839,10 @@
         <v>36</v>
       </c>
       <c r="N625" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O625" t="n">
-        <v>269873.1277533036</v>
+        <v>269280</v>
       </c>
       <c r="P625" t="n">
         <v>9500</v>
@@ -28931,10 +28931,10 @@
         <v>89</v>
       </c>
       <c r="N627" t="n">
-        <v>5320.824742268</v>
+        <v>5280</v>
       </c>
       <c r="O627" t="n">
-        <v>473553.402061852</v>
+        <v>469920</v>
       </c>
       <c r="P627" t="n">
         <v>6900</v>
@@ -29305,10 +29305,10 @@
         <v>31</v>
       </c>
       <c r="N635" t="n">
-        <v>965.501</v>
+        <v>910.85</v>
       </c>
       <c r="O635" t="n">
-        <v>29930.531</v>
+        <v>28236.35</v>
       </c>
       <c r="P635" t="n">
         <v>7900</v>
@@ -29737,10 +29737,10 @@
         <v>158</v>
       </c>
       <c r="N644" t="n">
-        <v>2547.0191593353</v>
+        <v>2539.5717399804</v>
       </c>
       <c r="O644" t="n">
-        <v>402429.0271749774</v>
+        <v>401252.3349169032</v>
       </c>
       <c r="P644" t="n">
         <v>2900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -9071,10 +9071,10 @@
         <v>609</v>
       </c>
       <c r="N197" t="n">
-        <v>1302.8935476464</v>
+        <v>1301.3994029851</v>
       </c>
       <c r="O197" t="n">
-        <v>793462.1705166576</v>
+        <v>792552.2364179259</v>
       </c>
       <c r="P197" t="n">
         <v>2000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3093916756</v>
+        <v>1830.8488673139</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3093916756</v>
+        <v>1830.8488673139</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -786,22 +786,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N10" t="n">
         <v>5758.9597772829</v>
       </c>
       <c r="O10" t="n">
-        <v>316742.7877505595</v>
+        <v>247635.2704231647</v>
       </c>
       <c r="P10" t="n">
         <v>16900</v>
       </c>
       <c r="Q10" t="n">
-        <v>929500</v>
+        <v>726700</v>
       </c>
     </row>
     <row r="11">
@@ -1267,22 +1267,22 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="N22" t="n">
         <v>2413.0010989011</v>
       </c>
       <c r="O22" t="n">
-        <v>221996.1010989012</v>
+        <v>108585.0494505495</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
       </c>
       <c r="Q22" t="n">
-        <v>432400</v>
+        <v>211500</v>
       </c>
     </row>
     <row r="23">
@@ -1749,22 +1749,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N34" t="n">
         <v>16486.406666667</v>
       </c>
       <c r="O34" t="n">
-        <v>395673.760000008</v>
+        <v>263782.506666672</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
       </c>
       <c r="Q34" t="n">
-        <v>732000</v>
+        <v>488000</v>
       </c>
     </row>
     <row r="35">
@@ -1835,22 +1835,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>19314.017254902</v>
       </c>
       <c r="O36" t="n">
-        <v>96570.08627450999</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>33500</v>
       </c>
       <c r="Q36" t="n">
-        <v>167500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2305,22 +2305,22 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M47" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N47" t="n">
         <v>580.3659400545</v>
       </c>
       <c r="O47" t="n">
-        <v>83572.69536784801</v>
+        <v>81251.23160763</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
       </c>
       <c r="Q47" t="n">
-        <v>979200</v>
+        <v>952000</v>
       </c>
     </row>
     <row r="48">
@@ -2606,22 +2606,22 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M54" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>2791.02</v>
       </c>
       <c r="O54" t="n">
-        <v>78148.56</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>3900</v>
       </c>
       <c r="Q54" t="n">
-        <v>109200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2645,22 +2645,22 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M55" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="N55" t="n">
         <v>3564.14</v>
       </c>
       <c r="O55" t="n">
-        <v>406311.96</v>
+        <v>342157.44</v>
       </c>
       <c r="P55" t="n">
         <v>5500</v>
       </c>
       <c r="Q55" t="n">
-        <v>627000</v>
+        <v>528000</v>
       </c>
     </row>
     <row r="56">
@@ -3096,10 +3096,10 @@
         <v>1127</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.0684371373</v>
+        <v>1098.0685808709</v>
       </c>
       <c r="O65" t="n">
-        <v>1237523.128653737</v>
+        <v>1237523.290641504</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -3626,22 +3626,22 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M77" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N77" t="n">
         <v>6543</v>
       </c>
       <c r="O77" t="n">
-        <v>372951</v>
+        <v>333693</v>
       </c>
       <c r="P77" t="n">
         <v>6500</v>
       </c>
       <c r="Q77" t="n">
-        <v>370500</v>
+        <v>331500</v>
       </c>
     </row>
     <row r="78">
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O86" t="n">
-        <v>1719781.804734424</v>
+        <v>1719781.803885674</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.661213927</v>
+        <v>3474452.659966576</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O93" t="n">
-        <v>10004112.27767736</v>
+        <v>10004112.27780974</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4433,22 +4433,22 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M95" t="n">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="N95" t="n">
         <v>8214</v>
       </c>
       <c r="O95" t="n">
-        <v>2152068</v>
+        <v>2037072</v>
       </c>
       <c r="P95" t="n">
         <v>7900</v>
       </c>
       <c r="Q95" t="n">
-        <v>2069800</v>
+        <v>1959200</v>
       </c>
     </row>
     <row r="96">
@@ -4947,10 +4947,10 @@
         <v>581</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O106" t="n">
-        <v>2205307.514425825</v>
+        <v>2205307.514429195</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -5172,10 +5172,10 @@
         <v>309</v>
       </c>
       <c r="N111" t="n">
-        <v>4890.9300534045</v>
+        <v>4890.9300534402</v>
       </c>
       <c r="O111" t="n">
-        <v>1511297.38650199</v>
+        <v>1511297.386513022</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5351,10 +5351,10 @@
         <v>309</v>
       </c>
       <c r="N115" t="n">
-        <v>2267.0480923608</v>
+        <v>2267.0480857514</v>
       </c>
       <c r="O115" t="n">
-        <v>700517.8605394872</v>
+        <v>700517.8584971826</v>
       </c>
       <c r="P115" t="n">
         <v>3900</v>
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.724363632</v>
+        <v>862620.7194748321</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -6394,10 +6394,10 @@
         <v>2376</v>
       </c>
       <c r="N138" t="n">
-        <v>3472.2762167406</v>
+        <v>3472.276224504</v>
       </c>
       <c r="O138" t="n">
-        <v>8250128.290975666</v>
+        <v>8250128.309421504</v>
       </c>
       <c r="P138" t="n">
         <v>5900</v>
@@ -6623,10 +6623,10 @@
         <v>207</v>
       </c>
       <c r="N143" t="n">
-        <v>3041.6600141844</v>
+        <v>3041.6600141945</v>
       </c>
       <c r="O143" t="n">
-        <v>629623.6229361708</v>
+        <v>629623.6229382615</v>
       </c>
       <c r="P143" t="n">
         <v>5500</v>
@@ -6751,10 +6751,10 @@
         <v>1930</v>
       </c>
       <c r="N146" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O146" t="n">
-        <v>8436360.537506817</v>
+        <v>8437511.316464312</v>
       </c>
       <c r="P146" t="n">
         <v>8900</v>
@@ -6969,10 +6969,10 @@
         <v>753</v>
       </c>
       <c r="N151" t="n">
-        <v>3655.96</v>
+        <v>3668.2806919793</v>
       </c>
       <c r="O151" t="n">
-        <v>2752937.88</v>
+        <v>2762215.361060413</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -7195,10 +7195,10 @@
         <v>1572</v>
       </c>
       <c r="N156" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O156" t="n">
-        <v>7307599.2</v>
+        <v>7308877.422704238</v>
       </c>
       <c r="P156" t="n">
         <v>8900</v>
@@ -8485,22 +8485,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M184" t="n">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="N184" t="n">
         <v>3751</v>
       </c>
       <c r="O184" t="n">
-        <v>1920512</v>
+        <v>1875500</v>
       </c>
       <c r="P184" t="n">
         <v>6400</v>
       </c>
       <c r="Q184" t="n">
-        <v>3276800</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="185">
@@ -8586,10 +8586,10 @@
         <v>556</v>
       </c>
       <c r="N186" t="n">
-        <v>1630.9246047904</v>
+        <v>1630.9246075494</v>
       </c>
       <c r="O186" t="n">
-        <v>906794.0802634624</v>
+        <v>906794.0817974664</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8678,10 +8678,10 @@
         <v>176</v>
       </c>
       <c r="N188" t="n">
-        <v>1690.5796701847</v>
+        <v>1699.5482625995</v>
       </c>
       <c r="O188" t="n">
-        <v>297542.0219525072</v>
+        <v>299120.494217512</v>
       </c>
       <c r="P188" t="n">
         <v>2900</v>
@@ -8724,10 +8724,10 @@
         <v>1294</v>
       </c>
       <c r="N189" t="n">
-        <v>1550.1946673374</v>
+        <v>1551.3666948085</v>
       </c>
       <c r="O189" t="n">
-        <v>2005951.899534596</v>
+        <v>2007468.503082199</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8816,10 +8816,10 @@
         <v>174</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5202775057</v>
+        <v>2407.4618268285</v>
       </c>
       <c r="O191" t="n">
-        <v>418212.5282859918</v>
+        <v>418898.357868159</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -9434,22 +9434,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M205" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N205" t="n">
         <v>14118.32</v>
       </c>
       <c r="O205" t="n">
-        <v>635324.4</v>
+        <v>578851.12</v>
       </c>
       <c r="P205" t="n">
         <v>17900</v>
       </c>
       <c r="Q205" t="n">
-        <v>805500</v>
+        <v>733900</v>
       </c>
     </row>
     <row r="206">
@@ -10110,10 +10110,10 @@
         <v>87</v>
       </c>
       <c r="N220" t="n">
-        <v>2610</v>
+        <v>2613.8724035608</v>
       </c>
       <c r="O220" t="n">
-        <v>227070</v>
+        <v>227406.8991097896</v>
       </c>
       <c r="P220" t="n">
         <v>3200</v>
@@ -10151,10 +10151,10 @@
         <v>133</v>
       </c>
       <c r="N221" t="n">
-        <v>2081</v>
+        <v>2086.0024038462</v>
       </c>
       <c r="O221" t="n">
-        <v>276773</v>
+        <v>277438.3197115446</v>
       </c>
       <c r="P221" t="n">
         <v>3200</v>
@@ -10410,10 +10410,10 @@
         <v>129</v>
       </c>
       <c r="N227" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O227" t="n">
-        <v>3165404.58</v>
+        <v>3282101.523041502</v>
       </c>
       <c r="P227" t="n">
         <v>52900</v>
@@ -10757,22 +10757,22 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M235" t="n">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="N235" t="n">
         <v>6207.9882238578</v>
       </c>
       <c r="O235" t="n">
-        <v>5885172.836217195</v>
+        <v>5835508.930426332</v>
       </c>
       <c r="P235" t="n">
         <v>9900</v>
       </c>
       <c r="Q235" t="n">
-        <v>9385200</v>
+        <v>9306000</v>
       </c>
     </row>
     <row r="236">
@@ -10858,10 +10858,10 @@
         <v>89</v>
       </c>
       <c r="N237" t="n">
-        <v>4285.1963420724</v>
+        <v>4285.1963819095</v>
       </c>
       <c r="O237" t="n">
-        <v>381382.4744444436</v>
+        <v>381382.4779899455</v>
       </c>
       <c r="P237" t="n">
         <v>6900</v>
@@ -11290,22 +11290,22 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M247" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N247" t="n">
         <v>4793.53</v>
       </c>
       <c r="O247" t="n">
-        <v>86283.53999999999</v>
+        <v>67109.42</v>
       </c>
       <c r="P247" t="n">
         <v>7900</v>
       </c>
       <c r="Q247" t="n">
-        <v>142200</v>
+        <v>110600</v>
       </c>
     </row>
     <row r="248">
@@ -11562,10 +11562,10 @@
         <v>1328</v>
       </c>
       <c r="N253" t="n">
-        <v>4100.45</v>
+        <v>4107.6818342152</v>
       </c>
       <c r="O253" t="n">
-        <v>5445397.6</v>
+        <v>5455001.475837786</v>
       </c>
       <c r="P253" t="n">
         <v>26900</v>
@@ -11608,10 +11608,10 @@
         <v>55</v>
       </c>
       <c r="N254" t="n">
-        <v>8332.779612403099</v>
+        <v>8332.7796073298</v>
       </c>
       <c r="O254" t="n">
-        <v>458302.8786821705</v>
+        <v>458302.878403139</v>
       </c>
       <c r="P254" t="n">
         <v>14900</v>
@@ -11648,22 +11648,22 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M255" t="n">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="N255" t="n">
-        <v>1561.0051173709</v>
+        <v>1600.4118322476</v>
       </c>
       <c r="O255" t="n">
-        <v>814844.6712676098</v>
+        <v>785802.2096335716</v>
       </c>
       <c r="P255" t="n">
         <v>2900</v>
       </c>
       <c r="Q255" t="n">
-        <v>1513800</v>
+        <v>1423900</v>
       </c>
     </row>
     <row r="256">
@@ -11792,10 +11792,10 @@
         <v>188</v>
       </c>
       <c r="N258" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O258" t="n">
-        <v>1498350.632037174</v>
+        <v>1498350.632086881</v>
       </c>
       <c r="P258" t="n">
         <v>12900</v>
@@ -11977,10 +11977,10 @@
         <v>256</v>
       </c>
       <c r="N262" t="n">
-        <v>548.14707537688</v>
+        <v>548.1470665322601</v>
       </c>
       <c r="O262" t="n">
-        <v>140325.6512964813</v>
+        <v>140325.6490322586</v>
       </c>
       <c r="P262" t="n">
         <v>2000</v>
@@ -12158,22 +12158,22 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M266" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N266" t="n">
         <v>4720</v>
       </c>
       <c r="O266" t="n">
-        <v>882640</v>
+        <v>868480</v>
       </c>
       <c r="P266" t="n">
         <v>5900</v>
       </c>
       <c r="Q266" t="n">
-        <v>1103300</v>
+        <v>1085600</v>
       </c>
     </row>
     <row r="267">
@@ -13510,10 +13510,10 @@
         <v>768</v>
       </c>
       <c r="N295" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O295" t="n">
-        <v>1365867.142144819</v>
+        <v>1365867.147841382</v>
       </c>
       <c r="P295" t="n">
         <v>4900</v>
@@ -14706,22 +14706,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M321" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N321" t="n">
         <v>3424</v>
       </c>
       <c r="O321" t="n">
-        <v>202016</v>
+        <v>160928</v>
       </c>
       <c r="P321" t="n">
         <v>5900</v>
       </c>
       <c r="Q321" t="n">
-        <v>348100</v>
+        <v>277300</v>
       </c>
     </row>
     <row r="322">
@@ -14850,10 +14850,10 @@
         <v>5</v>
       </c>
       <c r="N324" t="n">
-        <v>2252.298328125</v>
+        <v>2252.2983673469</v>
       </c>
       <c r="O324" t="n">
-        <v>11261.491640625</v>
+        <v>11261.4918367345</v>
       </c>
       <c r="P324" t="n">
         <v>3900</v>
@@ -15814,22 +15814,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M345" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="N345" t="n">
         <v>4907.822690678</v>
       </c>
       <c r="O345" t="n">
-        <v>672371.708622886</v>
+        <v>618385.659025428</v>
       </c>
       <c r="P345" t="n">
         <v>8200</v>
       </c>
       <c r="Q345" t="n">
-        <v>1123400</v>
+        <v>1033200</v>
       </c>
     </row>
     <row r="346">
@@ -15866,10 +15866,10 @@
         <v>30</v>
       </c>
       <c r="N346" t="n">
-        <v>6414</v>
+        <v>6426.9445005045</v>
       </c>
       <c r="O346" t="n">
-        <v>192420</v>
+        <v>192808.335015135</v>
       </c>
       <c r="P346" t="n">
         <v>10900</v>
@@ -16004,10 +16004,10 @@
         <v>240</v>
       </c>
       <c r="N349" t="n">
-        <v>3903.7394479074</v>
+        <v>3903.7394652406</v>
       </c>
       <c r="O349" t="n">
-        <v>936897.467497776</v>
+        <v>936897.471657744</v>
       </c>
       <c r="P349" t="n">
         <v>7500</v>
@@ -16223,22 +16223,22 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M354" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="N354" t="n">
         <v>6849.2</v>
       </c>
       <c r="O354" t="n">
-        <v>2616394.4</v>
+        <v>2588997.6</v>
       </c>
       <c r="P354" t="n">
         <v>11500</v>
       </c>
       <c r="Q354" t="n">
-        <v>4393000</v>
+        <v>4347000</v>
       </c>
     </row>
     <row r="355">
@@ -16361,22 +16361,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M357" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="N357" t="n">
-        <v>6645</v>
+        <v>6648.7102177554</v>
       </c>
       <c r="O357" t="n">
-        <v>292380</v>
+        <v>212758.7269681728</v>
       </c>
       <c r="P357" t="n">
         <v>10900</v>
       </c>
       <c r="Q357" t="n">
-        <v>479600</v>
+        <v>348800</v>
       </c>
     </row>
     <row r="358">
@@ -16459,10 +16459,10 @@
         <v>127</v>
       </c>
       <c r="N359" t="n">
-        <v>3898</v>
+        <v>3904.464344942</v>
       </c>
       <c r="O359" t="n">
-        <v>495046</v>
+        <v>495866.971807634</v>
       </c>
       <c r="P359" t="n">
         <v>6900</v>
@@ -17744,22 +17744,22 @@
         <v>0</v>
       </c>
       <c r="L387" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M387" t="n">
-        <v>1126</v>
+        <v>1100</v>
       </c>
       <c r="N387" t="n">
         <v>3821</v>
       </c>
       <c r="O387" t="n">
-        <v>4302446</v>
+        <v>4203100</v>
       </c>
       <c r="P387" t="n">
         <v>5900</v>
       </c>
       <c r="Q387" t="n">
-        <v>6643400</v>
+        <v>6490000</v>
       </c>
     </row>
     <row r="388">
@@ -17882,22 +17882,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M390" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N390" t="n">
         <v>7253</v>
       </c>
       <c r="O390" t="n">
-        <v>282867</v>
+        <v>224843</v>
       </c>
       <c r="P390" t="n">
         <v>11900</v>
       </c>
       <c r="Q390" t="n">
-        <v>464100</v>
+        <v>368900</v>
       </c>
     </row>
     <row r="391">
@@ -18434,22 +18434,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="N402" t="n">
         <v>2454</v>
       </c>
       <c r="O402" t="n">
-        <v>3536214</v>
+        <v>3533760</v>
       </c>
       <c r="P402" t="n">
         <v>4200</v>
       </c>
       <c r="Q402" t="n">
-        <v>6052200</v>
+        <v>6048000</v>
       </c>
     </row>
     <row r="403">
@@ -18486,10 +18486,10 @@
         <v>224</v>
       </c>
       <c r="N403" t="n">
-        <v>1592.2838740157</v>
+        <v>1592.2847324415</v>
       </c>
       <c r="O403" t="n">
-        <v>356671.5877795168</v>
+        <v>356671.780066896</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
@@ -18663,10 +18663,10 @@
         <v>400</v>
       </c>
       <c r="N407" t="n">
-        <v>1259.2749291992</v>
+        <v>1262.9750514202</v>
       </c>
       <c r="O407" t="n">
-        <v>503709.97167968</v>
+        <v>505190.02056808</v>
       </c>
       <c r="P407" t="n">
         <v>1900</v>
@@ -19782,10 +19782,10 @@
         <v>348</v>
       </c>
       <c r="N431" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O431" t="n">
-        <v>532596.5714871072</v>
+        <v>535227.7608069072</v>
       </c>
       <c r="P431" t="n">
         <v>2600</v>
@@ -19868,22 +19868,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M433" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="N433" t="n">
         <v>3629.36</v>
       </c>
       <c r="O433" t="n">
-        <v>881934.48</v>
+        <v>852899.6</v>
       </c>
       <c r="P433" t="n">
         <v>3900</v>
       </c>
       <c r="Q433" t="n">
-        <v>947700</v>
+        <v>916500</v>
       </c>
     </row>
     <row r="434">
@@ -21458,10 +21458,10 @@
         <v>631</v>
       </c>
       <c r="N467" t="n">
-        <v>3110.8368831169</v>
+        <v>3110.8366754617</v>
       </c>
       <c r="O467" t="n">
-        <v>1962938.073246764</v>
+        <v>1962937.942216333</v>
       </c>
       <c r="P467" t="n">
         <v>4500</v>
@@ -21909,10 +21909,10 @@
         <v>18026</v>
       </c>
       <c r="N477" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O477" t="n">
-        <v>12686603.94049368</v>
+        <v>12686603.88076868</v>
       </c>
       <c r="P477" t="n">
         <v>900</v>
@@ -23909,22 +23909,22 @@
         <v>0</v>
       </c>
       <c r="L519" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M519" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N519" t="n">
         <v>875.6901793722</v>
       </c>
       <c r="O519" t="n">
-        <v>143613.1894170408</v>
+        <v>137483.3581614354</v>
       </c>
       <c r="P519" t="n">
         <v>4500</v>
       </c>
       <c r="Q519" t="n">
-        <v>738000</v>
+        <v>706500</v>
       </c>
     </row>
     <row r="520">
@@ -24429,22 +24429,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M530" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N530" t="n">
         <v>4190.77</v>
       </c>
       <c r="O530" t="n">
-        <v>678904.7400000001</v>
+        <v>657950.89</v>
       </c>
       <c r="P530" t="n">
         <v>5900</v>
       </c>
       <c r="Q530" t="n">
-        <v>955800</v>
+        <v>926300</v>
       </c>
     </row>
     <row r="531">
@@ -24478,22 +24478,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M531" t="n">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="N531" t="n">
         <v>3499.72</v>
       </c>
       <c r="O531" t="n">
-        <v>1193404.52</v>
+        <v>1172406.2</v>
       </c>
       <c r="P531" t="n">
         <v>6900</v>
       </c>
       <c r="Q531" t="n">
-        <v>2352900</v>
+        <v>2311500</v>
       </c>
     </row>
     <row r="532">
@@ -24527,22 +24527,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M532" t="n">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="N532" t="n">
         <v>5347.88</v>
       </c>
       <c r="O532" t="n">
-        <v>1727365.24</v>
+        <v>1684582.2</v>
       </c>
       <c r="P532" t="n">
         <v>7900</v>
       </c>
       <c r="Q532" t="n">
-        <v>2551700</v>
+        <v>2488500</v>
       </c>
     </row>
     <row r="533">
@@ -24576,22 +24576,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M533" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N533" t="n">
         <v>4578.04</v>
       </c>
       <c r="O533" t="n">
-        <v>1336787.68</v>
+        <v>1318475.52</v>
       </c>
       <c r="P533" t="n">
         <v>7500</v>
       </c>
       <c r="Q533" t="n">
-        <v>2190000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="534">
@@ -25107,10 +25107,10 @@
         <v>17</v>
       </c>
       <c r="N544" t="n">
-        <v>10737.525714286</v>
+        <v>10737.525609756</v>
       </c>
       <c r="O544" t="n">
-        <v>182537.937142862</v>
+        <v>182537.935365852</v>
       </c>
       <c r="P544" t="n">
         <v>18900</v>
@@ -26040,22 +26040,22 @@
         <v>0</v>
       </c>
       <c r="L564" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M564" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="N564" t="n">
         <v>1024.29</v>
       </c>
       <c r="O564" t="n">
-        <v>166959.27</v>
+        <v>158764.95</v>
       </c>
       <c r="P564" t="n">
         <v>2900</v>
       </c>
       <c r="Q564" t="n">
-        <v>472700</v>
+        <v>449500</v>
       </c>
     </row>
     <row r="565">
@@ -26089,22 +26089,22 @@
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M565" t="n">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="N565" t="n">
         <v>711.48</v>
       </c>
       <c r="O565" t="n">
-        <v>479537.52</v>
+        <v>472422.72</v>
       </c>
       <c r="P565" t="n">
         <v>2500</v>
       </c>
       <c r="Q565" t="n">
-        <v>1685000</v>
+        <v>1660000</v>
       </c>
     </row>
     <row r="566">
@@ -28649,22 +28649,22 @@
         <v>0</v>
       </c>
       <c r="L621" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M621" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="N621" t="n">
         <v>1952.41</v>
       </c>
       <c r="O621" t="n">
-        <v>333862.11</v>
+        <v>310433.19</v>
       </c>
       <c r="P621" t="n">
         <v>2700</v>
       </c>
       <c r="Q621" t="n">
-        <v>461700</v>
+        <v>429300</v>
       </c>
     </row>
     <row r="622">
@@ -28928,22 +28928,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M627" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="N627" t="n">
         <v>7920</v>
       </c>
       <c r="O627" t="n">
-        <v>712800</v>
+        <v>554400</v>
       </c>
       <c r="P627" t="n">
         <v>10500</v>
       </c>
       <c r="Q627" t="n">
-        <v>945000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="628">
@@ -29490,22 +29490,22 @@
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M639" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="N639" t="n">
         <v>571.87</v>
       </c>
       <c r="O639" t="n">
-        <v>76058.71000000001</v>
+        <v>69196.27</v>
       </c>
       <c r="P639" t="n">
         <v>2500</v>
       </c>
       <c r="Q639" t="n">
-        <v>332500</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="640">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -6183,10 +6183,10 @@
         <v>320</v>
       </c>
       <c r="N133" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O133" t="n">
-        <v>3975188.14706656</v>
+        <v>3975188.1474784</v>
       </c>
       <c r="P133" t="n">
         <v>19900</v>
@@ -8738,10 +8738,10 @@
         <v>174</v>
       </c>
       <c r="N189" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O189" t="n">
-        <v>418212.6047831952</v>
+        <v>418212.6071895804</v>
       </c>
       <c r="P189" t="n">
         <v>3500</v>
@@ -18362,10 +18362,10 @@
         <v>224</v>
       </c>
       <c r="N400" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="O400" t="n">
-        <v>356672.0040000096</v>
+        <v>356672.0103041088</v>
       </c>
       <c r="P400" t="n">
         <v>2500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -1390,10 +1390,10 @@
         <v>120</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O25" t="n">
-        <v>445959.623606556</v>
+        <v>445959.623645316</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -5593,10 +5593,10 @@
         <v>240</v>
       </c>
       <c r="N120" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O120" t="n">
-        <v>862620.703387344</v>
+        <v>862620.7021370641</v>
       </c>
       <c r="P120" t="n">
         <v>6500</v>
@@ -6177,22 +6177,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M133" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="N133" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O133" t="n">
-        <v>3975188.15578944</v>
+        <v>3826118.601159316</v>
       </c>
       <c r="P133" t="n">
         <v>19900</v>
       </c>
       <c r="Q133" t="n">
-        <v>6368000</v>
+        <v>6129200</v>
       </c>
     </row>
     <row r="134">
@@ -6504,10 +6504,10 @@
         <v>157</v>
       </c>
       <c r="N140" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O140" t="n">
-        <v>477540.6223276506</v>
+        <v>477540.6223311046</v>
       </c>
       <c r="P140" t="n">
         <v>5500</v>
@@ -8467,10 +8467,10 @@
         <v>556</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O183" t="n">
-        <v>906794.1223372056</v>
+        <v>906794.1318753856</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -10739,10 +10739,10 @@
         <v>89</v>
       </c>
       <c r="N234" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O234" t="n">
-        <v>381382.4808585846</v>
+        <v>381382.4823037933</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -17861,10 +17861,10 @@
         <v>1152</v>
       </c>
       <c r="N389" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O389" t="n">
-        <v>1746476.623434701</v>
+        <v>1746476.618028826</v>
       </c>
       <c r="P389" t="n">
         <v>2300</v>
@@ -29431,10 +29431,10 @@
         <v>158</v>
       </c>
       <c r="N637" t="n">
-        <v>2539.571774676</v>
+        <v>2539.5717817818</v>
       </c>
       <c r="O637" t="n">
-        <v>401252.340398808</v>
+        <v>401252.3415215244</v>
       </c>
       <c r="P637" t="n">
         <v>2900</v>
@@ -29477,10 +29477,10 @@
         <v>95</v>
       </c>
       <c r="N638" t="n">
-        <v>4171.6684503311</v>
+        <v>4171.6684420772</v>
       </c>
       <c r="O638" t="n">
-        <v>396308.5027814545</v>
+        <v>396308.501997334</v>
       </c>
       <c r="P638" t="n">
         <v>5000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -553,19 +553,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>8640000</v>
+        <v>8478000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6400000</v>
+        <v>6280000</v>
       </c>
     </row>
     <row r="5">
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3103165299</v>
+        <v>1811.3106796117</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3103165299</v>
+        <v>1811.3106796117</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -953,19 +953,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N14" t="n">
         <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>4212000</v>
+        <v>4131000</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3120000</v>
+        <v>3060000</v>
       </c>
     </row>
     <row r="15">
@@ -1312,10 +1312,10 @@
         <v>66</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.7035205993</v>
+        <v>2474.7035084428</v>
       </c>
       <c r="O23" t="n">
-        <v>163330.4323595538</v>
+        <v>163330.4315572248</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1802,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>13712.833333333</v>
+        <v>13712.764</v>
       </c>
       <c r="O35" t="n">
-        <v>13712.833333333</v>
+        <v>13712.764</v>
       </c>
       <c r="P35" t="n">
         <v>22600</v>
@@ -3018,10 +3018,10 @@
         <v>1127</v>
       </c>
       <c r="N63" t="n">
-        <v>1098.0688500785</v>
+        <v>1098.0691359493</v>
       </c>
       <c r="O63" t="n">
-        <v>1237523.594038469</v>
+        <v>1237523.916214861</v>
       </c>
       <c r="P63" t="n">
         <v>1500</v>
@@ -3951,10 +3951,10 @@
         <v>666</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.2549274255</v>
+        <v>2582.2549040675</v>
       </c>
       <c r="O84" t="n">
-        <v>1719781.781665383</v>
+        <v>1719781.766108955</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -4043,10 +4043,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>5216.8958543674</v>
+        <v>5216.8958410068</v>
       </c>
       <c r="O86" t="n">
-        <v>3474452.639008688</v>
+        <v>3474452.630110529</v>
       </c>
       <c r="P86" t="n">
         <v>8500</v>
@@ -4274,10 +4274,10 @@
         <v>3167</v>
       </c>
       <c r="N91" t="n">
-        <v>3158.8608400976</v>
+        <v>3158.8608413965</v>
       </c>
       <c r="O91" t="n">
-        <v>10004112.2805891</v>
+        <v>10004112.28470271</v>
       </c>
       <c r="P91" t="n">
         <v>5600</v>
@@ -4320,10 +4320,10 @@
         <v>80</v>
       </c>
       <c r="N92" t="n">
-        <v>3841.6251265823</v>
+        <v>3841.6251483051</v>
       </c>
       <c r="O92" t="n">
-        <v>307330.010126584</v>
+        <v>307330.011864408</v>
       </c>
       <c r="P92" t="n">
         <v>6900</v>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4358,19 +4358,19 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N93" t="n">
         <v>8214</v>
       </c>
       <c r="O93" t="n">
-        <v>2037072</v>
+        <v>2004216</v>
       </c>
       <c r="P93" t="n">
         <v>7900</v>
       </c>
       <c r="Q93" t="n">
-        <v>1959200</v>
+        <v>1927600</v>
       </c>
     </row>
     <row r="94">
@@ -4410,10 +4410,10 @@
         <v>144</v>
       </c>
       <c r="N94" t="n">
-        <v>3230.0661983471</v>
+        <v>3230.0661344538</v>
       </c>
       <c r="O94" t="n">
-        <v>465129.5325619824</v>
+        <v>465129.5233613472</v>
       </c>
       <c r="P94" t="n">
         <v>6200</v>
@@ -4549,10 +4549,10 @@
         <v>259</v>
       </c>
       <c r="N97" t="n">
-        <v>2694.8230192308</v>
+        <v>2694.8229787234</v>
       </c>
       <c r="O97" t="n">
-        <v>697959.1619807773</v>
+        <v>697959.1514893606</v>
       </c>
       <c r="P97" t="n">
         <v>4900</v>
@@ -4869,10 +4869,10 @@
         <v>581</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100076292</v>
+        <v>3795.7100076321</v>
       </c>
       <c r="O104" t="n">
-        <v>2205307.514432565</v>
+        <v>2205307.51443425</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300535117</v>
+        <v>4890.9300537634</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.386535115</v>
+        <v>1511297.386612891</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5593,10 +5593,10 @@
         <v>240</v>
       </c>
       <c r="N120" t="n">
-        <v>3594.2529255711</v>
+        <v>3594.252920354</v>
       </c>
       <c r="O120" t="n">
-        <v>862620.7021370641</v>
+        <v>862620.7008849599</v>
       </c>
       <c r="P120" t="n">
         <v>6500</v>
@@ -5634,10 +5634,10 @@
         <v>108</v>
       </c>
       <c r="N121" t="n">
-        <v>3240.8500542005</v>
+        <v>3240.8500537634</v>
       </c>
       <c r="O121" t="n">
-        <v>350011.805853654</v>
+        <v>350011.8058064472</v>
       </c>
       <c r="P121" t="n">
         <v>5200</v>
@@ -6171,22 +6171,22 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>308</v>
       </c>
       <c r="N133" t="n">
-        <v>12422.462990777</v>
+        <v>12422.462992091</v>
       </c>
       <c r="O133" t="n">
-        <v>3826118.601159316</v>
+        <v>3826118.601564028</v>
       </c>
       <c r="P133" t="n">
         <v>19900</v>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>2226</v>
+        <v>2094</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -6313,19 +6313,19 @@
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>2226</v>
+        <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.2762824732</v>
+        <v>3472.2762877567</v>
       </c>
       <c r="O136" t="n">
-        <v>7729287.004785343</v>
+        <v>7270946.54656253</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
       </c>
       <c r="Q136" t="n">
-        <v>13133400</v>
+        <v>12354600</v>
       </c>
     </row>
     <row r="137">
@@ -6455,10 +6455,10 @@
         <v>16</v>
       </c>
       <c r="N139" t="n">
-        <v>4242.5422660099</v>
+        <v>4242.5422885572</v>
       </c>
       <c r="O139" t="n">
-        <v>67880.6762561584</v>
+        <v>67880.6766169152</v>
       </c>
       <c r="P139" t="n">
         <v>5900</v>
@@ -6632,10 +6632,10 @@
         <v>1930</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1712631292</v>
+        <v>4371.1712633877</v>
       </c>
       <c r="O143" t="n">
-        <v>8436360.537839357</v>
+        <v>8436360.538338261</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -6722,10 +6722,10 @@
         <v>181</v>
       </c>
       <c r="N145" t="n">
-        <v>1592.5648717949</v>
+        <v>1592.5648207171</v>
       </c>
       <c r="O145" t="n">
-        <v>288254.2417948769</v>
+        <v>288254.2325497951</v>
       </c>
       <c r="P145" t="n">
         <v>3900</v>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7756,19 +7756,19 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="N168" t="n">
         <v>16897</v>
       </c>
       <c r="O168" t="n">
-        <v>1470039</v>
+        <v>1301069</v>
       </c>
       <c r="P168" t="n">
         <v>27900</v>
       </c>
       <c r="Q168" t="n">
-        <v>2427300</v>
+        <v>2148300</v>
       </c>
     </row>
     <row r="169">
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7998,19 +7998,19 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N173" t="n">
         <v>11921.4</v>
       </c>
       <c r="O173" t="n">
-        <v>1299432.6</v>
+        <v>1287511.2</v>
       </c>
       <c r="P173" t="n">
         <v>19900</v>
       </c>
       <c r="Q173" t="n">
-        <v>2169100</v>
+        <v>2149200</v>
       </c>
     </row>
     <row r="174">
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8418,19 +8418,19 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="N182" t="n">
         <v>9903</v>
       </c>
       <c r="O182" t="n">
-        <v>1911279</v>
+        <v>1792443</v>
       </c>
       <c r="P182" t="n">
         <v>15900</v>
       </c>
       <c r="Q182" t="n">
-        <v>3068700</v>
+        <v>2877900</v>
       </c>
     </row>
     <row r="183">
@@ -8467,10 +8467,10 @@
         <v>556</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9246976176</v>
+        <v>1630.9246990529</v>
       </c>
       <c r="O183" t="n">
-        <v>906794.1318753856</v>
+        <v>906794.1326734124</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8513,10 +8513,10 @@
         <v>5</v>
       </c>
       <c r="N184" t="n">
-        <v>1467.303968254</v>
+        <v>1467.3012605042</v>
       </c>
       <c r="O184" t="n">
-        <v>7336.51984127</v>
+        <v>7336.506302521</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
@@ -8559,10 +8559,10 @@
         <v>176</v>
       </c>
       <c r="N185" t="n">
-        <v>1690.5782946794</v>
+        <v>1690.5776592798</v>
       </c>
       <c r="O185" t="n">
-        <v>297541.7798635744</v>
+        <v>297541.6680332448</v>
       </c>
       <c r="P185" t="n">
         <v>2900</v>
@@ -8605,10 +8605,10 @@
         <v>1294</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1947406745</v>
+        <v>1550.1947552537</v>
       </c>
       <c r="O186" t="n">
-        <v>2005951.994432803</v>
+        <v>2005952.013298288</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5210828242</v>
+        <v>2403.5211979522</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.6684114108</v>
+        <v>418212.6884436828</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -8738,10 +8738,10 @@
         <v>59</v>
       </c>
       <c r="N189" t="n">
-        <v>1232.8059585492</v>
+        <v>1232.8058115183</v>
       </c>
       <c r="O189" t="n">
-        <v>72735.5515544028</v>
+        <v>72735.54287957971</v>
       </c>
       <c r="P189" t="n">
         <v>2400</v>
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9272,19 +9272,19 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N201" t="n">
         <v>7028</v>
       </c>
       <c r="O201" t="n">
-        <v>611436</v>
+        <v>604408</v>
       </c>
       <c r="P201" t="n">
         <v>15900</v>
       </c>
       <c r="Q201" t="n">
-        <v>1383300</v>
+        <v>1367400</v>
       </c>
     </row>
     <row r="202">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9824,19 +9824,19 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N213" t="n">
         <v>4485.03</v>
       </c>
       <c r="O213" t="n">
-        <v>121095.81</v>
+        <v>85215.56999999999</v>
       </c>
       <c r="P213" t="n">
         <v>9900</v>
       </c>
       <c r="Q213" t="n">
-        <v>267300</v>
+        <v>188100</v>
       </c>
     </row>
     <row r="214">
@@ -10644,10 +10644,10 @@
         <v>940</v>
       </c>
       <c r="N232" t="n">
-        <v>6207.9882238578</v>
+        <v>6207.9882231175</v>
       </c>
       <c r="O232" t="n">
-        <v>5835508.930426332</v>
+        <v>5835508.92973045</v>
       </c>
       <c r="P232" t="n">
         <v>9900</v>
@@ -10998,10 +10998,10 @@
         <v>1280</v>
       </c>
       <c r="N240" t="n">
-        <v>4814.2679256837</v>
+        <v>4814.2679250376</v>
       </c>
       <c r="O240" t="n">
-        <v>6162262.944875136</v>
+        <v>6162262.944048129</v>
       </c>
       <c r="P240" t="n">
         <v>9900</v>
@@ -11085,10 +11085,10 @@
         <v>32</v>
       </c>
       <c r="N242" t="n">
-        <v>11562.0384</v>
+        <v>11562.038395415</v>
       </c>
       <c r="O242" t="n">
-        <v>369985.2288</v>
+        <v>369985.22865328</v>
       </c>
       <c r="P242" t="n">
         <v>18500</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11220,19 +11220,19 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N245" t="n">
         <v>22730.48</v>
       </c>
       <c r="O245" t="n">
-        <v>363687.68</v>
+        <v>340957.2</v>
       </c>
       <c r="P245" t="n">
         <v>36900</v>
       </c>
       <c r="Q245" t="n">
-        <v>590400</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="246">
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11399,19 +11399,19 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="N249" t="n">
         <v>16974.69</v>
       </c>
       <c r="O249" t="n">
-        <v>848734.4999999999</v>
+        <v>746886.36</v>
       </c>
       <c r="P249" t="n">
         <v>26900</v>
       </c>
       <c r="Q249" t="n">
-        <v>1345000</v>
+        <v>1183600</v>
       </c>
     </row>
     <row r="250">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11440,19 +11440,19 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="N250" t="n">
         <v>4100.45</v>
       </c>
       <c r="O250" t="n">
-        <v>5445397.6</v>
+        <v>5396192.2</v>
       </c>
       <c r="P250" t="n">
         <v>26900</v>
       </c>
       <c r="Q250" t="n">
-        <v>35723200</v>
+        <v>35400400</v>
       </c>
     </row>
     <row r="251">
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11486,19 +11486,19 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N251" t="n">
-        <v>8332.7796073298</v>
+        <v>8332.7796062992</v>
       </c>
       <c r="O251" t="n">
-        <v>458302.878403139</v>
+        <v>391640.6414960624</v>
       </c>
       <c r="P251" t="n">
         <v>14900</v>
       </c>
       <c r="Q251" t="n">
-        <v>819500</v>
+        <v>700300</v>
       </c>
     </row>
     <row r="252">
@@ -11535,10 +11535,10 @@
         <v>467</v>
       </c>
       <c r="N252" t="n">
-        <v>1561.0055305466</v>
+        <v>1561.0057714286</v>
       </c>
       <c r="O252" t="n">
-        <v>728989.5827652622</v>
+        <v>728989.6952571562</v>
       </c>
       <c r="P252" t="n">
         <v>2900</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11806,19 +11806,19 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N258" t="n">
         <v>10900</v>
       </c>
       <c r="O258" t="n">
-        <v>174400</v>
+        <v>152600</v>
       </c>
       <c r="P258" t="n">
         <v>18900</v>
       </c>
       <c r="Q258" t="n">
-        <v>302400</v>
+        <v>264600</v>
       </c>
     </row>
     <row r="259">
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12830,19 +12830,19 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="N280" t="n">
         <v>5194</v>
       </c>
       <c r="O280" t="n">
-        <v>908950</v>
+        <v>805070</v>
       </c>
       <c r="P280" t="n">
         <v>9000</v>
       </c>
       <c r="Q280" t="n">
-        <v>1575000</v>
+        <v>1395000</v>
       </c>
     </row>
     <row r="281">
@@ -13287,7 +13287,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13296,19 +13296,19 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N290" t="n">
         <v>42899</v>
       </c>
       <c r="O290" t="n">
-        <v>815081</v>
+        <v>729283</v>
       </c>
       <c r="P290" t="n">
         <v>70900</v>
       </c>
       <c r="Q290" t="n">
-        <v>1347100</v>
+        <v>1205300</v>
       </c>
     </row>
     <row r="291">
@@ -13391,10 +13391,10 @@
         <v>768</v>
       </c>
       <c r="N292" t="n">
-        <v>1778.4728585462</v>
+        <v>1778.4728622951</v>
       </c>
       <c r="O292" t="n">
-        <v>1365867.155363482</v>
+        <v>1365867.158242637</v>
       </c>
       <c r="P292" t="n">
         <v>4900</v>
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13526,19 +13526,19 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="N295" t="n">
         <v>10571</v>
       </c>
       <c r="O295" t="n">
-        <v>264275</v>
+        <v>137423</v>
       </c>
       <c r="P295" t="n">
         <v>18900</v>
       </c>
       <c r="Q295" t="n">
-        <v>472500</v>
+        <v>245700</v>
       </c>
     </row>
     <row r="296">
@@ -14731,10 +14731,10 @@
         <v>5</v>
       </c>
       <c r="N321" t="n">
-        <v>2252.2983673469</v>
+        <v>2252.3005544554</v>
       </c>
       <c r="O321" t="n">
-        <v>11261.4918367345</v>
+        <v>11261.502772277</v>
       </c>
       <c r="P321" t="n">
         <v>3900</v>
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>324</v>
+        <v>228</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15054,19 +15054,19 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>324</v>
+        <v>228</v>
       </c>
       <c r="N328" t="n">
-        <v>2328.118653478</v>
+        <v>2328.1186430868</v>
       </c>
       <c r="O328" t="n">
-        <v>754310.443726872</v>
+        <v>530811.0506237905</v>
       </c>
       <c r="P328" t="n">
         <v>4500</v>
       </c>
       <c r="Q328" t="n">
-        <v>1458000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="329">
@@ -15701,10 +15701,10 @@
         <v>126</v>
       </c>
       <c r="N342" t="n">
-        <v>4907.8226963907</v>
+        <v>4907.8227078891</v>
       </c>
       <c r="O342" t="n">
-        <v>618385.6597452282</v>
+        <v>618385.6611940266</v>
       </c>
       <c r="P342" t="n">
         <v>8200</v>
@@ -15960,7 +15960,7 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -15969,19 +15969,19 @@
         <v>0</v>
       </c>
       <c r="M348" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N348" t="n">
         <v>33000</v>
       </c>
       <c r="O348" t="n">
-        <v>759000</v>
+        <v>528000</v>
       </c>
       <c r="P348" t="n">
         <v>52900</v>
       </c>
       <c r="Q348" t="n">
-        <v>1216700</v>
+        <v>846400</v>
       </c>
     </row>
     <row r="349">
@@ -16846,10 +16846,10 @@
         <v>291</v>
       </c>
       <c r="N367" t="n">
-        <v>17075.989518156</v>
+        <v>17075.98951782</v>
       </c>
       <c r="O367" t="n">
-        <v>4969112.949783396</v>
+        <v>4969112.949685619</v>
       </c>
       <c r="P367" t="n">
         <v>27500</v>
@@ -17861,10 +17861,10 @@
         <v>1152</v>
       </c>
       <c r="N389" t="n">
-        <v>1516.0387309278</v>
+        <v>1516.0387272539</v>
       </c>
       <c r="O389" t="n">
-        <v>1746476.618028826</v>
+        <v>1746476.613796493</v>
       </c>
       <c r="P389" t="n">
         <v>2300</v>
@@ -17953,10 +17953,10 @@
         <v>72</v>
       </c>
       <c r="N391" t="n">
-        <v>2079.3832679245</v>
+        <v>2079.3832653832</v>
       </c>
       <c r="O391" t="n">
-        <v>149715.595290564</v>
+        <v>149715.5951075904</v>
       </c>
       <c r="P391" t="n">
         <v>2900</v>
@@ -17999,10 +17999,10 @@
         <v>96</v>
       </c>
       <c r="N392" t="n">
-        <v>3306.5944012442</v>
+        <v>3306.5943925234</v>
       </c>
       <c r="O392" t="n">
-        <v>317433.0625194432</v>
+        <v>317433.0616822464</v>
       </c>
       <c r="P392" t="n">
         <v>4900</v>
@@ -18045,10 +18045,10 @@
         <v>96</v>
       </c>
       <c r="N393" t="n">
-        <v>2056.0819719953</v>
+        <v>2056.0819217221</v>
       </c>
       <c r="O393" t="n">
-        <v>197383.8693115488</v>
+        <v>197383.8644853216</v>
       </c>
       <c r="P393" t="n">
         <v>2900</v>
@@ -18091,10 +18091,10 @@
         <v>216</v>
       </c>
       <c r="N394" t="n">
-        <v>1655.929144427</v>
+        <v>1655.9291188041</v>
       </c>
       <c r="O394" t="n">
-        <v>357680.695196232</v>
+        <v>357680.6896616856</v>
       </c>
       <c r="P394" t="n">
         <v>2500</v>
@@ -18321,10 +18321,10 @@
         <v>224</v>
       </c>
       <c r="N399" t="n">
-        <v>1592.2857885305</v>
+        <v>1592.2858453237</v>
       </c>
       <c r="O399" t="n">
-        <v>356672.016630832</v>
+        <v>356672.0293525088</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -18498,10 +18498,10 @@
         <v>400</v>
       </c>
       <c r="N403" t="n">
-        <v>1259.2749729064</v>
+        <v>1259.2750273904</v>
       </c>
       <c r="O403" t="n">
-        <v>503709.98916256</v>
+        <v>503710.01095616</v>
       </c>
       <c r="P403" t="n">
         <v>1900</v>
@@ -18675,10 +18675,10 @@
         <v>516</v>
       </c>
       <c r="N407" t="n">
-        <v>692.15244995571</v>
+        <v>692.1524551748601</v>
       </c>
       <c r="O407" t="n">
-        <v>357150.6641771464</v>
+        <v>357150.6668702278</v>
       </c>
       <c r="P407" t="n">
         <v>1200</v>
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
@@ -18862,19 +18862,19 @@
         <v>0</v>
       </c>
       <c r="M411" t="n">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="N411" t="n">
         <v>11690</v>
       </c>
       <c r="O411" t="n">
-        <v>5050080</v>
+        <v>4816280</v>
       </c>
       <c r="P411" t="n">
         <v>18900</v>
       </c>
       <c r="Q411" t="n">
-        <v>8164800</v>
+        <v>7786800</v>
       </c>
     </row>
     <row r="412">
@@ -18951,7 +18951,7 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="K413" t="n">
         <v>0</v>
@@ -18960,19 +18960,19 @@
         <v>0</v>
       </c>
       <c r="M413" t="n">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="N413" t="n">
         <v>9736</v>
       </c>
       <c r="O413" t="n">
-        <v>6893088</v>
+        <v>6776256</v>
       </c>
       <c r="P413" t="n">
         <v>15900</v>
       </c>
       <c r="Q413" t="n">
-        <v>11257200</v>
+        <v>11066400</v>
       </c>
     </row>
     <row r="414">
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="J414" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K414" t="n">
         <v>0</v>
@@ -19009,19 +19009,19 @@
         <v>0</v>
       </c>
       <c r="M414" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N414" t="n">
         <v>44470</v>
       </c>
       <c r="O414" t="n">
-        <v>1867740</v>
+        <v>1734330</v>
       </c>
       <c r="P414" t="n">
         <v>71900</v>
       </c>
       <c r="Q414" t="n">
-        <v>3019800</v>
+        <v>2804100</v>
       </c>
     </row>
     <row r="415">
@@ -19617,10 +19617,10 @@
         <v>348</v>
       </c>
       <c r="N427" t="n">
-        <v>1530.4499180664</v>
+        <v>1530.4499179655</v>
       </c>
       <c r="O427" t="n">
-        <v>532596.5714871072</v>
+        <v>532596.571451994</v>
       </c>
       <c r="P427" t="n">
         <v>2600</v>
@@ -20076,10 +20076,10 @@
         <v>306</v>
       </c>
       <c r="N437" t="n">
-        <v>1690.8700094518</v>
+        <v>1690.8700095238</v>
       </c>
       <c r="O437" t="n">
-        <v>517406.2228922507</v>
+        <v>517406.2229142828</v>
       </c>
       <c r="P437" t="n">
         <v>3000</v>
@@ -20409,10 +20409,10 @@
         <v>140</v>
       </c>
       <c r="N444" t="n">
-        <v>3907.5003809524</v>
+        <v>3907.5003864734</v>
       </c>
       <c r="O444" t="n">
-        <v>547050.053333336</v>
+        <v>547050.054106276</v>
       </c>
       <c r="P444" t="n">
         <v>3900</v>
@@ -20685,10 +20685,10 @@
         <v>99</v>
       </c>
       <c r="N450" t="n">
-        <v>1283.6523305085</v>
+        <v>1283.6520960699</v>
       </c>
       <c r="O450" t="n">
-        <v>127081.5807203415</v>
+        <v>127081.5575109201</v>
       </c>
       <c r="P450" t="n">
         <v>1900</v>
@@ -21293,10 +21293,10 @@
         <v>631</v>
       </c>
       <c r="N463" t="n">
-        <v>3110.8363143631</v>
+        <v>3110.8359666534</v>
       </c>
       <c r="O463" t="n">
-        <v>1962937.714363116</v>
+        <v>1962937.494958295</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>
@@ -21744,10 +21744,10 @@
         <v>18026</v>
       </c>
       <c r="N473" t="n">
-        <v>703.79470242023</v>
+        <v>703.79469605084</v>
       </c>
       <c r="O473" t="n">
-        <v>12686603.30582707</v>
+        <v>12686603.19101244</v>
       </c>
       <c r="P473" t="n">
         <v>900</v>
@@ -21885,10 +21885,10 @@
         <v>54</v>
       </c>
       <c r="N476" t="n">
-        <v>2501.3844041451</v>
+        <v>2501.3843455497</v>
       </c>
       <c r="O476" t="n">
-        <v>135074.7578238354</v>
+        <v>135074.7546596838</v>
       </c>
       <c r="P476" t="n">
         <v>4100</v>
@@ -23750,10 +23750,10 @@
         <v>157</v>
       </c>
       <c r="N515" t="n">
-        <v>875.6901793722</v>
+        <v>875.6901843318</v>
       </c>
       <c r="O515" t="n">
-        <v>137483.3581614354</v>
+        <v>137483.3589400926</v>
       </c>
       <c r="P515" t="n">
         <v>4500</v>
@@ -24126,10 +24126,10 @@
         <v>94</v>
       </c>
       <c r="N523" t="n">
-        <v>3067.0906164384</v>
+        <v>3067.0906185567</v>
       </c>
       <c r="O523" t="n">
-        <v>288306.5179452096</v>
+        <v>288306.5181443298</v>
       </c>
       <c r="P523" t="n">
         <v>7200</v>
@@ -26060,7 +26060,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -26069,19 +26069,19 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="N564" t="n">
         <v>1934.77</v>
       </c>
       <c r="O564" t="n">
-        <v>646213.1800000001</v>
+        <v>638474.1</v>
       </c>
       <c r="P564" t="n">
         <v>8900</v>
       </c>
       <c r="Q564" t="n">
-        <v>2972600</v>
+        <v>2937000</v>
       </c>
     </row>
     <row r="565">
@@ -27795,10 +27795,10 @@
         <v>325</v>
       </c>
       <c r="N602" t="n">
-        <v>22951.704689564</v>
+        <v>22951.70468254</v>
       </c>
       <c r="O602" t="n">
-        <v>7459304.024108301</v>
+        <v>7459304.0218255</v>
       </c>
       <c r="P602" t="n">
         <v>37900</v>
@@ -27841,10 +27841,10 @@
         <v>172</v>
       </c>
       <c r="N603" t="n">
-        <v>705.5279692307701</v>
+        <v>705.52796610169</v>
       </c>
       <c r="O603" t="n">
-        <v>121350.8107076924</v>
+        <v>121350.8101694907</v>
       </c>
       <c r="P603" t="n">
         <v>1500</v>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="J609" t="n">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="K609" t="n">
         <v>0</v>
@@ -28119,19 +28119,19 @@
         <v>0</v>
       </c>
       <c r="M609" t="n">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="N609" t="n">
-        <v>220.00020804114</v>
+        <v>219.99816658071</v>
       </c>
       <c r="O609" t="n">
-        <v>484000.457690508</v>
+        <v>373996.883187207</v>
       </c>
       <c r="P609" t="n">
         <v>260</v>
       </c>
       <c r="Q609" t="n">
-        <v>572000</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="610">
@@ -28386,7 +28386,7 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
@@ -28395,19 +28395,19 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N615" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O615" t="n">
-        <v>87373.71000000001</v>
+        <v>67957.33</v>
       </c>
       <c r="P615" t="n">
         <v>10200</v>
       </c>
       <c r="Q615" t="n">
-        <v>91800</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="616">
@@ -29176,7 +29176,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29185,19 +29185,19 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N632" t="n">
         <v>1319.3610344828</v>
       </c>
       <c r="O632" t="n">
-        <v>189987.9889655232</v>
+        <v>184710.544827592</v>
       </c>
       <c r="P632" t="n">
         <v>3500</v>
       </c>
       <c r="Q632" t="n">
-        <v>504000</v>
+        <v>490000</v>
       </c>
     </row>
     <row r="633">
@@ -29431,10 +29431,10 @@
         <v>158</v>
       </c>
       <c r="N637" t="n">
-        <v>2539.5717817818</v>
+        <v>2539.5717961655</v>
       </c>
       <c r="O637" t="n">
-        <v>401252.3415215244</v>
+        <v>401252.343794149</v>
       </c>
       <c r="P637" t="n">
         <v>2900</v>
@@ -29477,10 +29477,10 @@
         <v>95</v>
       </c>
       <c r="N638" t="n">
-        <v>4171.6684420772</v>
+        <v>4171.6683950617</v>
       </c>
       <c r="O638" t="n">
-        <v>396308.501997334</v>
+        <v>396308.4975308615</v>
       </c>
       <c r="P638" t="n">
         <v>5000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -3018,10 +3018,10 @@
         <v>1127</v>
       </c>
       <c r="N63" t="n">
-        <v>1098.0691359493</v>
+        <v>1098.0698699716</v>
       </c>
       <c r="O63" t="n">
-        <v>1237523.916214861</v>
+        <v>1237524.743457993</v>
       </c>
       <c r="P63" t="n">
         <v>1500</v>
@@ -4410,10 +4410,10 @@
         <v>144</v>
       </c>
       <c r="N94" t="n">
-        <v>3230.0661344538</v>
+        <v>3230.0661016949</v>
       </c>
       <c r="O94" t="n">
-        <v>465129.5233613472</v>
+        <v>465129.5186440657</v>
       </c>
       <c r="P94" t="n">
         <v>6200</v>
@@ -4869,10 +4869,10 @@
         <v>581</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O104" t="n">
-        <v>2205307.51443425</v>
+        <v>2205307.514437678</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.386612891</v>
+        <v>1511297.38668016</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5726,10 +5726,10 @@
         <v>121</v>
       </c>
       <c r="N123" t="n">
-        <v>4891</v>
+        <v>4906.5393169182</v>
       </c>
       <c r="O123" t="n">
-        <v>591811</v>
+        <v>593691.2573471022</v>
       </c>
       <c r="P123" t="n">
         <v>8200</v>
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.54656253</v>
+        <v>7270946.568745527</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -6632,10 +6632,10 @@
         <v>1930</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O143" t="n">
-        <v>8436360.538338261</v>
+        <v>8436360.53933665</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -8467,10 +8467,10 @@
         <v>556</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O183" t="n">
-        <v>906794.1326734124</v>
+        <v>906794.1358703012</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.6884436828</v>
+        <v>418212.6909631158</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -10644,10 +10644,10 @@
         <v>940</v>
       </c>
       <c r="N232" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O232" t="n">
-        <v>5835508.92973045</v>
+        <v>5840377.26309792</v>
       </c>
       <c r="P232" t="n">
         <v>9900</v>
@@ -11039,10 +11039,10 @@
         <v>921</v>
       </c>
       <c r="N241" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O241" t="n">
-        <v>3307430.73</v>
+        <v>3310961.794836283</v>
       </c>
       <c r="P241" t="n">
         <v>6300</v>
@@ -11719,10 +11719,10 @@
         <v>46</v>
       </c>
       <c r="N256" t="n">
-        <v>9627.34</v>
+        <v>9808.987924528299</v>
       </c>
       <c r="O256" t="n">
-        <v>442857.64</v>
+        <v>451213.4445283018</v>
       </c>
       <c r="P256" t="n">
         <v>15900</v>
@@ -11858,10 +11858,10 @@
         <v>256</v>
       </c>
       <c r="N259" t="n">
-        <v>548.14706357215</v>
+        <v>548.14704568528</v>
       </c>
       <c r="O259" t="n">
-        <v>140325.6482744704</v>
+        <v>140325.6436954317</v>
       </c>
       <c r="P259" t="n">
         <v>2000</v>
@@ -14639,10 +14639,10 @@
         <v>416</v>
       </c>
       <c r="N319" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O319" t="n">
-        <v>3684994.56</v>
+        <v>3691233.264108333</v>
       </c>
       <c r="P319" t="n">
         <v>15500</v>
@@ -16110,10 +16110,10 @@
         <v>378</v>
       </c>
       <c r="N351" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O351" t="n">
-        <v>2588997.6</v>
+        <v>2593960.534696482</v>
       </c>
       <c r="P351" t="n">
         <v>11500</v>
@@ -17861,10 +17861,10 @@
         <v>1152</v>
       </c>
       <c r="N389" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O389" t="n">
-        <v>1746476.613796493</v>
+        <v>1746476.613493287</v>
       </c>
       <c r="P389" t="n">
         <v>2300</v>
@@ -18091,10 +18091,10 @@
         <v>216</v>
       </c>
       <c r="N394" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O394" t="n">
-        <v>357680.6896616856</v>
+        <v>357680.6672597208</v>
       </c>
       <c r="P394" t="n">
         <v>2500</v>
@@ -21293,10 +21293,10 @@
         <v>631</v>
       </c>
       <c r="N463" t="n">
-        <v>3110.8359666534</v>
+        <v>3110.8359331476</v>
       </c>
       <c r="O463" t="n">
-        <v>1962937.494958295</v>
+        <v>1962937.473816135</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>
@@ -21744,10 +21744,10 @@
         <v>18026</v>
       </c>
       <c r="N473" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O473" t="n">
-        <v>12686603.19101244</v>
+        <v>12686602.98593262</v>
       </c>
       <c r="P473" t="n">
         <v>900</v>
@@ -22738,10 +22738,10 @@
         <v>24</v>
       </c>
       <c r="N494" t="n">
-        <v>2832.1953125</v>
+        <v>2832.1953968254</v>
       </c>
       <c r="O494" t="n">
-        <v>67972.6875</v>
+        <v>67972.6895238096</v>
       </c>
       <c r="P494" t="n">
         <v>12900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -2488,10 +2488,10 @@
         <v>48</v>
       </c>
       <c r="N51" t="n">
-        <v>2584.1380683507</v>
+        <v>2572.67</v>
       </c>
       <c r="O51" t="n">
-        <v>124038.6272808336</v>
+        <v>123488.16</v>
       </c>
       <c r="P51" t="n">
         <v>4700</v>
@@ -2797,10 +2797,10 @@
         <v>228</v>
       </c>
       <c r="N58" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="O58" t="n">
-        <v>1125706.719527197</v>
+        <v>1125706.719620859</v>
       </c>
       <c r="P58" t="n">
         <v>7500</v>
@@ -3018,10 +3018,10 @@
         <v>1127</v>
       </c>
       <c r="N63" t="n">
-        <v>1108.8838530981</v>
+        <v>1098.0703134021</v>
       </c>
       <c r="O63" t="n">
-        <v>1249712.102441559</v>
+        <v>1237525.243204167</v>
       </c>
       <c r="P63" t="n">
         <v>1500</v>
@@ -3951,10 +3951,10 @@
         <v>666</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.2548633316</v>
+        <v>2582.2548540429</v>
       </c>
       <c r="O84" t="n">
-        <v>1719781.738978846</v>
+        <v>1719781.732792572</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300540176</v>
+        <v>4890.9300540541</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.386691438</v>
+        <v>1511297.386702717</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5319,10 +5319,10 @@
         <v>584</v>
       </c>
       <c r="N114" t="n">
-        <v>7063.376059322</v>
+        <v>7041</v>
       </c>
       <c r="O114" t="n">
-        <v>4125011.618644048</v>
+        <v>4111944</v>
       </c>
       <c r="P114" t="n">
         <v>11500</v>
@@ -5593,10 +5593,10 @@
         <v>240</v>
       </c>
       <c r="N120" t="n">
-        <v>3594.2528730512</v>
+        <v>3594.2528624535</v>
       </c>
       <c r="O120" t="n">
-        <v>862620.689532288</v>
+        <v>862620.68698884</v>
       </c>
       <c r="P120" t="n">
         <v>6500</v>
@@ -5634,10 +5634,10 @@
         <v>108</v>
       </c>
       <c r="N121" t="n">
-        <v>3354.2325655977</v>
+        <v>3240.850058309</v>
       </c>
       <c r="O121" t="n">
-        <v>362257.1170845516</v>
+        <v>350011.806297372</v>
       </c>
       <c r="P121" t="n">
         <v>5200</v>
@@ -5680,10 +5680,10 @@
         <v>23</v>
       </c>
       <c r="N122" t="n">
-        <v>7767.2727272727</v>
+        <v>7120</v>
       </c>
       <c r="O122" t="n">
-        <v>178647.2727272721</v>
+        <v>163760</v>
       </c>
       <c r="P122" t="n">
         <v>8900</v>
@@ -5911,10 +5911,10 @@
         <v>1506</v>
       </c>
       <c r="N127" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O127" t="n">
-        <v>3152533.604945771</v>
+        <v>3148820.1</v>
       </c>
       <c r="P127" t="n">
         <v>2900</v>
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.276319645</v>
+        <v>3472.276322317</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.61333663</v>
+        <v>7270946.618931798</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -6722,10 +6722,10 @@
         <v>181</v>
       </c>
       <c r="N145" t="n">
-        <v>1592.5646884576</v>
+        <v>1592.5646666667</v>
       </c>
       <c r="O145" t="n">
-        <v>288254.2086108256</v>
+        <v>288254.2046666727</v>
       </c>
       <c r="P145" t="n">
         <v>3900</v>
@@ -6804,10 +6804,10 @@
         <v>199</v>
       </c>
       <c r="N147" t="n">
-        <v>2231.2604819277</v>
+        <v>2224.56</v>
       </c>
       <c r="O147" t="n">
-        <v>444020.8359036123</v>
+        <v>442687.44</v>
       </c>
       <c r="P147" t="n">
         <v>3900</v>
@@ -7434,10 +7434,10 @@
         <v>149</v>
       </c>
       <c r="N161" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O161" t="n">
-        <v>1441987.755018649</v>
+        <v>1402732.19</v>
       </c>
       <c r="P161" t="n">
         <v>16900</v>
@@ -8467,10 +8467,10 @@
         <v>556</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9247235872</v>
+        <v>1630.9247279434</v>
       </c>
       <c r="O183" t="n">
-        <v>906794.1463144833</v>
+        <v>906794.1487365304</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5218851304</v>
+        <v>2403.5220092133</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.8080126896</v>
+        <v>418212.8296031142</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9188,10 +9188,10 @@
         <v>5</v>
       </c>
       <c r="N199" t="n">
-        <v>22288</v>
+        <v>15920</v>
       </c>
       <c r="O199" t="n">
-        <v>111440</v>
+        <v>79600</v>
       </c>
       <c r="P199" t="n">
         <v>19900</v>
@@ -10598,10 +10598,10 @@
         <v>918</v>
       </c>
       <c r="N231" t="n">
-        <v>6207.988218663</v>
+        <v>6207.9882181666</v>
       </c>
       <c r="O231" t="n">
-        <v>5698933.184732635</v>
+        <v>5698933.184276938</v>
       </c>
       <c r="P231" t="n">
         <v>9900</v>
@@ -10952,10 +10952,10 @@
         <v>1260</v>
       </c>
       <c r="N239" t="n">
-        <v>4814.2679247144</v>
+        <v>4814.2679243911</v>
       </c>
       <c r="O239" t="n">
-        <v>6065977.585140144</v>
+        <v>6065977.584732786</v>
       </c>
       <c r="P239" t="n">
         <v>9900</v>
@@ -11489,10 +11489,10 @@
         <v>467</v>
       </c>
       <c r="N251" t="n">
-        <v>1561.0061538462</v>
+        <v>1561.0062900506</v>
       </c>
       <c r="O251" t="n">
-        <v>728989.8738461754</v>
+        <v>728989.9374536301</v>
       </c>
       <c r="P251" t="n">
         <v>2900</v>
@@ -11722,10 +11722,10 @@
         <v>1770</v>
       </c>
       <c r="N256" t="n">
-        <v>1200.9029345372</v>
+        <v>1200</v>
       </c>
       <c r="O256" t="n">
-        <v>2125598.194130844</v>
+        <v>2124000</v>
       </c>
       <c r="P256" t="n">
         <v>1500</v>
@@ -13762,10 +13762,10 @@
         <v>9</v>
       </c>
       <c r="N300" t="n">
-        <v>5188.8571428571</v>
+        <v>5148</v>
       </c>
       <c r="O300" t="n">
-        <v>46699.7142857139</v>
+        <v>46332</v>
       </c>
       <c r="P300" t="n">
         <v>8600</v>
@@ -14455,10 +14455,10 @@
         <v>582</v>
       </c>
       <c r="N315" t="n">
-        <v>3957.6262600321</v>
+        <v>3938.66</v>
       </c>
       <c r="O315" t="n">
-        <v>2303338.483338682</v>
+        <v>2292300.12</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14639,10 +14639,10 @@
         <v>15</v>
       </c>
       <c r="N319" t="n">
-        <v>10448.721014493</v>
+        <v>10411</v>
       </c>
       <c r="O319" t="n">
-        <v>156730.815217395</v>
+        <v>156165</v>
       </c>
       <c r="P319" t="n">
         <v>16900</v>
@@ -16156,10 +16156,10 @@
         <v>32</v>
       </c>
       <c r="N352" t="n">
-        <v>6650.5777839955</v>
+        <v>6645</v>
       </c>
       <c r="O352" t="n">
-        <v>212818.489087856</v>
+        <v>212640</v>
       </c>
       <c r="P352" t="n">
         <v>10900</v>
@@ -16938,10 +16938,10 @@
         <v>41</v>
       </c>
       <c r="N369" t="n">
-        <v>18170.288401254</v>
+        <v>18001</v>
       </c>
       <c r="O369" t="n">
-        <v>744981.8244514141</v>
+        <v>738041</v>
       </c>
       <c r="P369" t="n">
         <v>28900</v>
@@ -17769,10 +17769,10 @@
         <v>1152</v>
       </c>
       <c r="N387" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O387" t="n">
-        <v>1746476.597549606</v>
+        <v>1746476.596929485</v>
       </c>
       <c r="P387" t="n">
         <v>2300</v>
@@ -18229,10 +18229,10 @@
         <v>224</v>
       </c>
       <c r="N397" t="n">
-        <v>1592.2864981273</v>
+        <v>1592.2866856061</v>
       </c>
       <c r="O397" t="n">
-        <v>356672.1755805152</v>
+        <v>356672.2175757664</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
@@ -18360,10 +18360,10 @@
         <v>312</v>
       </c>
       <c r="N400" t="n">
-        <v>2072.7973006135</v>
+        <v>2060.1582208589</v>
       </c>
       <c r="O400" t="n">
-        <v>646712.7577914119</v>
+        <v>642769.3649079768</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -18583,10 +18583,10 @@
         <v>504</v>
       </c>
       <c r="N405" t="n">
-        <v>692.15249234096</v>
+        <v>692.15249774246</v>
       </c>
       <c r="O405" t="n">
-        <v>348844.8561398438</v>
+        <v>348844.8588621998</v>
       </c>
       <c r="P405" t="n">
         <v>1200</v>
@@ -18632,10 +18632,10 @@
         <v>70</v>
       </c>
       <c r="N406" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="O406" t="n">
-        <v>1333593.33333331</v>
+        <v>1294370</v>
       </c>
       <c r="P406" t="n">
         <v>13500</v>
@@ -21652,10 +21652,10 @@
         <v>18026</v>
       </c>
       <c r="N471" t="n">
-        <v>703.79465893216</v>
+        <v>703.79465786602</v>
       </c>
       <c r="O471" t="n">
-        <v>12686602.52191112</v>
+        <v>12686602.50269288</v>
       </c>
       <c r="P471" t="n">
         <v>900</v>
@@ -22159,10 +22159,10 @@
         <v>47</v>
       </c>
       <c r="N482" t="n">
-        <v>1595.4982940252</v>
+        <v>1595.4982440945</v>
       </c>
       <c r="O482" t="n">
-        <v>74988.4198191844</v>
+        <v>74988.41747244151</v>
       </c>
       <c r="P482" t="n">
         <v>2500</v>
@@ -23076,10 +23076,10 @@
         <v>8</v>
       </c>
       <c r="N501" t="n">
-        <v>14670.891428571</v>
+        <v>12837.03</v>
       </c>
       <c r="O501" t="n">
-        <v>117367.131428568</v>
+        <v>102696.24</v>
       </c>
       <c r="P501" t="n">
         <v>15500</v>
@@ -23756,10 +23756,10 @@
         <v>75</v>
       </c>
       <c r="N515" t="n">
-        <v>7190.9555769231</v>
+        <v>6989.34</v>
       </c>
       <c r="O515" t="n">
-        <v>539321.6682692325</v>
+        <v>524200.5</v>
       </c>
       <c r="P515" t="n">
         <v>10900</v>
@@ -24034,10 +24034,10 @@
         <v>94</v>
       </c>
       <c r="N521" t="n">
-        <v>3099.0394791667</v>
+        <v>3067.090625</v>
       </c>
       <c r="O521" t="n">
-        <v>291309.7110416698</v>
+        <v>288306.51875</v>
       </c>
       <c r="P521" t="n">
         <v>7200</v>
@@ -24178,10 +24178,10 @@
         <v>157</v>
       </c>
       <c r="N524" t="n">
-        <v>4234.8833684211</v>
+        <v>4190.77</v>
       </c>
       <c r="O524" t="n">
-        <v>664876.6888421128</v>
+        <v>657950.89</v>
       </c>
       <c r="P524" t="n">
         <v>5900</v>
@@ -25887,10 +25887,10 @@
         <v>3</v>
       </c>
       <c r="N560" t="n">
-        <v>1517.945625</v>
+        <v>1278.27</v>
       </c>
       <c r="O560" t="n">
-        <v>4553.836875</v>
+        <v>3834.81</v>
       </c>
       <c r="P560" t="n">
         <v>5900</v>
@@ -26559,10 +26559,10 @@
         <v>12</v>
       </c>
       <c r="N574" t="n">
-        <v>548.38743842365</v>
+        <v>540.40123152709</v>
       </c>
       <c r="O574" t="n">
-        <v>6580.6492610838</v>
+        <v>6484.81477832508</v>
       </c>
       <c r="P574" t="n">
         <v>2500</v>
@@ -27892,10 +27892,10 @@
         <v>289</v>
       </c>
       <c r="N604" t="n">
-        <v>1757.3206341463</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O604" t="n">
-        <v>507865.6632682807</v>
+        <v>507865.6637163752</v>
       </c>
       <c r="P604" t="n">
         <v>2000</v>
@@ -29050,10 +29050,10 @@
         <v>140</v>
       </c>
       <c r="N629" t="n">
-        <v>1333.5477419355</v>
+        <v>1319.3610452962</v>
       </c>
       <c r="O629" t="n">
-        <v>186696.68387097</v>
+        <v>184710.546341468</v>
       </c>
       <c r="P629" t="n">
         <v>3500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q650"/>
+  <dimension ref="A1:Q648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3107843137</v>
+        <v>1811.3108241082</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3107843137</v>
+        <v>1811.3108241082</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.746386014</v>
+        <v>3376.7463829787</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.805236376</v>
+        <v>2985043.802553171</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1195,10 +1195,10 @@
         <v>194</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370726607</v>
+        <v>3926.8370711297</v>
       </c>
       <c r="O20" t="n">
-        <v>761806.3920961758</v>
+        <v>761806.3917991618</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1273,10 +1273,10 @@
         <v>45</v>
       </c>
       <c r="N22" t="n">
-        <v>2413.0010989011</v>
+        <v>2413.0011037528</v>
       </c>
       <c r="O22" t="n">
-        <v>108585.0494505495</v>
+        <v>108585.049668876</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1755,10 +1755,10 @@
         <v>16</v>
       </c>
       <c r="N34" t="n">
-        <v>16486.406019417</v>
+        <v>16486.405882353</v>
       </c>
       <c r="O34" t="n">
-        <v>263782.496310672</v>
+        <v>263782.494117648</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
@@ -3018,10 +3018,10 @@
         <v>1127</v>
       </c>
       <c r="N63" t="n">
-        <v>1098.0703134021</v>
+        <v>1098.0716580534</v>
       </c>
       <c r="O63" t="n">
-        <v>1237525.243204167</v>
+        <v>1237526.758626182</v>
       </c>
       <c r="P63" t="n">
         <v>1500</v>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3948,19 +3948,19 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.2548540429</v>
+        <v>2582.2548393782</v>
       </c>
       <c r="O84" t="n">
-        <v>1719781.732792572</v>
+        <v>1681047.900435208</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
       </c>
       <c r="Q84" t="n">
-        <v>2997000</v>
+        <v>2929500</v>
       </c>
     </row>
     <row r="85">
@@ -4274,10 +4274,10 @@
         <v>3167</v>
       </c>
       <c r="N91" t="n">
-        <v>3158.8608413965</v>
+        <v>3158.8608416484</v>
       </c>
       <c r="O91" t="n">
-        <v>10004112.28470271</v>
+        <v>10004112.28550048</v>
       </c>
       <c r="P91" t="n">
         <v>5600</v>
@@ -4410,10 +4410,10 @@
         <v>144</v>
       </c>
       <c r="N94" t="n">
-        <v>3230.0658928571</v>
+        <v>3230.0657538462</v>
       </c>
       <c r="O94" t="n">
-        <v>465129.4885714224</v>
+        <v>465129.4685538528</v>
       </c>
       <c r="P94" t="n">
         <v>6200</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300540541</v>
+        <v>4890.9300548321</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.386702717</v>
+        <v>1511297.386943119</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5273,10 +5273,10 @@
         <v>309</v>
       </c>
       <c r="N113" t="n">
-        <v>2267.0480857514</v>
+        <v>2267.048084922</v>
       </c>
       <c r="O113" t="n">
-        <v>700517.8584971826</v>
+        <v>700517.858240898</v>
       </c>
       <c r="P113" t="n">
         <v>3900</v>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>962</v>
+        <v>942</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>962</v>
+        <v>942</v>
       </c>
       <c r="N115" t="n">
         <v>5667.94</v>
       </c>
       <c r="O115" t="n">
-        <v>5452558.279999999</v>
+        <v>5339199.48</v>
       </c>
       <c r="P115" t="n">
         <v>9500</v>
       </c>
       <c r="Q115" t="n">
-        <v>9139000</v>
+        <v>8949000</v>
       </c>
     </row>
     <row r="116">
@@ -5593,10 +5593,10 @@
         <v>240</v>
       </c>
       <c r="N120" t="n">
-        <v>3594.2528624535</v>
+        <v>3594.2528571429</v>
       </c>
       <c r="O120" t="n">
-        <v>862620.68698884</v>
+        <v>862620.6857142961</v>
       </c>
       <c r="P120" t="n">
         <v>6500</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5815,19 +5815,19 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N125" t="n">
         <v>14822.378817006</v>
       </c>
       <c r="O125" t="n">
-        <v>4520825.53918683</v>
+        <v>4491180.781552818</v>
       </c>
       <c r="P125" t="n">
         <v>24900</v>
       </c>
       <c r="Q125" t="n">
-        <v>7594500</v>
+        <v>7544700</v>
       </c>
     </row>
     <row r="126">
@@ -6455,10 +6455,10 @@
         <v>16</v>
       </c>
       <c r="N139" t="n">
-        <v>4242.5422885572</v>
+        <v>4242.5422942643</v>
       </c>
       <c r="O139" t="n">
-        <v>67880.6766169152</v>
+        <v>67880.6767082288</v>
       </c>
       <c r="P139" t="n">
         <v>5900</v>
@@ -6504,10 +6504,10 @@
         <v>157</v>
       </c>
       <c r="N140" t="n">
-        <v>3041.6600148588</v>
+        <v>3041.6600149031</v>
       </c>
       <c r="O140" t="n">
-        <v>477540.6223328316</v>
+        <v>477540.6223397867</v>
       </c>
       <c r="P140" t="n">
         <v>5500</v>
@@ -6632,10 +6632,10 @@
         <v>1915</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1712639913</v>
+        <v>4371.1712646818</v>
       </c>
       <c r="O143" t="n">
-        <v>8370792.97054334</v>
+        <v>8370792.971865647</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -6722,10 +6722,10 @@
         <v>181</v>
       </c>
       <c r="N145" t="n">
-        <v>1592.5646666667</v>
+        <v>1592.5645945946</v>
       </c>
       <c r="O145" t="n">
-        <v>288254.2046666727</v>
+        <v>288254.1916216226</v>
       </c>
       <c r="P145" t="n">
         <v>3900</v>
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>556</v>
+        <v>337</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8464,19 +8464,19 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>556</v>
+        <v>337</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9247279434</v>
+        <v>1630.9248152786</v>
       </c>
       <c r="O183" t="n">
-        <v>906794.1487365304</v>
+        <v>549621.6627488881</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
       </c>
       <c r="Q183" t="n">
-        <v>1390000</v>
+        <v>842500</v>
       </c>
     </row>
     <row r="184">
@@ -8513,10 +8513,10 @@
         <v>5</v>
       </c>
       <c r="N184" t="n">
-        <v>1467.3012605042</v>
+        <v>1467.3004273504</v>
       </c>
       <c r="O184" t="n">
-        <v>7336.506302521</v>
+        <v>7336.502136752</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
@@ -8559,10 +8559,10 @@
         <v>32</v>
       </c>
       <c r="N185" t="n">
-        <v>1690.5767609618</v>
+        <v>1690.5762660944</v>
       </c>
       <c r="O185" t="n">
-        <v>54098.4563507776</v>
+        <v>54098.4405150208</v>
       </c>
       <c r="P185" t="n">
         <v>2900</v>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>1294</v>
+        <v>1282</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8602,19 +8602,19 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>1294</v>
+        <v>1282</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1948069948</v>
+        <v>1550.1948402243</v>
       </c>
       <c r="O186" t="n">
-        <v>2005952.080251271</v>
+        <v>1987349.785167553</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
       </c>
       <c r="Q186" t="n">
-        <v>3235000</v>
+        <v>3205000</v>
       </c>
     </row>
     <row r="187">
@@ -8651,10 +8651,10 @@
         <v>22</v>
       </c>
       <c r="N187" t="n">
-        <v>1579.3814948454</v>
+        <v>1579.3812041885</v>
       </c>
       <c r="O187" t="n">
-        <v>34746.3928865988</v>
+        <v>34746.386492147</v>
       </c>
       <c r="P187" t="n">
         <v>2900</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5220092133</v>
+        <v>2403.5223176428</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.8296031142</v>
+        <v>418212.8832698472</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -8738,10 +8738,10 @@
         <v>59</v>
       </c>
       <c r="N189" t="n">
-        <v>1232.8058115183</v>
+        <v>1232.8056613757</v>
       </c>
       <c r="O189" t="n">
-        <v>72735.54287957971</v>
+        <v>72735.5340211663</v>
       </c>
       <c r="P189" t="n">
         <v>2400</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10329,19 +10329,19 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N225" t="n">
         <v>11431.604625</v>
       </c>
       <c r="O225" t="n">
-        <v>114316.04625</v>
+        <v>102884.441625</v>
       </c>
       <c r="P225" t="n">
         <v>48900</v>
       </c>
       <c r="Q225" t="n">
-        <v>489000</v>
+        <v>440100</v>
       </c>
     </row>
     <row r="226">
@@ -10598,10 +10598,10 @@
         <v>918</v>
       </c>
       <c r="N231" t="n">
-        <v>6207.9882181666</v>
+        <v>6207.9882044083</v>
       </c>
       <c r="O231" t="n">
-        <v>5698933.184276938</v>
+        <v>5698933.171646819</v>
       </c>
       <c r="P231" t="n">
         <v>9900</v>
@@ -10693,10 +10693,10 @@
         <v>89</v>
       </c>
       <c r="N233" t="n">
-        <v>4285.1964713376</v>
+        <v>4285.196521181</v>
       </c>
       <c r="O233" t="n">
-        <v>381382.4859490464</v>
+        <v>381382.490385109</v>
       </c>
       <c r="P233" t="n">
         <v>6900</v>
@@ -10952,10 +10952,10 @@
         <v>1260</v>
       </c>
       <c r="N239" t="n">
-        <v>4814.2679243911</v>
+        <v>4814.2679220172</v>
       </c>
       <c r="O239" t="n">
-        <v>6065977.584732786</v>
+        <v>6065977.581741672</v>
       </c>
       <c r="P239" t="n">
         <v>9900</v>
@@ -11489,10 +11489,10 @@
         <v>467</v>
       </c>
       <c r="N251" t="n">
-        <v>1561.0062900506</v>
+        <v>1561.0063590178</v>
       </c>
       <c r="O251" t="n">
-        <v>728989.9374536301</v>
+        <v>728989.9696613125</v>
       </c>
       <c r="P251" t="n">
         <v>2900</v>
@@ -14685,10 +14685,10 @@
         <v>5</v>
       </c>
       <c r="N320" t="n">
-        <v>2252.3006175299</v>
+        <v>2252.300877551</v>
       </c>
       <c r="O320" t="n">
-        <v>11261.5030876495</v>
+        <v>11261.504387755</v>
       </c>
       <c r="P320" t="n">
         <v>3900</v>
@@ -15011,10 +15011,10 @@
         <v>228</v>
       </c>
       <c r="N327" t="n">
-        <v>2328.1186430868</v>
+        <v>2328.1186426504</v>
       </c>
       <c r="O327" t="n">
-        <v>530811.0506237905</v>
+        <v>530811.0505242912</v>
       </c>
       <c r="P327" t="n">
         <v>4500</v>
@@ -15609,10 +15609,10 @@
         <v>126</v>
       </c>
       <c r="N340" t="n">
-        <v>4907.8227311828</v>
+        <v>4907.8227489177</v>
       </c>
       <c r="O340" t="n">
-        <v>618385.6641290329</v>
+        <v>618385.6663636302</v>
       </c>
       <c r="P340" t="n">
         <v>8200</v>
@@ -15972,10 +15972,10 @@
         <v>24</v>
       </c>
       <c r="N348" t="n">
-        <v>5869.1723216187</v>
+        <v>5869.1723052295</v>
       </c>
       <c r="O348" t="n">
-        <v>140860.1357188488</v>
+        <v>140860.135325508</v>
       </c>
       <c r="P348" t="n">
         <v>9500</v>
@@ -16754,10 +16754,10 @@
         <v>291</v>
       </c>
       <c r="N365" t="n">
-        <v>17075.989516129</v>
+        <v>17075.989515789</v>
       </c>
       <c r="O365" t="n">
-        <v>4969112.949193539</v>
+        <v>4969112.949094598</v>
       </c>
       <c r="P365" t="n">
         <v>27500</v>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="J374" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="K374" t="n">
         <v>0</v>
@@ -17168,19 +17168,19 @@
         <v>0</v>
       </c>
       <c r="M374" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="N374" t="n">
         <v>8700</v>
       </c>
       <c r="O374" t="n">
-        <v>443700</v>
+        <v>313200</v>
       </c>
       <c r="P374" t="n">
         <v>14900</v>
       </c>
       <c r="Q374" t="n">
-        <v>759900</v>
+        <v>536400</v>
       </c>
     </row>
     <row r="375">
@@ -17343,7 +17343,7 @@
         </is>
       </c>
       <c r="J378" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K378" t="n">
         <v>0</v>
@@ -17352,19 +17352,19 @@
         <v>0</v>
       </c>
       <c r="M378" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N378" t="n">
         <v>10817</v>
       </c>
       <c r="O378" t="n">
-        <v>324510</v>
+        <v>216340</v>
       </c>
       <c r="P378" t="n">
         <v>17900</v>
       </c>
       <c r="Q378" t="n">
-        <v>537000</v>
+        <v>358000</v>
       </c>
     </row>
     <row r="379">
@@ -17757,7 +17757,7 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>1152</v>
+        <v>1008</v>
       </c>
       <c r="K387" t="n">
         <v>0</v>
@@ -17766,19 +17766,19 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>1152</v>
+        <v>1008</v>
       </c>
       <c r="N387" t="n">
-        <v>1516.0387126124</v>
+        <v>1516.0387122084</v>
       </c>
       <c r="O387" t="n">
-        <v>1746476.596929485</v>
+        <v>1528167.021906067</v>
       </c>
       <c r="P387" t="n">
         <v>2300</v>
       </c>
       <c r="Q387" t="n">
-        <v>2649600</v>
+        <v>2318400</v>
       </c>
     </row>
     <row r="388">
@@ -17861,10 +17861,10 @@
         <v>72</v>
       </c>
       <c r="N389" t="n">
-        <v>2079.383244983</v>
+        <v>2079.383183034</v>
       </c>
       <c r="O389" t="n">
-        <v>149715.593638776</v>
+        <v>149715.589178448</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17907,10 +17907,10 @@
         <v>96</v>
       </c>
       <c r="N390" t="n">
-        <v>3306.5943307087</v>
+        <v>3306.5942766296</v>
       </c>
       <c r="O390" t="n">
-        <v>317433.0557480352</v>
+        <v>317433.0505564416</v>
       </c>
       <c r="P390" t="n">
         <v>4900</v>
@@ -17953,10 +17953,10 @@
         <v>96</v>
       </c>
       <c r="N391" t="n">
-        <v>2056.081835443</v>
+        <v>2056.0813131313</v>
       </c>
       <c r="O391" t="n">
-        <v>197383.856202528</v>
+        <v>197383.8060606048</v>
       </c>
       <c r="P391" t="n">
         <v>2900</v>
@@ -17999,10 +17999,10 @@
         <v>216</v>
       </c>
       <c r="N392" t="n">
-        <v>1655.9289976134</v>
+        <v>1655.9289844683</v>
       </c>
       <c r="O392" t="n">
-        <v>357680.6634844944</v>
+        <v>357680.6606451528</v>
       </c>
       <c r="P392" t="n">
         <v>2500</v>
@@ -18229,10 +18229,10 @@
         <v>224</v>
       </c>
       <c r="N397" t="n">
-        <v>1592.2866856061</v>
+        <v>1592.2867809524</v>
       </c>
       <c r="O397" t="n">
-        <v>356672.2175757664</v>
+        <v>356672.2389333376</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
@@ -18406,10 +18406,10 @@
         <v>400</v>
       </c>
       <c r="N401" t="n">
-        <v>1259.2751217656</v>
+        <v>1259.2751100987</v>
       </c>
       <c r="O401" t="n">
-        <v>503710.04870624</v>
+        <v>503710.04403948</v>
       </c>
       <c r="P401" t="n">
         <v>1900</v>
@@ -18493,10 +18493,10 @@
         <v>97</v>
       </c>
       <c r="N403" t="n">
-        <v>2842.2743909348</v>
+        <v>2842.2743829787</v>
       </c>
       <c r="O403" t="n">
-        <v>275700.6159206756</v>
+        <v>275700.6151489339</v>
       </c>
       <c r="P403" t="n">
         <v>4900</v>
@@ -18583,10 +18583,10 @@
         <v>504</v>
       </c>
       <c r="N405" t="n">
-        <v>692.15249774246</v>
+        <v>692.15251408835</v>
       </c>
       <c r="O405" t="n">
-        <v>348844.8588621998</v>
+        <v>348844.8671005284</v>
       </c>
       <c r="P405" t="n">
         <v>1200</v>
@@ -18908,7 +18908,7 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -18917,19 +18917,19 @@
         <v>0</v>
       </c>
       <c r="M412" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N412" t="n">
         <v>44470</v>
       </c>
       <c r="O412" t="n">
-        <v>1734330</v>
+        <v>1556450</v>
       </c>
       <c r="P412" t="n">
         <v>71900</v>
       </c>
       <c r="Q412" t="n">
-        <v>2804100</v>
+        <v>2516500</v>
       </c>
     </row>
     <row r="413">
@@ -20131,10 +20131,10 @@
         <v>3</v>
       </c>
       <c r="N438" t="n">
-        <v>2270.3213157895</v>
+        <v>2270.3215151515</v>
       </c>
       <c r="O438" t="n">
-        <v>6810.9639473685</v>
+        <v>6810.964545454501</v>
       </c>
       <c r="P438" t="n">
         <v>3900</v>
@@ -21201,10 +21201,10 @@
         <v>631</v>
       </c>
       <c r="N461" t="n">
-        <v>3110.8357056207</v>
+        <v>3110.8356475842</v>
       </c>
       <c r="O461" t="n">
-        <v>1962937.330246662</v>
+        <v>1962937.29362563</v>
       </c>
       <c r="P461" t="n">
         <v>4500</v>
@@ -21564,10 +21564,10 @@
         <v>240</v>
       </c>
       <c r="N469" t="n">
-        <v>3002.0210028653</v>
+        <v>3002.0210043042</v>
       </c>
       <c r="O469" t="n">
-        <v>720485.040687672</v>
+        <v>720485.0410330079</v>
       </c>
       <c r="P469" t="n">
         <v>4500</v>
@@ -21652,10 +21652,10 @@
         <v>18026</v>
       </c>
       <c r="N471" t="n">
-        <v>703.79465786602</v>
+        <v>703.79463731331</v>
       </c>
       <c r="O471" t="n">
-        <v>12686602.50269288</v>
+        <v>12686602.13220973</v>
       </c>
       <c r="P471" t="n">
         <v>900</v>
@@ -21701,10 +21701,10 @@
         <v>55</v>
       </c>
       <c r="N472" t="n">
-        <v>3182.2511342155</v>
+        <v>3182.2511650485</v>
       </c>
       <c r="O472" t="n">
-        <v>175023.8123818525</v>
+        <v>175023.8140776675</v>
       </c>
       <c r="P472" t="n">
         <v>6900</v>
@@ -21793,10 +21793,10 @@
         <v>52</v>
       </c>
       <c r="N474" t="n">
-        <v>2501.3841304348</v>
+        <v>2501.384</v>
       </c>
       <c r="O474" t="n">
-        <v>130071.9747826096</v>
+        <v>130071.968</v>
       </c>
       <c r="P474" t="n">
         <v>4100</v>
@@ -22257,10 +22257,10 @@
         <v>296</v>
       </c>
       <c r="N484" t="n">
-        <v>6078.9926048565</v>
+        <v>6078.992616408</v>
       </c>
       <c r="O484" t="n">
-        <v>1799381.811037524</v>
+        <v>1799381.814456768</v>
       </c>
       <c r="P484" t="n">
         <v>18500</v>
@@ -22880,10 +22880,10 @@
         <v>18</v>
       </c>
       <c r="N497" t="n">
-        <v>11866.994642857</v>
+        <v>11866.994814815</v>
       </c>
       <c r="O497" t="n">
-        <v>213605.903571426</v>
+        <v>213605.90666667</v>
       </c>
       <c r="P497" t="n">
         <v>55000</v>
@@ -23238,20 +23238,17 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>C7175</t>
-        </is>
-      </c>
-      <c r="B505" t="n">
-        <v>6902040807110</v>
+          <t>C7176-B</t>
+        </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>ROBOT DRAGON 4EN1 C7175</t>
+          <t>FICHAS DE ARMAR CASA EL ARBOL C7176-B</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>FICHAS DE ARMAR</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -23260,7 +23257,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -23269,35 +23266,38 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="N505" t="n">
-        <v>7230.04</v>
+        <v>23475.657272727</v>
       </c>
       <c r="O505" t="n">
-        <v>216901.2</v>
+        <v>305183.544545451</v>
       </c>
       <c r="P505" t="n">
-        <v>15900</v>
+        <v>31900</v>
       </c>
       <c r="Q505" t="n">
-        <v>477000</v>
+        <v>414700</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>C7176-B</t>
-        </is>
+          <t>C7190</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>8695742011999</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR CASA EL ARBOL C7176-B</t>
+          <t>PISTA DINOSAURIO C7190</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -23306,7 +23306,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -23315,33 +23315,33 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N506" t="n">
-        <v>23475.657272727</v>
+        <v>17208.63</v>
       </c>
       <c r="O506" t="n">
-        <v>305183.544545451</v>
+        <v>68834.52</v>
       </c>
       <c r="P506" t="n">
-        <v>31900</v>
+        <v>69900</v>
       </c>
       <c r="Q506" t="n">
-        <v>414700</v>
+        <v>279600</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>C7190</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>8695742011999</v>
+        <v>6987540143012</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>PISTA DINOSAURIO C7190</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -23355,7 +23355,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23364,33 +23364,33 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N507" t="n">
-        <v>17208.63</v>
+        <v>9746.8802061856</v>
       </c>
       <c r="O507" t="n">
-        <v>68834.52</v>
+        <v>146203.203092784</v>
       </c>
       <c r="P507" t="n">
-        <v>69900</v>
+        <v>18500</v>
       </c>
       <c r="Q507" t="n">
-        <v>279600</v>
+        <v>277500</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7217</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>6987540143012</v>
+        <v>6921202413129</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>JUEGO PESCA EN BLISTER C721</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23413,33 +23413,33 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N508" t="n">
-        <v>9746.8802061856</v>
+        <v>10296.29</v>
       </c>
       <c r="O508" t="n">
-        <v>146203.203092784</v>
+        <v>92666.61000000002</v>
       </c>
       <c r="P508" t="n">
-        <v>18500</v>
+        <v>16900</v>
       </c>
       <c r="Q508" t="n">
-        <v>277500</v>
+        <v>152100</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>C7217</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>6921202413129</v>
+        <v>7453100037446</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>JUEGO PESCA EN BLISTER C721</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -23453,7 +23453,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>9</v>
+        <v>351</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -23462,33 +23462,33 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>9</v>
+        <v>351</v>
       </c>
       <c r="N509" t="n">
-        <v>10296.29</v>
+        <v>2672.89</v>
       </c>
       <c r="O509" t="n">
-        <v>92666.61000000002</v>
+        <v>938184.3899999999</v>
       </c>
       <c r="P509" t="n">
-        <v>16900</v>
+        <v>10200</v>
       </c>
       <c r="Q509" t="n">
-        <v>152100</v>
+        <v>3580200</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -23502,7 +23502,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>351</v>
+        <v>242</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23511,33 +23511,33 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>351</v>
+        <v>242</v>
       </c>
       <c r="N510" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O510" t="n">
-        <v>938184.3899999999</v>
+        <v>1160556.98</v>
       </c>
       <c r="P510" t="n">
         <v>10200</v>
       </c>
       <c r="Q510" t="n">
-        <v>3580200</v>
+        <v>2468400</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7229-AB</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>7453100037453</v>
+        <v>8981252652549</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>LAMPARA LED ANIMALITOS C7229-AB</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -23551,7 +23551,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23560,33 +23560,30 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="N511" t="n">
-        <v>4795.69</v>
+        <v>6773.85</v>
       </c>
       <c r="O511" t="n">
-        <v>1160556.98</v>
+        <v>6773.85</v>
       </c>
       <c r="P511" t="n">
-        <v>10200</v>
+        <v>9500</v>
       </c>
       <c r="Q511" t="n">
-        <v>2468400</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>C7229-AB</t>
-        </is>
-      </c>
-      <c r="B512" t="n">
-        <v>8981252652549</v>
+          <t>C7247</t>
+        </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>LAMPARA LED ANIMALITOS C7229-AB</t>
+          <t>PATINETA BLISTER C7247</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -23600,7 +23597,7 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23609,30 +23606,33 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="N512" t="n">
-        <v>6773.85</v>
+        <v>875.6901843318</v>
       </c>
       <c r="O512" t="n">
-        <v>6773.85</v>
+        <v>137483.3589400926</v>
       </c>
       <c r="P512" t="n">
-        <v>9500</v>
+        <v>4500</v>
       </c>
       <c r="Q512" t="n">
-        <v>9500</v>
+        <v>706500</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>C7247</t>
-        </is>
+          <t>C7255</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>4680448622444</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PATINETA BLISTER C7247</t>
+          <t>SET DE BELLEZA GIRL C7255</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -23646,7 +23646,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -23655,38 +23655,38 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="N513" t="n">
-        <v>875.6901843318</v>
+        <v>5430.86</v>
       </c>
       <c r="O513" t="n">
-        <v>137483.3589400926</v>
+        <v>54308.6</v>
       </c>
       <c r="P513" t="n">
-        <v>4500</v>
+        <v>13900</v>
       </c>
       <c r="Q513" t="n">
-        <v>706500</v>
+        <v>139000</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>C7255</t>
+          <t>C7259</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>4680448622444</v>
+        <v>7856754657488</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA GIRL C7255</t>
+          <t>CARRO RETRO EN BOLSA C7259</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -23704,38 +23704,38 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="N514" t="n">
-        <v>5430.86</v>
+        <v>6989.34</v>
       </c>
       <c r="O514" t="n">
-        <v>54308.6</v>
+        <v>524200.5</v>
       </c>
       <c r="P514" t="n">
-        <v>13900</v>
+        <v>10900</v>
       </c>
       <c r="Q514" t="n">
-        <v>139000</v>
+        <v>817500</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>C7259</t>
+          <t>C7280</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>7856754657488</v>
+        <v>9620012072805</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>CARRO RETRO EN BOLSA C7259</t>
+          <t>SET BELLEZA MUÑECA Y RULOS C7280</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -23744,7 +23744,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23753,38 +23753,38 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N515" t="n">
-        <v>6989.34</v>
+        <v>4568.55</v>
       </c>
       <c r="O515" t="n">
-        <v>524200.5</v>
+        <v>246701.7</v>
       </c>
       <c r="P515" t="n">
-        <v>10900</v>
+        <v>6900</v>
       </c>
       <c r="Q515" t="n">
-        <v>817500</v>
+        <v>372600</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>C7280</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>9620012072805</v>
+        <v>6895675680022</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>SET BELLEZA MUÑECA Y RULOS C7280</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -23793,7 +23793,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -23802,38 +23802,35 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N516" t="n">
-        <v>4568.55</v>
+        <v>4337.31</v>
       </c>
       <c r="O516" t="n">
-        <v>255838.8</v>
+        <v>286262.46</v>
       </c>
       <c r="P516" t="n">
-        <v>6900</v>
+        <v>12900</v>
       </c>
       <c r="Q516" t="n">
-        <v>386400</v>
+        <v>851400</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>C7294</t>
-        </is>
-      </c>
-      <c r="B517" t="n">
-        <v>6895675680022</v>
+          <t>C73-IO</t>
+        </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>INFLABLE RANA C73</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -23842,7 +23839,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -23851,44 +23848,42 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="N517" t="n">
-        <v>4337.31</v>
+        <v>3000.33</v>
       </c>
       <c r="O517" t="n">
-        <v>286262.46</v>
+        <v>1962215.82</v>
       </c>
       <c r="P517" t="n">
-        <v>12900</v>
+        <v>2900</v>
       </c>
       <c r="Q517" t="n">
-        <v>851400</v>
+        <v>1896600</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>C73-IO</t>
-        </is>
+          <t>C731</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>6903728884218</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>INFLABLE RANA C73</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>ATARI CEL ANIMALES</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J518" t="n">
-        <v>654</v>
+        <v>3</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -23897,33 +23892,30 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>654</v>
+        <v>3</v>
       </c>
       <c r="N518" t="n">
-        <v>3000.33</v>
+        <v>19632.66</v>
       </c>
       <c r="O518" t="n">
-        <v>1962215.82</v>
+        <v>58897.98</v>
       </c>
       <c r="P518" t="n">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="Q518" t="n">
-        <v>1896600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>C731</t>
-        </is>
-      </c>
-      <c r="B519" t="n">
-        <v>6903728884218</v>
+          <t>C732</t>
+        </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>ATARI CEL ANIMALES</t>
+          <t>GLOBOS BOUQUET HROES</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -23932,7 +23924,7 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -23941,39 +23933,47 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="N519" t="n">
-        <v>19632.66</v>
+        <v>3414.5659584665</v>
       </c>
       <c r="O519" t="n">
-        <v>58897.98</v>
+        <v>1065344.579041548</v>
       </c>
       <c r="P519" t="n">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="Q519" t="n">
-        <v>8400</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>C732</t>
-        </is>
+          <t>C7325</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>6974555555022</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET HROES</t>
+          <t>PISTA EN BLISTER C7325</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J520" t="n">
-        <v>312</v>
+        <v>94</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -23982,38 +23982,38 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>312</v>
+        <v>94</v>
       </c>
       <c r="N520" t="n">
-        <v>3414.5659584665</v>
+        <v>3067.090625</v>
       </c>
       <c r="O520" t="n">
-        <v>1065344.579041548</v>
+        <v>288306.51875</v>
       </c>
       <c r="P520" t="n">
-        <v>3500</v>
+        <v>7200</v>
       </c>
       <c r="Q520" t="n">
-        <v>1092000</v>
+        <v>676800</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>C7325</t>
+          <t>C7332</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>6974555555022</v>
+        <v>9092407809158</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>FICHAS DE ARMAR MUÑECO SOLDADO EN BOLSA C7332</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -24031,38 +24031,35 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="N521" t="n">
-        <v>3067.090625</v>
+        <v>507.37</v>
       </c>
       <c r="O521" t="n">
-        <v>288306.51875</v>
+        <v>12176.88</v>
       </c>
       <c r="P521" t="n">
-        <v>7200</v>
+        <v>2500</v>
       </c>
       <c r="Q521" t="n">
-        <v>676800</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>C7332</t>
-        </is>
-      </c>
-      <c r="B522" t="n">
-        <v>9092407809158</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR MUÑECO SOLDADO EN BOLSA C7332</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -24071,7 +24068,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -24080,35 +24077,38 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="N522" t="n">
-        <v>507.37</v>
+        <v>640</v>
       </c>
       <c r="O522" t="n">
-        <v>12176.88</v>
+        <v>32000</v>
       </c>
       <c r="P522" t="n">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="Q522" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -24117,7 +24117,7 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -24126,33 +24126,33 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="N523" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O523" t="n">
-        <v>32000</v>
+        <v>657950.89</v>
       </c>
       <c r="P523" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q523" t="n">
-        <v>40000</v>
+        <v>926300</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -24166,7 +24166,7 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>157</v>
+        <v>335</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -24175,33 +24175,33 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>157</v>
+        <v>335</v>
       </c>
       <c r="N524" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O524" t="n">
-        <v>657950.89</v>
+        <v>1172406.2</v>
       </c>
       <c r="P524" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q524" t="n">
-        <v>926300</v>
+        <v>2311500</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7367</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>6920240750098</v>
+        <v>6.9202407501356e+18</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>HELICPTERODIDACTICO EN BOLSA C7367</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -24215,7 +24215,7 @@
         </is>
       </c>
       <c r="J525" t="n">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24224,33 +24224,33 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="N525" t="n">
-        <v>3499.72</v>
+        <v>5347.88</v>
       </c>
       <c r="O525" t="n">
-        <v>1172406.2</v>
+        <v>1684582.2</v>
       </c>
       <c r="P525" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="Q525" t="n">
-        <v>2311500</v>
+        <v>2488500</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>C7367</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B526" t="n">
-        <v>6.9202407501356e+18</v>
+        <v>6920240750159</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>HELICPTERODIDACTICO EN BOLSA C7367</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -24264,7 +24264,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24273,38 +24273,35 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="N526" t="n">
-        <v>5347.88</v>
+        <v>4578.04</v>
       </c>
       <c r="O526" t="n">
-        <v>1684582.2</v>
+        <v>1318475.52</v>
       </c>
       <c r="P526" t="n">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="Q526" t="n">
-        <v>2488500</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B527" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -24313,7 +24310,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>288</v>
+        <v>2568</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24322,35 +24319,38 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>288</v>
+        <v>2568</v>
       </c>
       <c r="N527" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O527" t="n">
-        <v>1318475.52</v>
+        <v>1232640</v>
       </c>
       <c r="P527" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q527" t="n">
-        <v>2160000</v>
+        <v>1540800</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7400</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>6920240228207</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>GALLINA PONE HUEVOS CON LUZ Y SONIDO C7400/2282</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>2568</v>
+        <v>51</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24368,33 +24368,33 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>2568</v>
+        <v>51</v>
       </c>
       <c r="N528" t="n">
-        <v>480</v>
+        <v>10378.12</v>
       </c>
       <c r="O528" t="n">
-        <v>1232640</v>
+        <v>529284.12</v>
       </c>
       <c r="P528" t="n">
-        <v>600</v>
+        <v>13500</v>
       </c>
       <c r="Q528" t="n">
-        <v>1540800</v>
+        <v>688500</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>C7400</t>
+          <t>C7401</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>6920240228207</v>
+        <v>6920601877884</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>GALLINA PONE HUEVOS CON LUZ Y SONIDO C7400/2282</t>
+          <t>SONAJERO PANDERETA Y TROMPETA EN BOLSA C7401</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -24408,7 +24408,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24417,38 +24417,38 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="N529" t="n">
-        <v>10378.12</v>
+        <v>3828.03</v>
       </c>
       <c r="O529" t="n">
-        <v>529284.12</v>
+        <v>750293.88</v>
       </c>
       <c r="P529" t="n">
-        <v>13500</v>
+        <v>7500</v>
       </c>
       <c r="Q529" t="n">
-        <v>688500</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>C7401</t>
+          <t>C7409</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>6920601877884</v>
+        <v>6954446905013</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>SONAJERO PANDERETA Y TROMPETA EN BOLSA C7401</t>
+          <t>CARRO METALICO CAMARO 1/24 C7409</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -24457,7 +24457,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>196</v>
+        <v>16</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24466,33 +24466,33 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>196</v>
+        <v>16</v>
       </c>
       <c r="N530" t="n">
-        <v>3828.03</v>
+        <v>23229.8</v>
       </c>
       <c r="O530" t="n">
-        <v>750293.88</v>
+        <v>371676.8</v>
       </c>
       <c r="P530" t="n">
-        <v>7500</v>
+        <v>56000</v>
       </c>
       <c r="Q530" t="n">
-        <v>1470000</v>
+        <v>896000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>C7409</t>
+          <t>C7411</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>6954446905013</v>
+        <v>6954446905037</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CARRO METALICO CAMARO 1/24 C7409</t>
+          <t>CARRO METALICO TOYOTA 1/24 C7411</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24515,38 +24515,38 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="N531" t="n">
-        <v>23229.8</v>
+        <v>20983.74</v>
       </c>
       <c r="O531" t="n">
-        <v>371676.8</v>
+        <v>839349.6000000001</v>
       </c>
       <c r="P531" t="n">
-        <v>56000</v>
+        <v>65900</v>
       </c>
       <c r="Q531" t="n">
-        <v>896000</v>
+        <v>2636000</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>C7411</t>
+          <t>C7415</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>6954446905037</v>
+        <v>3400869890861</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CARRO METALICO TOYOTA 1/24 C7411</t>
+          <t>JUEGO MOLDEABLE DINOSAURIO EN TARRO C7415</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24564,47 +24564,42 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="N532" t="n">
-        <v>20983.74</v>
+        <v>2296.45</v>
       </c>
       <c r="O532" t="n">
-        <v>839349.6000000001</v>
+        <v>2296.45</v>
       </c>
       <c r="P532" t="n">
-        <v>65900</v>
+        <v>8900</v>
       </c>
       <c r="Q532" t="n">
-        <v>2636000</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>C7415</t>
+          <t>C743</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>3400869890861</v>
+        <v>8596162180329</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>JUEGO MOLDEABLE DINOSAURIO EN TARRO C7415</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO MENSAJE 10 STD</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J533" t="n">
-        <v>1</v>
+        <v>2950</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24613,42 +24608,44 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>1</v>
+        <v>2950</v>
       </c>
       <c r="N533" t="n">
-        <v>2296.45</v>
+        <v>286.61335546613</v>
       </c>
       <c r="O533" t="n">
-        <v>2296.45</v>
+        <v>845509.3986250834</v>
       </c>
       <c r="P533" t="n">
-        <v>8900</v>
+        <v>350</v>
       </c>
       <c r="Q533" t="n">
-        <v>8900</v>
+        <v>1032500</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>C743</t>
-        </is>
-      </c>
-      <c r="B534" t="n">
-        <v>8596162180329</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE 10 STD</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J534" t="n">
-        <v>2950</v>
+        <v>155</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24657,30 +24654,33 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>2950</v>
+        <v>155</v>
       </c>
       <c r="N534" t="n">
-        <v>286.61335546613</v>
+        <v>1554.12</v>
       </c>
       <c r="O534" t="n">
-        <v>845509.3986250834</v>
+        <v>240888.6</v>
       </c>
       <c r="P534" t="n">
-        <v>350</v>
+        <v>1900</v>
       </c>
       <c r="Q534" t="n">
-        <v>1032500</v>
+        <v>294500</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>C7437</t>
-        </is>
+          <t>C7443</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>6998799866621</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA PARA UÑAS C7437</t>
+          <t>COCINA EN CAJA LUZ Y SONIDO C7443</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -24694,7 +24694,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24703,35 +24703,38 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="N535" t="n">
-        <v>5876.81</v>
+        <v>12229.63</v>
       </c>
       <c r="O535" t="n">
-        <v>152797.06</v>
+        <v>73377.78</v>
       </c>
       <c r="P535" t="n">
-        <v>22900</v>
+        <v>49900</v>
       </c>
       <c r="Q535" t="n">
-        <v>595400</v>
+        <v>299400</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>C744-IO</t>
-        </is>
+          <t>C7448</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>1263626363211</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>CAMION JAULA C7448</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24740,7 +24743,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24749,47 +24752,42 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="N536" t="n">
-        <v>1554.12</v>
+        <v>10737.525609756</v>
       </c>
       <c r="O536" t="n">
-        <v>240888.6</v>
+        <v>182537.935365852</v>
       </c>
       <c r="P536" t="n">
-        <v>1900</v>
+        <v>18900</v>
       </c>
       <c r="Q536" t="n">
-        <v>294500</v>
+        <v>321300</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>C7443</t>
+          <t>C745</t>
         </is>
       </c>
       <c r="B537" t="n">
-        <v>6998799866621</v>
+        <v>8596162180343</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>COCINA EN CAJA LUZ Y SONIDO C7443</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J537" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24798,38 +24796,35 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="N537" t="n">
-        <v>12229.63</v>
+        <v>3097.9492241379</v>
       </c>
       <c r="O537" t="n">
-        <v>73377.78</v>
+        <v>405831.3483620649</v>
       </c>
       <c r="P537" t="n">
-        <v>49900</v>
+        <v>2400</v>
       </c>
       <c r="Q537" t="n">
-        <v>299400</v>
+        <v>314400</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>C7448</t>
-        </is>
-      </c>
-      <c r="B538" t="n">
-        <v>1263626363211</v>
+          <t>C7458</t>
+        </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CAMION JAULA C7448</t>
+          <t>COCINA EN CAJA C7458</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -24838,7 +24833,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24847,42 +24842,47 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N538" t="n">
-        <v>10737.525609756</v>
+        <v>36004.28</v>
       </c>
       <c r="O538" t="n">
-        <v>182537.935365852</v>
+        <v>396047.08</v>
       </c>
       <c r="P538" t="n">
-        <v>18900</v>
+        <v>83500</v>
       </c>
       <c r="Q538" t="n">
-        <v>321300</v>
+        <v>918500</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>C745</t>
+          <t>C7459</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>8596162180343</v>
+        <v>3790120020022</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
+          <t>PIANO MUSICAL LEONCITO C7459</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J539" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24891,30 +24891,30 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="N539" t="n">
-        <v>3097.9492241379</v>
+        <v>7258.5</v>
       </c>
       <c r="O539" t="n">
-        <v>405831.3483620649</v>
+        <v>65326.5</v>
       </c>
       <c r="P539" t="n">
-        <v>2400</v>
+        <v>17500</v>
       </c>
       <c r="Q539" t="n">
-        <v>314400</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>C7458</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>COCINA EN CAJA C7458</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -24928,7 +24928,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24937,38 +24937,35 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N540" t="n">
-        <v>36004.28</v>
+        <v>14751.820338983</v>
       </c>
       <c r="O540" t="n">
-        <v>396047.08</v>
+        <v>132766.383050847</v>
       </c>
       <c r="P540" t="n">
-        <v>83500</v>
+        <v>37100</v>
       </c>
       <c r="Q540" t="n">
-        <v>918500</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>C7459</t>
-        </is>
-      </c>
-      <c r="B541" t="n">
-        <v>3790120020022</v>
+          <t>C7463</t>
+        </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>PIANO MUSICAL LEONCITO C7459</t>
+          <t>DINOSAURIO C7463</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24977,7 +24974,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24986,35 +24983,35 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N541" t="n">
-        <v>7258.5</v>
+        <v>9372</v>
       </c>
       <c r="O541" t="n">
-        <v>65326.5</v>
+        <v>112464</v>
       </c>
       <c r="P541" t="n">
-        <v>17500</v>
+        <v>17900</v>
       </c>
       <c r="Q541" t="n">
-        <v>157500</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>C7462</t>
+          <t>C7470</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -25023,7 +25020,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -25032,35 +25029,38 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="N542" t="n">
-        <v>14751.820338983</v>
+        <v>14170.65</v>
       </c>
       <c r="O542" t="n">
-        <v>132766.383050847</v>
+        <v>340095.6</v>
       </c>
       <c r="P542" t="n">
-        <v>37100</v>
+        <v>49000</v>
       </c>
       <c r="Q542" t="n">
-        <v>333900</v>
+        <v>1176000</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>C7463</t>
-        </is>
+          <t>C7471</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>6973673170247</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>DINOSAURIO C7463</t>
+          <t>CARRO METALICO COLECCION TOYOTA PRADO C7471</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -25069,7 +25069,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -25078,30 +25078,33 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N543" t="n">
-        <v>9372</v>
+        <v>13168.16</v>
       </c>
       <c r="O543" t="n">
-        <v>112464</v>
+        <v>105345.28</v>
       </c>
       <c r="P543" t="n">
-        <v>17900</v>
+        <v>49000</v>
       </c>
       <c r="Q543" t="n">
-        <v>214800</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>C7470</t>
-        </is>
+          <t>C7473</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>6896896988512500</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
+          <t>CARRO METALICO COLECCIO TOYOTA MODEL C7473</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -25115,7 +25118,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -25124,33 +25127,33 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="N544" t="n">
-        <v>14170.65</v>
+        <v>10504.37</v>
       </c>
       <c r="O544" t="n">
-        <v>340095.6</v>
+        <v>546227.24</v>
       </c>
       <c r="P544" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q544" t="n">
-        <v>1176000</v>
+        <v>2340000</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>C7471</t>
+          <t>C7474</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>6973673170247</v>
+        <v>6896988512529</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION TOYOTA PRADO C7471</t>
+          <t>CARRO METALICO COLECCION CHELVI GT500 C7474</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -25164,7 +25167,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -25173,33 +25176,33 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N545" t="n">
-        <v>13168.16</v>
+        <v>9526.51</v>
       </c>
       <c r="O545" t="n">
-        <v>105345.28</v>
+        <v>304848.32</v>
       </c>
       <c r="P545" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q545" t="n">
-        <v>392000</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>C7473</t>
+          <t>C7475</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>6896896988512500</v>
+        <v>6896988512536</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCIO TOYOTA MODEL C7473</t>
+          <t>CARRO METALICO COLECCION BMW C7475</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -25213,7 +25216,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25222,33 +25225,30 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N546" t="n">
-        <v>10504.37</v>
+        <v>10798.03</v>
       </c>
       <c r="O546" t="n">
-        <v>546227.24</v>
+        <v>431921.2</v>
       </c>
       <c r="P546" t="n">
         <v>45000</v>
       </c>
       <c r="Q546" t="n">
-        <v>2340000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>C7474</t>
-        </is>
-      </c>
-      <c r="B547" t="n">
-        <v>6896988512529</v>
+          <t>C7479</t>
+        </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION CHELVI GT500 C7474</t>
+          <t>CARRO COLECCION METALICO MERCEDES C7479</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -25262,7 +25262,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25271,33 +25271,30 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="N547" t="n">
-        <v>9526.51</v>
+        <v>8473.91</v>
       </c>
       <c r="O547" t="n">
-        <v>304848.32</v>
+        <v>135582.56</v>
       </c>
       <c r="P547" t="n">
-        <v>45000</v>
+        <v>49000</v>
       </c>
       <c r="Q547" t="n">
-        <v>1440000</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>C7475</t>
-        </is>
-      </c>
-      <c r="B548" t="n">
-        <v>6896988512536</v>
+          <t>C7480</t>
+        </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7475</t>
+          <t>CARRO METALICO COLECCION BMW C7480</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -25311,7 +25308,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25320,30 +25317,30 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="N548" t="n">
-        <v>10798.03</v>
+        <v>10541.34</v>
       </c>
       <c r="O548" t="n">
-        <v>431921.2</v>
+        <v>168661.44</v>
       </c>
       <c r="P548" t="n">
-        <v>45000</v>
+        <v>49000</v>
       </c>
       <c r="Q548" t="n">
-        <v>1800000</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>C7479</t>
+          <t>C7481</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCEDES C7479</t>
+          <t>CARRO COLECCION METALICO AUDI A7 C7481</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -25357,7 +25354,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25366,30 +25363,30 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N549" t="n">
-        <v>8473.91</v>
+        <v>6006.77</v>
       </c>
       <c r="O549" t="n">
-        <v>135582.56</v>
+        <v>216243.72</v>
       </c>
       <c r="P549" t="n">
         <v>49000</v>
       </c>
       <c r="Q549" t="n">
-        <v>784000</v>
+        <v>1764000</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>C7480</t>
+          <t>C7482</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7480</t>
+          <t>CARRO METALICO COLECCION BMW C7482</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -25403,7 +25400,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25412,30 +25409,30 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N550" t="n">
-        <v>10541.34</v>
+        <v>7205.37</v>
       </c>
       <c r="O550" t="n">
-        <v>168661.44</v>
+        <v>86464.44</v>
       </c>
       <c r="P550" t="n">
         <v>49000</v>
       </c>
       <c r="Q550" t="n">
-        <v>784000</v>
+        <v>588000</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>C7481</t>
+          <t>C7483</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO AUDI A7 C7481</t>
+          <t>CARRO COLECCION METALICO TOYOTA C7483</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -25449,7 +25446,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25458,30 +25455,30 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="N551" t="n">
-        <v>6006.77</v>
+        <v>9031.370000000001</v>
       </c>
       <c r="O551" t="n">
-        <v>216243.72</v>
+        <v>72250.96000000001</v>
       </c>
       <c r="P551" t="n">
         <v>49000</v>
       </c>
       <c r="Q551" t="n">
-        <v>1764000</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>C7482</t>
+          <t>C7484</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7482</t>
+          <t>CARRO COLECCION METALICO MERCEDES AMG C7484</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -25495,7 +25492,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25504,30 +25501,30 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N552" t="n">
-        <v>7205.37</v>
+        <v>7884.67</v>
       </c>
       <c r="O552" t="n">
-        <v>86464.44</v>
+        <v>47308.02</v>
       </c>
       <c r="P552" t="n">
         <v>49000</v>
       </c>
       <c r="Q552" t="n">
-        <v>588000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>C7483</t>
+          <t>C7486</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO TOYOTA C7483</t>
+          <t>CARRO COLECCCION METALICO TESLA C7486</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -25541,7 +25538,7 @@
         </is>
       </c>
       <c r="J553" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25550,35 +25547,38 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N553" t="n">
-        <v>9031.370000000001</v>
+        <v>6529.54</v>
       </c>
       <c r="O553" t="n">
-        <v>72250.96000000001</v>
+        <v>261181.6</v>
       </c>
       <c r="P553" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q553" t="n">
-        <v>392000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>C7484</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCEDES AMG C7484</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25596,35 +25596,35 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="N554" t="n">
-        <v>7884.67</v>
+        <v>8919.16</v>
       </c>
       <c r="O554" t="n">
-        <v>47308.02</v>
+        <v>552987.92</v>
       </c>
       <c r="P554" t="n">
-        <v>49000</v>
+        <v>10000</v>
       </c>
       <c r="Q554" t="n">
-        <v>294000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>C7486</t>
+          <t>C7503</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>CARRO COLECCCION METALICO TESLA C7486</t>
+          <t>BOLSO ALAS CON ACCESORIOS DE BELLEZA C7503</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -25633,7 +25633,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25642,38 +25642,38 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="N555" t="n">
-        <v>6529.54</v>
+        <v>5216.9</v>
       </c>
       <c r="O555" t="n">
-        <v>261181.6</v>
+        <v>380833.7</v>
       </c>
       <c r="P555" t="n">
-        <v>45000</v>
+        <v>20500</v>
       </c>
       <c r="Q555" t="n">
-        <v>1800000</v>
+        <v>1496500</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>6945158254520</v>
+        <v>6905698382824</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -25682,7 +25682,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25691,30 +25691,33 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="N556" t="n">
-        <v>8919.16</v>
+        <v>1024.29</v>
       </c>
       <c r="O556" t="n">
-        <v>552987.92</v>
+        <v>158764.95</v>
       </c>
       <c r="P556" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q556" t="n">
-        <v>620000</v>
+        <v>449500</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>C7503</t>
-        </is>
+          <t>C7514</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>6905698386815</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>BOLSO ALAS CON ACCESORIOS DE BELLEZA C7503</t>
+          <t>SONAJERO LUZ BOLSA C7514</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -25728,7 +25731,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>73</v>
+        <v>664</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25737,33 +25740,33 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>73</v>
+        <v>664</v>
       </c>
       <c r="N557" t="n">
-        <v>5216.9</v>
+        <v>711.48</v>
       </c>
       <c r="O557" t="n">
-        <v>380833.7</v>
+        <v>472422.72</v>
       </c>
       <c r="P557" t="n">
-        <v>20500</v>
+        <v>2500</v>
       </c>
       <c r="Q557" t="n">
-        <v>1496500</v>
+        <v>1660000</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C7517</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>6905698382824</v>
+        <v>9872447770119</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
+          <t>SET HERRAMIENTA EN BOLSA C7517</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -25777,7 +25780,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25786,47 +25789,42 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="N558" t="n">
-        <v>1024.29</v>
+        <v>1278.27</v>
       </c>
       <c r="O558" t="n">
-        <v>158764.95</v>
+        <v>3834.81</v>
       </c>
       <c r="P558" t="n">
-        <v>2900</v>
+        <v>5900</v>
       </c>
       <c r="Q558" t="n">
-        <v>449500</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>C7514</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B559" t="n">
-        <v>6905698386815</v>
+        <v>8596162180497</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ BOLSA C7514</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J559" t="n">
-        <v>664</v>
+        <v>619</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25835,38 +25833,38 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>664</v>
+        <v>619</v>
       </c>
       <c r="N559" t="n">
-        <v>711.48</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O559" t="n">
-        <v>472422.72</v>
+        <v>720358.0180402457</v>
       </c>
       <c r="P559" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="Q559" t="n">
-        <v>1660000</v>
+        <v>928500</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>C7517</t>
+          <t>C7524</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>9872447770119</v>
+        <v>6905454130201</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>SET HERRAMIENTA EN BOLSA C7517</t>
+          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -25875,7 +25873,7 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>3</v>
+        <v>330</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
@@ -25884,42 +25882,47 @@
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>3</v>
+        <v>330</v>
       </c>
       <c r="N560" t="n">
-        <v>1278.27</v>
+        <v>1934.77</v>
       </c>
       <c r="O560" t="n">
-        <v>3834.81</v>
+        <v>638474.1</v>
       </c>
       <c r="P560" t="n">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="Q560" t="n">
-        <v>17700</v>
+        <v>2937000</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>8596162180497</v>
+        <v>6951241752002</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J561" t="n">
-        <v>619</v>
+        <v>1085</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25928,33 +25931,30 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>619</v>
+        <v>1085</v>
       </c>
       <c r="N561" t="n">
-        <v>1163.7447787403</v>
+        <v>7046.9398263512</v>
       </c>
       <c r="O561" t="n">
-        <v>720358.0180402457</v>
+        <v>7645929.711591052</v>
       </c>
       <c r="P561" t="n">
-        <v>1500</v>
+        <v>9900</v>
       </c>
       <c r="Q561" t="n">
-        <v>928500</v>
+        <v>10741500</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>C7524</t>
-        </is>
-      </c>
-      <c r="B562" t="n">
-        <v>6905454130201</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -25968,7 +25968,7 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>330</v>
+        <v>116</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
@@ -25977,38 +25977,38 @@
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>330</v>
+        <v>116</v>
       </c>
       <c r="N562" t="n">
-        <v>1934.77</v>
+        <v>24338.47</v>
       </c>
       <c r="O562" t="n">
-        <v>638474.1</v>
+        <v>2823262.52</v>
       </c>
       <c r="P562" t="n">
-        <v>8900</v>
+        <v>27900</v>
       </c>
       <c r="Q562" t="n">
-        <v>2937000</v>
+        <v>3236400</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>C7534</t>
+          <t>C7555-B</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>6951241752002</v>
+        <v>6970635795388</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -26017,7 +26017,7 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>1085</v>
+        <v>1</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -26026,35 +26026,35 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>1085</v>
+        <v>1</v>
       </c>
       <c r="N563" t="n">
-        <v>7046.9398263889</v>
+        <v>16146.498181818</v>
       </c>
       <c r="O563" t="n">
-        <v>7645929.711631957</v>
+        <v>16146.498181818</v>
       </c>
       <c r="P563" t="n">
-        <v>9900</v>
+        <v>26900</v>
       </c>
       <c r="Q563" t="n">
-        <v>10741500</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7561-AB</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -26063,7 +26063,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -26072,38 +26072,38 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="N564" t="n">
-        <v>24338.47</v>
+        <v>38508.28</v>
       </c>
       <c r="O564" t="n">
-        <v>2823262.52</v>
+        <v>924198.72</v>
       </c>
       <c r="P564" t="n">
-        <v>27900</v>
+        <v>40000</v>
       </c>
       <c r="Q564" t="n">
-        <v>3236400</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>C7555-B</t>
+          <t>C7586</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>6970635795388</v>
+        <v>7808880075865</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
+          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -26112,7 +26112,7 @@
         </is>
       </c>
       <c r="J565" t="n">
-        <v>1</v>
+        <v>648</v>
       </c>
       <c r="K565" t="n">
         <v>0</v>
@@ -26121,35 +26121,38 @@
         <v>0</v>
       </c>
       <c r="M565" t="n">
-        <v>1</v>
+        <v>648</v>
       </c>
       <c r="N565" t="n">
-        <v>16146.498181818</v>
+        <v>665.32402885111</v>
       </c>
       <c r="O565" t="n">
-        <v>16146.498181818</v>
+        <v>431129.9706955193</v>
       </c>
       <c r="P565" t="n">
-        <v>26900</v>
+        <v>2900</v>
       </c>
       <c r="Q565" t="n">
-        <v>26900</v>
+        <v>1879200</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>C7561-AB</t>
-        </is>
+          <t>C7587</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>7587228020247</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
+          <t>TROMPO LUCES DEPORTES C7587</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -26158,7 +26161,7 @@
         </is>
       </c>
       <c r="J566" t="n">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="K566" t="n">
         <v>0</v>
@@ -26167,33 +26170,33 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="N566" t="n">
-        <v>38508.28</v>
+        <v>1080.18</v>
       </c>
       <c r="O566" t="n">
-        <v>924198.72</v>
+        <v>276526.08</v>
       </c>
       <c r="P566" t="n">
-        <v>40000</v>
+        <v>4900</v>
       </c>
       <c r="Q566" t="n">
-        <v>960000</v>
+        <v>1254400</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>C7586</t>
+          <t>C7588</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>7808880075865</v>
+        <v>7588228020244</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -26207,7 +26210,7 @@
         </is>
       </c>
       <c r="J567" t="n">
-        <v>648</v>
+        <v>720</v>
       </c>
       <c r="K567" t="n">
         <v>0</v>
@@ -26216,38 +26219,38 @@
         <v>0</v>
       </c>
       <c r="M567" t="n">
-        <v>648</v>
+        <v>720</v>
       </c>
       <c r="N567" t="n">
-        <v>665.32402677652</v>
+        <v>641.78</v>
       </c>
       <c r="O567" t="n">
-        <v>431129.969351185</v>
+        <v>462081.6</v>
       </c>
       <c r="P567" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q567" t="n">
-        <v>1879200</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>C7587</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>7587228020247</v>
+        <v>6999899236093</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>TROMPO LUCES DEPORTES C7587</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -26256,7 +26259,7 @@
         </is>
       </c>
       <c r="J568" t="n">
-        <v>256</v>
+        <v>550</v>
       </c>
       <c r="K568" t="n">
         <v>0</v>
@@ -26265,38 +26268,38 @@
         <v>0</v>
       </c>
       <c r="M568" t="n">
-        <v>256</v>
+        <v>550</v>
       </c>
       <c r="N568" t="n">
-        <v>1080.18</v>
+        <v>7811.9</v>
       </c>
       <c r="O568" t="n">
-        <v>276526.08</v>
+        <v>4296545</v>
       </c>
       <c r="P568" t="n">
-        <v>4900</v>
+        <v>13900</v>
       </c>
       <c r="Q568" t="n">
-        <v>1254400</v>
+        <v>7645000</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7614</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>7588228020244</v>
+        <v>6999899236130</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>FLOTADOR DONA PATO C7614</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -26305,7 +26308,7 @@
         </is>
       </c>
       <c r="J569" t="n">
-        <v>720</v>
+        <v>50</v>
       </c>
       <c r="K569" t="n">
         <v>0</v>
@@ -26314,38 +26317,38 @@
         <v>0</v>
       </c>
       <c r="M569" t="n">
-        <v>720</v>
+        <v>50</v>
       </c>
       <c r="N569" t="n">
-        <v>641.78</v>
+        <v>4581.84</v>
       </c>
       <c r="O569" t="n">
-        <v>462081.6</v>
+        <v>229092</v>
       </c>
       <c r="P569" t="n">
-        <v>2500</v>
+        <v>7900</v>
       </c>
       <c r="Q569" t="n">
-        <v>1800000</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -26354,7 +26357,7 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>550</v>
+        <v>177</v>
       </c>
       <c r="K570" t="n">
         <v>0</v>
@@ -26363,33 +26366,30 @@
         <v>0</v>
       </c>
       <c r="M570" t="n">
-        <v>550</v>
+        <v>177</v>
       </c>
       <c r="N570" t="n">
-        <v>7811.9</v>
+        <v>3155</v>
       </c>
       <c r="O570" t="n">
-        <v>4296545</v>
+        <v>558435</v>
       </c>
       <c r="P570" t="n">
-        <v>13900</v>
+        <v>5900</v>
       </c>
       <c r="Q570" t="n">
-        <v>7645000</v>
+        <v>1044300</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>C7614</t>
-        </is>
-      </c>
-      <c r="B571" t="n">
-        <v>6999899236130</v>
+          <t>C7615</t>
+        </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA PATO C7614</t>
+          <t>CHALECO PISCINA ALITAS C7615</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -26403,7 +26403,7 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="K571" t="n">
         <v>0</v>
@@ -26412,38 +26412,38 @@
         <v>0</v>
       </c>
       <c r="M571" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="N571" t="n">
-        <v>4581.84</v>
+        <v>1262.07</v>
       </c>
       <c r="O571" t="n">
-        <v>229092</v>
+        <v>277655.4</v>
       </c>
       <c r="P571" t="n">
-        <v>7900</v>
+        <v>8900</v>
       </c>
       <c r="Q571" t="n">
-        <v>395000</v>
+        <v>1958000</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C7617</t>
         </is>
       </c>
       <c r="B572" t="n">
-        <v>6999899236130</v>
+        <v>6999899236192</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
+          <t>BRAZITOS PISCINA #A 12PCS</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -26452,7 +26452,7 @@
         </is>
       </c>
       <c r="J572" t="n">
-        <v>177</v>
+        <v>12</v>
       </c>
       <c r="K572" t="n">
         <v>0</v>
@@ -26461,30 +26461,33 @@
         <v>0</v>
       </c>
       <c r="M572" t="n">
-        <v>177</v>
+        <v>12</v>
       </c>
       <c r="N572" t="n">
-        <v>3155</v>
+        <v>540.40123762376</v>
       </c>
       <c r="O572" t="n">
-        <v>558435</v>
+        <v>6484.81485148512</v>
       </c>
       <c r="P572" t="n">
-        <v>5900</v>
+        <v>2500</v>
       </c>
       <c r="Q572" t="n">
-        <v>1044300</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>C7615</t>
-        </is>
+          <t>C7618</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>6999899236208</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>CHALECO PISCINA ALITAS C7615</t>
+          <t>BRAZITO PISCINA  27X17 C7618</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -26498,7 +26501,7 @@
         </is>
       </c>
       <c r="J573" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="K573" t="n">
         <v>0</v>
@@ -26507,33 +26510,33 @@
         <v>0</v>
       </c>
       <c r="M573" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="N573" t="n">
-        <v>1262.07</v>
+        <v>616.4</v>
       </c>
       <c r="O573" t="n">
-        <v>277655.4</v>
+        <v>616.4</v>
       </c>
       <c r="P573" t="n">
-        <v>8900</v>
+        <v>2900</v>
       </c>
       <c r="Q573" t="n">
-        <v>1958000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>C7617</t>
+          <t>C7631</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>6999899236192</v>
+        <v>6999899236352</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>BRAZITOS PISCINA #A 12PCS</t>
+          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -26547,7 +26550,7 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="K574" t="n">
         <v>0</v>
@@ -26556,47 +26559,39 @@
         <v>0</v>
       </c>
       <c r="M574" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="N574" t="n">
-        <v>540.40123152709</v>
+        <v>315.02745788668</v>
       </c>
       <c r="O574" t="n">
-        <v>6484.81477832508</v>
+        <v>29927.6084992346</v>
       </c>
       <c r="P574" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="Q574" t="n">
-        <v>30000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>C7618</t>
-        </is>
-      </c>
-      <c r="B575" t="n">
-        <v>6999899236208</v>
+          <t>C766</t>
+        </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>BRAZITO PISCINA  27X17 C7618</t>
-        </is>
-      </c>
-      <c r="E575" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>DOMIN PEQUEO</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J575" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K575" t="n">
         <v>0</v>
@@ -26605,47 +26600,39 @@
         <v>0</v>
       </c>
       <c r="M575" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N575" t="n">
-        <v>616.4</v>
+        <v>2752.52</v>
       </c>
       <c r="O575" t="n">
-        <v>616.4</v>
+        <v>38535.28</v>
       </c>
       <c r="P575" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="Q575" t="n">
-        <v>2900</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>C7631</t>
-        </is>
-      </c>
-      <c r="B576" t="n">
-        <v>6999899236352</v>
+          <t>C771</t>
+        </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO LOVE YOU</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J576" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="K576" t="n">
         <v>0</v>
@@ -26654,30 +26641,33 @@
         <v>0</v>
       </c>
       <c r="M576" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="N576" t="n">
-        <v>315.02745788668</v>
+        <v>1244.5992565056</v>
       </c>
       <c r="O576" t="n">
-        <v>29927.6084992346</v>
+        <v>88366.54721189759</v>
       </c>
       <c r="P576" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="Q576" t="n">
-        <v>209000</v>
+        <v>106500</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>C766</t>
-        </is>
+          <t>C773</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>2021071411128</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>DOMIN PEQUEO</t>
+          <t>GLOBO HBD 32</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -26686,7 +26676,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -26695,39 +26685,47 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="N577" t="n">
-        <v>2752.52</v>
+        <v>2703.2000014451</v>
       </c>
       <c r="O577" t="n">
-        <v>38535.28</v>
+        <v>113534.4000606942</v>
       </c>
       <c r="P577" t="n">
         <v>4500</v>
       </c>
       <c r="Q577" t="n">
-        <v>63000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>C771</t>
-        </is>
+          <t>C80-IO</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>6524521011221</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>GLOBO LOVE YOU</t>
+          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J578" t="n">
-        <v>71</v>
+        <v>311</v>
       </c>
       <c r="K578" t="n">
         <v>0</v>
@@ -26736,33 +26734,30 @@
         <v>0</v>
       </c>
       <c r="M578" t="n">
-        <v>71</v>
+        <v>311</v>
       </c>
       <c r="N578" t="n">
-        <v>1244.5992565056</v>
+        <v>2235.19</v>
       </c>
       <c r="O578" t="n">
-        <v>88366.54721189759</v>
+        <v>695144.09</v>
       </c>
       <c r="P578" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="Q578" t="n">
-        <v>106500</v>
+        <v>933000</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>C773</t>
-        </is>
-      </c>
-      <c r="B579" t="n">
-        <v>2021071411128</v>
+          <t>C815</t>
+        </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>GLOBO HBD 32</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -26771,7 +26766,7 @@
         </is>
       </c>
       <c r="J579" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K579" t="n">
         <v>0</v>
@@ -26780,47 +26775,42 @@
         <v>0</v>
       </c>
       <c r="M579" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="N579" t="n">
-        <v>2703.2000014451</v>
+        <v>110520.77</v>
       </c>
       <c r="O579" t="n">
-        <v>113534.4000606942</v>
+        <v>1989373.86</v>
       </c>
       <c r="P579" t="n">
-        <v>4500</v>
+        <v>176900</v>
       </c>
       <c r="Q579" t="n">
-        <v>189000</v>
+        <v>3184200</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>C80-IO</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>6524521011221</v>
+        <v>2087202108190</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
-        </is>
-      </c>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J580" t="n">
-        <v>311</v>
+        <v>600</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
@@ -26829,30 +26819,30 @@
         <v>0</v>
       </c>
       <c r="M580" t="n">
-        <v>311</v>
+        <v>600</v>
       </c>
       <c r="N580" t="n">
-        <v>2235.19</v>
+        <v>6761.25</v>
       </c>
       <c r="O580" t="n">
-        <v>695144.09</v>
+        <v>4056750</v>
       </c>
       <c r="P580" t="n">
-        <v>3000</v>
+        <v>5200</v>
       </c>
       <c r="Q580" t="n">
-        <v>933000</v>
+        <v>3120000</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>C815</t>
+          <t>C822</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -26861,7 +26851,7 @@
         </is>
       </c>
       <c r="J581" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K581" t="n">
         <v>0</v>
@@ -26870,33 +26860,33 @@
         <v>0</v>
       </c>
       <c r="M581" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="N581" t="n">
-        <v>110520.77</v>
+        <v>5577.2680373832</v>
       </c>
       <c r="O581" t="n">
-        <v>1989373.86</v>
+        <v>167318.041121496</v>
       </c>
       <c r="P581" t="n">
-        <v>176900</v>
+        <v>6500</v>
       </c>
       <c r="Q581" t="n">
-        <v>3184200</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C828</t>
         </is>
       </c>
       <c r="B582" t="n">
-        <v>2087202108190</v>
+        <v>6900159908285</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -26905,7 +26895,7 @@
         </is>
       </c>
       <c r="J582" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="K582" t="n">
         <v>0</v>
@@ -26914,30 +26904,33 @@
         <v>0</v>
       </c>
       <c r="M582" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="N582" t="n">
-        <v>6761.25</v>
+        <v>6243.3531884058</v>
       </c>
       <c r="O582" t="n">
-        <v>4056750</v>
+        <v>249734.127536232</v>
       </c>
       <c r="P582" t="n">
-        <v>5200</v>
+        <v>9900</v>
       </c>
       <c r="Q582" t="n">
-        <v>3120000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>C822</t>
-        </is>
+          <t>C848</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>6900159908483</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
+          <t>BLOBO GRANDE SORPRESA NINONINA</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -26946,7 +26939,7 @@
         </is>
       </c>
       <c r="J583" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="K583" t="n">
         <v>0</v>
@@ -26955,33 +26948,30 @@
         <v>0</v>
       </c>
       <c r="M583" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N583" t="n">
-        <v>5577.2680373832</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O583" t="n">
-        <v>167318.041121496</v>
+        <v>224025.773659551</v>
       </c>
       <c r="P583" t="n">
-        <v>6500</v>
+        <v>3000</v>
       </c>
       <c r="Q583" t="n">
-        <v>195000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>C828</t>
-        </is>
-      </c>
-      <c r="B584" t="n">
-        <v>6900159908285</v>
+          <t>C855</t>
+        </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
+          <t>GLOBOS BUQUET CERVEZA</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -26990,7 +26980,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -26999,33 +26989,30 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N584" t="n">
-        <v>6243.3531884058</v>
+        <v>2129.8331743119</v>
       </c>
       <c r="O584" t="n">
-        <v>249734.127536232</v>
+        <v>42596.663486238</v>
       </c>
       <c r="P584" t="n">
-        <v>9900</v>
+        <v>2700</v>
       </c>
       <c r="Q584" t="n">
-        <v>396000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>C848</t>
-        </is>
-      </c>
-      <c r="B585" t="n">
-        <v>6900159908483</v>
+          <t>C863</t>
+        </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>BLOBO GRANDE SORPRESA NINONINA</t>
+          <t>GLOBOS BOUQUET FELIZ DIA</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -27034,7 +27021,7 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
@@ -27043,30 +27030,30 @@
         <v>0</v>
       </c>
       <c r="M585" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="N585" t="n">
-        <v>2489.1752628839</v>
+        <v>5497.1752906977</v>
       </c>
       <c r="O585" t="n">
-        <v>224025.773659551</v>
+        <v>27485.8764534885</v>
       </c>
       <c r="P585" t="n">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="Q585" t="n">
-        <v>270000</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>C855</t>
+          <t>C866</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>GLOBOS BUQUET CERVEZA</t>
+          <t>YOYO SURTIDO</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -27075,7 +27062,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>20</v>
+        <v>1178</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -27084,30 +27071,33 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>20</v>
+        <v>1178</v>
       </c>
       <c r="N586" t="n">
-        <v>2129.8331743119</v>
+        <v>1176.57</v>
       </c>
       <c r="O586" t="n">
-        <v>42596.663486238</v>
+        <v>1385999.46</v>
       </c>
       <c r="P586" t="n">
-        <v>2700</v>
+        <v>1900</v>
       </c>
       <c r="Q586" t="n">
-        <v>54000</v>
+        <v>2238200</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>C863</t>
-        </is>
+          <t>C887</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>6920210213929</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET FELIZ DIA</t>
+          <t>BALON FOOTBALL SURTIDO #2</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -27116,7 +27106,7 @@
         </is>
       </c>
       <c r="J587" t="n">
-        <v>5</v>
+        <v>553</v>
       </c>
       <c r="K587" t="n">
         <v>0</v>
@@ -27125,30 +27115,30 @@
         <v>0</v>
       </c>
       <c r="M587" t="n">
-        <v>5</v>
+        <v>553</v>
       </c>
       <c r="N587" t="n">
-        <v>5497.1752906977</v>
+        <v>3181.9</v>
       </c>
       <c r="O587" t="n">
-        <v>27485.8764534885</v>
+        <v>1759590.7</v>
       </c>
       <c r="P587" t="n">
-        <v>6500</v>
+        <v>5100</v>
       </c>
       <c r="Q587" t="n">
-        <v>32500</v>
+        <v>2820300</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>C866</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>YOYO SURTIDO</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -27157,7 +27147,7 @@
         </is>
       </c>
       <c r="J588" t="n">
-        <v>1178</v>
+        <v>4</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
@@ -27166,33 +27156,33 @@
         <v>0</v>
       </c>
       <c r="M588" t="n">
-        <v>1178</v>
+        <v>4</v>
       </c>
       <c r="N588" t="n">
-        <v>1176.57</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O588" t="n">
-        <v>1385999.46</v>
+        <v>4854.7285603112</v>
       </c>
       <c r="P588" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q588" t="n">
-        <v>2238200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>C887</t>
+          <t>C890</t>
         </is>
       </c>
       <c r="B589" t="n">
-        <v>6920210213929</v>
+        <v>6913545113699</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>BALON FOOTBALL SURTIDO #2</t>
+          <t>CORTINA FEST</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -27201,7 +27191,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>553</v>
+        <v>450</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -27210,30 +27200,33 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>553</v>
+        <v>450</v>
       </c>
       <c r="N589" t="n">
-        <v>3181.9</v>
+        <v>1794.2879512478</v>
       </c>
       <c r="O589" t="n">
-        <v>1759590.7</v>
+        <v>807429.57806151</v>
       </c>
       <c r="P589" t="n">
-        <v>5100</v>
+        <v>1600</v>
       </c>
       <c r="Q589" t="n">
-        <v>2820300</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>C888</t>
-        </is>
+          <t>C895</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>6913545115815</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>CORTINA FESTIN TORNASOL</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -27242,7 +27235,7 @@
         </is>
       </c>
       <c r="J590" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="K590" t="n">
         <v>0</v>
@@ -27251,33 +27244,33 @@
         <v>0</v>
       </c>
       <c r="M590" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="N590" t="n">
-        <v>1213.6821400778</v>
+        <v>2830.2252424242</v>
       </c>
       <c r="O590" t="n">
-        <v>4854.7285603112</v>
+        <v>124529.9106666648</v>
       </c>
       <c r="P590" t="n">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="Q590" t="n">
-        <v>6000</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>C890</t>
+          <t>C899</t>
         </is>
       </c>
       <c r="B591" t="n">
-        <v>6913545113699</v>
+        <v>6920202108998</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>CORTINA FEST</t>
+          <t>GLOBO BOUQUET ARCO GRANDE</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -27286,7 +27279,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>450</v>
+        <v>28</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -27295,33 +27288,33 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>450</v>
+        <v>28</v>
       </c>
       <c r="N591" t="n">
-        <v>1794.2879512478</v>
+        <v>15219.155119048</v>
       </c>
       <c r="O591" t="n">
-        <v>807429.57806151</v>
+        <v>426136.343333344</v>
       </c>
       <c r="P591" t="n">
-        <v>1600</v>
+        <v>16000</v>
       </c>
       <c r="Q591" t="n">
-        <v>720000</v>
+        <v>448000</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>C895</t>
+          <t>C91</t>
         </is>
       </c>
       <c r="B592" t="n">
-        <v>6913545115815</v>
+        <v>6803012120018</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>CORTINA FESTIN TORNASOL</t>
+          <t>GLOBO BOUQUET SURTIDO</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -27330,7 +27323,7 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
@@ -27339,42 +27332,47 @@
         <v>0</v>
       </c>
       <c r="M592" t="n">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="N592" t="n">
-        <v>2830.2252424242</v>
+        <v>2523.3377277904</v>
       </c>
       <c r="O592" t="n">
-        <v>124529.9106666648</v>
+        <v>479434.168280176</v>
       </c>
       <c r="P592" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="Q592" t="n">
-        <v>105600</v>
+        <v>532000</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>C899</t>
+          <t>C91-IO</t>
         </is>
       </c>
       <c r="B593" t="n">
-        <v>6920202108998</v>
+        <v>6524521011108</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET ARCO GRANDE</t>
+          <t>GLOBO BOUQUET X 7 MAS BASE 2021-17</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J593" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
@@ -27383,33 +27381,33 @@
         <v>0</v>
       </c>
       <c r="M593" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="N593" t="n">
-        <v>15219.155119048</v>
+        <v>4648.51</v>
       </c>
       <c r="O593" t="n">
-        <v>426136.343333344</v>
+        <v>278910.6</v>
       </c>
       <c r="P593" t="n">
-        <v>16000</v>
+        <v>5500</v>
       </c>
       <c r="Q593" t="n">
-        <v>448000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>C91</t>
+          <t>C913</t>
         </is>
       </c>
       <c r="B594" t="n">
-        <v>6803012120018</v>
+        <v>6920210204279</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET SURTIDO</t>
+          <t>BLISTER HERRAMIENTAS DINO</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -27418,7 +27416,7 @@
         </is>
       </c>
       <c r="J594" t="n">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="K594" t="n">
         <v>0</v>
@@ -27427,33 +27425,30 @@
         <v>0</v>
       </c>
       <c r="M594" t="n">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="N594" t="n">
-        <v>2523.3377277904</v>
+        <v>8922.2155844156</v>
       </c>
       <c r="O594" t="n">
-        <v>479434.168280176</v>
+        <v>428266.3480519488</v>
       </c>
       <c r="P594" t="n">
-        <v>2800</v>
+        <v>8200</v>
       </c>
       <c r="Q594" t="n">
-        <v>532000</v>
+        <v>393600</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>C91-IO</t>
-        </is>
-      </c>
-      <c r="B595" t="n">
-        <v>6524521011108</v>
+          <t>C92-IO</t>
+        </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 7 MAS BASE 2021-17</t>
+          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -27467,7 +27462,7 @@
         </is>
       </c>
       <c r="J595" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="K595" t="n">
         <v>0</v>
@@ -27476,33 +27471,33 @@
         <v>0</v>
       </c>
       <c r="M595" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="N595" t="n">
-        <v>4648.51</v>
+        <v>1520</v>
       </c>
       <c r="O595" t="n">
-        <v>278910.6</v>
+        <v>167200</v>
       </c>
       <c r="P595" t="n">
-        <v>5500</v>
+        <v>1900</v>
       </c>
       <c r="Q595" t="n">
-        <v>330000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>C913</t>
+          <t>C928</t>
         </is>
       </c>
       <c r="B596" t="n">
-        <v>6920210204279</v>
+        <v>6920202109285</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>BLISTER HERRAMIENTAS DINO</t>
+          <t>GLOBO BOUQUET COLA SIRENA</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -27511,7 +27506,7 @@
         </is>
       </c>
       <c r="J596" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K596" t="n">
         <v>0</v>
@@ -27520,44 +27515,42 @@
         <v>0</v>
       </c>
       <c r="M596" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="N596" t="n">
-        <v>8922.2155844156</v>
+        <v>12251</v>
       </c>
       <c r="O596" t="n">
-        <v>428266.3480519488</v>
+        <v>343028</v>
       </c>
       <c r="P596" t="n">
-        <v>8200</v>
+        <v>13000</v>
       </c>
       <c r="Q596" t="n">
-        <v>393600</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>C92-IO</t>
-        </is>
+          <t>C935</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>6920202109353</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO BOUQUET</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J597" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K597" t="n">
         <v>0</v>
@@ -27566,33 +27559,35 @@
         <v>0</v>
       </c>
       <c r="M597" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="N597" t="n">
-        <v>1520</v>
+        <v>3683.6327464789</v>
       </c>
       <c r="O597" t="n">
-        <v>167200</v>
+        <v>368363.27464789</v>
       </c>
       <c r="P597" t="n">
-        <v>1900</v>
+        <v>3600</v>
       </c>
       <c r="Q597" t="n">
-        <v>209000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>C928</t>
-        </is>
-      </c>
-      <c r="B598" t="n">
-        <v>6920202109285</v>
+          <t>C943</t>
+        </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET COLA SIRENA</t>
+          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -27601,7 +27596,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -27610,33 +27605,35 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="N598" t="n">
-        <v>12251</v>
+        <v>22951.704647137</v>
       </c>
       <c r="O598" t="n">
-        <v>343028</v>
+        <v>7459304.010319525</v>
       </c>
       <c r="P598" t="n">
-        <v>13000</v>
+        <v>37900</v>
       </c>
       <c r="Q598" t="n">
-        <v>364000</v>
+        <v>12317500</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>C935</t>
-        </is>
-      </c>
-      <c r="B599" t="n">
-        <v>6920202109353</v>
+          <t>C984</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>CG2016531</t>
+        </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET</t>
+          <t>TANGRAM</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -27645,7 +27642,7 @@
         </is>
       </c>
       <c r="J599" t="n">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="K599" t="n">
         <v>0</v>
@@ -27654,35 +27651,30 @@
         <v>0</v>
       </c>
       <c r="M599" t="n">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="N599" t="n">
-        <v>3683.6327464789</v>
+        <v>705.52795348837</v>
       </c>
       <c r="O599" t="n">
-        <v>368363.27464789</v>
+        <v>121350.8079999996</v>
       </c>
       <c r="P599" t="n">
-        <v>3600</v>
+        <v>1500</v>
       </c>
       <c r="Q599" t="n">
-        <v>360000</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>C943</t>
+          <t>C99</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
-        </is>
-      </c>
-      <c r="E600" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -27691,7 +27683,7 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>325</v>
+        <v>38</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
@@ -27700,44 +27692,49 @@
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>325</v>
+        <v>38</v>
       </c>
       <c r="N600" t="n">
-        <v>22951.704654255</v>
+        <v>4985.4083333333</v>
       </c>
       <c r="O600" t="n">
-        <v>7459304.012632876</v>
+        <v>189445.5166666654</v>
       </c>
       <c r="P600" t="n">
-        <v>37900</v>
+        <v>7900</v>
       </c>
       <c r="Q600" t="n">
-        <v>12317500</v>
+        <v>300200</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>C984</t>
+          <t>CA1673</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>CG2016531</t>
+          <t>CA11673</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>TANGRAM</t>
+          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J601" t="n">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="K601" t="n">
         <v>0</v>
@@ -27746,39 +27743,49 @@
         <v>0</v>
       </c>
       <c r="M601" t="n">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="N601" t="n">
-        <v>705.52796610169</v>
+        <v>1547.8828813559</v>
       </c>
       <c r="O601" t="n">
-        <v>121350.8101694907</v>
+        <v>3095.7657627118</v>
       </c>
       <c r="P601" t="n">
-        <v>1500</v>
+        <v>5500</v>
       </c>
       <c r="Q601" t="n">
-        <v>258000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>CA886</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>CA886</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
+          <t>ANIMAL TAMBOR  CERDITO CA886</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J602" t="n">
-        <v>38</v>
+        <v>289</v>
       </c>
       <c r="K602" t="n">
         <v>0</v>
@@ -27787,40 +27794,35 @@
         <v>0</v>
       </c>
       <c r="M602" t="n">
-        <v>38</v>
+        <v>289</v>
       </c>
       <c r="N602" t="n">
-        <v>4985.4075471698</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O602" t="n">
-        <v>189445.4867924524</v>
+        <v>507865.6637163752</v>
       </c>
       <c r="P602" t="n">
-        <v>7900</v>
+        <v>2000</v>
       </c>
       <c r="Q602" t="n">
-        <v>300200</v>
+        <v>578000</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>CA1673</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>CA11673</t>
+          <t>CA891</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+          <t>MUÑECA TAMBOR CA891</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -27829,7 +27831,7 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
@@ -27838,40 +27840,35 @@
         <v>0</v>
       </c>
       <c r="M603" t="n">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="N603" t="n">
-        <v>1547.8828813559</v>
+        <v>1561.33</v>
       </c>
       <c r="O603" t="n">
-        <v>3095.7657627118</v>
+        <v>518361.56</v>
       </c>
       <c r="P603" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="Q603" t="n">
-        <v>11000</v>
+        <v>664000</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>CA886</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>CA886</t>
+          <t>DPB087</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>ANIMAL TAMBOR  CERDITO CA886</t>
+          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -27880,7 +27877,7 @@
         </is>
       </c>
       <c r="J604" t="n">
-        <v>289</v>
+        <v>10</v>
       </c>
       <c r="K604" t="n">
         <v>0</v>
@@ -27889,35 +27886,35 @@
         <v>0</v>
       </c>
       <c r="M604" t="n">
-        <v>289</v>
+        <v>10</v>
       </c>
       <c r="N604" t="n">
-        <v>1757.3206356968</v>
+        <v>13520</v>
       </c>
       <c r="O604" t="n">
-        <v>507865.6637163752</v>
+        <v>135200</v>
       </c>
       <c r="P604" t="n">
-        <v>2000</v>
+        <v>16900</v>
       </c>
       <c r="Q604" t="n">
-        <v>578000</v>
+        <v>169000</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>CA891</t>
+          <t>DV052</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>MUÑECA TAMBOR CA891</t>
+          <t>PELOTA PISCINA DV052</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -27926,7 +27923,7 @@
         </is>
       </c>
       <c r="J605" t="n">
-        <v>332</v>
+        <v>1700</v>
       </c>
       <c r="K605" t="n">
         <v>0</v>
@@ -27935,35 +27932,35 @@
         <v>0</v>
       </c>
       <c r="M605" t="n">
-        <v>332</v>
+        <v>1700</v>
       </c>
       <c r="N605" t="n">
-        <v>1561.33</v>
+        <v>219.99816658071</v>
       </c>
       <c r="O605" t="n">
-        <v>518361.56</v>
+        <v>373996.883187207</v>
       </c>
       <c r="P605" t="n">
-        <v>2000</v>
+        <v>260</v>
       </c>
       <c r="Q605" t="n">
-        <v>664000</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>DPB087</t>
+          <t>FG021</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
+          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -27984,32 +27981,32 @@
         <v>10</v>
       </c>
       <c r="N606" t="n">
-        <v>13520</v>
+        <v>3504.16</v>
       </c>
       <c r="O606" t="n">
-        <v>135200</v>
+        <v>35041.6</v>
       </c>
       <c r="P606" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q606" t="n">
-        <v>169000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>DV052</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DV052</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -28018,7 +28015,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>1700</v>
+        <v>76</v>
       </c>
       <c r="K607" t="n">
         <v>0</v>
@@ -28027,35 +28024,35 @@
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>1700</v>
+        <v>76</v>
       </c>
       <c r="N607" t="n">
-        <v>219.99816658071</v>
+        <v>13493.858287462</v>
       </c>
       <c r="O607" t="n">
-        <v>373996.883187207</v>
+        <v>1025533.229847112</v>
       </c>
       <c r="P607" t="n">
-        <v>260</v>
+        <v>16900</v>
       </c>
       <c r="Q607" t="n">
-        <v>442000</v>
+        <v>1284400</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>FG021</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -28064,7 +28061,7 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>10</v>
+        <v>439</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
@@ -28073,35 +28070,35 @@
         <v>0</v>
       </c>
       <c r="M608" t="n">
-        <v>10</v>
+        <v>439</v>
       </c>
       <c r="N608" t="n">
-        <v>3504.16</v>
+        <v>2644.9</v>
       </c>
       <c r="O608" t="n">
-        <v>35041.6</v>
+        <v>1161111.1</v>
       </c>
       <c r="P608" t="n">
         <v>3900</v>
       </c>
       <c r="Q608" t="n">
-        <v>39000</v>
+        <v>1712100</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG042</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>BURBUJERO PANDA BLISTER 43043</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -28110,7 +28107,7 @@
         </is>
       </c>
       <c r="J609" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="K609" t="n">
         <v>0</v>
@@ -28119,35 +28116,35 @@
         <v>0</v>
       </c>
       <c r="M609" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="N609" t="n">
-        <v>13493.858292683</v>
+        <v>14576.2</v>
       </c>
       <c r="O609" t="n">
-        <v>1025533.230243908</v>
+        <v>102033.4</v>
       </c>
       <c r="P609" t="n">
-        <v>16900</v>
+        <v>19000</v>
       </c>
       <c r="Q609" t="n">
-        <v>1284400</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -28156,7 +28153,7 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>439</v>
+        <v>351</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
@@ -28165,35 +28162,35 @@
         <v>0</v>
       </c>
       <c r="M610" t="n">
-        <v>439</v>
+        <v>351</v>
       </c>
       <c r="N610" t="n">
-        <v>2644.9</v>
+        <v>1952.66</v>
       </c>
       <c r="O610" t="n">
-        <v>1161111.1</v>
+        <v>685383.66</v>
       </c>
       <c r="P610" t="n">
-        <v>3900</v>
+        <v>3500</v>
       </c>
       <c r="Q610" t="n">
-        <v>1712100</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>FG042</t>
+          <t>FG050</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>BURBUJERO PANDA BLISTER 43043</t>
+          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -28214,32 +28211,32 @@
         <v>7</v>
       </c>
       <c r="N611" t="n">
-        <v>14576.2</v>
+        <v>9708.190000000001</v>
       </c>
       <c r="O611" t="n">
-        <v>102033.4</v>
+        <v>67957.33</v>
       </c>
       <c r="P611" t="n">
-        <v>19000</v>
+        <v>10200</v>
       </c>
       <c r="Q611" t="n">
-        <v>133000</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG057</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>ABACO BOLSA 8022</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -28248,7 +28245,7 @@
         </is>
       </c>
       <c r="J612" t="n">
-        <v>351</v>
+        <v>232</v>
       </c>
       <c r="K612" t="n">
         <v>0</v>
@@ -28257,35 +28254,35 @@
         <v>0</v>
       </c>
       <c r="M612" t="n">
-        <v>351</v>
+        <v>232</v>
       </c>
       <c r="N612" t="n">
-        <v>1952.66</v>
+        <v>2293.26</v>
       </c>
       <c r="O612" t="n">
-        <v>685383.66</v>
+        <v>532036.3200000001</v>
       </c>
       <c r="P612" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="Q612" t="n">
-        <v>1228500</v>
+        <v>1113600</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>FG050</t>
+          <t>FG083</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
+          <t>SONAJERO BOLSA RANA XZM5XS</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -28294,7 +28291,7 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="K613" t="n">
         <v>0</v>
@@ -28303,35 +28300,35 @@
         <v>0</v>
       </c>
       <c r="M613" t="n">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="N613" t="n">
-        <v>9708.190000000001</v>
+        <v>1952.41</v>
       </c>
       <c r="O613" t="n">
-        <v>67957.33</v>
+        <v>310433.19</v>
       </c>
       <c r="P613" t="n">
-        <v>10200</v>
+        <v>2700</v>
       </c>
       <c r="Q613" t="n">
-        <v>71400</v>
+        <v>429300</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>FG057</t>
+          <t>FG092</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>ABACO BOLSA 8022</t>
+          <t>BLISTER  TETERA SJ377-1</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -28340,7 +28337,7 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="K614" t="n">
         <v>0</v>
@@ -28349,35 +28346,35 @@
         <v>0</v>
       </c>
       <c r="M614" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="N614" t="n">
-        <v>2293.26</v>
+        <v>9855.038</v>
       </c>
       <c r="O614" t="n">
-        <v>532036.3200000001</v>
+        <v>9855.038</v>
       </c>
       <c r="P614" t="n">
-        <v>4800</v>
+        <v>15500</v>
       </c>
       <c r="Q614" t="n">
-        <v>1113600</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>FG083</t>
+          <t>FG097</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA RANA XZM5XS</t>
+          <t>MUÑECO ROBOT BLISTER 5090B</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -28386,7 +28383,7 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
@@ -28395,35 +28392,35 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="N615" t="n">
-        <v>1952.41</v>
+        <v>17986.24</v>
       </c>
       <c r="O615" t="n">
-        <v>310433.19</v>
+        <v>1438899.2</v>
       </c>
       <c r="P615" t="n">
-        <v>2700</v>
+        <v>18500</v>
       </c>
       <c r="Q615" t="n">
-        <v>429300</v>
+        <v>1480000</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>FG092</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>BLISTER  TETERA SJ377-1</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -28432,7 +28429,7 @@
         </is>
       </c>
       <c r="J616" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K616" t="n">
         <v>0</v>
@@ -28441,35 +28438,35 @@
         <v>0</v>
       </c>
       <c r="M616" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="N616" t="n">
-        <v>9855.038</v>
+        <v>7480</v>
       </c>
       <c r="O616" t="n">
-        <v>9855.038</v>
+        <v>269280</v>
       </c>
       <c r="P616" t="n">
-        <v>15500</v>
+        <v>9500</v>
       </c>
       <c r="Q616" t="n">
-        <v>15500</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>FG097</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>MUÑECO ROBOT BLISTER 5090B</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -28478,7 +28475,7 @@
         </is>
       </c>
       <c r="J617" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="K617" t="n">
         <v>0</v>
@@ -28487,30 +28484,30 @@
         <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N617" t="n">
-        <v>17986.24</v>
+        <v>5280</v>
       </c>
       <c r="O617" t="n">
-        <v>1438899.2</v>
+        <v>242880</v>
       </c>
       <c r="P617" t="n">
-        <v>18500</v>
+        <v>6900</v>
       </c>
       <c r="Q617" t="n">
-        <v>1480000</v>
+        <v>317400</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -28524,7 +28521,7 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="K618" t="n">
         <v>0</v>
@@ -28533,30 +28530,33 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="N618" t="n">
-        <v>7480</v>
+        <v>5280</v>
       </c>
       <c r="O618" t="n">
-        <v>269280</v>
+        <v>469920</v>
       </c>
       <c r="P618" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="Q618" t="n">
-        <v>342000</v>
+        <v>614100</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>J-1316</t>
-        </is>
+          <t>J-1386</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
+          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -28570,7 +28570,7 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
@@ -28579,30 +28579,30 @@
         <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="N619" t="n">
-        <v>5280</v>
+        <v>7920</v>
       </c>
       <c r="O619" t="n">
-        <v>242880</v>
+        <v>427680</v>
       </c>
       <c r="P619" t="n">
-        <v>6900</v>
+        <v>10500</v>
       </c>
       <c r="Q619" t="n">
-        <v>317400</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>J-1317</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -28616,7 +28616,7 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
@@ -28625,33 +28625,30 @@
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="N620" t="n">
-        <v>5280</v>
+        <v>4576</v>
       </c>
       <c r="O620" t="n">
-        <v>469920</v>
+        <v>439296</v>
       </c>
       <c r="P620" t="n">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="Q620" t="n">
-        <v>614100</v>
+        <v>566400</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>J-1386</t>
-        </is>
-      </c>
-      <c r="B621" t="n">
-        <v>7700154271143</v>
+          <t>J-719</t>
+        </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -28665,7 +28662,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
@@ -28674,30 +28671,30 @@
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="N621" t="n">
-        <v>7920</v>
+        <v>5280</v>
       </c>
       <c r="O621" t="n">
-        <v>427680</v>
+        <v>1140480</v>
       </c>
       <c r="P621" t="n">
-        <v>10500</v>
+        <v>6900</v>
       </c>
       <c r="Q621" t="n">
-        <v>567000</v>
+        <v>1490400</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -28711,7 +28708,7 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
@@ -28720,35 +28717,35 @@
         <v>0</v>
       </c>
       <c r="M622" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="N622" t="n">
-        <v>4576</v>
+        <v>46491.75</v>
       </c>
       <c r="O622" t="n">
-        <v>439296</v>
+        <v>2743013.25</v>
       </c>
       <c r="P622" t="n">
-        <v>5900</v>
+        <v>52900</v>
       </c>
       <c r="Q622" t="n">
-        <v>566400</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -28757,7 +28754,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>216</v>
+        <v>25</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -28766,35 +28763,35 @@
         <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>216</v>
+        <v>25</v>
       </c>
       <c r="N623" t="n">
-        <v>5280</v>
+        <v>910.85</v>
       </c>
       <c r="O623" t="n">
-        <v>1140480</v>
+        <v>22771.25</v>
       </c>
       <c r="P623" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="Q623" t="n">
-        <v>1490400</v>
+        <v>197500</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -28803,7 +28800,7 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="K624" t="n">
         <v>0</v>
@@ -28812,30 +28809,30 @@
         <v>0</v>
       </c>
       <c r="M624" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="N624" t="n">
-        <v>46491.75</v>
+        <v>1129.14</v>
       </c>
       <c r="O624" t="n">
-        <v>2743013.25</v>
+        <v>13549.68</v>
       </c>
       <c r="P624" t="n">
-        <v>52900</v>
+        <v>6900</v>
       </c>
       <c r="Q624" t="n">
-        <v>3121100</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -28849,7 +28846,7 @@
         </is>
       </c>
       <c r="J625" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K625" t="n">
         <v>0</v>
@@ -28858,35 +28855,40 @@
         <v>0</v>
       </c>
       <c r="M625" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="N625" t="n">
-        <v>910.85</v>
+        <v>11433.53</v>
       </c>
       <c r="O625" t="n">
-        <v>22771.25</v>
+        <v>68601.18000000001</v>
       </c>
       <c r="P625" t="n">
-        <v>7900</v>
+        <v>15000</v>
       </c>
       <c r="Q625" t="n">
-        <v>197500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -28895,7 +28897,7 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
@@ -28904,35 +28906,35 @@
         <v>0</v>
       </c>
       <c r="M626" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N626" t="n">
-        <v>1129.14</v>
+        <v>15452.21</v>
       </c>
       <c r="O626" t="n">
-        <v>13549.68</v>
+        <v>46356.63</v>
       </c>
       <c r="P626" t="n">
-        <v>6900</v>
+        <v>36500</v>
       </c>
       <c r="Q626" t="n">
-        <v>82800</v>
+        <v>109500</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -28941,7 +28943,7 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
@@ -28950,40 +28952,40 @@
         <v>0</v>
       </c>
       <c r="M627" t="n">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="N627" t="n">
-        <v>11433.53</v>
+        <v>1319.3610676157</v>
       </c>
       <c r="O627" t="n">
-        <v>68601.18000000001</v>
+        <v>184710.549466198</v>
       </c>
       <c r="P627" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="Q627" t="n">
-        <v>90000</v>
+        <v>490000</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -28992,7 +28994,7 @@
         </is>
       </c>
       <c r="J628" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K628" t="n">
         <v>0</v>
@@ -29001,35 +29003,35 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N628" t="n">
-        <v>15452.21</v>
+        <v>751.45</v>
       </c>
       <c r="O628" t="n">
-        <v>61808.84</v>
+        <v>751.45</v>
       </c>
       <c r="P628" t="n">
-        <v>36500</v>
+        <v>2500</v>
       </c>
       <c r="Q628" t="n">
-        <v>146000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -29038,7 +29040,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -29047,40 +29049,35 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="N629" t="n">
-        <v>1319.3610452962</v>
+        <v>571.87</v>
       </c>
       <c r="O629" t="n">
-        <v>184710.546341468</v>
+        <v>69196.27</v>
       </c>
       <c r="P629" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="Q629" t="n">
-        <v>490000</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -29089,7 +29086,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -29098,35 +29095,40 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="N630" t="n">
-        <v>751.45</v>
+        <v>227.41615210843</v>
       </c>
       <c r="O630" t="n">
-        <v>751.45</v>
+        <v>154642.9834337324</v>
       </c>
       <c r="P630" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q630" t="n">
-        <v>2500</v>
+        <v>816000</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -29135,7 +29137,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -29144,44 +29146,47 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="N631" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O631" t="n">
-        <v>69196.27</v>
+        <v>208257.84</v>
       </c>
       <c r="P631" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q631" t="n">
-        <v>302500</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>MG40334</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J632" t="n">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29190,40 +29195,35 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="N632" t="n">
-        <v>227.41615210843</v>
+        <v>2539.5718796199</v>
       </c>
       <c r="O632" t="n">
-        <v>154642.9834337324</v>
+        <v>401252.3569799442</v>
       </c>
       <c r="P632" t="n">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="Q632" t="n">
-        <v>816000</v>
+        <v>458200</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -29232,7 +29232,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -29241,47 +29241,44 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="N633" t="n">
-        <v>9917.040000000001</v>
+        <v>4171.6683165468</v>
       </c>
       <c r="O633" t="n">
-        <v>208257.84</v>
+        <v>396308.490071946</v>
       </c>
       <c r="P633" t="n">
-        <v>15900</v>
+        <v>5000</v>
       </c>
       <c r="Q633" t="n">
-        <v>333900</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B634" t="n">
-        <v>7700154271143</v>
+          <t>SEB010</t>
+        </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J634" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -29290,35 +29287,35 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="N634" t="n">
-        <v>2539.5718599791</v>
+        <v>7600</v>
       </c>
       <c r="O634" t="n">
-        <v>401252.3538766978</v>
+        <v>364800</v>
       </c>
       <c r="P634" t="n">
-        <v>2900</v>
+        <v>9500</v>
       </c>
       <c r="Q634" t="n">
-        <v>458200</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -29339,32 +29336,32 @@
         <v>95</v>
       </c>
       <c r="N635" t="n">
-        <v>4171.668314121</v>
+        <v>5520</v>
       </c>
       <c r="O635" t="n">
-        <v>396308.4898414949</v>
+        <v>524400</v>
       </c>
       <c r="P635" t="n">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="Q635" t="n">
-        <v>475000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -29373,7 +29370,7 @@
         </is>
       </c>
       <c r="J636" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="K636" t="n">
         <v>0</v>
@@ -29382,30 +29379,30 @@
         <v>0</v>
       </c>
       <c r="M636" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="N636" t="n">
-        <v>7600</v>
+        <v>1600</v>
       </c>
       <c r="O636" t="n">
-        <v>364800</v>
+        <v>132800</v>
       </c>
       <c r="P636" t="n">
-        <v>9500</v>
+        <v>2000</v>
       </c>
       <c r="Q636" t="n">
-        <v>456000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -29419,7 +29416,7 @@
         </is>
       </c>
       <c r="J637" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K637" t="n">
         <v>0</v>
@@ -29428,35 +29425,38 @@
         <v>0</v>
       </c>
       <c r="M637" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="N637" t="n">
-        <v>5520</v>
+        <v>4091.4</v>
       </c>
       <c r="O637" t="n">
-        <v>524400</v>
+        <v>4091.4</v>
       </c>
       <c r="P637" t="n">
-        <v>6900</v>
+        <v>10000</v>
       </c>
       <c r="Q637" t="n">
-        <v>655500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>SEB09</t>
-        </is>
+          <t>SLT3728</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -29465,7 +29465,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -29474,35 +29474,38 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="N638" t="n">
-        <v>1600</v>
+        <v>2465</v>
       </c>
       <c r="O638" t="n">
-        <v>132800</v>
+        <v>788800</v>
       </c>
       <c r="P638" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="Q638" t="n">
-        <v>166000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
-        </is>
+          <t>SLT4037</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -29511,7 +29514,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -29520,33 +29523,30 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="N639" t="n">
-        <v>4091.4</v>
+        <v>1700</v>
       </c>
       <c r="O639" t="n">
-        <v>4091.4</v>
+        <v>652800</v>
       </c>
       <c r="P639" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="Q639" t="n">
-        <v>10000</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>SLT3728</t>
-        </is>
-      </c>
-      <c r="B640" t="n">
-        <v>7700154271143</v>
+          <t>T040-LJ</t>
+        </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -29560,7 +29560,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -29569,33 +29569,30 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="N640" t="n">
-        <v>2465</v>
+        <v>3661.88</v>
       </c>
       <c r="O640" t="n">
-        <v>788800</v>
+        <v>10985.64</v>
       </c>
       <c r="P640" t="n">
-        <v>3000</v>
+        <v>38900</v>
       </c>
       <c r="Q640" t="n">
-        <v>960000</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>SLT4037</t>
-        </is>
-      </c>
-      <c r="B641" t="n">
-        <v>7700154271143</v>
+          <t>T041-LJ</t>
+        </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -29609,7 +29606,7 @@
         </is>
       </c>
       <c r="J641" t="n">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="K641" t="n">
         <v>0</v>
@@ -29618,30 +29615,30 @@
         <v>0</v>
       </c>
       <c r="M641" t="n">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="N641" t="n">
-        <v>1700</v>
+        <v>2797.08</v>
       </c>
       <c r="O641" t="n">
-        <v>652800</v>
+        <v>13985.4</v>
       </c>
       <c r="P641" t="n">
-        <v>2000</v>
+        <v>30900</v>
       </c>
       <c r="Q641" t="n">
-        <v>768000</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -29655,7 +29652,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -29664,30 +29661,30 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N642" t="n">
-        <v>3661.88</v>
+        <v>3462.255</v>
       </c>
       <c r="O642" t="n">
-        <v>10985.64</v>
+        <v>38084.805</v>
       </c>
       <c r="P642" t="n">
-        <v>38900</v>
+        <v>42000</v>
       </c>
       <c r="Q642" t="n">
-        <v>116700</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -29701,7 +29698,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -29710,30 +29707,30 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="N643" t="n">
-        <v>2797.08</v>
+        <v>24882.58</v>
       </c>
       <c r="O643" t="n">
-        <v>13985.4</v>
+        <v>696712.24</v>
       </c>
       <c r="P643" t="n">
-        <v>30900</v>
+        <v>31500</v>
       </c>
       <c r="Q643" t="n">
-        <v>154500</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -29747,7 +29744,7 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -29756,35 +29753,35 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N644" t="n">
-        <v>3462.255</v>
+        <v>0.8</v>
       </c>
       <c r="O644" t="n">
-        <v>38084.805</v>
+        <v>15.2</v>
       </c>
       <c r="P644" t="n">
-        <v>42000</v>
+        <v>22900</v>
       </c>
       <c r="Q644" t="n">
-        <v>462000</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -29793,7 +29790,7 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -29802,35 +29799,35 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N645" t="n">
-        <v>24882.58</v>
+        <v>5186.45</v>
       </c>
       <c r="O645" t="n">
-        <v>696712.24</v>
+        <v>82983.2</v>
       </c>
       <c r="P645" t="n">
-        <v>31500</v>
+        <v>7200</v>
       </c>
       <c r="Q645" t="n">
-        <v>882000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>TB028</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -29839,7 +29836,7 @@
         </is>
       </c>
       <c r="J646" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K646" t="n">
         <v>0</v>
@@ -29848,30 +29845,30 @@
         <v>0</v>
       </c>
       <c r="M646" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N646" t="n">
-        <v>0.8</v>
+        <v>47796.1625</v>
       </c>
       <c r="O646" t="n">
-        <v>15.2</v>
+        <v>95592.325</v>
       </c>
       <c r="P646" t="n">
-        <v>22900</v>
+        <v>54000</v>
       </c>
       <c r="Q646" t="n">
-        <v>435100</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>TB115</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -29885,7 +29882,7 @@
         </is>
       </c>
       <c r="J647" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="K647" t="n">
         <v>0</v>
@@ -29894,30 +29891,30 @@
         <v>0</v>
       </c>
       <c r="M647" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="N647" t="n">
-        <v>5186.45</v>
+        <v>8006.3731111111</v>
       </c>
       <c r="O647" t="n">
-        <v>82983.2</v>
+        <v>344274.0437777773</v>
       </c>
       <c r="P647" t="n">
-        <v>7200</v>
+        <v>10000</v>
       </c>
       <c r="Q647" t="n">
-        <v>115200</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>TB122</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -29931,7 +29928,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -29940,110 +29937,18 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N648" t="n">
-        <v>47796.1625</v>
+        <v>47920</v>
       </c>
       <c r="O648" t="n">
-        <v>95592.325</v>
+        <v>191680</v>
       </c>
       <c r="P648" t="n">
-        <v>54000</v>
+        <v>59900</v>
       </c>
       <c r="Q648" t="n">
-        <v>108000</v>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>TB115</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
-        </is>
-      </c>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I649" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J649" t="n">
-        <v>43</v>
-      </c>
-      <c r="K649" t="n">
-        <v>0</v>
-      </c>
-      <c r="L649" t="n">
-        <v>0</v>
-      </c>
-      <c r="M649" t="n">
-        <v>43</v>
-      </c>
-      <c r="N649" t="n">
-        <v>8006.3731111111</v>
-      </c>
-      <c r="O649" t="n">
-        <v>344274.0437777773</v>
-      </c>
-      <c r="P649" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Q649" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>TB122</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>PELUCHE DRAGON 50CM DRAG-50</t>
-        </is>
-      </c>
-      <c r="E650" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I650" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J650" t="n">
-        <v>4</v>
-      </c>
-      <c r="K650" t="n">
-        <v>0</v>
-      </c>
-      <c r="L650" t="n">
-        <v>0</v>
-      </c>
-      <c r="M650" t="n">
-        <v>4</v>
-      </c>
-      <c r="N650" t="n">
-        <v>47920</v>
-      </c>
-      <c r="O650" t="n">
-        <v>191680</v>
-      </c>
-      <c r="P650" t="n">
-        <v>59900</v>
-      </c>
-      <c r="Q650" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -16987,10 +16987,10 @@
         <v>120</v>
       </c>
       <c r="N370" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O370" t="n">
-        <v>1290600</v>
+        <v>1295488.63636368</v>
       </c>
       <c r="P370" t="n">
         <v>17900</v>
@@ -21652,10 +21652,10 @@
         <v>18026</v>
       </c>
       <c r="N471" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O471" t="n">
-        <v>12686602.13220973</v>
+        <v>12686602.10120753</v>
       </c>
       <c r="P471" t="n">
         <v>900</v>
@@ -29244,10 +29244,10 @@
         <v>95</v>
       </c>
       <c r="N633" t="n">
-        <v>4171.6683165468</v>
+        <v>4171.668314121</v>
       </c>
       <c r="O633" t="n">
-        <v>396308.490071946</v>
+        <v>396308.4898414949</v>
       </c>
       <c r="P633" t="n">
         <v>5000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -556,10 +556,10 @@
         <v>308</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>8316000</v>
+        <v>8336233.576642356</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -595,10 +595,10 @@
         <v>97</v>
       </c>
       <c r="N5" t="n">
-        <v>27000</v>
+        <v>27109.756097561</v>
       </c>
       <c r="O5" t="n">
-        <v>2619000</v>
+        <v>2629646.341463417</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -708,22 +708,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="N8" t="n">
         <v>3376.7463799384</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.799865546</v>
+        <v>2944522.843306285</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3978000</v>
+        <v>3924000</v>
       </c>
     </row>
     <row r="9">
@@ -956,10 +956,10 @@
         <v>153</v>
       </c>
       <c r="N14" t="n">
-        <v>27000</v>
+        <v>27267.326732673</v>
       </c>
       <c r="O14" t="n">
-        <v>4131000</v>
+        <v>4171900.990098969</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
@@ -995,10 +995,10 @@
         <v>162</v>
       </c>
       <c r="N15" t="n">
-        <v>27000</v>
+        <v>27151.898734177</v>
       </c>
       <c r="O15" t="n">
-        <v>4374000</v>
+        <v>4398607.594936674</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
@@ -1195,10 +1195,10 @@
         <v>194</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O20" t="n">
-        <v>761806.3917991618</v>
+        <v>761806.390906238</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1390,10 +1390,10 @@
         <v>120</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301970443</v>
+        <v>3716.3301973684</v>
       </c>
       <c r="O25" t="n">
-        <v>445959.623645316</v>
+        <v>445959.623684208</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -2060,10 +2060,10 @@
         <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>27000</v>
+        <v>27352.173913043</v>
       </c>
       <c r="O41" t="n">
-        <v>2160000</v>
+        <v>2188173.91304344</v>
       </c>
       <c r="P41" t="n">
         <v>20000</v>
@@ -2927,22 +2927,22 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M61" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="N61" t="n">
         <v>39171.85</v>
       </c>
       <c r="O61" t="n">
-        <v>3016232.45</v>
+        <v>1841076.95</v>
       </c>
       <c r="P61" t="n">
         <v>68900</v>
       </c>
       <c r="Q61" t="n">
-        <v>5305300</v>
+        <v>3238300</v>
       </c>
     </row>
     <row r="62">
@@ -3018,10 +3018,10 @@
         <v>1127</v>
       </c>
       <c r="N63" t="n">
-        <v>1098.072297891</v>
+        <v>1098.0725121628</v>
       </c>
       <c r="O63" t="n">
-        <v>1237527.479723157</v>
+        <v>1237527.721207476</v>
       </c>
       <c r="P63" t="n">
         <v>1500</v>
@@ -3417,22 +3417,22 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M72" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="N72" t="n">
         <v>17207.41</v>
       </c>
       <c r="O72" t="n">
-        <v>825955.6799999999</v>
+        <v>378563.02</v>
       </c>
       <c r="P72" t="n">
         <v>20000</v>
       </c>
       <c r="Q72" t="n">
-        <v>960000</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="73">
@@ -3951,10 +3951,10 @@
         <v>651</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O84" t="n">
-        <v>1681047.8829375</v>
+        <v>1681047.874120096</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -3997,10 +3997,10 @@
         <v>1235</v>
       </c>
       <c r="N85" t="n">
-        <v>10600</v>
+        <v>10614.851138354</v>
       </c>
       <c r="O85" t="n">
-        <v>13091000</v>
+        <v>13109341.15586719</v>
       </c>
       <c r="P85" t="n">
         <v>17200</v>
@@ -4410,10 +4410,10 @@
         <v>144</v>
       </c>
       <c r="N94" t="n">
-        <v>3230.0657538462</v>
+        <v>3230.0657009346</v>
       </c>
       <c r="O94" t="n">
-        <v>465129.4685538528</v>
+        <v>465129.4609345824</v>
       </c>
       <c r="P94" t="n">
         <v>6200</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.387083621</v>
+        <v>1511297.387154753</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5226,22 +5226,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M112" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N112" t="n">
         <v>41064.84</v>
       </c>
       <c r="O112" t="n">
-        <v>1560463.92</v>
+        <v>1314074.88</v>
       </c>
       <c r="P112" t="n">
         <v>68900</v>
       </c>
       <c r="Q112" t="n">
-        <v>2618200</v>
+        <v>2204800</v>
       </c>
     </row>
     <row r="113">
@@ -5818,10 +5818,10 @@
         <v>303</v>
       </c>
       <c r="N125" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O125" t="n">
-        <v>4491180.781552818</v>
+        <v>4491180.780667149</v>
       </c>
       <c r="P125" t="n">
         <v>24900</v>
@@ -6183,10 +6183,10 @@
         <v>308</v>
       </c>
       <c r="N133" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O133" t="n">
-        <v>3826118.606448908</v>
+        <v>3826118.608088392</v>
       </c>
       <c r="P133" t="n">
         <v>19900</v>
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.677026059</v>
+        <v>7270946.72235362</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -6504,10 +6504,10 @@
         <v>157</v>
       </c>
       <c r="N140" t="n">
-        <v>3041.6600149925</v>
+        <v>3041.660015015</v>
       </c>
       <c r="O140" t="n">
-        <v>477540.6223538225</v>
+        <v>477540.622357355</v>
       </c>
       <c r="P140" t="n">
         <v>5500</v>
@@ -6632,10 +6632,10 @@
         <v>1915</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O143" t="n">
-        <v>8370796.235444074</v>
+        <v>8370796.238179652</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -6722,10 +6722,10 @@
         <v>181</v>
       </c>
       <c r="N145" t="n">
-        <v>1592.5645263158</v>
+        <v>1592.5644086022</v>
       </c>
       <c r="O145" t="n">
-        <v>288254.1792631598</v>
+        <v>288254.1579569982</v>
       </c>
       <c r="P145" t="n">
         <v>3900</v>
@@ -7622,10 +7622,10 @@
         <v>109</v>
       </c>
       <c r="N165" t="n">
-        <v>4635.49</v>
+        <v>4768.3543630573</v>
       </c>
       <c r="O165" t="n">
-        <v>505268.41</v>
+        <v>519750.6255732458</v>
       </c>
       <c r="P165" t="n">
         <v>7500</v>
@@ -8366,22 +8366,22 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M181" t="n">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="N181" t="n">
         <v>3751</v>
       </c>
       <c r="O181" t="n">
-        <v>1875500</v>
+        <v>1830488</v>
       </c>
       <c r="P181" t="n">
         <v>6400</v>
       </c>
       <c r="Q181" t="n">
-        <v>3200000</v>
+        <v>3123200</v>
       </c>
     </row>
     <row r="182">
@@ -8467,10 +8467,10 @@
         <v>337</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9249342316</v>
+        <v>1630.925009772</v>
       </c>
       <c r="O183" t="n">
-        <v>549621.7028360493</v>
+        <v>549621.7282931641</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8559,10 +8559,10 @@
         <v>32</v>
       </c>
       <c r="N185" t="n">
-        <v>1690.5739608434</v>
+        <v>1690.5736115326</v>
       </c>
       <c r="O185" t="n">
-        <v>54098.3667469888</v>
+        <v>54098.3555690432</v>
       </c>
       <c r="P185" t="n">
         <v>2900</v>
@@ -8605,10 +8605,10 @@
         <v>1282</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1949322169</v>
+        <v>1550.1949414115</v>
       </c>
       <c r="O186" t="n">
-        <v>1987349.903102066</v>
+        <v>1987349.914889543</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5224548084</v>
+        <v>2403.5228513613</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.9071366616</v>
+        <v>418212.9761368662</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9182,22 +9182,22 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M199" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
         <v>15920</v>
       </c>
       <c r="O199" t="n">
-        <v>79600</v>
+        <v>0</v>
       </c>
       <c r="P199" t="n">
         <v>19900</v>
       </c>
       <c r="Q199" t="n">
-        <v>99500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -9939,22 +9939,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M216" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="N216" t="n">
         <v>2610</v>
       </c>
       <c r="O216" t="n">
-        <v>227070</v>
+        <v>214020</v>
       </c>
       <c r="P216" t="n">
         <v>3200</v>
       </c>
       <c r="Q216" t="n">
-        <v>278400</v>
+        <v>262400</v>
       </c>
     </row>
     <row r="217">
@@ -10286,10 +10286,10 @@
         <v>155</v>
       </c>
       <c r="N224" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O224" t="n">
-        <v>415514.6524420785</v>
+        <v>415514.6524122875</v>
       </c>
       <c r="P224" t="n">
         <v>4900</v>
@@ -10332,10 +10332,10 @@
         <v>9</v>
       </c>
       <c r="N225" t="n">
-        <v>11431.604625</v>
+        <v>11724.722692308</v>
       </c>
       <c r="O225" t="n">
-        <v>102884.441625</v>
+        <v>105522.504230772</v>
       </c>
       <c r="P225" t="n">
         <v>48900</v>
@@ -10419,10 +10419,10 @@
         <v>55</v>
       </c>
       <c r="N227" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O227" t="n">
-        <v>1683605</v>
+        <v>1690978.452554765</v>
       </c>
       <c r="P227" t="n">
         <v>38900</v>
@@ -10552,10 +10552,10 @@
         <v>918</v>
       </c>
       <c r="N230" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O230" t="n">
-        <v>5698933.169561399</v>
+        <v>5698933.168865096</v>
       </c>
       <c r="P230" t="n">
         <v>9900</v>
@@ -10647,10 +10647,10 @@
         <v>89</v>
       </c>
       <c r="N232" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="O232" t="n">
-        <v>381382.4941343674</v>
+        <v>381382.4986979137</v>
       </c>
       <c r="P232" t="n">
         <v>6900</v>
@@ -10731,22 +10731,22 @@
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M234" t="n">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="N234" t="n">
         <v>8963</v>
       </c>
       <c r="O234" t="n">
-        <v>2428973</v>
+        <v>2375195</v>
       </c>
       <c r="P234" t="n">
         <v>15200</v>
       </c>
       <c r="Q234" t="n">
-        <v>4119200</v>
+        <v>4028000</v>
       </c>
     </row>
     <row r="235">
@@ -10772,22 +10772,22 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M235" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="N235" t="n">
         <v>16275</v>
       </c>
       <c r="O235" t="n">
-        <v>927675</v>
+        <v>846300</v>
       </c>
       <c r="P235" t="n">
         <v>27600</v>
       </c>
       <c r="Q235" t="n">
-        <v>1573200</v>
+        <v>1435200</v>
       </c>
     </row>
     <row r="236">
@@ -10819,10 +10819,10 @@
         <v>32</v>
       </c>
       <c r="N236" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O236" t="n">
-        <v>35392</v>
+        <v>35557.2544747072</v>
       </c>
       <c r="P236" t="n">
         <v>2100</v>
@@ -10906,10 +10906,10 @@
         <v>1260</v>
       </c>
       <c r="N238" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O238" t="n">
-        <v>6065971.854979303</v>
+        <v>6065971.850828862</v>
       </c>
       <c r="P238" t="n">
         <v>9900</v>
@@ -10993,10 +10993,10 @@
         <v>32</v>
       </c>
       <c r="N240" t="n">
-        <v>11562.038395415</v>
+        <v>11562.038381503</v>
       </c>
       <c r="O240" t="n">
-        <v>369985.22865328</v>
+        <v>369985.228208096</v>
       </c>
       <c r="P240" t="n">
         <v>18500</v>
@@ -11039,10 +11039,10 @@
         <v>17</v>
       </c>
       <c r="N241" t="n">
-        <v>13513.643534483</v>
+        <v>13513.643727273</v>
       </c>
       <c r="O241" t="n">
-        <v>229731.940086211</v>
+        <v>229731.943363641</v>
       </c>
       <c r="P241" t="n">
         <v>21900</v>
@@ -11177,10 +11177,10 @@
         <v>86</v>
       </c>
       <c r="N244" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O244" t="n">
-        <v>2332643.763236542</v>
+        <v>2332643.756505236</v>
       </c>
       <c r="P244" t="n">
         <v>44500</v>
@@ -11258,22 +11258,22 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M246" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N246" t="n">
         <v>16974.69</v>
       </c>
       <c r="O246" t="n">
-        <v>678987.6</v>
+        <v>373443.18</v>
       </c>
       <c r="P246" t="n">
         <v>26900</v>
       </c>
       <c r="Q246" t="n">
-        <v>1076000</v>
+        <v>591800</v>
       </c>
     </row>
     <row r="247">
@@ -11345,22 +11345,22 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M248" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="N248" t="n">
-        <v>8332.7796042216</v>
+        <v>8332.7795967742</v>
       </c>
       <c r="O248" t="n">
-        <v>391640.6413984152</v>
+        <v>308312.8450806454</v>
       </c>
       <c r="P248" t="n">
         <v>14900</v>
       </c>
       <c r="Q248" t="n">
-        <v>700300</v>
+        <v>551300</v>
       </c>
     </row>
     <row r="249">
@@ -11391,22 +11391,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M249" t="n">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="N249" t="n">
-        <v>1561.0066122098</v>
+        <v>1561.0072654155</v>
       </c>
       <c r="O249" t="n">
-        <v>728990.0879019767</v>
+        <v>655623.05147451</v>
       </c>
       <c r="P249" t="n">
         <v>2900</v>
       </c>
       <c r="Q249" t="n">
-        <v>1354300</v>
+        <v>1218000</v>
       </c>
     </row>
     <row r="250">
@@ -11489,10 +11489,10 @@
         <v>21</v>
       </c>
       <c r="N251" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O251" t="n">
-        <v>563934</v>
+        <v>568699.639436628</v>
       </c>
       <c r="P251" t="n">
         <v>43900</v>
@@ -12137,22 +12137,22 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M265" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="N265" t="n">
         <v>5164.33</v>
       </c>
       <c r="O265" t="n">
-        <v>877936.1</v>
+        <v>748827.85</v>
       </c>
       <c r="P265" t="n">
         <v>10200</v>
       </c>
       <c r="Q265" t="n">
-        <v>1734000</v>
+        <v>1479000</v>
       </c>
     </row>
     <row r="266">
@@ -12189,10 +12189,10 @@
         <v>348</v>
       </c>
       <c r="N266" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="O266" t="n">
-        <v>2679600</v>
+        <v>2692832.592592584</v>
       </c>
       <c r="P266" t="n">
         <v>13900</v>
@@ -13253,10 +13253,10 @@
         <v>744</v>
       </c>
       <c r="N289" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O289" t="n">
-        <v>1323183.825728438</v>
+        <v>1323183.828567617</v>
       </c>
       <c r="P289" t="n">
         <v>4900</v>
@@ -13431,22 +13431,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M293" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N293" t="n">
-        <v>22739</v>
+        <v>22935.194995686</v>
       </c>
       <c r="O293" t="n">
-        <v>3274416</v>
+        <v>3073316.129421924</v>
       </c>
       <c r="P293" t="n">
         <v>36900</v>
       </c>
       <c r="Q293" t="n">
-        <v>5313600</v>
+        <v>4944600</v>
       </c>
     </row>
     <row r="294">
@@ -13477,22 +13477,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M294" t="n">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="N294" t="n">
         <v>18016</v>
       </c>
       <c r="O294" t="n">
-        <v>5134560</v>
+        <v>4522016</v>
       </c>
       <c r="P294" t="n">
         <v>29900</v>
       </c>
       <c r="Q294" t="n">
-        <v>8521500</v>
+        <v>7504900</v>
       </c>
     </row>
     <row r="295">
@@ -13523,22 +13523,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M295" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="N295" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O295" t="n">
-        <v>1975134</v>
+        <v>1828035.084695449</v>
       </c>
       <c r="P295" t="n">
         <v>25900</v>
       </c>
       <c r="Q295" t="n">
-        <v>3185700</v>
+        <v>2926700</v>
       </c>
     </row>
     <row r="296">
@@ -13569,22 +13569,22 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M296" t="n">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="N296" t="n">
         <v>25534</v>
       </c>
       <c r="O296" t="n">
-        <v>7736802</v>
+        <v>6868646</v>
       </c>
       <c r="P296" t="n">
         <v>40900</v>
       </c>
       <c r="Q296" t="n">
-        <v>12392700</v>
+        <v>11002100</v>
       </c>
     </row>
     <row r="297">
@@ -14219,22 +14219,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M310" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="N310" t="n">
         <v>13687</v>
       </c>
       <c r="O310" t="n">
-        <v>780159</v>
+        <v>615915</v>
       </c>
       <c r="P310" t="n">
         <v>21900</v>
       </c>
       <c r="Q310" t="n">
-        <v>1248300</v>
+        <v>985500</v>
       </c>
     </row>
     <row r="311">
@@ -14357,22 +14357,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M313" t="n">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="N313" t="n">
         <v>3938.66</v>
       </c>
       <c r="O313" t="n">
-        <v>2292300.12</v>
+        <v>2268668.16</v>
       </c>
       <c r="P313" t="n">
         <v>4500</v>
       </c>
       <c r="Q313" t="n">
-        <v>2619000</v>
+        <v>2592000</v>
       </c>
     </row>
     <row r="314">
@@ -14409,10 +14409,10 @@
         <v>22</v>
       </c>
       <c r="N314" t="n">
-        <v>28116</v>
+        <v>28661.941747573</v>
       </c>
       <c r="O314" t="n">
-        <v>618552</v>
+        <v>630562.7184466061</v>
       </c>
       <c r="P314" t="n">
         <v>45900</v>
@@ -14449,22 +14449,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M315" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N315" t="n">
         <v>3424</v>
       </c>
       <c r="O315" t="n">
-        <v>160928</v>
+        <v>140384</v>
       </c>
       <c r="P315" t="n">
         <v>5900</v>
       </c>
       <c r="Q315" t="n">
-        <v>277300</v>
+        <v>241900</v>
       </c>
     </row>
     <row r="316">
@@ -14593,10 +14593,10 @@
         <v>5</v>
       </c>
       <c r="N318" t="n">
-        <v>2252.3008997955</v>
+        <v>2252.3011740042</v>
       </c>
       <c r="O318" t="n">
-        <v>11261.5044989775</v>
+        <v>11261.505870021</v>
       </c>
       <c r="P318" t="n">
         <v>3900</v>
@@ -15005,22 +15005,22 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M327" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N327" t="n">
         <v>29105.23</v>
       </c>
       <c r="O327" t="n">
-        <v>436578.45</v>
+        <v>232841.84</v>
       </c>
       <c r="P327" t="n">
         <v>39900</v>
       </c>
       <c r="Q327" t="n">
-        <v>598500</v>
+        <v>319200</v>
       </c>
     </row>
     <row r="328">
@@ -15057,10 +15057,10 @@
         <v>1</v>
       </c>
       <c r="N328" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O328" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="P328" t="n">
         <v>5900</v>
@@ -15333,10 +15333,10 @@
         <v>10</v>
       </c>
       <c r="N334" t="n">
-        <v>16285.911125</v>
+        <v>16703.498589744</v>
       </c>
       <c r="O334" t="n">
-        <v>162859.11125</v>
+        <v>167034.98589744</v>
       </c>
       <c r="P334" t="n">
         <v>29900</v>
@@ -15379,10 +15379,10 @@
         <v>1</v>
       </c>
       <c r="N335" t="n">
-        <v>17981</v>
+        <v>18487.507042254</v>
       </c>
       <c r="O335" t="n">
-        <v>17981</v>
+        <v>18487.507042254</v>
       </c>
       <c r="P335" t="n">
         <v>29900</v>
@@ -15419,22 +15419,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M336" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="N336" t="n">
         <v>3396.38</v>
       </c>
       <c r="O336" t="n">
-        <v>506060.62</v>
+        <v>485682.34</v>
       </c>
       <c r="P336" t="n">
         <v>6500</v>
       </c>
       <c r="Q336" t="n">
-        <v>968500</v>
+        <v>929500</v>
       </c>
     </row>
     <row r="337">
@@ -15471,10 +15471,10 @@
         <v>126</v>
       </c>
       <c r="N337" t="n">
-        <v>4907.8227973568</v>
+        <v>4907.8228159645</v>
       </c>
       <c r="O337" t="n">
-        <v>618385.6724669568</v>
+        <v>618385.6748115269</v>
       </c>
       <c r="P337" t="n">
         <v>8200</v>
@@ -15696,10 +15696,10 @@
         <v>14</v>
       </c>
       <c r="N342" t="n">
-        <v>20726</v>
+        <v>21286.162162162</v>
       </c>
       <c r="O342" t="n">
-        <v>290164</v>
+        <v>298006.270270268</v>
       </c>
       <c r="P342" t="n">
         <v>33900</v>
@@ -16110,10 +16110,10 @@
         <v>146</v>
       </c>
       <c r="N351" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O351" t="n">
-        <v>1980490</v>
+        <v>1983555.773993752</v>
       </c>
       <c r="P351" t="n">
         <v>22500</v>
@@ -16248,10 +16248,10 @@
         <v>23</v>
       </c>
       <c r="N354" t="n">
-        <v>16086</v>
+        <v>16443.466666667</v>
       </c>
       <c r="O354" t="n">
-        <v>369978</v>
+        <v>378199.733333341</v>
       </c>
       <c r="P354" t="n">
         <v>25900</v>
@@ -16340,10 +16340,10 @@
         <v>12</v>
       </c>
       <c r="N356" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="O356" t="n">
-        <v>281268</v>
+        <v>288480</v>
       </c>
       <c r="P356" t="n">
         <v>37900</v>
@@ -16386,10 +16386,10 @@
         <v>60</v>
       </c>
       <c r="N357" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O357" t="n">
-        <v>1140480</v>
+        <v>1143549.93270522</v>
       </c>
       <c r="P357" t="n">
         <v>30900</v>
@@ -16478,10 +16478,10 @@
         <v>54</v>
       </c>
       <c r="N359" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O359" t="n">
-        <v>971568</v>
+        <v>974098.1250000179</v>
       </c>
       <c r="P359" t="n">
         <v>28900</v>
@@ -16570,10 +16570,10 @@
         <v>291</v>
       </c>
       <c r="N361" t="n">
-        <v>17075.989515789</v>
+        <v>17112.014810127</v>
       </c>
       <c r="O361" t="n">
-        <v>4969112.949094598</v>
+        <v>4979596.309746956</v>
       </c>
       <c r="P361" t="n">
         <v>27500</v>
@@ -17217,10 +17217,10 @@
         <v>20</v>
       </c>
       <c r="N375" t="n">
-        <v>10817</v>
+        <v>10997.283333333</v>
       </c>
       <c r="O375" t="n">
-        <v>216340</v>
+        <v>219945.66666666</v>
       </c>
       <c r="P375" t="n">
         <v>17900</v>
@@ -17533,22 +17533,22 @@
         <v>0</v>
       </c>
       <c r="L382" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M382" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="N382" t="n">
         <v>15223.06</v>
       </c>
       <c r="O382" t="n">
-        <v>715483.8199999999</v>
+        <v>380576.5</v>
       </c>
       <c r="P382" t="n">
         <v>17500</v>
       </c>
       <c r="Q382" t="n">
-        <v>822500</v>
+        <v>437500</v>
       </c>
     </row>
     <row r="383">
@@ -17769,10 +17769,10 @@
         <v>96</v>
       </c>
       <c r="N387" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942583732</v>
       </c>
       <c r="O387" t="n">
-        <v>317433.0496815264</v>
+        <v>317433.0488038272</v>
       </c>
       <c r="P387" t="n">
         <v>4900</v>
@@ -17815,10 +17815,10 @@
         <v>96</v>
       </c>
       <c r="N388" t="n">
-        <v>2056.0812616427</v>
+        <v>2056.081010453</v>
       </c>
       <c r="O388" t="n">
-        <v>197383.8011176992</v>
+        <v>197383.777003488</v>
       </c>
       <c r="P388" t="n">
         <v>2900</v>
@@ -17861,10 +17861,10 @@
         <v>216</v>
       </c>
       <c r="N389" t="n">
-        <v>1655.9287880016</v>
+        <v>1655.9287789047</v>
       </c>
       <c r="O389" t="n">
-        <v>357680.6182083456</v>
+        <v>357680.6162434152</v>
       </c>
       <c r="P389" t="n">
         <v>2500</v>
@@ -18091,10 +18091,10 @@
         <v>224</v>
       </c>
       <c r="N394" t="n">
-        <v>1592.2874455446</v>
+        <v>1592.2885084034</v>
       </c>
       <c r="O394" t="n">
-        <v>356672.3878019904</v>
+        <v>356672.6258823616</v>
       </c>
       <c r="P394" t="n">
         <v>2500</v>
@@ -18445,10 +18445,10 @@
         <v>504</v>
       </c>
       <c r="N402" t="n">
-        <v>692.15251958462</v>
+        <v>692.1525362185999</v>
       </c>
       <c r="O402" t="n">
-        <v>348844.8698706485</v>
+        <v>348844.8782541744</v>
       </c>
       <c r="P402" t="n">
         <v>1200</v>
@@ -18488,22 +18488,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M403" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="N403" t="n">
         <v>18491</v>
       </c>
       <c r="O403" t="n">
-        <v>1294370</v>
+        <v>1090969</v>
       </c>
       <c r="P403" t="n">
         <v>13500</v>
       </c>
       <c r="Q403" t="n">
-        <v>945000</v>
+        <v>796500</v>
       </c>
     </row>
     <row r="404">
@@ -18959,22 +18959,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M413" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N413" t="n">
         <v>15423.36</v>
       </c>
       <c r="O413" t="n">
-        <v>709474.5600000001</v>
+        <v>539817.6</v>
       </c>
       <c r="P413" t="n">
         <v>24900</v>
       </c>
       <c r="Q413" t="n">
-        <v>1145400</v>
+        <v>871500</v>
       </c>
     </row>
     <row r="414">
@@ -19846,10 +19846,10 @@
         <v>306</v>
       </c>
       <c r="N432" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="O432" t="n">
-        <v>517406.2229366514</v>
+        <v>517406.2229853666</v>
       </c>
       <c r="P432" t="n">
         <v>3000</v>
@@ -20406,10 +20406,10 @@
         <v>99</v>
       </c>
       <c r="N444" t="n">
-        <v>1283.6512980769</v>
+        <v>1283.6501630435</v>
       </c>
       <c r="O444" t="n">
-        <v>127081.4785096131</v>
+        <v>127081.3661413065</v>
       </c>
       <c r="P444" t="n">
         <v>1900</v>
@@ -20965,10 +20965,10 @@
         <v>20</v>
       </c>
       <c r="N456" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="O456" t="n">
-        <v>65182.693670886</v>
+        <v>65182.695689656</v>
       </c>
       <c r="P456" t="n">
         <v>3600</v>
@@ -21014,10 +21014,10 @@
         <v>631</v>
       </c>
       <c r="N457" t="n">
-        <v>3110.8352523988</v>
+        <v>3110.8351781971</v>
       </c>
       <c r="O457" t="n">
-        <v>1962937.044263643</v>
+        <v>1962936.99744237</v>
       </c>
       <c r="P457" t="n">
         <v>4500</v>
@@ -21419,10 +21419,10 @@
         <v>17742</v>
       </c>
       <c r="N466" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O466" t="n">
-        <v>12486723.70581941</v>
+        <v>12486723.66190175</v>
       </c>
       <c r="P466" t="n">
         <v>900</v>
@@ -21462,22 +21462,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M467" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N467" t="n">
         <v>3182.2511650485</v>
       </c>
       <c r="O467" t="n">
-        <v>175023.8140776675</v>
+        <v>136836.8000970855</v>
       </c>
       <c r="P467" t="n">
         <v>6900</v>
       </c>
       <c r="Q467" t="n">
-        <v>379500</v>
+        <v>296700</v>
       </c>
     </row>
     <row r="468">
@@ -21554,22 +21554,22 @@
         <v>0</v>
       </c>
       <c r="L469" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M469" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N469" t="n">
-        <v>2501.384</v>
+        <v>2501.3837931034</v>
       </c>
       <c r="O469" t="n">
-        <v>130071.968</v>
+        <v>100055.351724136</v>
       </c>
       <c r="P469" t="n">
         <v>4100</v>
       </c>
       <c r="Q469" t="n">
-        <v>213200</v>
+        <v>164000</v>
       </c>
     </row>
     <row r="470">
@@ -21644,22 +21644,22 @@
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M471" t="n">
-        <v>518</v>
+        <v>468</v>
       </c>
       <c r="N471" t="n">
         <v>2529.19</v>
       </c>
       <c r="O471" t="n">
-        <v>1310120.42</v>
+        <v>1183660.92</v>
       </c>
       <c r="P471" t="n">
         <v>5100</v>
       </c>
       <c r="Q471" t="n">
-        <v>2641800</v>
+        <v>2386800</v>
       </c>
     </row>
     <row r="472">
@@ -22413,10 +22413,10 @@
         <v>18</v>
       </c>
       <c r="N487" t="n">
-        <v>2832.195862069</v>
+        <v>2986.6792727273</v>
       </c>
       <c r="O487" t="n">
-        <v>50979.525517242</v>
+        <v>53760.2269090914</v>
       </c>
       <c r="P487" t="n">
         <v>12900</v>
@@ -22555,10 +22555,10 @@
         <v>8</v>
       </c>
       <c r="N490" t="n">
-        <v>16313.41</v>
+        <v>18488.531333333</v>
       </c>
       <c r="O490" t="n">
-        <v>130507.28</v>
+        <v>147908.250666664</v>
       </c>
       <c r="P490" t="n">
         <v>33500</v>
@@ -22843,10 +22843,10 @@
         <v>2</v>
       </c>
       <c r="N496" t="n">
-        <v>13164.13</v>
+        <v>15985.015</v>
       </c>
       <c r="O496" t="n">
-        <v>26328.26</v>
+        <v>31970.03</v>
       </c>
       <c r="P496" t="n">
         <v>39900</v>
@@ -22932,22 +22932,22 @@
         <v>0</v>
       </c>
       <c r="L498" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M498" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N498" t="n">
         <v>23475.657272727</v>
       </c>
       <c r="O498" t="n">
-        <v>305183.544545451</v>
+        <v>234756.57272727</v>
       </c>
       <c r="P498" t="n">
         <v>31900</v>
       </c>
       <c r="Q498" t="n">
-        <v>414700</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="499">
@@ -23556,10 +23556,10 @@
         <v>94</v>
       </c>
       <c r="N511" t="n">
-        <v>3067.0906293706</v>
+        <v>3099.6039575972</v>
       </c>
       <c r="O511" t="n">
-        <v>288306.5191608364</v>
+        <v>291362.7720141368</v>
       </c>
       <c r="P511" t="n">
         <v>7200</v>
@@ -24326,10 +24326,10 @@
         <v>17</v>
       </c>
       <c r="N527" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="O527" t="n">
-        <v>182537.9335</v>
+        <v>182537.931538455</v>
       </c>
       <c r="P527" t="n">
         <v>18900</v>
@@ -24416,10 +24416,10 @@
         <v>11</v>
       </c>
       <c r="N529" t="n">
-        <v>36004.28</v>
+        <v>43719.482857143</v>
       </c>
       <c r="O529" t="n">
-        <v>396047.08</v>
+        <v>480914.311428573</v>
       </c>
       <c r="P529" t="n">
         <v>83500</v>
@@ -24459,22 +24459,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M530" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N530" t="n">
         <v>7258.5</v>
       </c>
       <c r="O530" t="n">
-        <v>65326.5</v>
+        <v>21775.5</v>
       </c>
       <c r="P530" t="n">
         <v>17500</v>
       </c>
       <c r="Q530" t="n">
-        <v>157500</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="531">
@@ -24511,10 +24511,10 @@
         <v>9</v>
       </c>
       <c r="N531" t="n">
-        <v>14751.820338983</v>
+        <v>15571.365925926</v>
       </c>
       <c r="O531" t="n">
-        <v>132766.383050847</v>
+        <v>140142.293333334</v>
       </c>
       <c r="P531" t="n">
         <v>37100</v>
@@ -25216,10 +25216,10 @@
         <v>73</v>
       </c>
       <c r="N546" t="n">
-        <v>5216.9</v>
+        <v>5254.1635714286</v>
       </c>
       <c r="O546" t="n">
-        <v>380833.7</v>
+        <v>383553.9407142878</v>
       </c>
       <c r="P546" t="n">
         <v>20500</v>
@@ -25551,10 +25551,10 @@
         <v>116</v>
       </c>
       <c r="N553" t="n">
-        <v>24338.47</v>
+        <v>24856.309787234</v>
       </c>
       <c r="O553" t="n">
-        <v>2823262.52</v>
+        <v>2883331.935319144</v>
       </c>
       <c r="P553" t="n">
         <v>27900</v>
@@ -26343,22 +26343,22 @@
         <v>0</v>
       </c>
       <c r="L570" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M570" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N570" t="n">
         <v>110520.77</v>
       </c>
       <c r="O570" t="n">
-        <v>1989373.86</v>
+        <v>1326249.24</v>
       </c>
       <c r="P570" t="n">
         <v>176900</v>
       </c>
       <c r="Q570" t="n">
-        <v>3184200</v>
+        <v>2122800</v>
       </c>
     </row>
     <row r="571">
@@ -27173,22 +27173,22 @@
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M589" t="n">
-        <v>325</v>
+        <v>280</v>
       </c>
       <c r="N589" t="n">
-        <v>22951.704647137</v>
+        <v>22951.704432133</v>
       </c>
       <c r="O589" t="n">
-        <v>7459304.010319525</v>
+        <v>6426477.24099724</v>
       </c>
       <c r="P589" t="n">
         <v>37900</v>
       </c>
       <c r="Q589" t="n">
-        <v>12317500</v>
+        <v>10612000</v>
       </c>
     </row>
     <row r="590">
@@ -28193,22 +28193,22 @@
         <v>0</v>
       </c>
       <c r="L611" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M611" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="N611" t="n">
         <v>4576</v>
       </c>
       <c r="O611" t="n">
-        <v>439296</v>
+        <v>329472</v>
       </c>
       <c r="P611" t="n">
         <v>5900</v>
       </c>
       <c r="Q611" t="n">
-        <v>566400</v>
+        <v>424800</v>
       </c>
     </row>
     <row r="612">
@@ -28239,22 +28239,22 @@
         <v>0</v>
       </c>
       <c r="L612" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M612" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="N612" t="n">
         <v>5280</v>
       </c>
       <c r="O612" t="n">
-        <v>1140480</v>
+        <v>1077120</v>
       </c>
       <c r="P612" t="n">
         <v>6900</v>
       </c>
       <c r="Q612" t="n">
-        <v>1490400</v>
+        <v>1407600</v>
       </c>
     </row>
     <row r="613">
@@ -28480,10 +28480,10 @@
         <v>3</v>
       </c>
       <c r="N617" t="n">
-        <v>15452.21</v>
+        <v>16024.514074074</v>
       </c>
       <c r="O617" t="n">
-        <v>46356.63</v>
+        <v>48073.542222222</v>
       </c>
       <c r="P617" t="n">
         <v>36500</v>
@@ -28769,10 +28769,10 @@
         <v>158</v>
       </c>
       <c r="N623" t="n">
-        <v>2539.5719057816</v>
+        <v>2539.5719098712</v>
       </c>
       <c r="O623" t="n">
-        <v>401252.3611134928</v>
+        <v>401252.3617596496</v>
       </c>
       <c r="P623" t="n">
         <v>2900</v>
@@ -28815,10 +28815,10 @@
         <v>95</v>
       </c>
       <c r="N624" t="n">
-        <v>4171.6683018868</v>
+        <v>4171.6682869693</v>
       </c>
       <c r="O624" t="n">
-        <v>396308.488679246</v>
+        <v>396308.4872620836</v>
       </c>
       <c r="P624" t="n">
         <v>5000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -595,10 +595,10 @@
         <v>97</v>
       </c>
       <c r="N5" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>2629646.341463417</v>
+        <v>2619000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3112820513</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3112820513</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -3018,10 +3018,10 @@
         <v>1127</v>
       </c>
       <c r="N63" t="n">
-        <v>1098.0729937163</v>
+        <v>1098.0730382022</v>
       </c>
       <c r="O63" t="n">
-        <v>1237528.26391827</v>
+        <v>1237528.314053879</v>
       </c>
       <c r="P63" t="n">
         <v>1500</v>
@@ -3951,10 +3951,10 @@
         <v>651</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O84" t="n">
-        <v>1681047.85008153</v>
+        <v>1683722.524821013</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -4410,10 +4410,10 @@
         <v>144</v>
       </c>
       <c r="N94" t="n">
-        <v>3230.0657009346</v>
+        <v>3230.0656603774</v>
       </c>
       <c r="O94" t="n">
-        <v>465129.4609345824</v>
+        <v>465129.4550943456</v>
       </c>
       <c r="P94" t="n">
         <v>6200</v>
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.728041134</v>
+        <v>7270946.739431027</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -7622,10 +7622,10 @@
         <v>109</v>
       </c>
       <c r="N165" t="n">
-        <v>4768.3543630573</v>
+        <v>4635.49</v>
       </c>
       <c r="O165" t="n">
-        <v>519750.6255732458</v>
+        <v>505268.41</v>
       </c>
       <c r="P165" t="n">
         <v>7500</v>
@@ -8513,10 +8513,10 @@
         <v>5</v>
       </c>
       <c r="N184" t="n">
-        <v>1467.2914141414</v>
+        <v>1467.3004273504</v>
       </c>
       <c r="O184" t="n">
-        <v>7336.457070707001</v>
+        <v>7336.502136752</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
@@ -8559,10 +8559,10 @@
         <v>32</v>
       </c>
       <c r="N185" t="n">
-        <v>1690.5719339623</v>
+        <v>1690.5726046512</v>
       </c>
       <c r="O185" t="n">
-        <v>54098.3018867936</v>
+        <v>54098.3233488384</v>
       </c>
       <c r="P185" t="n">
         <v>2900</v>
@@ -8605,10 +8605,10 @@
         <v>1282</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O186" t="n">
-        <v>1987349.9934564</v>
+        <v>1987349.941997817</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.522961183</v>
+        <v>2403.5229357459</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.995245842</v>
+        <v>418212.9908197866</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -10240,10 +10240,10 @@
         <v>9</v>
       </c>
       <c r="N223" t="n">
-        <v>11724.722692308</v>
+        <v>11431.604487179</v>
       </c>
       <c r="O223" t="n">
-        <v>105522.504230772</v>
+        <v>102884.440384611</v>
       </c>
       <c r="P223" t="n">
         <v>48900</v>
@@ -10327,10 +10327,10 @@
         <v>55</v>
       </c>
       <c r="N225" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O225" t="n">
-        <v>1690978.452554765</v>
+        <v>1683605</v>
       </c>
       <c r="P225" t="n">
         <v>38900</v>
@@ -10460,10 +10460,10 @@
         <v>918</v>
       </c>
       <c r="N228" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O228" t="n">
-        <v>5698933.167935804</v>
+        <v>5698933.168865096</v>
       </c>
       <c r="P228" t="n">
         <v>9900</v>
@@ -10814,10 +10814,10 @@
         <v>1260</v>
       </c>
       <c r="N236" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O236" t="n">
-        <v>6065971.817476662</v>
+        <v>6065971.823053926</v>
       </c>
       <c r="P236" t="n">
         <v>9900</v>
@@ -11085,10 +11085,10 @@
         <v>86</v>
       </c>
       <c r="N242" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O242" t="n">
-        <v>2332643.756505236</v>
+        <v>2332643.754545468</v>
       </c>
       <c r="P242" t="n">
         <v>44500</v>
@@ -11397,10 +11397,10 @@
         <v>21</v>
       </c>
       <c r="N249" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O249" t="n">
-        <v>568699.639436628</v>
+        <v>563934</v>
       </c>
       <c r="P249" t="n">
         <v>43900</v>
@@ -13017,22 +13017,22 @@
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M284" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N284" t="n">
-        <v>9188.98</v>
+        <v>9456.2957818182</v>
       </c>
       <c r="O284" t="n">
-        <v>101078.78</v>
+        <v>28368.8873454546</v>
       </c>
       <c r="P284" t="n">
         <v>12900</v>
       </c>
       <c r="Q284" t="n">
-        <v>141900</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="285">
@@ -13345,10 +13345,10 @@
         <v>134</v>
       </c>
       <c r="N291" t="n">
-        <v>22935.194995686</v>
+        <v>22739</v>
       </c>
       <c r="O291" t="n">
-        <v>3073316.129421924</v>
+        <v>3047026</v>
       </c>
       <c r="P291" t="n">
         <v>36900</v>
@@ -14268,10 +14268,10 @@
         <v>22</v>
       </c>
       <c r="N311" t="n">
-        <v>28661.941747573</v>
+        <v>28116</v>
       </c>
       <c r="O311" t="n">
-        <v>630562.7184466061</v>
+        <v>618552</v>
       </c>
       <c r="P311" t="n">
         <v>45900</v>
@@ -14400,22 +14400,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M314" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N314" t="n">
-        <v>10411</v>
+        <v>10642.355555556</v>
       </c>
       <c r="O314" t="n">
-        <v>156165</v>
+        <v>95781.200000004</v>
       </c>
       <c r="P314" t="n">
         <v>16900</v>
       </c>
       <c r="Q314" t="n">
-        <v>253500</v>
+        <v>152100</v>
       </c>
     </row>
     <row r="315">
@@ -15192,10 +15192,10 @@
         <v>10</v>
       </c>
       <c r="N331" t="n">
-        <v>16703.498589744</v>
+        <v>16285.911153846</v>
       </c>
       <c r="O331" t="n">
-        <v>167034.98589744</v>
+        <v>162859.11153846</v>
       </c>
       <c r="P331" t="n">
         <v>29900</v>
@@ -15238,10 +15238,10 @@
         <v>1</v>
       </c>
       <c r="N332" t="n">
-        <v>18487.507042254</v>
+        <v>17981</v>
       </c>
       <c r="O332" t="n">
-        <v>18487.507042254</v>
+        <v>17981</v>
       </c>
       <c r="P332" t="n">
         <v>29900</v>
@@ -15555,10 +15555,10 @@
         <v>14</v>
       </c>
       <c r="N339" t="n">
-        <v>21286.162162162</v>
+        <v>20726</v>
       </c>
       <c r="O339" t="n">
-        <v>298006.270270268</v>
+        <v>290164</v>
       </c>
       <c r="P339" t="n">
         <v>33900</v>
@@ -15595,22 +15595,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M340" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N340" t="n">
-        <v>33000</v>
+        <v>35444.444444444</v>
       </c>
       <c r="O340" t="n">
-        <v>528000</v>
+        <v>354444.44444444</v>
       </c>
       <c r="P340" t="n">
         <v>52900</v>
       </c>
       <c r="Q340" t="n">
-        <v>846400</v>
+        <v>529000</v>
       </c>
     </row>
     <row r="341">
@@ -15969,10 +15969,10 @@
         <v>146</v>
       </c>
       <c r="N348" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O348" t="n">
-        <v>1983555.773993752</v>
+        <v>1980490</v>
       </c>
       <c r="P348" t="n">
         <v>22500</v>
@@ -16107,10 +16107,10 @@
         <v>23</v>
       </c>
       <c r="N351" t="n">
-        <v>16443.466666667</v>
+        <v>16086</v>
       </c>
       <c r="O351" t="n">
-        <v>378199.733333341</v>
+        <v>369978</v>
       </c>
       <c r="P351" t="n">
         <v>25900</v>
@@ -16245,10 +16245,10 @@
         <v>60</v>
       </c>
       <c r="N354" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O354" t="n">
-        <v>1143549.93270522</v>
+        <v>1140480</v>
       </c>
       <c r="P354" t="n">
         <v>30900</v>
@@ -16337,10 +16337,10 @@
         <v>54</v>
       </c>
       <c r="N356" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O356" t="n">
-        <v>974098.1250000179</v>
+        <v>971568</v>
       </c>
       <c r="P356" t="n">
         <v>28900</v>
@@ -16429,10 +16429,10 @@
         <v>291</v>
       </c>
       <c r="N358" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O358" t="n">
-        <v>4979596.309746956</v>
+        <v>4969112.948797488</v>
       </c>
       <c r="P358" t="n">
         <v>27500</v>
@@ -17490,10 +17490,10 @@
         <v>1008</v>
       </c>
       <c r="N381" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O381" t="n">
-        <v>1528167.006933336</v>
+        <v>1528167.008598653</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
@@ -17720,10 +17720,10 @@
         <v>216</v>
       </c>
       <c r="N386" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O386" t="n">
-        <v>357680.6162434152</v>
+        <v>357680.5803211248</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
@@ -17950,10 +17950,10 @@
         <v>224</v>
       </c>
       <c r="N391" t="n">
-        <v>1592.2886257928</v>
+        <v>1592.2887446809</v>
       </c>
       <c r="O391" t="n">
-        <v>356672.6521775872</v>
+        <v>356672.6788085216</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -18127,10 +18127,10 @@
         <v>400</v>
       </c>
       <c r="N395" t="n">
-        <v>1259.2752009274</v>
+        <v>1259.2751769231</v>
       </c>
       <c r="O395" t="n">
-        <v>503710.08037096</v>
+        <v>503710.07076924</v>
       </c>
       <c r="P395" t="n">
         <v>1900</v>
@@ -18304,10 +18304,10 @@
         <v>504</v>
       </c>
       <c r="N399" t="n">
-        <v>692.1525418121701</v>
+        <v>692.15254743047</v>
       </c>
       <c r="O399" t="n">
-        <v>348844.8810733337</v>
+        <v>348844.8839049569</v>
       </c>
       <c r="P399" t="n">
         <v>1200</v>
@@ -19058,10 +19058,10 @@
         <v>877</v>
       </c>
       <c r="N415" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O415" t="n">
-        <v>7845098.259999999</v>
+        <v>7848634.743062347</v>
       </c>
       <c r="P415" t="n">
         <v>14900</v>
@@ -21278,10 +21278,10 @@
         <v>17742</v>
       </c>
       <c r="N463" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O463" t="n">
-        <v>12486723.59206746</v>
+        <v>12486723.62311738</v>
       </c>
       <c r="P463" t="n">
         <v>900</v>
@@ -22272,10 +22272,10 @@
         <v>18</v>
       </c>
       <c r="N484" t="n">
-        <v>2986.6792727273</v>
+        <v>2832.1961818182</v>
       </c>
       <c r="O484" t="n">
-        <v>53760.2269090914</v>
+        <v>50979.5312727276</v>
       </c>
       <c r="P484" t="n">
         <v>12900</v>
@@ -22414,10 +22414,10 @@
         <v>8</v>
       </c>
       <c r="N487" t="n">
-        <v>18488.531333333</v>
+        <v>16313.41</v>
       </c>
       <c r="O487" t="n">
-        <v>147908.250666664</v>
+        <v>130507.28</v>
       </c>
       <c r="P487" t="n">
         <v>33500</v>
@@ -22702,10 +22702,10 @@
         <v>2</v>
       </c>
       <c r="N493" t="n">
-        <v>15985.015</v>
+        <v>13164.13</v>
       </c>
       <c r="O493" t="n">
-        <v>31970.03</v>
+        <v>26328.26</v>
       </c>
       <c r="P493" t="n">
         <v>39900</v>
@@ -22846,10 +22846,10 @@
         <v>15</v>
       </c>
       <c r="N496" t="n">
-        <v>9746.8802061856</v>
+        <v>9746.8802105263</v>
       </c>
       <c r="O496" t="n">
-        <v>146203.203092784</v>
+        <v>146203.2031578945</v>
       </c>
       <c r="P496" t="n">
         <v>18500</v>
@@ -24179,22 +24179,22 @@
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M524" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N524" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="O524" t="n">
-        <v>182537.931538455</v>
+        <v>0</v>
       </c>
       <c r="P524" t="n">
         <v>18900</v>
       </c>
       <c r="Q524" t="n">
-        <v>321300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -24269,22 +24269,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M526" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N526" t="n">
-        <v>43719.482857143</v>
+        <v>36004.28</v>
       </c>
       <c r="O526" t="n">
-        <v>480914.311428573</v>
+        <v>288034.24</v>
       </c>
       <c r="P526" t="n">
         <v>83500</v>
       </c>
       <c r="Q526" t="n">
-        <v>918500</v>
+        <v>668000</v>
       </c>
     </row>
     <row r="527">
@@ -25075,10 +25075,10 @@
         <v>73</v>
       </c>
       <c r="N543" t="n">
-        <v>5254.1635714286</v>
+        <v>5216.9</v>
       </c>
       <c r="O543" t="n">
-        <v>383553.9407142878</v>
+        <v>380833.7</v>
       </c>
       <c r="P543" t="n">
         <v>20500</v>
@@ -27038,10 +27038,10 @@
         <v>280</v>
       </c>
       <c r="N586" t="n">
-        <v>22951.704393305</v>
+        <v>22951.704377622</v>
       </c>
       <c r="O586" t="n">
-        <v>6426477.2301254</v>
+        <v>6426477.22573416</v>
       </c>
       <c r="P586" t="n">
         <v>37900</v>
@@ -28339,10 +28339,10 @@
         <v>3</v>
       </c>
       <c r="N614" t="n">
-        <v>16024.514074074</v>
+        <v>15452.21</v>
       </c>
       <c r="O614" t="n">
-        <v>48073.542222222</v>
+        <v>46356.63</v>
       </c>
       <c r="P614" t="n">
         <v>36500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q636"/>
+  <dimension ref="A1:Q635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -792,10 +792,10 @@
         <v>43</v>
       </c>
       <c r="N10" t="n">
-        <v>5758.9597772829</v>
+        <v>5758.9597767857</v>
       </c>
       <c r="O10" t="n">
-        <v>247635.2704231647</v>
+        <v>247635.2704017851</v>
       </c>
       <c r="P10" t="n">
         <v>16900</v>
@@ -1390,10 +1390,10 @@
         <v>120</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301973684</v>
+        <v>3716.3301980198</v>
       </c>
       <c r="O25" t="n">
-        <v>445959.623684208</v>
+        <v>445959.623762376</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1966,10 +1966,10 @@
         <v>46</v>
       </c>
       <c r="N39" t="n">
-        <v>141416.88463576</v>
+        <v>141416.88465116</v>
       </c>
       <c r="O39" t="n">
-        <v>6505176.69324496</v>
+        <v>6505176.69395336</v>
       </c>
       <c r="P39" t="n">
         <v>251900</v>
@@ -2013,10 +2013,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>344599.17805556</v>
+        <v>344599.178</v>
       </c>
       <c r="O40" t="n">
-        <v>3790590.95861116</v>
+        <v>3790590.958</v>
       </c>
       <c r="P40" t="n">
         <v>532900</v>
@@ -3951,10 +3951,10 @@
         <v>651</v>
       </c>
       <c r="N84" t="n">
-        <v>2586.3633253779</v>
+        <v>2582.2547091633</v>
       </c>
       <c r="O84" t="n">
-        <v>1683722.524821013</v>
+        <v>1681047.815665308</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -4043,10 +4043,10 @@
         <v>651</v>
       </c>
       <c r="N86" t="n">
-        <v>5216.8958101422</v>
+        <v>5216.8958023544</v>
       </c>
       <c r="O86" t="n">
-        <v>3396199.172402572</v>
+        <v>3396199.167332714</v>
       </c>
       <c r="P86" t="n">
         <v>8500</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4135,19 +4135,19 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="N88" t="n">
         <v>5503.85</v>
       </c>
       <c r="O88" t="n">
-        <v>539377.3</v>
+        <v>374261.8</v>
       </c>
       <c r="P88" t="n">
         <v>9500</v>
       </c>
       <c r="Q88" t="n">
-        <v>931000</v>
+        <v>646000</v>
       </c>
     </row>
     <row r="89">
@@ -4274,10 +4274,10 @@
         <v>3167</v>
       </c>
       <c r="N91" t="n">
-        <v>3158.8608436687</v>
+        <v>3158.8608437109</v>
       </c>
       <c r="O91" t="n">
-        <v>10004112.29189877</v>
+        <v>10004112.29203242</v>
       </c>
       <c r="P91" t="n">
         <v>5600</v>
@@ -4869,10 +4869,10 @@
         <v>581</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100076453</v>
+        <v>3795.7100076628</v>
       </c>
       <c r="O104" t="n">
-        <v>2205307.514441919</v>
+        <v>2205307.514452087</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5100,10 +5100,10 @@
         <v>1511297.387469964</v>
       </c>
       <c r="P109" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q109" t="n">
-        <v>2533800</v>
+        <v>2750100</v>
       </c>
     </row>
     <row r="110">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -5316,19 +5316,19 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="N114" t="n">
         <v>7041</v>
       </c>
       <c r="O114" t="n">
-        <v>4111944</v>
+        <v>4041534</v>
       </c>
       <c r="P114" t="n">
         <v>11500</v>
       </c>
       <c r="Q114" t="n">
-        <v>6716000</v>
+        <v>6601000</v>
       </c>
     </row>
     <row r="115">
@@ -5732,10 +5732,10 @@
         <v>518446</v>
       </c>
       <c r="P123" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q123" t="n">
-        <v>869200</v>
+        <v>943400</v>
       </c>
     </row>
     <row r="124">
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.276379862</v>
+        <v>3472.276393501</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.739431027</v>
+        <v>7270946.767991094</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -6504,10 +6504,10 @@
         <v>157</v>
       </c>
       <c r="N140" t="n">
-        <v>3041.6600151515</v>
+        <v>3041.660015186</v>
       </c>
       <c r="O140" t="n">
-        <v>477540.6223787855</v>
+        <v>477540.622384202</v>
       </c>
       <c r="P140" t="n">
         <v>5500</v>
@@ -6722,10 +6722,10 @@
         <v>181</v>
       </c>
       <c r="N145" t="n">
-        <v>1592.5643478261</v>
+        <v>1592.564335512</v>
       </c>
       <c r="O145" t="n">
-        <v>288254.1469565241</v>
+        <v>288254.144727672</v>
       </c>
       <c r="P145" t="n">
         <v>3900</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7800,19 +7800,19 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="N169" t="n">
         <v>8341.030000000001</v>
       </c>
       <c r="O169" t="n">
-        <v>633918.28</v>
+        <v>542166.9500000001</v>
       </c>
       <c r="P169" t="n">
         <v>13900</v>
       </c>
       <c r="Q169" t="n">
-        <v>1056400</v>
+        <v>903500</v>
       </c>
     </row>
     <row r="170">
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8418,19 +8418,19 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N182" t="n">
         <v>9903</v>
       </c>
       <c r="O182" t="n">
-        <v>1782540</v>
+        <v>1723122</v>
       </c>
       <c r="P182" t="n">
         <v>15900</v>
       </c>
       <c r="Q182" t="n">
-        <v>2862000</v>
+        <v>2766600</v>
       </c>
     </row>
     <row r="183">
@@ -8467,10 +8467,10 @@
         <v>337</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9251181364</v>
+        <v>1630.9251335113</v>
       </c>
       <c r="O183" t="n">
-        <v>549621.7648119668</v>
+        <v>549621.7699933081</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5229357459</v>
+        <v>2403.523063498</v>
       </c>
       <c r="O188" t="n">
-        <v>418212.9908197866</v>
+        <v>418213.013048652</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9643,10 +9643,10 @@
         <v>361</v>
       </c>
       <c r="N209" t="n">
-        <v>4196.8725467746</v>
+        <v>4196.8725524769</v>
       </c>
       <c r="O209" t="n">
-        <v>1515070.98938563</v>
+        <v>1515070.991444161</v>
       </c>
       <c r="P209" t="n">
         <v>5900</v>
@@ -10194,10 +10194,10 @@
         <v>155</v>
       </c>
       <c r="N222" t="n">
-        <v>2680.7396929825</v>
+        <v>2680.7396925972</v>
       </c>
       <c r="O222" t="n">
-        <v>415514.6524122875</v>
+        <v>415514.652352566</v>
       </c>
       <c r="P222" t="n">
         <v>4900</v>
@@ -10460,10 +10460,10 @@
         <v>918</v>
       </c>
       <c r="N228" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9881978301</v>
       </c>
       <c r="O228" t="n">
-        <v>5698933.168865096</v>
+        <v>5698933.165608032</v>
       </c>
       <c r="P228" t="n">
         <v>9900</v>
@@ -10555,10 +10555,10 @@
         <v>89</v>
       </c>
       <c r="N230" t="n">
-        <v>4285.1966145833</v>
+        <v>4285.1966318538</v>
       </c>
       <c r="O230" t="n">
-        <v>381382.4986979137</v>
+        <v>381382.5002349882</v>
       </c>
       <c r="P230" t="n">
         <v>6900</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10642,19 +10642,19 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N232" t="n">
         <v>8963</v>
       </c>
       <c r="O232" t="n">
-        <v>2375195</v>
+        <v>2348306</v>
       </c>
       <c r="P232" t="n">
         <v>15200</v>
       </c>
       <c r="Q232" t="n">
-        <v>4028000</v>
+        <v>3982400</v>
       </c>
     </row>
     <row r="233">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10683,19 +10683,19 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N233" t="n">
         <v>16275</v>
       </c>
       <c r="O233" t="n">
-        <v>781200</v>
+        <v>716100</v>
       </c>
       <c r="P233" t="n">
         <v>27600</v>
       </c>
       <c r="Q233" t="n">
-        <v>1324800</v>
+        <v>1214400</v>
       </c>
     </row>
     <row r="234">
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10811,19 +10811,19 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="N236" t="n">
-        <v>4814.2633516301</v>
+        <v>4814.2633494176</v>
       </c>
       <c r="O236" t="n">
-        <v>6065971.823053926</v>
+        <v>6008200.660073165</v>
       </c>
       <c r="P236" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="Q236" t="n">
-        <v>12474000</v>
+        <v>9859200</v>
       </c>
     </row>
     <row r="237">
@@ -10901,10 +10901,10 @@
         <v>32</v>
       </c>
       <c r="N238" t="n">
-        <v>11562.038381503</v>
+        <v>11562.038362573</v>
       </c>
       <c r="O238" t="n">
-        <v>369985.228208096</v>
+        <v>369985.227602336</v>
       </c>
       <c r="P238" t="n">
         <v>18500</v>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10944,19 +10944,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N239" t="n">
-        <v>13513.643727273</v>
+        <v>13513.644019608</v>
       </c>
       <c r="O239" t="n">
-        <v>229731.943363641</v>
+        <v>121622.796176472</v>
       </c>
       <c r="P239" t="n">
         <v>21900</v>
       </c>
       <c r="Q239" t="n">
-        <v>372300</v>
+        <v>197100</v>
       </c>
     </row>
     <row r="240">
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11210,19 +11210,19 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="N245" t="n">
         <v>4100.45</v>
       </c>
       <c r="O245" t="n">
-        <v>5396192.2</v>
+        <v>5371589.5</v>
       </c>
       <c r="P245" t="n">
         <v>26900</v>
       </c>
       <c r="Q245" t="n">
-        <v>35400400</v>
+        <v>35239000</v>
       </c>
     </row>
     <row r="246">
@@ -11259,10 +11259,10 @@
         <v>37</v>
       </c>
       <c r="N246" t="n">
-        <v>8332.7795967742</v>
+        <v>8332.7795945946</v>
       </c>
       <c r="O246" t="n">
-        <v>308312.8450806454</v>
+        <v>308312.8450000002</v>
       </c>
       <c r="P246" t="n">
         <v>14900</v>
@@ -11305,10 +11305,10 @@
         <v>420</v>
       </c>
       <c r="N247" t="n">
-        <v>1561.0074054054</v>
+        <v>1561.0125437573</v>
       </c>
       <c r="O247" t="n">
-        <v>655623.1102702681</v>
+        <v>655625.268378066</v>
       </c>
       <c r="P247" t="n">
         <v>2900</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12695,19 +12695,19 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="N277" t="n">
         <v>3920</v>
       </c>
       <c r="O277" t="n">
-        <v>1873760</v>
+        <v>1830640</v>
       </c>
       <c r="P277" t="n">
         <v>4900</v>
       </c>
       <c r="Q277" t="n">
-        <v>2342200</v>
+        <v>2288300</v>
       </c>
     </row>
     <row r="278">
@@ -13011,22 +13011,22 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
         <v>3</v>
       </c>
       <c r="N284" t="n">
-        <v>9456.2957818182</v>
+        <v>9188.98</v>
       </c>
       <c r="O284" t="n">
-        <v>28368.8873454546</v>
+        <v>27566.94</v>
       </c>
       <c r="P284" t="n">
         <v>12900</v>
@@ -14256,7 +14256,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14265,19 +14265,19 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N311" t="n">
         <v>28116</v>
       </c>
       <c r="O311" t="n">
-        <v>618552</v>
+        <v>56232</v>
       </c>
       <c r="P311" t="n">
         <v>45900</v>
       </c>
       <c r="Q311" t="n">
-        <v>1009800</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="312">
@@ -14394,22 +14394,22 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>9</v>
       </c>
       <c r="N314" t="n">
-        <v>10642.355555556</v>
+        <v>10411</v>
       </c>
       <c r="O314" t="n">
-        <v>95781.200000004</v>
+        <v>93699</v>
       </c>
       <c r="P314" t="n">
         <v>16900</v>
@@ -14950,7 +14950,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -14959,19 +14959,19 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N326" t="n">
         <v>9003</v>
       </c>
       <c r="O326" t="n">
-        <v>1251417</v>
+        <v>1215405</v>
       </c>
       <c r="P326" t="n">
         <v>14900</v>
       </c>
       <c r="Q326" t="n">
-        <v>2071100</v>
+        <v>2011500</v>
       </c>
     </row>
     <row r="327">
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15005,19 +15005,19 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N327" t="n">
         <v>9178</v>
       </c>
       <c r="O327" t="n">
-        <v>1578616</v>
+        <v>1560260</v>
       </c>
       <c r="P327" t="n">
         <v>14900</v>
       </c>
       <c r="Q327" t="n">
-        <v>2562800</v>
+        <v>2533000</v>
       </c>
     </row>
     <row r="328">
@@ -15330,10 +15330,10 @@
         <v>118</v>
       </c>
       <c r="N334" t="n">
-        <v>4907.8228222222</v>
+        <v>4907.8228863636</v>
       </c>
       <c r="O334" t="n">
-        <v>579123.0930222196</v>
+        <v>579123.1005909048</v>
       </c>
       <c r="P334" t="n">
         <v>8200</v>
@@ -15514,10 +15514,10 @@
         <v>240</v>
       </c>
       <c r="N338" t="n">
-        <v>3903.7403351955</v>
+        <v>3903.7404686036</v>
       </c>
       <c r="O338" t="n">
-        <v>936897.68044692</v>
+        <v>936897.712464864</v>
       </c>
       <c r="P338" t="n">
         <v>7500</v>
@@ -15589,22 +15589,22 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
         <v>10</v>
       </c>
       <c r="N340" t="n">
-        <v>35444.444444444</v>
+        <v>33000</v>
       </c>
       <c r="O340" t="n">
-        <v>354444.44444444</v>
+        <v>330000</v>
       </c>
       <c r="P340" t="n">
         <v>52900</v>
@@ -15693,10 +15693,10 @@
         <v>24</v>
       </c>
       <c r="N342" t="n">
-        <v>5869.1723052295</v>
+        <v>5869.1722639485</v>
       </c>
       <c r="O342" t="n">
-        <v>140860.135325508</v>
+        <v>140860.134334764</v>
       </c>
       <c r="P342" t="n">
         <v>9500</v>
@@ -17490,10 +17490,10 @@
         <v>1008</v>
       </c>
       <c r="N381" t="n">
-        <v>1516.0386990066</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O381" t="n">
-        <v>1528167.008598653</v>
+        <v>1528167.006933336</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
@@ -17674,10 +17674,10 @@
         <v>96</v>
       </c>
       <c r="N385" t="n">
-        <v>2056.081010453</v>
+        <v>2056.0810065359</v>
       </c>
       <c r="O385" t="n">
-        <v>197383.777003488</v>
+        <v>197383.7766274464</v>
       </c>
       <c r="P385" t="n">
         <v>2900</v>
@@ -17950,10 +17950,10 @@
         <v>224</v>
       </c>
       <c r="N391" t="n">
-        <v>1592.2887446809</v>
+        <v>1592.2892358079</v>
       </c>
       <c r="O391" t="n">
-        <v>356672.6788085216</v>
+        <v>356672.7888209696</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -18127,10 +18127,10 @@
         <v>400</v>
       </c>
       <c r="N395" t="n">
-        <v>1259.2751769231</v>
+        <v>1259.2751809084</v>
       </c>
       <c r="O395" t="n">
-        <v>503710.07076924</v>
+        <v>503710.07236336</v>
       </c>
       <c r="P395" t="n">
         <v>1900</v>
@@ -18304,10 +18304,10 @@
         <v>504</v>
       </c>
       <c r="N399" t="n">
-        <v>692.15254743047</v>
+        <v>692.15255307366</v>
       </c>
       <c r="O399" t="n">
-        <v>348844.8839049569</v>
+        <v>348844.8867491246</v>
       </c>
       <c r="P399" t="n">
         <v>1200</v>
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -18638,19 +18638,19 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N406" t="n">
         <v>44470</v>
       </c>
       <c r="O406" t="n">
-        <v>1556450</v>
+        <v>1423040</v>
       </c>
       <c r="P406" t="n">
         <v>71900</v>
       </c>
       <c r="Q406" t="n">
-        <v>2516500</v>
+        <v>2300800</v>
       </c>
     </row>
     <row r="407">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -18687,19 +18687,19 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="N407" t="n">
         <v>5215</v>
       </c>
       <c r="O407" t="n">
-        <v>4563125</v>
+        <v>4437965</v>
       </c>
       <c r="P407" t="n">
         <v>8900</v>
       </c>
       <c r="Q407" t="n">
-        <v>7787500</v>
+        <v>7573900</v>
       </c>
     </row>
     <row r="408">
@@ -19058,10 +19058,10 @@
         <v>877</v>
       </c>
       <c r="N415" t="n">
-        <v>8949.4124778362</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O415" t="n">
-        <v>7848634.743062347</v>
+        <v>7845098.259999999</v>
       </c>
       <c r="P415" t="n">
         <v>14900</v>
@@ -19705,10 +19705,10 @@
         <v>306</v>
       </c>
       <c r="N429" t="n">
-        <v>1690.8700097895</v>
+        <v>1690.8700098184</v>
       </c>
       <c r="O429" t="n">
-        <v>517406.222995587</v>
+        <v>517406.2230044304</v>
       </c>
       <c r="P429" t="n">
         <v>3000</v>
@@ -21278,10 +21278,10 @@
         <v>17742</v>
       </c>
       <c r="N463" t="n">
-        <v>703.7945904135599</v>
+        <v>703.79458486774</v>
       </c>
       <c r="O463" t="n">
-        <v>12486723.62311738</v>
+        <v>12486723.52472344</v>
       </c>
       <c r="P463" t="n">
         <v>900</v>
@@ -21456,7 +21456,7 @@
         </is>
       </c>
       <c r="J467" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -21465,19 +21465,19 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N467" t="n">
         <v>14260.14</v>
       </c>
       <c r="O467" t="n">
-        <v>370763.64</v>
+        <v>299462.94</v>
       </c>
       <c r="P467" t="n">
         <v>15900</v>
       </c>
       <c r="Q467" t="n">
-        <v>413400</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="468">
@@ -22402,7 +22402,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -22411,19 +22411,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N487" t="n">
         <v>16313.41</v>
       </c>
       <c r="O487" t="n">
-        <v>130507.28</v>
+        <v>97880.45999999999</v>
       </c>
       <c r="P487" t="n">
         <v>33500</v>
       </c>
       <c r="Q487" t="n">
-        <v>268000</v>
+        <v>201000</v>
       </c>
     </row>
     <row r="488">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -22843,19 +22843,19 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N496" t="n">
         <v>9746.8802105263</v>
       </c>
       <c r="O496" t="n">
-        <v>146203.2031578945</v>
+        <v>116962.5625263156</v>
       </c>
       <c r="P496" t="n">
         <v>18500</v>
       </c>
       <c r="Q496" t="n">
-        <v>277500</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="497">
@@ -23789,7 +23789,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -23798,19 +23798,19 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N516" t="n">
         <v>10378.12</v>
       </c>
       <c r="O516" t="n">
-        <v>373612.32</v>
+        <v>363234.2</v>
       </c>
       <c r="P516" t="n">
         <v>13500</v>
       </c>
       <c r="Q516" t="n">
-        <v>486000</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="517">
@@ -24151,73 +24151,70 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>C7448</t>
+          <t>C745</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>1263626363211</v>
+        <v>8596162180343</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>CAMION JAULA C7448</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>CARROS</t>
+          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J524" t="n">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="N524" t="n">
-        <v>19429.807619048</v>
+        <v>3097.9492241379</v>
       </c>
       <c r="O524" t="n">
-        <v>0</v>
+        <v>405831.3483620649</v>
       </c>
       <c r="P524" t="n">
-        <v>18900</v>
+        <v>2400</v>
       </c>
       <c r="Q524" t="n">
-        <v>0</v>
+        <v>314400</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>C745</t>
-        </is>
-      </c>
-      <c r="B525" t="n">
-        <v>8596162180343</v>
+          <t>C7458</t>
+        </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
+          <t>COCINA EN CAJA C7458</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J525" t="n">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24226,35 +24223,38 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="N525" t="n">
-        <v>3097.9492241379</v>
+        <v>36004.28</v>
       </c>
       <c r="O525" t="n">
-        <v>405831.3483620649</v>
+        <v>180021.4</v>
       </c>
       <c r="P525" t="n">
-        <v>2400</v>
+        <v>83500</v>
       </c>
       <c r="Q525" t="n">
-        <v>314400</v>
+        <v>417500</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>C7458</t>
-        </is>
+          <t>C7459</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>3790120020022</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>COCINA EN CAJA C7458</t>
+          <t>PIANO MUSICAL LEONCITO C7459</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -24263,47 +24263,44 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N526" t="n">
-        <v>36004.28</v>
+        <v>7258.5</v>
       </c>
       <c r="O526" t="n">
-        <v>288034.24</v>
+        <v>14517</v>
       </c>
       <c r="P526" t="n">
-        <v>83500</v>
+        <v>17500</v>
       </c>
       <c r="Q526" t="n">
-        <v>668000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>C7459</t>
-        </is>
-      </c>
-      <c r="B527" t="n">
-        <v>3790120020022</v>
+          <t>C7462</t>
+        </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>PIANO MUSICAL LEONCITO C7459</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -24312,7 +24309,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24321,30 +24318,30 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N527" t="n">
-        <v>7258.5</v>
+        <v>14751.820377358</v>
       </c>
       <c r="O527" t="n">
-        <v>21775.5</v>
+        <v>132766.383396222</v>
       </c>
       <c r="P527" t="n">
-        <v>17500</v>
+        <v>37100</v>
       </c>
       <c r="Q527" t="n">
-        <v>52500</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>C7462</t>
+          <t>C7463</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>DINOSAURIO C7463</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -24358,7 +24355,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24367,35 +24364,35 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N528" t="n">
-        <v>14751.820377358</v>
+        <v>9372</v>
       </c>
       <c r="O528" t="n">
-        <v>132766.383396222</v>
+        <v>112464</v>
       </c>
       <c r="P528" t="n">
-        <v>37100</v>
+        <v>17900</v>
       </c>
       <c r="Q528" t="n">
-        <v>333900</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>C7463</t>
+          <t>C7470</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>DINOSAURIO C7463</t>
+          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -24404,7 +24401,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24413,30 +24410,33 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N529" t="n">
-        <v>9372</v>
+        <v>14170.65</v>
       </c>
       <c r="O529" t="n">
-        <v>112464</v>
+        <v>340095.6</v>
       </c>
       <c r="P529" t="n">
-        <v>17900</v>
+        <v>49000</v>
       </c>
       <c r="Q529" t="n">
-        <v>214800</v>
+        <v>1176000</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>C7470</t>
-        </is>
+          <t>C7471</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>6973673170247</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
+          <t>CARRO METALICO COLECCION TOYOTA PRADO C7471</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -24450,7 +24450,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24459,33 +24459,33 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N530" t="n">
-        <v>14170.65</v>
+        <v>13168.16</v>
       </c>
       <c r="O530" t="n">
-        <v>340095.6</v>
+        <v>105345.28</v>
       </c>
       <c r="P530" t="n">
         <v>49000</v>
       </c>
       <c r="Q530" t="n">
-        <v>1176000</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>C7471</t>
+          <t>C7473</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>6973673170247</v>
+        <v>6896896988512500</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION TOYOTA PRADO C7471</t>
+          <t>CARRO METALICO COLECCIO TOYOTA MODEL C7473</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -24499,7 +24499,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24508,33 +24508,33 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="N531" t="n">
-        <v>13168.16</v>
+        <v>10504.37</v>
       </c>
       <c r="O531" t="n">
-        <v>105345.28</v>
+        <v>546227.24</v>
       </c>
       <c r="P531" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q531" t="n">
-        <v>392000</v>
+        <v>2340000</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>C7473</t>
+          <t>C7474</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>6896896988512500</v>
+        <v>6896988512529</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCIO TOYOTA MODEL C7473</t>
+          <t>CARRO METALICO COLECCION CHELVI GT500 C7474</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -24548,7 +24548,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24557,33 +24557,33 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="N532" t="n">
-        <v>10504.37</v>
+        <v>9526.51</v>
       </c>
       <c r="O532" t="n">
-        <v>546227.24</v>
+        <v>304848.32</v>
       </c>
       <c r="P532" t="n">
         <v>45000</v>
       </c>
       <c r="Q532" t="n">
-        <v>2340000</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>C7474</t>
+          <t>C7475</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>6896988512529</v>
+        <v>6896988512536</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION CHELVI GT500 C7474</t>
+          <t>CARRO METALICO COLECCION BMW C7475</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24606,33 +24606,30 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="N533" t="n">
-        <v>9526.51</v>
+        <v>10798.03</v>
       </c>
       <c r="O533" t="n">
-        <v>304848.32</v>
+        <v>431921.2</v>
       </c>
       <c r="P533" t="n">
         <v>45000</v>
       </c>
       <c r="Q533" t="n">
-        <v>1440000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>C7475</t>
-        </is>
-      </c>
-      <c r="B534" t="n">
-        <v>6896988512536</v>
+          <t>C7479</t>
+        </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7475</t>
+          <t>CARRO COLECCION METALICO MERCEDES C7479</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -24646,7 +24643,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24655,30 +24652,30 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="N534" t="n">
-        <v>10798.03</v>
+        <v>8473.91</v>
       </c>
       <c r="O534" t="n">
-        <v>431921.2</v>
+        <v>135582.56</v>
       </c>
       <c r="P534" t="n">
-        <v>45000</v>
+        <v>49000</v>
       </c>
       <c r="Q534" t="n">
-        <v>1800000</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>C7479</t>
+          <t>C7480</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCEDES C7479</t>
+          <t>CARRO METALICO COLECCION BMW C7480</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -24704,10 +24701,10 @@
         <v>16</v>
       </c>
       <c r="N535" t="n">
-        <v>8473.91</v>
+        <v>10541.34</v>
       </c>
       <c r="O535" t="n">
-        <v>135582.56</v>
+        <v>168661.44</v>
       </c>
       <c r="P535" t="n">
         <v>49000</v>
@@ -24719,12 +24716,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>C7480</t>
+          <t>C7481</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7480</t>
+          <t>CARRO COLECCION METALICO AUDI A7 C7481</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -24738,7 +24735,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24747,30 +24744,30 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N536" t="n">
-        <v>10541.34</v>
+        <v>6006.77</v>
       </c>
       <c r="O536" t="n">
-        <v>168661.44</v>
+        <v>216243.72</v>
       </c>
       <c r="P536" t="n">
         <v>49000</v>
       </c>
       <c r="Q536" t="n">
-        <v>784000</v>
+        <v>1764000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>C7481</t>
+          <t>C7482</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO AUDI A7 C7481</t>
+          <t>CARRO METALICO COLECCION BMW C7482</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -24784,7 +24781,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24793,30 +24790,30 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="N537" t="n">
-        <v>6006.77</v>
+        <v>7205.37</v>
       </c>
       <c r="O537" t="n">
-        <v>216243.72</v>
+        <v>86464.44</v>
       </c>
       <c r="P537" t="n">
         <v>49000</v>
       </c>
       <c r="Q537" t="n">
-        <v>1764000</v>
+        <v>588000</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>C7482</t>
+          <t>C7483</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7482</t>
+          <t>CARRO COLECCION METALICO TOYOTA C7483</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -24830,7 +24827,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24839,30 +24836,30 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N538" t="n">
-        <v>7205.37</v>
+        <v>9031.370000000001</v>
       </c>
       <c r="O538" t="n">
-        <v>86464.44</v>
+        <v>72250.96000000001</v>
       </c>
       <c r="P538" t="n">
         <v>49000</v>
       </c>
       <c r="Q538" t="n">
-        <v>588000</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>C7483</t>
+          <t>C7484</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO TOYOTA C7483</t>
+          <t>CARRO COLECCION METALICO MERCEDES AMG C7484</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -24876,7 +24873,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24885,30 +24882,30 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N539" t="n">
-        <v>9031.370000000001</v>
+        <v>7884.67</v>
       </c>
       <c r="O539" t="n">
-        <v>72250.96000000001</v>
+        <v>47308.02</v>
       </c>
       <c r="P539" t="n">
         <v>49000</v>
       </c>
       <c r="Q539" t="n">
-        <v>392000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>C7484</t>
+          <t>C7486</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCEDES AMG C7484</t>
+          <t>CARRO COLECCCION METALICO TESLA C7486</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -24922,7 +24919,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24931,35 +24928,38 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="N540" t="n">
-        <v>7884.67</v>
+        <v>6529.54</v>
       </c>
       <c r="O540" t="n">
-        <v>47308.02</v>
+        <v>261181.6</v>
       </c>
       <c r="P540" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q540" t="n">
-        <v>294000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>C7486</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>CARRO COLECCCION METALICO TESLA C7486</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24968,7 +24968,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24977,38 +24977,35 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N541" t="n">
-        <v>6529.54</v>
+        <v>8919.16</v>
       </c>
       <c r="O541" t="n">
-        <v>261181.6</v>
+        <v>552987.92</v>
       </c>
       <c r="P541" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="Q541" t="n">
-        <v>1800000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>C7488</t>
-        </is>
-      </c>
-      <c r="B542" t="n">
-        <v>6945158254520</v>
+          <t>C7503</t>
+        </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>BOLSO ALAS CON ACCESORIOS DE BELLEZA C7503</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -25017,7 +25014,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -25026,30 +25023,33 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="N542" t="n">
-        <v>8919.16</v>
+        <v>5216.9</v>
       </c>
       <c r="O542" t="n">
-        <v>552987.92</v>
+        <v>380833.7</v>
       </c>
       <c r="P542" t="n">
-        <v>10000</v>
+        <v>20500</v>
       </c>
       <c r="Q542" t="n">
-        <v>620000</v>
+        <v>1496500</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>C7503</t>
-        </is>
+          <t>C7513</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>6905698382824</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>BOLSO ALAS CON ACCESORIOS DE BELLEZA C7503</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -25063,7 +25063,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -25072,33 +25072,33 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="N543" t="n">
-        <v>5216.9</v>
+        <v>1024.29</v>
       </c>
       <c r="O543" t="n">
-        <v>380833.7</v>
+        <v>158764.95</v>
       </c>
       <c r="P543" t="n">
-        <v>20500</v>
+        <v>2900</v>
       </c>
       <c r="Q543" t="n">
-        <v>1496500</v>
+        <v>449500</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C7514</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>6905698382824</v>
+        <v>6905698386815</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
+          <t>SONAJERO LUZ BOLSA C7514</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -25112,7 +25112,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>155</v>
+        <v>664</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -25121,33 +25121,33 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>155</v>
+        <v>664</v>
       </c>
       <c r="N544" t="n">
-        <v>1024.29</v>
+        <v>711.48</v>
       </c>
       <c r="O544" t="n">
-        <v>158764.95</v>
+        <v>472422.72</v>
       </c>
       <c r="P544" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q544" t="n">
-        <v>449500</v>
+        <v>1660000</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>C7514</t>
+          <t>C7517</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>6905698386815</v>
+        <v>9872447770119</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ BOLSA C7514</t>
+          <t>SET HERRAMIENTA EN BOLSA C7517</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -25161,7 +25161,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -25170,47 +25170,42 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="N545" t="n">
-        <v>711.48</v>
+        <v>1278.27</v>
       </c>
       <c r="O545" t="n">
-        <v>472422.72</v>
+        <v>3834.81</v>
       </c>
       <c r="P545" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="Q545" t="n">
-        <v>1660000</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>C7517</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>9872447770119</v>
+        <v>8596162180497</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>SET HERRAMIENTA EN BOLSA C7517</t>
-        </is>
-      </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J546" t="n">
-        <v>3</v>
+        <v>619</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25219,42 +25214,47 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>3</v>
+        <v>619</v>
       </c>
       <c r="N546" t="n">
-        <v>1278.27</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O546" t="n">
-        <v>3834.81</v>
+        <v>720358.0180402457</v>
       </c>
       <c r="P546" t="n">
-        <v>5900</v>
+        <v>1500</v>
       </c>
       <c r="Q546" t="n">
-        <v>17700</v>
+        <v>928500</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7524</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>8596162180497</v>
+        <v>6905454130201</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J547" t="n">
-        <v>619</v>
+        <v>300</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25263,38 +25263,38 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>619</v>
+        <v>300</v>
       </c>
       <c r="N547" t="n">
-        <v>1163.7447787403</v>
+        <v>1934.77</v>
       </c>
       <c r="O547" t="n">
-        <v>720358.0180402457</v>
+        <v>580431</v>
       </c>
       <c r="P547" t="n">
-        <v>1500</v>
+        <v>8900</v>
       </c>
       <c r="Q547" t="n">
-        <v>928500</v>
+        <v>2670000</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>C7524</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>6905454130201</v>
+        <v>6951241752002</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>300</v>
+        <v>1085</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25312,38 +25312,35 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>300</v>
+        <v>1085</v>
       </c>
       <c r="N548" t="n">
-        <v>1934.77</v>
+        <v>7046.9398262758</v>
       </c>
       <c r="O548" t="n">
-        <v>580431</v>
+        <v>7645929.711509244</v>
       </c>
       <c r="P548" t="n">
-        <v>8900</v>
+        <v>9900</v>
       </c>
       <c r="Q548" t="n">
-        <v>2670000</v>
+        <v>10741500</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B549" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -25352,7 +25349,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>1085</v>
+        <v>116</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25361,35 +25358,38 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>1085</v>
+        <v>116</v>
       </c>
       <c r="N549" t="n">
-        <v>7046.9398262758</v>
+        <v>24338.47</v>
       </c>
       <c r="O549" t="n">
-        <v>7645929.711509244</v>
+        <v>2823262.52</v>
       </c>
       <c r="P549" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q549" t="n">
-        <v>10741500</v>
+        <v>3236400</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C7555-B</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>6970635795388</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25407,38 +25407,35 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="N550" t="n">
-        <v>24338.47</v>
+        <v>16146.498181818</v>
       </c>
       <c r="O550" t="n">
-        <v>2823262.52</v>
+        <v>16146.498181818</v>
       </c>
       <c r="P550" t="n">
-        <v>27900</v>
+        <v>26900</v>
       </c>
       <c r="Q550" t="n">
-        <v>3236400</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>C7555-B</t>
-        </is>
-      </c>
-      <c r="B551" t="n">
-        <v>6970635795388</v>
+          <t>C7561-AB</t>
+        </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
+          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -25447,7 +25444,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25456,35 +25453,38 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N551" t="n">
-        <v>16146.498181818</v>
+        <v>38508.28</v>
       </c>
       <c r="O551" t="n">
-        <v>16146.498181818</v>
+        <v>924198.72</v>
       </c>
       <c r="P551" t="n">
-        <v>26900</v>
+        <v>40000</v>
       </c>
       <c r="Q551" t="n">
-        <v>26900</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>C7561-AB</t>
-        </is>
+          <t>C7586</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>7808880075865</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
+          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -25493,7 +25493,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>24</v>
+        <v>648</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25502,33 +25502,33 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>24</v>
+        <v>648</v>
       </c>
       <c r="N552" t="n">
-        <v>38508.28</v>
+        <v>665.3240434332999</v>
       </c>
       <c r="O552" t="n">
-        <v>924198.72</v>
+        <v>431129.9801447784</v>
       </c>
       <c r="P552" t="n">
-        <v>40000</v>
+        <v>2900</v>
       </c>
       <c r="Q552" t="n">
-        <v>960000</v>
+        <v>1879200</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>C7586</t>
+          <t>C7587</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>7808880075865</v>
+        <v>7587228020247</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
+          <t>TROMPO LUCES DEPORTES C7587</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -25542,7 +25542,7 @@
         </is>
       </c>
       <c r="J553" t="n">
-        <v>648</v>
+        <v>256</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25551,33 +25551,33 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>648</v>
+        <v>256</v>
       </c>
       <c r="N553" t="n">
-        <v>665.3240434332999</v>
+        <v>1080.18</v>
       </c>
       <c r="O553" t="n">
-        <v>431129.9801447784</v>
+        <v>276526.08</v>
       </c>
       <c r="P553" t="n">
-        <v>2900</v>
+        <v>4900</v>
       </c>
       <c r="Q553" t="n">
-        <v>1879200</v>
+        <v>1254400</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>C7587</t>
+          <t>C7588</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>7587228020247</v>
+        <v>7588228020244</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>TROMPO LUCES DEPORTES C7587</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -25591,7 +25591,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>256</v>
+        <v>720</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25600,38 +25600,38 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>256</v>
+        <v>720</v>
       </c>
       <c r="N554" t="n">
-        <v>1080.18</v>
+        <v>641.78</v>
       </c>
       <c r="O554" t="n">
-        <v>276526.08</v>
+        <v>462081.6</v>
       </c>
       <c r="P554" t="n">
-        <v>4900</v>
+        <v>2500</v>
       </c>
       <c r="Q554" t="n">
-        <v>1254400</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>720</v>
+        <v>550</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25649,33 +25649,33 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>720</v>
+        <v>550</v>
       </c>
       <c r="N555" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O555" t="n">
-        <v>462081.6</v>
+        <v>4296545</v>
       </c>
       <c r="P555" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q555" t="n">
-        <v>1800000</v>
+        <v>7645000</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA PATO C7614</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -25689,7 +25689,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25698,25 +25698,25 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="N556" t="n">
-        <v>7811.9</v>
+        <v>4581.84</v>
       </c>
       <c r="O556" t="n">
-        <v>4296545</v>
+        <v>229092</v>
       </c>
       <c r="P556" t="n">
-        <v>13900</v>
+        <v>7900</v>
       </c>
       <c r="Q556" t="n">
-        <v>7645000</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>C7614</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -25724,12 +25724,12 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA PATO C7614</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -25738,7 +25738,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25747,38 +25747,35 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="N557" t="n">
-        <v>4581.84</v>
+        <v>3155</v>
       </c>
       <c r="O557" t="n">
-        <v>229092</v>
+        <v>558435</v>
       </c>
       <c r="P557" t="n">
-        <v>7900</v>
+        <v>5900</v>
       </c>
       <c r="Q557" t="n">
-        <v>395000</v>
+        <v>1044300</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>C7614-F</t>
-        </is>
-      </c>
-      <c r="B558" t="n">
-        <v>6999899236130</v>
+          <t>C7615</t>
+        </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
+          <t>CHALECO PISCINA ALITAS C7615</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -25787,7 +25784,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25796,30 +25793,33 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="N558" t="n">
-        <v>3155</v>
+        <v>1262.07</v>
       </c>
       <c r="O558" t="n">
-        <v>558435</v>
+        <v>277655.4</v>
       </c>
       <c r="P558" t="n">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="Q558" t="n">
-        <v>1044300</v>
+        <v>1958000</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>C7615</t>
-        </is>
+          <t>C7617</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>6999899236192</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>CHALECO PISCINA ALITAS C7615</t>
+          <t>BRAZITOS PISCINA #A 12PCS</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -25833,7 +25833,7 @@
         </is>
       </c>
       <c r="J559" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25842,33 +25842,33 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="N559" t="n">
-        <v>1262.07</v>
+        <v>540.40123762376</v>
       </c>
       <c r="O559" t="n">
-        <v>277655.4</v>
+        <v>6484.81485148512</v>
       </c>
       <c r="P559" t="n">
-        <v>8900</v>
+        <v>2500</v>
       </c>
       <c r="Q559" t="n">
-        <v>1958000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>C7617</t>
+          <t>C7618</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>6999899236192</v>
+        <v>6999899236208</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>BRAZITOS PISCINA #A 12PCS</t>
+          <t>BRAZITO PISCINA  27X17 C7618</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -25882,7 +25882,7 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
@@ -25891,33 +25891,33 @@
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N560" t="n">
-        <v>540.40123762376</v>
+        <v>616.4</v>
       </c>
       <c r="O560" t="n">
-        <v>6484.81485148512</v>
+        <v>616.4</v>
       </c>
       <c r="P560" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q560" t="n">
-        <v>30000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>C7618</t>
+          <t>C7631</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>6999899236208</v>
+        <v>6999899236352</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>BRAZITO PISCINA  27X17 C7618</t>
+          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -25931,7 +25931,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25940,47 +25940,39 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="N561" t="n">
-        <v>616.4</v>
+        <v>315.02766929134</v>
       </c>
       <c r="O561" t="n">
-        <v>616.4</v>
+        <v>29927.6285826773</v>
       </c>
       <c r="P561" t="n">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="Q561" t="n">
-        <v>2900</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>C7631</t>
-        </is>
-      </c>
-      <c r="B562" t="n">
-        <v>6999899236352</v>
+          <t>C766</t>
+        </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
-        </is>
-      </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>DOMIN PEQUEO</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J562" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
@@ -25989,30 +25981,30 @@
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="N562" t="n">
-        <v>315.02766929134</v>
+        <v>2752.52</v>
       </c>
       <c r="O562" t="n">
-        <v>29927.6285826773</v>
+        <v>38535.28</v>
       </c>
       <c r="P562" t="n">
-        <v>2200</v>
+        <v>4500</v>
       </c>
       <c r="Q562" t="n">
-        <v>209000</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>C766</t>
+          <t>C771</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>DOMIN PEQUEO</t>
+          <t>GLOBO LOVE YOU</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -26021,7 +26013,7 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -26030,30 +26022,33 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="N563" t="n">
-        <v>2752.52</v>
+        <v>1244.5992565056</v>
       </c>
       <c r="O563" t="n">
-        <v>38535.28</v>
+        <v>88366.54721189759</v>
       </c>
       <c r="P563" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="Q563" t="n">
-        <v>63000</v>
+        <v>106500</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>C771</t>
-        </is>
+          <t>C773</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>2021071411128</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>GLOBO LOVE YOU</t>
+          <t>GLOBO HBD 32</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -26062,7 +26057,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -26071,42 +26066,47 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="N564" t="n">
-        <v>1244.5992565056</v>
+        <v>2703.2000014451</v>
       </c>
       <c r="O564" t="n">
-        <v>88366.54721189759</v>
+        <v>113534.4000606942</v>
       </c>
       <c r="P564" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="Q564" t="n">
-        <v>106500</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>C773</t>
+          <t>C80-IO</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>2021071411128</v>
+        <v>6524521011221</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>GLOBO HBD 32</t>
+          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J565" t="n">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="K565" t="n">
         <v>0</v>
@@ -26115,47 +26115,39 @@
         <v>0</v>
       </c>
       <c r="M565" t="n">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="N565" t="n">
-        <v>2703.2000014451</v>
+        <v>2235.19</v>
       </c>
       <c r="O565" t="n">
-        <v>113534.4000606942</v>
+        <v>695144.09</v>
       </c>
       <c r="P565" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="Q565" t="n">
-        <v>189000</v>
+        <v>933000</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>C80-IO</t>
-        </is>
-      </c>
-      <c r="B566" t="n">
-        <v>6524521011221</v>
+          <t>C815</t>
+        </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
-        </is>
-      </c>
-      <c r="E566" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J566" t="n">
-        <v>311</v>
+        <v>12</v>
       </c>
       <c r="K566" t="n">
         <v>0</v>
@@ -26164,30 +26156,33 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>311</v>
+        <v>12</v>
       </c>
       <c r="N566" t="n">
-        <v>2235.19</v>
+        <v>110520.77</v>
       </c>
       <c r="O566" t="n">
-        <v>695144.09</v>
+        <v>1326249.24</v>
       </c>
       <c r="P566" t="n">
-        <v>3000</v>
+        <v>176900</v>
       </c>
       <c r="Q566" t="n">
-        <v>933000</v>
+        <v>2122800</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>C815</t>
-        </is>
+          <t>C819</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>2087202108190</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -26196,7 +26191,7 @@
         </is>
       </c>
       <c r="J567" t="n">
-        <v>12</v>
+        <v>600</v>
       </c>
       <c r="K567" t="n">
         <v>0</v>
@@ -26205,33 +26200,30 @@
         <v>0</v>
       </c>
       <c r="M567" t="n">
-        <v>12</v>
+        <v>600</v>
       </c>
       <c r="N567" t="n">
-        <v>110520.77</v>
+        <v>6761.25</v>
       </c>
       <c r="O567" t="n">
-        <v>1326249.24</v>
+        <v>4056750</v>
       </c>
       <c r="P567" t="n">
-        <v>176900</v>
+        <v>5200</v>
       </c>
       <c r="Q567" t="n">
-        <v>2122800</v>
+        <v>3120000</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B568" t="n">
-        <v>2087202108190</v>
+          <t>C822</t>
+        </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -26240,7 +26232,7 @@
         </is>
       </c>
       <c r="J568" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="K568" t="n">
         <v>0</v>
@@ -26249,30 +26241,33 @@
         <v>0</v>
       </c>
       <c r="M568" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="N568" t="n">
-        <v>6761.25</v>
+        <v>5577.2680373832</v>
       </c>
       <c r="O568" t="n">
-        <v>4056750</v>
+        <v>167318.041121496</v>
       </c>
       <c r="P568" t="n">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="Q568" t="n">
-        <v>3120000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>C822</t>
-        </is>
+          <t>C828</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>6900159908285</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
+          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -26281,7 +26276,7 @@
         </is>
       </c>
       <c r="J569" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K569" t="n">
         <v>0</v>
@@ -26290,33 +26285,33 @@
         <v>0</v>
       </c>
       <c r="M569" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N569" t="n">
-        <v>5577.2680373832</v>
+        <v>6243.3531884058</v>
       </c>
       <c r="O569" t="n">
-        <v>167318.041121496</v>
+        <v>249734.127536232</v>
       </c>
       <c r="P569" t="n">
-        <v>6500</v>
+        <v>9900</v>
       </c>
       <c r="Q569" t="n">
-        <v>195000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>C828</t>
+          <t>C848</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>6900159908285</v>
+        <v>6900159908483</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
+          <t>BLOBO GRANDE SORPRESA NINONINA</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -26325,7 +26320,7 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K570" t="n">
         <v>0</v>
@@ -26334,33 +26329,30 @@
         <v>0</v>
       </c>
       <c r="M570" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="N570" t="n">
-        <v>6243.3531884058</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O570" t="n">
-        <v>249734.127536232</v>
+        <v>224025.773659551</v>
       </c>
       <c r="P570" t="n">
-        <v>9900</v>
+        <v>3000</v>
       </c>
       <c r="Q570" t="n">
-        <v>396000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>C848</t>
-        </is>
-      </c>
-      <c r="B571" t="n">
-        <v>6900159908483</v>
+          <t>C855</t>
+        </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>BLOBO GRANDE SORPRESA NINONINA</t>
+          <t>GLOBOS BUQUET CERVEZA</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -26369,7 +26361,7 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K571" t="n">
         <v>0</v>
@@ -26378,30 +26370,30 @@
         <v>0</v>
       </c>
       <c r="M571" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="N571" t="n">
-        <v>2489.1752628839</v>
+        <v>2129.8331743119</v>
       </c>
       <c r="O571" t="n">
-        <v>224025.773659551</v>
+        <v>42596.663486238</v>
       </c>
       <c r="P571" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="Q571" t="n">
-        <v>270000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>C855</t>
+          <t>C863</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>GLOBOS BUQUET CERVEZA</t>
+          <t>GLOBOS BOUQUET FELIZ DIA</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -26410,7 +26402,7 @@
         </is>
       </c>
       <c r="J572" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K572" t="n">
         <v>0</v>
@@ -26419,30 +26411,30 @@
         <v>0</v>
       </c>
       <c r="M572" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N572" t="n">
-        <v>2129.8331743119</v>
+        <v>5497.1752906977</v>
       </c>
       <c r="O572" t="n">
-        <v>42596.663486238</v>
+        <v>27485.8764534885</v>
       </c>
       <c r="P572" t="n">
-        <v>2700</v>
+        <v>6500</v>
       </c>
       <c r="Q572" t="n">
-        <v>54000</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>C863</t>
+          <t>C866</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET FELIZ DIA</t>
+          <t>YOYO SURTIDO</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -26451,7 +26443,7 @@
         </is>
       </c>
       <c r="J573" t="n">
-        <v>5</v>
+        <v>1178</v>
       </c>
       <c r="K573" t="n">
         <v>0</v>
@@ -26460,30 +26452,33 @@
         <v>0</v>
       </c>
       <c r="M573" t="n">
-        <v>5</v>
+        <v>1178</v>
       </c>
       <c r="N573" t="n">
-        <v>5497.1752906977</v>
+        <v>1176.57</v>
       </c>
       <c r="O573" t="n">
-        <v>27485.8764534885</v>
+        <v>1385999.46</v>
       </c>
       <c r="P573" t="n">
-        <v>6500</v>
+        <v>1900</v>
       </c>
       <c r="Q573" t="n">
-        <v>32500</v>
+        <v>2238200</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>C866</t>
-        </is>
+          <t>C887</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>6920210213929</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>YOYO SURTIDO</t>
+          <t>BALON FOOTBALL SURTIDO #2</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -26492,7 +26487,7 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>1178</v>
+        <v>553</v>
       </c>
       <c r="K574" t="n">
         <v>0</v>
@@ -26501,33 +26496,30 @@
         <v>0</v>
       </c>
       <c r="M574" t="n">
-        <v>1178</v>
+        <v>553</v>
       </c>
       <c r="N574" t="n">
-        <v>1176.57</v>
+        <v>3181.9</v>
       </c>
       <c r="O574" t="n">
-        <v>1385999.46</v>
+        <v>1759590.7</v>
       </c>
       <c r="P574" t="n">
-        <v>1900</v>
+        <v>5100</v>
       </c>
       <c r="Q574" t="n">
-        <v>2238200</v>
+        <v>2820300</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>C887</t>
-        </is>
-      </c>
-      <c r="B575" t="n">
-        <v>6920210213929</v>
+          <t>C888</t>
+        </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>BALON FOOTBALL SURTIDO #2</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -26536,7 +26528,7 @@
         </is>
       </c>
       <c r="J575" t="n">
-        <v>553</v>
+        <v>4</v>
       </c>
       <c r="K575" t="n">
         <v>0</v>
@@ -26545,30 +26537,33 @@
         <v>0</v>
       </c>
       <c r="M575" t="n">
-        <v>553</v>
+        <v>4</v>
       </c>
       <c r="N575" t="n">
-        <v>3181.9</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O575" t="n">
-        <v>1759590.7</v>
+        <v>4854.7285603112</v>
       </c>
       <c r="P575" t="n">
-        <v>5100</v>
+        <v>1500</v>
       </c>
       <c r="Q575" t="n">
-        <v>2820300</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>C888</t>
-        </is>
+          <t>C890</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>6913545113699</v>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>CORTINA FEST</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -26577,7 +26572,7 @@
         </is>
       </c>
       <c r="J576" t="n">
-        <v>4</v>
+        <v>450</v>
       </c>
       <c r="K576" t="n">
         <v>0</v>
@@ -26586,33 +26581,33 @@
         <v>0</v>
       </c>
       <c r="M576" t="n">
-        <v>4</v>
+        <v>450</v>
       </c>
       <c r="N576" t="n">
-        <v>1213.6821400778</v>
+        <v>1794.2879512478</v>
       </c>
       <c r="O576" t="n">
-        <v>4854.7285603112</v>
+        <v>807429.57806151</v>
       </c>
       <c r="P576" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="Q576" t="n">
-        <v>6000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>C890</t>
+          <t>C895</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>6913545113699</v>
+        <v>6913545115815</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>CORTINA FEST</t>
+          <t>CORTINA FESTIN TORNASOL</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -26621,7 +26616,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>450</v>
+        <v>44</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -26630,33 +26625,33 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>450</v>
+        <v>44</v>
       </c>
       <c r="N577" t="n">
-        <v>1794.2879512478</v>
+        <v>2830.2252424242</v>
       </c>
       <c r="O577" t="n">
-        <v>807429.57806151</v>
+        <v>124529.9106666648</v>
       </c>
       <c r="P577" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="Q577" t="n">
-        <v>720000</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>C895</t>
+          <t>C899</t>
         </is>
       </c>
       <c r="B578" t="n">
-        <v>6913545115815</v>
+        <v>6920202108998</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>CORTINA FESTIN TORNASOL</t>
+          <t>GLOBO BOUQUET ARCO GRANDE</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -26665,7 +26660,7 @@
         </is>
       </c>
       <c r="J578" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K578" t="n">
         <v>0</v>
@@ -26674,33 +26669,33 @@
         <v>0</v>
       </c>
       <c r="M578" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="N578" t="n">
-        <v>2830.2252424242</v>
+        <v>15219.155119048</v>
       </c>
       <c r="O578" t="n">
-        <v>124529.9106666648</v>
+        <v>426136.343333344</v>
       </c>
       <c r="P578" t="n">
-        <v>2400</v>
+        <v>16000</v>
       </c>
       <c r="Q578" t="n">
-        <v>105600</v>
+        <v>448000</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>C899</t>
+          <t>C91</t>
         </is>
       </c>
       <c r="B579" t="n">
-        <v>6920202108998</v>
+        <v>6803012120018</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET ARCO GRANDE</t>
+          <t>GLOBO BOUQUET SURTIDO</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -26709,7 +26704,7 @@
         </is>
       </c>
       <c r="J579" t="n">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="K579" t="n">
         <v>0</v>
@@ -26718,42 +26713,47 @@
         <v>0</v>
       </c>
       <c r="M579" t="n">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="N579" t="n">
-        <v>15219.155119048</v>
+        <v>2523.3377277904</v>
       </c>
       <c r="O579" t="n">
-        <v>426136.343333344</v>
+        <v>479434.168280176</v>
       </c>
       <c r="P579" t="n">
-        <v>16000</v>
+        <v>2800</v>
       </c>
       <c r="Q579" t="n">
-        <v>448000</v>
+        <v>532000</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>C91</t>
+          <t>C91-IO</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>6803012120018</v>
+        <v>6524521011108</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET SURTIDO</t>
+          <t>GLOBO BOUQUET X 7 MAS BASE 2021-17</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J580" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
@@ -26762,47 +26762,42 @@
         <v>0</v>
       </c>
       <c r="M580" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="N580" t="n">
-        <v>2523.3377277904</v>
+        <v>4648.51</v>
       </c>
       <c r="O580" t="n">
-        <v>479434.168280176</v>
+        <v>278910.6</v>
       </c>
       <c r="P580" t="n">
-        <v>2800</v>
+        <v>5500</v>
       </c>
       <c r="Q580" t="n">
-        <v>532000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>C91-IO</t>
+          <t>C913</t>
         </is>
       </c>
       <c r="B581" t="n">
-        <v>6524521011108</v>
+        <v>6920210204279</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 7 MAS BASE 2021-17</t>
-        </is>
-      </c>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>BLISTER HERRAMIENTAS DINO</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J581" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K581" t="n">
         <v>0</v>
@@ -26811,42 +26806,44 @@
         <v>0</v>
       </c>
       <c r="M581" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N581" t="n">
-        <v>4648.51</v>
+        <v>8922.2155844156</v>
       </c>
       <c r="O581" t="n">
-        <v>278910.6</v>
+        <v>401499.701298702</v>
       </c>
       <c r="P581" t="n">
-        <v>5500</v>
+        <v>8200</v>
       </c>
       <c r="Q581" t="n">
-        <v>330000</v>
+        <v>369000</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>C913</t>
-        </is>
-      </c>
-      <c r="B582" t="n">
-        <v>6920210204279</v>
+          <t>C92-IO</t>
+        </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>BLISTER HERRAMIENTAS DINO</t>
+          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J582" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="K582" t="n">
         <v>0</v>
@@ -26855,44 +26852,42 @@
         <v>0</v>
       </c>
       <c r="M582" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="N582" t="n">
-        <v>8922.2155844156</v>
+        <v>1520</v>
       </c>
       <c r="O582" t="n">
-        <v>401499.701298702</v>
+        <v>167200</v>
       </c>
       <c r="P582" t="n">
-        <v>8200</v>
+        <v>1900</v>
       </c>
       <c r="Q582" t="n">
-        <v>369000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>C92-IO</t>
-        </is>
+          <t>C928</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>6920202109285</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO BOUQUET COLA SIRENA</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J583" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="K583" t="n">
         <v>0</v>
@@ -26901,33 +26896,33 @@
         <v>0</v>
       </c>
       <c r="M583" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="N583" t="n">
-        <v>1520</v>
+        <v>12251</v>
       </c>
       <c r="O583" t="n">
-        <v>167200</v>
+        <v>343028</v>
       </c>
       <c r="P583" t="n">
-        <v>1900</v>
+        <v>13000</v>
       </c>
       <c r="Q583" t="n">
-        <v>209000</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>C928</t>
+          <t>C935</t>
         </is>
       </c>
       <c r="B584" t="n">
-        <v>6920202109285</v>
+        <v>6920202109353</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET COLA SIRENA</t>
+          <t>GLOBO BOUQUET</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -26936,7 +26931,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -26945,33 +26940,35 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="N584" t="n">
-        <v>12251</v>
+        <v>3683.6327464789</v>
       </c>
       <c r="O584" t="n">
-        <v>343028</v>
+        <v>368363.27464789</v>
       </c>
       <c r="P584" t="n">
-        <v>13000</v>
+        <v>3600</v>
       </c>
       <c r="Q584" t="n">
-        <v>364000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>C935</t>
-        </is>
-      </c>
-      <c r="B585" t="n">
-        <v>6920202109353</v>
+          <t>C943</t>
+        </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET</t>
+          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -26980,7 +26977,7 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
@@ -26989,35 +26986,35 @@
         <v>0</v>
       </c>
       <c r="M585" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="N585" t="n">
-        <v>3683.6327464789</v>
+        <v>22951.704377622</v>
       </c>
       <c r="O585" t="n">
-        <v>368363.27464789</v>
+        <v>6426477.22573416</v>
       </c>
       <c r="P585" t="n">
-        <v>3600</v>
+        <v>37900</v>
       </c>
       <c r="Q585" t="n">
-        <v>360000</v>
+        <v>10612000</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>C943</t>
+          <t>C984</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>CG2016531</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
-        </is>
-      </c>
-      <c r="E586" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TANGRAM</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -27026,7 +27023,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>280</v>
+        <v>172</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -27035,35 +27032,30 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>280</v>
+        <v>172</v>
       </c>
       <c r="N586" t="n">
-        <v>22951.704377622</v>
+        <v>705.52795348837</v>
       </c>
       <c r="O586" t="n">
-        <v>6426477.22573416</v>
+        <v>121350.8079999996</v>
       </c>
       <c r="P586" t="n">
-        <v>37900</v>
+        <v>1500</v>
       </c>
       <c r="Q586" t="n">
-        <v>10612000</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>C984</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>CG2016531</t>
+          <t>C99</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>TANGRAM</t>
+          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -27072,7 +27064,7 @@
         </is>
       </c>
       <c r="J587" t="n">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="K587" t="n">
         <v>0</v>
@@ -27081,39 +27073,49 @@
         <v>0</v>
       </c>
       <c r="M587" t="n">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="N587" t="n">
-        <v>705.52795348837</v>
+        <v>4985.4086330935</v>
       </c>
       <c r="O587" t="n">
-        <v>121350.8079999996</v>
+        <v>189445.528057553</v>
       </c>
       <c r="P587" t="n">
-        <v>1500</v>
+        <v>7900</v>
       </c>
       <c r="Q587" t="n">
-        <v>258000</v>
+        <v>300200</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>CA1673</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>CA11673</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
+          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J588" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
@@ -27122,40 +27124,40 @@
         <v>0</v>
       </c>
       <c r="M588" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="N588" t="n">
-        <v>4985.4086330935</v>
+        <v>1547.8829824561</v>
       </c>
       <c r="O588" t="n">
-        <v>189445.528057553</v>
+        <v>3095.7659649122</v>
       </c>
       <c r="P588" t="n">
-        <v>7900</v>
+        <v>5500</v>
       </c>
       <c r="Q588" t="n">
-        <v>300200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CA1673</t>
+          <t>CA886</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>CA11673</t>
+          <t>CA886</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+          <t>ANIMAL TAMBOR  CERDITO CA886</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -27164,7 +27166,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -27173,35 +27175,30 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="N589" t="n">
-        <v>1547.8829824561</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O589" t="n">
-        <v>3095.7659649122</v>
+        <v>507865.6637163752</v>
       </c>
       <c r="P589" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="Q589" t="n">
-        <v>11000</v>
+        <v>578000</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CA886</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>CA886</t>
+          <t>CA891</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>ANIMAL TAMBOR  CERDITO CA886</t>
+          <t>MUÑECA TAMBOR CA891</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -27215,7 +27212,7 @@
         </is>
       </c>
       <c r="J590" t="n">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="K590" t="n">
         <v>0</v>
@@ -27224,35 +27221,35 @@
         <v>0</v>
       </c>
       <c r="M590" t="n">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="N590" t="n">
-        <v>1757.3206356968</v>
+        <v>1561.33</v>
       </c>
       <c r="O590" t="n">
-        <v>507865.6637163752</v>
+        <v>518361.56</v>
       </c>
       <c r="P590" t="n">
         <v>2000</v>
       </c>
       <c r="Q590" t="n">
-        <v>578000</v>
+        <v>664000</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CA891</t>
+          <t>DPB087</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>MUÑECA TAMBOR CA891</t>
+          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -27261,7 +27258,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -27270,35 +27267,35 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="N591" t="n">
-        <v>1561.33</v>
+        <v>13520</v>
       </c>
       <c r="O591" t="n">
-        <v>518361.56</v>
+        <v>135200</v>
       </c>
       <c r="P591" t="n">
-        <v>2000</v>
+        <v>16900</v>
       </c>
       <c r="Q591" t="n">
-        <v>664000</v>
+        <v>169000</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>DPB087</t>
+          <t>DV052</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
+          <t>PELOTA PISCINA DV052</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -27307,7 +27304,7 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>10</v>
+        <v>1700</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
@@ -27316,35 +27313,35 @@
         <v>0</v>
       </c>
       <c r="M592" t="n">
-        <v>10</v>
+        <v>1700</v>
       </c>
       <c r="N592" t="n">
-        <v>13520</v>
+        <v>219.9969793366</v>
       </c>
       <c r="O592" t="n">
-        <v>135200</v>
+        <v>373994.86487222</v>
       </c>
       <c r="P592" t="n">
-        <v>16900</v>
+        <v>260</v>
       </c>
       <c r="Q592" t="n">
-        <v>169000</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>DV052</t>
+          <t>FG021</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DV052</t>
+          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -27353,7 +27350,7 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>1700</v>
+        <v>10</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
@@ -27362,35 +27359,35 @@
         <v>0</v>
       </c>
       <c r="M593" t="n">
-        <v>1700</v>
+        <v>10</v>
       </c>
       <c r="N593" t="n">
-        <v>219.99758867125</v>
+        <v>3504.16</v>
       </c>
       <c r="O593" t="n">
-        <v>373995.900741125</v>
+        <v>35041.6</v>
       </c>
       <c r="P593" t="n">
-        <v>260</v>
+        <v>3900</v>
       </c>
       <c r="Q593" t="n">
-        <v>442000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>FG021</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -27399,7 +27396,7 @@
         </is>
       </c>
       <c r="J594" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="K594" t="n">
         <v>0</v>
@@ -27408,30 +27405,30 @@
         <v>0</v>
       </c>
       <c r="M594" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="N594" t="n">
-        <v>3504.16</v>
+        <v>13493.858287462</v>
       </c>
       <c r="O594" t="n">
-        <v>35041.6</v>
+        <v>1025533.229847112</v>
       </c>
       <c r="P594" t="n">
-        <v>3900</v>
+        <v>16900</v>
       </c>
       <c r="Q594" t="n">
-        <v>39000</v>
+        <v>1284400</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -27445,7 +27442,7 @@
         </is>
       </c>
       <c r="J595" t="n">
-        <v>76</v>
+        <v>439</v>
       </c>
       <c r="K595" t="n">
         <v>0</v>
@@ -27454,35 +27451,35 @@
         <v>0</v>
       </c>
       <c r="M595" t="n">
-        <v>76</v>
+        <v>439</v>
       </c>
       <c r="N595" t="n">
-        <v>13493.858287462</v>
+        <v>2644.9</v>
       </c>
       <c r="O595" t="n">
-        <v>1025533.229847112</v>
+        <v>1161111.1</v>
       </c>
       <c r="P595" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q595" t="n">
-        <v>1284400</v>
+        <v>1712100</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG042</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>BURBUJERO PANDA BLISTER 43043</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -27491,7 +27488,7 @@
         </is>
       </c>
       <c r="J596" t="n">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="K596" t="n">
         <v>0</v>
@@ -27500,30 +27497,30 @@
         <v>0</v>
       </c>
       <c r="M596" t="n">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="N596" t="n">
-        <v>2644.9</v>
+        <v>14576.2</v>
       </c>
       <c r="O596" t="n">
-        <v>1161111.1</v>
+        <v>102033.4</v>
       </c>
       <c r="P596" t="n">
-        <v>3900</v>
+        <v>19000</v>
       </c>
       <c r="Q596" t="n">
-        <v>1712100</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>FG042</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>BURBUJERO PANDA BLISTER 43043</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -27537,7 +27534,7 @@
         </is>
       </c>
       <c r="J597" t="n">
-        <v>7</v>
+        <v>351</v>
       </c>
       <c r="K597" t="n">
         <v>0</v>
@@ -27546,35 +27543,35 @@
         <v>0</v>
       </c>
       <c r="M597" t="n">
-        <v>7</v>
+        <v>351</v>
       </c>
       <c r="N597" t="n">
-        <v>14576.2</v>
+        <v>1952.66</v>
       </c>
       <c r="O597" t="n">
-        <v>102033.4</v>
+        <v>685383.66</v>
       </c>
       <c r="P597" t="n">
-        <v>19000</v>
+        <v>3500</v>
       </c>
       <c r="Q597" t="n">
-        <v>133000</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG050</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -27583,7 +27580,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -27592,35 +27589,35 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="N598" t="n">
-        <v>1952.66</v>
+        <v>9708.190000000001</v>
       </c>
       <c r="O598" t="n">
-        <v>685383.66</v>
+        <v>67957.33</v>
       </c>
       <c r="P598" t="n">
-        <v>3500</v>
+        <v>10200</v>
       </c>
       <c r="Q598" t="n">
-        <v>1228500</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>FG050</t>
+          <t>FG057</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
+          <t>ABACO BOLSA 8022</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -27629,7 +27626,7 @@
         </is>
       </c>
       <c r="J599" t="n">
-        <v>7</v>
+        <v>232</v>
       </c>
       <c r="K599" t="n">
         <v>0</v>
@@ -27638,30 +27635,30 @@
         <v>0</v>
       </c>
       <c r="M599" t="n">
-        <v>7</v>
+        <v>232</v>
       </c>
       <c r="N599" t="n">
-        <v>9708.190000000001</v>
+        <v>2293.26</v>
       </c>
       <c r="O599" t="n">
-        <v>67957.33</v>
+        <v>532036.3200000001</v>
       </c>
       <c r="P599" t="n">
-        <v>10200</v>
+        <v>4800</v>
       </c>
       <c r="Q599" t="n">
-        <v>71400</v>
+        <v>1113600</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>FG057</t>
+          <t>FG083</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>ABACO BOLSA 8022</t>
+          <t>SONAJERO BOLSA RANA XZM5XS</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -27675,7 +27672,7 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
@@ -27684,35 +27681,35 @@
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="N600" t="n">
-        <v>2293.26</v>
+        <v>1952.41</v>
       </c>
       <c r="O600" t="n">
-        <v>532036.3200000001</v>
+        <v>310433.19</v>
       </c>
       <c r="P600" t="n">
-        <v>4800</v>
+        <v>2700</v>
       </c>
       <c r="Q600" t="n">
-        <v>1113600</v>
+        <v>429300</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>FG083</t>
+          <t>FG092</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA RANA XZM5XS</t>
+          <t>BLISTER  TETERA SJ377-1</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -27721,7 +27718,7 @@
         </is>
       </c>
       <c r="J601" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="K601" t="n">
         <v>0</v>
@@ -27730,30 +27727,30 @@
         <v>0</v>
       </c>
       <c r="M601" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="N601" t="n">
-        <v>1952.41</v>
+        <v>9855.037826087</v>
       </c>
       <c r="O601" t="n">
-        <v>310433.19</v>
+        <v>9855.037826087</v>
       </c>
       <c r="P601" t="n">
-        <v>2700</v>
+        <v>15500</v>
       </c>
       <c r="Q601" t="n">
-        <v>429300</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>FG092</t>
+          <t>FG097</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>BLISTER  TETERA SJ377-1</t>
+          <t>MUÑECO ROBOT BLISTER 5090B</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -27767,7 +27764,7 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="K602" t="n">
         <v>0</v>
@@ -27776,35 +27773,35 @@
         <v>0</v>
       </c>
       <c r="M602" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="N602" t="n">
-        <v>9855.037826087</v>
+        <v>17986.24</v>
       </c>
       <c r="O602" t="n">
-        <v>9855.037826087</v>
+        <v>1438899.2</v>
       </c>
       <c r="P602" t="n">
-        <v>15500</v>
+        <v>18500</v>
       </c>
       <c r="Q602" t="n">
-        <v>15500</v>
+        <v>1480000</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>FG097</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>MUÑECO ROBOT BLISTER 5090B</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -27813,7 +27810,7 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
@@ -27822,30 +27819,30 @@
         <v>0</v>
       </c>
       <c r="M603" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="N603" t="n">
-        <v>17986.24</v>
+        <v>7480</v>
       </c>
       <c r="O603" t="n">
-        <v>1438899.2</v>
+        <v>269280</v>
       </c>
       <c r="P603" t="n">
-        <v>18500</v>
+        <v>9500</v>
       </c>
       <c r="Q603" t="n">
-        <v>1480000</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -27859,7 +27856,7 @@
         </is>
       </c>
       <c r="J604" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K604" t="n">
         <v>0</v>
@@ -27868,30 +27865,30 @@
         <v>0</v>
       </c>
       <c r="M604" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N604" t="n">
-        <v>7480</v>
+        <v>5280</v>
       </c>
       <c r="O604" t="n">
-        <v>269280</v>
+        <v>174240</v>
       </c>
       <c r="P604" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="Q604" t="n">
-        <v>342000</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>J-1316</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -27905,7 +27902,7 @@
         </is>
       </c>
       <c r="J605" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="K605" t="n">
         <v>0</v>
@@ -27914,30 +27911,33 @@
         <v>0</v>
       </c>
       <c r="M605" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="N605" t="n">
         <v>5280</v>
       </c>
       <c r="O605" t="n">
-        <v>174240</v>
+        <v>469920</v>
       </c>
       <c r="P605" t="n">
         <v>6900</v>
       </c>
       <c r="Q605" t="n">
-        <v>227700</v>
+        <v>614100</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>J-1317</t>
-        </is>
+          <t>J-1386</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
+          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -27951,7 +27951,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="K606" t="n">
         <v>0</v>
@@ -27960,33 +27960,30 @@
         <v>0</v>
       </c>
       <c r="M606" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="N606" t="n">
-        <v>5280</v>
+        <v>7920</v>
       </c>
       <c r="O606" t="n">
-        <v>469920</v>
+        <v>427680</v>
       </c>
       <c r="P606" t="n">
-        <v>6900</v>
+        <v>10500</v>
       </c>
       <c r="Q606" t="n">
-        <v>614100</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>J-1386</t>
-        </is>
-      </c>
-      <c r="B607" t="n">
-        <v>7700154271143</v>
+          <t>J-718</t>
+        </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -28000,7 +27997,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="K607" t="n">
         <v>0</v>
@@ -28009,30 +28006,30 @@
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="N607" t="n">
-        <v>7920</v>
+        <v>4576</v>
       </c>
       <c r="O607" t="n">
-        <v>427680</v>
+        <v>329472</v>
       </c>
       <c r="P607" t="n">
-        <v>10500</v>
+        <v>5900</v>
       </c>
       <c r="Q607" t="n">
-        <v>567000</v>
+        <v>424800</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -28046,7 +28043,7 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>72</v>
+        <v>204</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
@@ -28055,30 +28052,30 @@
         <v>0</v>
       </c>
       <c r="M608" t="n">
-        <v>72</v>
+        <v>204</v>
       </c>
       <c r="N608" t="n">
-        <v>4576</v>
+        <v>5280</v>
       </c>
       <c r="O608" t="n">
-        <v>329472</v>
+        <v>1077120</v>
       </c>
       <c r="P608" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q608" t="n">
-        <v>424800</v>
+        <v>1407600</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -28092,7 +28089,7 @@
         </is>
       </c>
       <c r="J609" t="n">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="K609" t="n">
         <v>0</v>
@@ -28101,35 +28098,35 @@
         <v>0</v>
       </c>
       <c r="M609" t="n">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="N609" t="n">
-        <v>5280</v>
+        <v>46491.75</v>
       </c>
       <c r="O609" t="n">
-        <v>1077120</v>
+        <v>2743013.25</v>
       </c>
       <c r="P609" t="n">
-        <v>6900</v>
+        <v>52900</v>
       </c>
       <c r="Q609" t="n">
-        <v>1407600</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -28138,7 +28135,7 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
@@ -28147,35 +28144,35 @@
         <v>0</v>
       </c>
       <c r="M610" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="N610" t="n">
-        <v>46491.75</v>
+        <v>910.85</v>
       </c>
       <c r="O610" t="n">
-        <v>2743013.25</v>
+        <v>22771.25</v>
       </c>
       <c r="P610" t="n">
-        <v>52900</v>
+        <v>7900</v>
       </c>
       <c r="Q610" t="n">
-        <v>3121100</v>
+        <v>197500</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -28184,7 +28181,7 @@
         </is>
       </c>
       <c r="J611" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K611" t="n">
         <v>0</v>
@@ -28193,35 +28190,35 @@
         <v>0</v>
       </c>
       <c r="M611" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="N611" t="n">
-        <v>910.85</v>
+        <v>1129.14</v>
       </c>
       <c r="O611" t="n">
-        <v>22771.25</v>
+        <v>13549.68</v>
       </c>
       <c r="P611" t="n">
-        <v>7900</v>
+        <v>6900</v>
       </c>
       <c r="Q611" t="n">
-        <v>197500</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -28230,7 +28227,7 @@
         </is>
       </c>
       <c r="J612" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K612" t="n">
         <v>0</v>
@@ -28239,35 +28236,40 @@
         <v>0</v>
       </c>
       <c r="M612" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N612" t="n">
-        <v>1129.14</v>
+        <v>11433.53</v>
       </c>
       <c r="O612" t="n">
-        <v>13549.68</v>
+        <v>68601.18000000001</v>
       </c>
       <c r="P612" t="n">
-        <v>6900</v>
+        <v>15000</v>
       </c>
       <c r="Q612" t="n">
-        <v>82800</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -28276,7 +28278,7 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K613" t="n">
         <v>0</v>
@@ -28285,40 +28287,35 @@
         <v>0</v>
       </c>
       <c r="M613" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N613" t="n">
-        <v>11433.53</v>
+        <v>15452.21</v>
       </c>
       <c r="O613" t="n">
-        <v>68601.18000000001</v>
+        <v>46356.63</v>
       </c>
       <c r="P613" t="n">
-        <v>15000</v>
+        <v>36500</v>
       </c>
       <c r="Q613" t="n">
-        <v>90000</v>
+        <v>109500</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -28327,7 +28324,7 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="K614" t="n">
         <v>0</v>
@@ -28336,35 +28333,40 @@
         <v>0</v>
       </c>
       <c r="M614" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="N614" t="n">
-        <v>15452.21</v>
+        <v>1319.3611070111</v>
       </c>
       <c r="O614" t="n">
-        <v>46356.63</v>
+        <v>184710.554981554</v>
       </c>
       <c r="P614" t="n">
-        <v>36500</v>
+        <v>3500</v>
       </c>
       <c r="Q614" t="n">
-        <v>109500</v>
+        <v>490000</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -28373,7 +28375,7 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
@@ -28382,40 +28384,35 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="N615" t="n">
-        <v>1319.3610989011</v>
+        <v>751.45</v>
       </c>
       <c r="O615" t="n">
-        <v>184710.553846154</v>
+        <v>751.45</v>
       </c>
       <c r="P615" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="Q615" t="n">
-        <v>490000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -28424,7 +28421,7 @@
         </is>
       </c>
       <c r="J616" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="K616" t="n">
         <v>0</v>
@@ -28433,35 +28430,35 @@
         <v>0</v>
       </c>
       <c r="M616" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="N616" t="n">
-        <v>751.45</v>
+        <v>571.87</v>
       </c>
       <c r="O616" t="n">
-        <v>751.45</v>
+        <v>69196.27</v>
       </c>
       <c r="P616" t="n">
         <v>2500</v>
       </c>
       <c r="Q616" t="n">
-        <v>2500</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -28470,7 +28467,7 @@
         </is>
       </c>
       <c r="J617" t="n">
-        <v>121</v>
+        <v>680</v>
       </c>
       <c r="K617" t="n">
         <v>0</v>
@@ -28479,35 +28476,40 @@
         <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>121</v>
+        <v>680</v>
       </c>
       <c r="N617" t="n">
-        <v>571.87</v>
+        <v>227.41615210843</v>
       </c>
       <c r="O617" t="n">
-        <v>69196.27</v>
+        <v>154642.9834337324</v>
       </c>
       <c r="P617" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q617" t="n">
-        <v>302500</v>
+        <v>816000</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -28516,7 +28518,7 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>680</v>
+        <v>21</v>
       </c>
       <c r="K618" t="n">
         <v>0</v>
@@ -28525,49 +28527,47 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>680</v>
+        <v>21</v>
       </c>
       <c r="N618" t="n">
-        <v>227.41615210843</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O618" t="n">
-        <v>154642.9834337324</v>
+        <v>208257.84</v>
       </c>
       <c r="P618" t="n">
-        <v>1200</v>
+        <v>15900</v>
       </c>
       <c r="Q618" t="n">
-        <v>816000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J619" t="n">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
@@ -28576,33 +28576,30 @@
         <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="N619" t="n">
-        <v>9917.040000000001</v>
+        <v>2539.5719098712</v>
       </c>
       <c r="O619" t="n">
-        <v>208257.84</v>
+        <v>401252.3617596496</v>
       </c>
       <c r="P619" t="n">
-        <v>15900</v>
+        <v>2900</v>
       </c>
       <c r="Q619" t="n">
-        <v>333900</v>
+        <v>458200</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B620" t="n">
-        <v>7700154271143</v>
+          <t>MT4691</t>
+        </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -28612,11 +28609,11 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J620" t="n">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
@@ -28625,35 +28622,35 @@
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="N620" t="n">
-        <v>2539.5719098712</v>
+        <v>4171.6682164634</v>
       </c>
       <c r="O620" t="n">
-        <v>401252.3617596496</v>
+        <v>396308.480564023</v>
       </c>
       <c r="P620" t="n">
-        <v>2900</v>
+        <v>5000</v>
       </c>
       <c r="Q620" t="n">
-        <v>458200</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -28662,7 +28659,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
@@ -28671,35 +28668,35 @@
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="N621" t="n">
-        <v>4171.6682692308</v>
+        <v>7600</v>
       </c>
       <c r="O621" t="n">
-        <v>396308.485576926</v>
+        <v>364800</v>
       </c>
       <c r="P621" t="n">
-        <v>5000</v>
+        <v>9500</v>
       </c>
       <c r="Q621" t="n">
-        <v>475000</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -28708,7 +28705,7 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
@@ -28717,30 +28714,30 @@
         <v>0</v>
       </c>
       <c r="M622" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="N622" t="n">
-        <v>7600</v>
+        <v>5520</v>
       </c>
       <c r="O622" t="n">
-        <v>364800</v>
+        <v>524400</v>
       </c>
       <c r="P622" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="Q622" t="n">
-        <v>456000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -28754,7 +28751,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -28763,30 +28760,30 @@
         <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="N623" t="n">
-        <v>5520</v>
+        <v>1600</v>
       </c>
       <c r="O623" t="n">
-        <v>524400</v>
+        <v>132800</v>
       </c>
       <c r="P623" t="n">
-        <v>6900</v>
+        <v>2000</v>
       </c>
       <c r="Q623" t="n">
-        <v>655500</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -28800,7 +28797,7 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="K624" t="n">
         <v>0</v>
@@ -28809,35 +28806,38 @@
         <v>0</v>
       </c>
       <c r="M624" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="N624" t="n">
-        <v>1600</v>
+        <v>4091.4</v>
       </c>
       <c r="O624" t="n">
-        <v>132800</v>
+        <v>4091.4</v>
       </c>
       <c r="P624" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="Q624" t="n">
-        <v>166000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
-        </is>
+          <t>SLT3728</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -28846,7 +28846,7 @@
         </is>
       </c>
       <c r="J625" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="K625" t="n">
         <v>0</v>
@@ -28855,25 +28855,25 @@
         <v>0</v>
       </c>
       <c r="M625" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="N625" t="n">
-        <v>4091.4</v>
+        <v>2465</v>
       </c>
       <c r="O625" t="n">
-        <v>4091.4</v>
+        <v>788800</v>
       </c>
       <c r="P625" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="Q625" t="n">
-        <v>10000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>SLT3728</t>
+          <t>SLT4037</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
+          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -28895,7 +28895,7 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
@@ -28904,33 +28904,30 @@
         <v>0</v>
       </c>
       <c r="M626" t="n">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="N626" t="n">
-        <v>2465</v>
+        <v>1700</v>
       </c>
       <c r="O626" t="n">
-        <v>788800</v>
+        <v>652800</v>
       </c>
       <c r="P626" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="Q626" t="n">
-        <v>960000</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>SLT4037</t>
-        </is>
-      </c>
-      <c r="B627" t="n">
-        <v>7700154271143</v>
+          <t>T040-LJ</t>
+        </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -28944,7 +28941,7 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>384</v>
+        <v>3</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
@@ -28953,30 +28950,30 @@
         <v>0</v>
       </c>
       <c r="M627" t="n">
-        <v>384</v>
+        <v>3</v>
       </c>
       <c r="N627" t="n">
-        <v>1700</v>
+        <v>3661.88</v>
       </c>
       <c r="O627" t="n">
-        <v>652800</v>
+        <v>10985.64</v>
       </c>
       <c r="P627" t="n">
-        <v>2000</v>
+        <v>38900</v>
       </c>
       <c r="Q627" t="n">
-        <v>768000</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>T041-LJ</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -28990,7 +28987,7 @@
         </is>
       </c>
       <c r="J628" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K628" t="n">
         <v>0</v>
@@ -28999,30 +28996,30 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N628" t="n">
-        <v>3661.88</v>
+        <v>2797.08</v>
       </c>
       <c r="O628" t="n">
-        <v>10985.64</v>
+        <v>13985.4</v>
       </c>
       <c r="P628" t="n">
-        <v>38900</v>
+        <v>30900</v>
       </c>
       <c r="Q628" t="n">
-        <v>116700</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -29036,7 +29033,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -29045,30 +29042,30 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N629" t="n">
-        <v>2797.08</v>
+        <v>3462.255</v>
       </c>
       <c r="O629" t="n">
-        <v>13985.4</v>
+        <v>38084.805</v>
       </c>
       <c r="P629" t="n">
-        <v>30900</v>
+        <v>42000</v>
       </c>
       <c r="Q629" t="n">
-        <v>154500</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -29082,7 +29079,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -29091,30 +29088,30 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N630" t="n">
-        <v>3462.255</v>
+        <v>24882.58</v>
       </c>
       <c r="O630" t="n">
-        <v>38084.805</v>
+        <v>696712.24</v>
       </c>
       <c r="P630" t="n">
-        <v>42000</v>
+        <v>31500</v>
       </c>
       <c r="Q630" t="n">
-        <v>462000</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -29128,7 +29125,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -29137,35 +29134,35 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="N631" t="n">
-        <v>24882.58</v>
+        <v>0.8</v>
       </c>
       <c r="O631" t="n">
-        <v>696712.24</v>
+        <v>15.2</v>
       </c>
       <c r="P631" t="n">
-        <v>31500</v>
+        <v>22900</v>
       </c>
       <c r="Q631" t="n">
-        <v>882000</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -29174,7 +29171,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29183,30 +29180,30 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N632" t="n">
-        <v>0.8</v>
+        <v>5186.45</v>
       </c>
       <c r="O632" t="n">
-        <v>15.2</v>
+        <v>82983.2</v>
       </c>
       <c r="P632" t="n">
-        <v>22900</v>
+        <v>7200</v>
       </c>
       <c r="Q632" t="n">
-        <v>435100</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>TB028</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -29220,7 +29217,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -29229,30 +29226,30 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N633" t="n">
-        <v>5186.45</v>
+        <v>47796.1625</v>
       </c>
       <c r="O633" t="n">
-        <v>82983.2</v>
+        <v>95592.325</v>
       </c>
       <c r="P633" t="n">
-        <v>7200</v>
+        <v>54000</v>
       </c>
       <c r="Q633" t="n">
-        <v>115200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>TB115</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -29266,7 +29263,7 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -29275,30 +29272,30 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="N634" t="n">
-        <v>47796.1625</v>
+        <v>8006.3731111111</v>
       </c>
       <c r="O634" t="n">
-        <v>95592.325</v>
+        <v>344274.0437777773</v>
       </c>
       <c r="P634" t="n">
-        <v>54000</v>
+        <v>10000</v>
       </c>
       <c r="Q634" t="n">
-        <v>108000</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>TB122</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -29312,7 +29309,7 @@
         </is>
       </c>
       <c r="J635" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="K635" t="n">
         <v>0</v>
@@ -29321,64 +29318,18 @@
         <v>0</v>
       </c>
       <c r="M635" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="N635" t="n">
-        <v>8006.3731111111</v>
+        <v>47920</v>
       </c>
       <c r="O635" t="n">
-        <v>344274.0437777773</v>
+        <v>191680</v>
       </c>
       <c r="P635" t="n">
-        <v>10000</v>
+        <v>59900</v>
       </c>
       <c r="Q635" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>TB122</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>PELUCHE DRAGON 50CM DRAG-50</t>
-        </is>
-      </c>
-      <c r="E636" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I636" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J636" t="n">
-        <v>4</v>
-      </c>
-      <c r="K636" t="n">
-        <v>0</v>
-      </c>
-      <c r="L636" t="n">
-        <v>0</v>
-      </c>
-      <c r="M636" t="n">
-        <v>4</v>
-      </c>
-      <c r="N636" t="n">
-        <v>47920</v>
-      </c>
-      <c r="O636" t="n">
-        <v>191680</v>
-      </c>
-      <c r="P636" t="n">
-        <v>59900</v>
-      </c>
-      <c r="Q636" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -831,10 +831,10 @@
         <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>15238.01</v>
+        <v>15304.843377193</v>
       </c>
       <c r="O11" t="n">
-        <v>700948.46</v>
+        <v>704022.795350878</v>
       </c>
       <c r="P11" t="n">
         <v>40400</v>
@@ -1546,10 +1546,10 @@
         <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O29" t="n">
-        <v>490674.87</v>
+        <v>492780.770729624</v>
       </c>
       <c r="P29" t="n">
         <v>30000</v>
@@ -2060,10 +2060,10 @@
         <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="O41" t="n">
-        <v>2160000</v>
+        <v>2280000</v>
       </c>
       <c r="P41" t="n">
         <v>20000</v>
@@ -3382,10 +3382,10 @@
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O71" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="P71" t="n">
         <v>25500</v>
@@ -3951,10 +3951,10 @@
         <v>651</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O84" t="n">
-        <v>1681047.815665308</v>
+        <v>1681047.800042676</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.387469964</v>
+        <v>1511297.387619396</v>
       </c>
       <c r="P109" t="n">
         <v>8900</v>
@@ -5535,25 +5535,25 @@
         <v>5</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="N119" t="n">
         <v>10716.34</v>
       </c>
       <c r="O119" t="n">
-        <v>53581.7</v>
+        <v>589398.7</v>
       </c>
       <c r="P119" t="n">
         <v>39000</v>
       </c>
       <c r="Q119" t="n">
-        <v>195000</v>
+        <v>2145000</v>
       </c>
     </row>
     <row r="120">
@@ -5818,10 +5818,10 @@
         <v>303</v>
       </c>
       <c r="N125" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O125" t="n">
-        <v>4491180.780667149</v>
+        <v>4493956.54134726</v>
       </c>
       <c r="P125" t="n">
         <v>24900</v>
@@ -6183,10 +6183,10 @@
         <v>308</v>
       </c>
       <c r="N133" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O133" t="n">
-        <v>3826118.60685824</v>
+        <v>3826118.608088392</v>
       </c>
       <c r="P133" t="n">
         <v>19900</v>
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.767991094</v>
+        <v>7270946.796673658</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -6632,10 +6632,10 @@
         <v>1915</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O143" t="n">
-        <v>8370796.243658659</v>
+        <v>8370796.244572879</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -7622,10 +7622,10 @@
         <v>109</v>
       </c>
       <c r="N165" t="n">
-        <v>4635.49</v>
+        <v>4680.6408766234</v>
       </c>
       <c r="O165" t="n">
-        <v>505268.41</v>
+        <v>510189.8555519506</v>
       </c>
       <c r="P165" t="n">
         <v>7500</v>
@@ -8467,10 +8467,10 @@
         <v>337</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O183" t="n">
-        <v>549621.7699933081</v>
+        <v>550356.5584558883</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8605,10 +8605,10 @@
         <v>1282</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O186" t="n">
-        <v>1987349.941997817</v>
+        <v>1987349.943699801</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="O188" t="n">
-        <v>418213.013048652</v>
+        <v>418368.3670653804</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -10814,10 +10814,10 @@
         <v>1248</v>
       </c>
       <c r="N236" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O236" t="n">
-        <v>6008200.660073165</v>
+        <v>6008200.657310217</v>
       </c>
       <c r="P236" t="n">
         <v>7900</v>
@@ -10947,10 +10947,10 @@
         <v>9</v>
       </c>
       <c r="N239" t="n">
-        <v>13513.644019608</v>
+        <v>13513.644059406</v>
       </c>
       <c r="O239" t="n">
-        <v>121622.796176472</v>
+        <v>121622.796534654</v>
       </c>
       <c r="P239" t="n">
         <v>21900</v>
@@ -11085,10 +11085,10 @@
         <v>86</v>
       </c>
       <c r="N242" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O242" t="n">
-        <v>2332643.754545468</v>
+        <v>2332643.753559306</v>
       </c>
       <c r="P242" t="n">
         <v>44500</v>
@@ -11723,10 +11723,10 @@
         <v>19</v>
       </c>
       <c r="N256" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O256" t="n">
-        <v>246650.21</v>
+        <v>247644.767298392</v>
       </c>
       <c r="P256" t="n">
         <v>21900</v>
@@ -13023,10 +13023,10 @@
         <v>3</v>
       </c>
       <c r="N284" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O284" t="n">
-        <v>27566.94</v>
+        <v>27763.1459786478</v>
       </c>
       <c r="P284" t="n">
         <v>12900</v>
@@ -13483,10 +13483,10 @@
         <v>269</v>
       </c>
       <c r="N294" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O294" t="n">
-        <v>6868646</v>
+        <v>6880400.670849888</v>
       </c>
       <c r="P294" t="n">
         <v>40900</v>
@@ -14406,10 +14406,10 @@
         <v>9</v>
       </c>
       <c r="N314" t="n">
-        <v>10411</v>
+        <v>10448.858181818</v>
       </c>
       <c r="O314" t="n">
-        <v>93699</v>
+        <v>94039.72363636199</v>
       </c>
       <c r="P314" t="n">
         <v>16900</v>
@@ -14962,10 +14962,10 @@
         <v>135</v>
       </c>
       <c r="N326" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O326" t="n">
-        <v>1215405</v>
+        <v>1217451.136363641</v>
       </c>
       <c r="P326" t="n">
         <v>14900</v>
@@ -16337,10 +16337,10 @@
         <v>54</v>
       </c>
       <c r="N356" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O356" t="n">
-        <v>971568</v>
+        <v>972838.023529392</v>
       </c>
       <c r="P356" t="n">
         <v>28900</v>
@@ -16846,10 +16846,10 @@
         <v>26</v>
       </c>
       <c r="N367" t="n">
-        <v>8700</v>
+        <v>8711.0687022901</v>
       </c>
       <c r="O367" t="n">
-        <v>226200</v>
+        <v>226487.7862595426</v>
       </c>
       <c r="P367" t="n">
         <v>14900</v>
@@ -17490,10 +17490,10 @@
         <v>1008</v>
       </c>
       <c r="N381" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O381" t="n">
-        <v>1528167.006933336</v>
+        <v>1528167.006794333</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
@@ -17628,10 +17628,10 @@
         <v>96</v>
       </c>
       <c r="N384" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O384" t="n">
-        <v>317433.0496815264</v>
+        <v>317433.0479233248</v>
       </c>
       <c r="P384" t="n">
         <v>4900</v>
@@ -17950,10 +17950,10 @@
         <v>224</v>
       </c>
       <c r="N391" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="O391" t="n">
-        <v>356672.7888209696</v>
+        <v>357453.2544420096</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -18127,10 +18127,10 @@
         <v>400</v>
       </c>
       <c r="N395" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O395" t="n">
-        <v>503710.07236336</v>
+        <v>503710.07289528</v>
       </c>
       <c r="P395" t="n">
         <v>1900</v>
@@ -18543,10 +18543,10 @@
         <v>588</v>
       </c>
       <c r="N404" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O404" t="n">
-        <v>7948584</v>
+        <v>7950803.654845128</v>
       </c>
       <c r="P404" t="n">
         <v>21900</v>
@@ -18824,10 +18824,10 @@
         <v>35</v>
       </c>
       <c r="N410" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="O410" t="n">
-        <v>539817.6</v>
+        <v>544170.9677419401</v>
       </c>
       <c r="P410" t="n">
         <v>24900</v>
@@ -21278,10 +21278,10 @@
         <v>17742</v>
       </c>
       <c r="N463" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O463" t="n">
-        <v>12486723.52472344</v>
+        <v>12486723.49360965</v>
       </c>
       <c r="P463" t="n">
         <v>900</v>
@@ -23186,10 +23186,10 @@
         <v>54</v>
       </c>
       <c r="N503" t="n">
-        <v>4568.55</v>
+        <v>4627.1211538462</v>
       </c>
       <c r="O503" t="n">
-        <v>246701.7</v>
+        <v>249864.5423076948</v>
       </c>
       <c r="P503" t="n">
         <v>6900</v>
@@ -23325,10 +23325,10 @@
         <v>3</v>
       </c>
       <c r="N506" t="n">
-        <v>19632.66</v>
+        <v>19743.578983051</v>
       </c>
       <c r="O506" t="n">
-        <v>58897.98</v>
+        <v>59230.736949153</v>
       </c>
       <c r="P506" t="n">
         <v>2800</v>
@@ -24275,10 +24275,10 @@
         <v>2</v>
       </c>
       <c r="N526" t="n">
-        <v>7258.5</v>
+        <v>7742.4</v>
       </c>
       <c r="O526" t="n">
-        <v>14517</v>
+        <v>15484.8</v>
       </c>
       <c r="P526" t="n">
         <v>17500</v>
@@ -26989,10 +26989,10 @@
         <v>280</v>
       </c>
       <c r="N585" t="n">
-        <v>22951.704377622</v>
+        <v>22951.704345992</v>
       </c>
       <c r="O585" t="n">
-        <v>6426477.22573416</v>
+        <v>6426477.216877759</v>
       </c>
       <c r="P585" t="n">
         <v>37900</v>
@@ -27076,10 +27076,10 @@
         <v>38</v>
       </c>
       <c r="N587" t="n">
-        <v>4985.4086330935</v>
+        <v>5058.1883211679</v>
       </c>
       <c r="O587" t="n">
-        <v>189445.528057553</v>
+        <v>192211.1562043802</v>
       </c>
       <c r="P587" t="n">
         <v>7900</v>
@@ -28009,10 +28009,10 @@
         <v>72</v>
       </c>
       <c r="N607" t="n">
-        <v>4576</v>
+        <v>4591.2533333333</v>
       </c>
       <c r="O607" t="n">
-        <v>329472</v>
+        <v>330570.2399999976</v>
       </c>
       <c r="P607" t="n">
         <v>5900</v>
@@ -28055,10 +28055,10 @@
         <v>204</v>
       </c>
       <c r="N608" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O608" t="n">
-        <v>1077120</v>
+        <v>1078177.036310099</v>
       </c>
       <c r="P608" t="n">
         <v>6900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q635"/>
+  <dimension ref="A1:Q633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N5" t="n">
         <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>2619000</v>
+        <v>2295000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1940000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -672,19 +672,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="N7" t="n">
         <v>27000</v>
       </c>
       <c r="O7" t="n">
-        <v>1215000</v>
+        <v>567000</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1350000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="8">
@@ -831,10 +831,10 @@
         <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>15304.843377193</v>
+        <v>15238.01</v>
       </c>
       <c r="O11" t="n">
-        <v>704022.795350878</v>
+        <v>700948.46</v>
       </c>
       <c r="P11" t="n">
         <v>40400</v>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -953,19 +953,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="N14" t="n">
         <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>4131000</v>
+        <v>3807000</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3060000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="15">
@@ -1312,10 +1312,10 @@
         <v>66</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.7033461538</v>
+        <v>2474.7028512397</v>
       </c>
       <c r="O23" t="n">
-        <v>163330.4208461508</v>
+        <v>163330.3881818202</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1390,10 +1390,10 @@
         <v>120</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301980198</v>
+        <v>3716.3301983471</v>
       </c>
       <c r="O25" t="n">
-        <v>445959.623762376</v>
+        <v>445959.623801652</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1507,10 +1507,10 @@
         <v>93</v>
       </c>
       <c r="N28" t="n">
-        <v>27000</v>
+        <v>27051.823416507</v>
       </c>
       <c r="O28" t="n">
-        <v>2511000</v>
+        <v>2515819.577735151</v>
       </c>
       <c r="P28" t="n">
         <v>30000</v>
@@ -1546,10 +1546,10 @@
         <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>21425.250901288</v>
+        <v>21333.69</v>
       </c>
       <c r="O29" t="n">
-        <v>492780.770729624</v>
+        <v>490674.87</v>
       </c>
       <c r="P29" t="n">
         <v>30000</v>
@@ -1624,10 +1624,10 @@
         <v>23</v>
       </c>
       <c r="N31" t="n">
-        <v>14857.623287671</v>
+        <v>14857.623302752</v>
       </c>
       <c r="O31" t="n">
-        <v>341725.335616433</v>
+        <v>341725.335963296</v>
       </c>
       <c r="P31" t="n">
         <v>34900</v>
@@ -1755,10 +1755,10 @@
         <v>16</v>
       </c>
       <c r="N34" t="n">
-        <v>16486.4056</v>
+        <v>16486.405306122</v>
       </c>
       <c r="O34" t="n">
-        <v>263782.4896</v>
+        <v>263782.484897952</v>
       </c>
       <c r="P34" t="n">
         <v>30500</v>
@@ -2013,10 +2013,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>344599.178</v>
+        <v>344599.17787879</v>
       </c>
       <c r="O40" t="n">
-        <v>3790590.958</v>
+        <v>3790590.95666669</v>
       </c>
       <c r="P40" t="n">
         <v>532900</v>
@@ -2060,10 +2060,10 @@
         <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>28500</v>
+        <v>27000</v>
       </c>
       <c r="O41" t="n">
-        <v>2280000</v>
+        <v>2160000</v>
       </c>
       <c r="P41" t="n">
         <v>20000</v>
@@ -2226,10 +2226,10 @@
         <v>39</v>
       </c>
       <c r="N45" t="n">
-        <v>27000</v>
+        <v>27118.421052632</v>
       </c>
       <c r="O45" t="n">
-        <v>1053000</v>
+        <v>1057618.421052648</v>
       </c>
       <c r="P45" t="n">
         <v>20000</v>
@@ -2797,10 +2797,10 @@
         <v>228</v>
       </c>
       <c r="N58" t="n">
-        <v>4937.3101888412</v>
+        <v>4937.3101890034</v>
       </c>
       <c r="O58" t="n">
-        <v>1125706.723055794</v>
+        <v>1125706.723092775</v>
       </c>
       <c r="P58" t="n">
         <v>7500</v>
@@ -3382,10 +3382,10 @@
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>13694.165945612</v>
+        <v>13593.35</v>
       </c>
       <c r="O71" t="n">
-        <v>13694.165945612</v>
+        <v>13593.35</v>
       </c>
       <c r="P71" t="n">
         <v>25500</v>
@@ -3951,10 +3951,10 @@
         <v>651</v>
       </c>
       <c r="N84" t="n">
-        <v>2582.2546851654</v>
+        <v>2582.2546595174</v>
       </c>
       <c r="O84" t="n">
-        <v>1681047.800042676</v>
+        <v>1681047.783345827</v>
       </c>
       <c r="P84" t="n">
         <v>4500</v>
@@ -4274,10 +4274,10 @@
         <v>3167</v>
       </c>
       <c r="N91" t="n">
-        <v>3158.8608437109</v>
+        <v>3158.8608442176</v>
       </c>
       <c r="O91" t="n">
-        <v>10004112.29203242</v>
+        <v>10004112.29363714</v>
       </c>
       <c r="P91" t="n">
         <v>5600</v>
@@ -4869,10 +4869,10 @@
         <v>581</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100076628</v>
+        <v>3795.7100076717</v>
       </c>
       <c r="O104" t="n">
-        <v>2205307.514452087</v>
+        <v>2205307.514457258</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5094,10 +5094,10 @@
         <v>309</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300570207</v>
+        <v>4890.9300571837</v>
       </c>
       <c r="O109" t="n">
-        <v>1511297.387619396</v>
+        <v>1511297.387669763</v>
       </c>
       <c r="P109" t="n">
         <v>8900</v>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="K119" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5634,10 +5634,10 @@
         <v>108</v>
       </c>
       <c r="N121" t="n">
-        <v>3240.8500597015</v>
+        <v>3240.8500619195</v>
       </c>
       <c r="O121" t="n">
-        <v>350011.806447762</v>
+        <v>350011.806687306</v>
       </c>
       <c r="P121" t="n">
         <v>5200</v>
@@ -5818,10 +5818,10 @@
         <v>303</v>
       </c>
       <c r="N125" t="n">
-        <v>14831.53974042</v>
+        <v>14822.378811881</v>
       </c>
       <c r="O125" t="n">
-        <v>4493956.54134726</v>
+        <v>4491180.779999943</v>
       </c>
       <c r="P125" t="n">
         <v>24900</v>
@@ -6183,10 +6183,10 @@
         <v>308</v>
       </c>
       <c r="N133" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46301728</v>
       </c>
       <c r="O133" t="n">
-        <v>3826118.608088392</v>
+        <v>3826118.60932224</v>
       </c>
       <c r="P133" t="n">
         <v>19900</v>
@@ -6316,10 +6316,10 @@
         <v>2094</v>
       </c>
       <c r="N136" t="n">
-        <v>3472.2764071985</v>
+        <v>3472.2764292368</v>
       </c>
       <c r="O136" t="n">
-        <v>7270946.796673658</v>
+        <v>7270946.84282186</v>
       </c>
       <c r="P136" t="n">
         <v>5900</v>
@@ -6632,10 +6632,10 @@
         <v>1915</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1729736673</v>
+        <v>4371.1729765349</v>
       </c>
       <c r="O143" t="n">
-        <v>8370796.244572879</v>
+        <v>8370796.250064334</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -7622,10 +7622,10 @@
         <v>109</v>
       </c>
       <c r="N165" t="n">
-        <v>4680.6408766234</v>
+        <v>4635.49</v>
       </c>
       <c r="O165" t="n">
-        <v>510189.8555519506</v>
+        <v>505268.41</v>
       </c>
       <c r="P165" t="n">
         <v>7500</v>
@@ -8467,10 +8467,10 @@
         <v>337</v>
       </c>
       <c r="N183" t="n">
-        <v>1633.1055147059</v>
+        <v>1630.9252455662</v>
       </c>
       <c r="O183" t="n">
-        <v>550356.5584558883</v>
+        <v>549621.8077558094</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8559,10 +8559,10 @@
         <v>32</v>
       </c>
       <c r="N185" t="n">
-        <v>1690.5726046512</v>
+        <v>1690.5719339623</v>
       </c>
       <c r="O185" t="n">
-        <v>54098.3233488384</v>
+        <v>54098.3018867936</v>
       </c>
       <c r="P185" t="n">
         <v>2900</v>
@@ -8605,10 +8605,10 @@
         <v>1282</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1949638844</v>
+        <v>1550.1949858928</v>
       </c>
       <c r="O186" t="n">
-        <v>1987349.943699801</v>
+        <v>1987349.97191457</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8697,10 +8697,10 @@
         <v>174</v>
       </c>
       <c r="N188" t="n">
-        <v>2404.4159026746</v>
+        <v>2403.5234112326</v>
       </c>
       <c r="O188" t="n">
-        <v>418368.3670653804</v>
+        <v>418213.0735544724</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9771,10 +9771,10 @@
         <v>1</v>
       </c>
       <c r="N212" t="n">
-        <v>7537.4724786325</v>
+        <v>7537.4727619048</v>
       </c>
       <c r="O212" t="n">
-        <v>7537.4724786325</v>
+        <v>7537.4727619048</v>
       </c>
       <c r="P212" t="n">
         <v>8900</v>
@@ -10460,10 +10460,10 @@
         <v>918</v>
       </c>
       <c r="N228" t="n">
-        <v>6207.9881978301</v>
+        <v>6207.9881950325</v>
       </c>
       <c r="O228" t="n">
-        <v>5698933.165608032</v>
+        <v>5698933.163039835</v>
       </c>
       <c r="P228" t="n">
         <v>9900</v>
@@ -10814,10 +10814,10 @@
         <v>1248</v>
       </c>
       <c r="N236" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.263336112</v>
       </c>
       <c r="O236" t="n">
-        <v>6008200.657310217</v>
+        <v>6008200.643467776</v>
       </c>
       <c r="P236" t="n">
         <v>7900</v>
@@ -10901,10 +10901,10 @@
         <v>32</v>
       </c>
       <c r="N238" t="n">
-        <v>11562.038362573</v>
+        <v>11562.038338279</v>
       </c>
       <c r="O238" t="n">
-        <v>369985.227602336</v>
+        <v>369985.226824928</v>
       </c>
       <c r="P238" t="n">
         <v>18500</v>
@@ -10947,10 +10947,10 @@
         <v>9</v>
       </c>
       <c r="N239" t="n">
-        <v>13513.644059406</v>
+        <v>13513.644408602</v>
       </c>
       <c r="O239" t="n">
-        <v>121622.796534654</v>
+        <v>121622.799677418</v>
       </c>
       <c r="P239" t="n">
         <v>21900</v>
@@ -11259,10 +11259,10 @@
         <v>37</v>
       </c>
       <c r="N246" t="n">
-        <v>8332.7795945946</v>
+        <v>8332.7795901639</v>
       </c>
       <c r="O246" t="n">
-        <v>308312.8450000002</v>
+        <v>308312.8448360643</v>
       </c>
       <c r="P246" t="n">
         <v>14900</v>
@@ -11305,10 +11305,10 @@
         <v>420</v>
       </c>
       <c r="N247" t="n">
-        <v>1561.0125437573</v>
+        <v>1561.0077085243</v>
       </c>
       <c r="O247" t="n">
-        <v>655625.268378066</v>
+        <v>655623.237580206</v>
       </c>
       <c r="P247" t="n">
         <v>2900</v>
@@ -11723,10 +11723,10 @@
         <v>19</v>
       </c>
       <c r="N256" t="n">
-        <v>13033.935120968</v>
+        <v>12981.59</v>
       </c>
       <c r="O256" t="n">
-        <v>247644.767298392</v>
+        <v>246650.21</v>
       </c>
       <c r="P256" t="n">
         <v>21900</v>
@@ -13115,10 +13115,10 @@
         <v>169</v>
       </c>
       <c r="N286" t="n">
-        <v>3646</v>
+        <v>3656.7445972495</v>
       </c>
       <c r="O286" t="n">
-        <v>616174</v>
+        <v>617989.8369351656</v>
       </c>
       <c r="P286" t="n">
         <v>6900</v>
@@ -13161,10 +13161,10 @@
         <v>744</v>
       </c>
       <c r="N287" t="n">
-        <v>1778.4728955224</v>
+        <v>1779.3581483325</v>
       </c>
       <c r="O287" t="n">
-        <v>1323183.834268666</v>
+        <v>1323842.46235938</v>
       </c>
       <c r="P287" t="n">
         <v>4900</v>
@@ -13483,10 +13483,10 @@
         <v>269</v>
       </c>
       <c r="N294" t="n">
-        <v>25577.697661152</v>
+        <v>25534</v>
       </c>
       <c r="O294" t="n">
-        <v>6880400.670849888</v>
+        <v>6868646</v>
       </c>
       <c r="P294" t="n">
         <v>40900</v>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -13986,19 +13986,19 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="N305" t="n">
         <v>4917</v>
       </c>
       <c r="O305" t="n">
-        <v>270435</v>
+        <v>172095</v>
       </c>
       <c r="P305" t="n">
         <v>8600</v>
       </c>
       <c r="Q305" t="n">
-        <v>473000</v>
+        <v>301000</v>
       </c>
     </row>
     <row r="306">
@@ -14406,10 +14406,10 @@
         <v>9</v>
       </c>
       <c r="N314" t="n">
-        <v>10448.858181818</v>
+        <v>10411</v>
       </c>
       <c r="O314" t="n">
-        <v>94039.72363636199</v>
+        <v>93699</v>
       </c>
       <c r="P314" t="n">
         <v>16900</v>
@@ -14452,10 +14452,10 @@
         <v>5</v>
       </c>
       <c r="N315" t="n">
-        <v>2252.3013646055</v>
+        <v>2252.3013888889</v>
       </c>
       <c r="O315" t="n">
-        <v>11261.5068230275</v>
+        <v>11261.5069444445</v>
       </c>
       <c r="P315" t="n">
         <v>3900</v>
@@ -14732,10 +14732,10 @@
         <v>228</v>
       </c>
       <c r="N321" t="n">
-        <v>2328.1186316472</v>
+        <v>2328.1186298701</v>
       </c>
       <c r="O321" t="n">
-        <v>530811.0480155615</v>
+        <v>530811.0476103828</v>
       </c>
       <c r="P321" t="n">
         <v>4500</v>
@@ -14778,10 +14778,10 @@
         <v>119</v>
       </c>
       <c r="N322" t="n">
-        <v>21676</v>
+        <v>21700.382452193</v>
       </c>
       <c r="O322" t="n">
-        <v>2579444</v>
+        <v>2582345.511810967</v>
       </c>
       <c r="P322" t="n">
         <v>34900</v>
@@ -14824,10 +14824,10 @@
         <v>80</v>
       </c>
       <c r="N323" t="n">
-        <v>9384</v>
+        <v>9474.8129032258</v>
       </c>
       <c r="O323" t="n">
-        <v>750720</v>
+        <v>757985.032258064</v>
       </c>
       <c r="P323" t="n">
         <v>15900</v>
@@ -14962,10 +14962,10 @@
         <v>135</v>
       </c>
       <c r="N326" t="n">
-        <v>9018.1565656566</v>
+        <v>9003</v>
       </c>
       <c r="O326" t="n">
-        <v>1217451.136363641</v>
+        <v>1215405</v>
       </c>
       <c r="P326" t="n">
         <v>14900</v>
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15143,19 +15143,19 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N330" t="n">
         <v>13922</v>
       </c>
       <c r="O330" t="n">
-        <v>431582</v>
+        <v>361972</v>
       </c>
       <c r="P330" t="n">
         <v>22900</v>
       </c>
       <c r="Q330" t="n">
-        <v>709900</v>
+        <v>595400</v>
       </c>
     </row>
     <row r="331">
@@ -15318,7 +15318,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15327,19 +15327,19 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="N334" t="n">
-        <v>4907.8228863636</v>
+        <v>4907.8230382775</v>
       </c>
       <c r="O334" t="n">
-        <v>579123.1005909048</v>
+        <v>480966.657751195</v>
       </c>
       <c r="P334" t="n">
         <v>8200</v>
       </c>
       <c r="Q334" t="n">
-        <v>967600</v>
+        <v>803600</v>
       </c>
     </row>
     <row r="335">
@@ -16846,10 +16846,10 @@
         <v>26</v>
       </c>
       <c r="N367" t="n">
-        <v>8711.0687022901</v>
+        <v>8700</v>
       </c>
       <c r="O367" t="n">
-        <v>226487.7862595426</v>
+        <v>226200</v>
       </c>
       <c r="P367" t="n">
         <v>14900</v>
@@ -16880,7 +16880,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16889,19 +16889,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="N368" t="n">
         <v>3639.35</v>
       </c>
       <c r="O368" t="n">
-        <v>407607.2</v>
+        <v>262033.2</v>
       </c>
       <c r="P368" t="n">
         <v>7500</v>
       </c>
       <c r="Q368" t="n">
-        <v>840000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="369">
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>2341</v>
+        <v>2321</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16935,19 +16935,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>2341</v>
+        <v>2321</v>
       </c>
       <c r="N369" t="n">
         <v>1326</v>
       </c>
       <c r="O369" t="n">
-        <v>3104166</v>
+        <v>3077646</v>
       </c>
       <c r="P369" t="n">
         <v>2500</v>
       </c>
       <c r="Q369" t="n">
-        <v>5852500</v>
+        <v>5802500</v>
       </c>
     </row>
     <row r="370">
@@ -17030,10 +17030,10 @@
         <v>72</v>
       </c>
       <c r="N371" t="n">
-        <v>10713.21</v>
+        <v>10736.550326797</v>
       </c>
       <c r="O371" t="n">
-        <v>771351.1199999999</v>
+        <v>773031.623529384</v>
       </c>
       <c r="P371" t="n">
         <v>20900</v>
@@ -17398,10 +17398,10 @@
         <v>25</v>
       </c>
       <c r="N379" t="n">
-        <v>15223.06</v>
+        <v>15594.354146341</v>
       </c>
       <c r="O379" t="n">
-        <v>380576.5</v>
+        <v>389858.853658525</v>
       </c>
       <c r="P379" t="n">
         <v>17500</v>
@@ -17444,10 +17444,10 @@
         <v>174</v>
       </c>
       <c r="N380" t="n">
-        <v>1803</v>
+        <v>1820.7199017199</v>
       </c>
       <c r="O380" t="n">
-        <v>313722</v>
+        <v>316805.2628992626</v>
       </c>
       <c r="P380" t="n">
         <v>3900</v>
@@ -17490,10 +17490,10 @@
         <v>1008</v>
       </c>
       <c r="N381" t="n">
-        <v>1516.0386972166</v>
+        <v>1516.0386977679</v>
       </c>
       <c r="O381" t="n">
-        <v>1528167.006794333</v>
+        <v>1528167.007350043</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
@@ -17582,10 +17582,10 @@
         <v>72</v>
       </c>
       <c r="N383" t="n">
-        <v>2079.3831463696</v>
+        <v>2079.3831437356</v>
       </c>
       <c r="O383" t="n">
-        <v>149715.5865386112</v>
+        <v>149715.5863489632</v>
       </c>
       <c r="P383" t="n">
         <v>2900</v>
@@ -17950,10 +17950,10 @@
         <v>224</v>
       </c>
       <c r="N391" t="n">
-        <v>1595.7734573304</v>
+        <v>1592.2894481236</v>
       </c>
       <c r="O391" t="n">
-        <v>357453.2544420096</v>
+        <v>356672.8363796864</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -18081,10 +18081,10 @@
         <v>312</v>
       </c>
       <c r="N394" t="n">
-        <v>2060.1582208589</v>
+        <v>2060.1580497925</v>
       </c>
       <c r="O394" t="n">
-        <v>642769.3649079768</v>
+        <v>642769.3115352601</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
@@ -18127,10 +18127,10 @@
         <v>400</v>
       </c>
       <c r="N395" t="n">
-        <v>1259.2751822382</v>
+        <v>1259.2752022675</v>
       </c>
       <c r="O395" t="n">
-        <v>503710.07289528</v>
+        <v>503710.080907</v>
       </c>
       <c r="P395" t="n">
         <v>1900</v>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
@@ -18170,19 +18170,19 @@
         <v>0</v>
       </c>
       <c r="M396" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="N396" t="n">
         <v>2980</v>
       </c>
       <c r="O396" t="n">
-        <v>140060</v>
+        <v>80460</v>
       </c>
       <c r="P396" t="n">
         <v>4800</v>
       </c>
       <c r="Q396" t="n">
-        <v>225600</v>
+        <v>129600</v>
       </c>
     </row>
     <row r="397">
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="K400" t="n">
         <v>0</v>
@@ -18350,19 +18350,19 @@
         <v>0</v>
       </c>
       <c r="M400" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="N400" t="n">
         <v>18491</v>
       </c>
       <c r="O400" t="n">
-        <v>869077</v>
+        <v>129437</v>
       </c>
       <c r="P400" t="n">
         <v>13500</v>
       </c>
       <c r="Q400" t="n">
-        <v>634500</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="401">
@@ -18543,10 +18543,10 @@
         <v>588</v>
       </c>
       <c r="N404" t="n">
-        <v>13521.774923206</v>
+        <v>13518</v>
       </c>
       <c r="O404" t="n">
-        <v>7950803.654845128</v>
+        <v>7948584</v>
       </c>
       <c r="P404" t="n">
         <v>21900</v>
@@ -18824,10 +18824,10 @@
         <v>35</v>
       </c>
       <c r="N410" t="n">
-        <v>15547.741935484</v>
+        <v>15423.36</v>
       </c>
       <c r="O410" t="n">
-        <v>544170.9677419401</v>
+        <v>539817.6</v>
       </c>
       <c r="P410" t="n">
         <v>24900</v>
@@ -19326,7 +19326,7 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -19335,19 +19335,19 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="N421" t="n">
         <v>3629.36</v>
       </c>
       <c r="O421" t="n">
-        <v>765794.9600000001</v>
+        <v>693207.76</v>
       </c>
       <c r="P421" t="n">
         <v>3900</v>
       </c>
       <c r="Q421" t="n">
-        <v>822900</v>
+        <v>744900</v>
       </c>
     </row>
     <row r="422">
@@ -19705,10 +19705,10 @@
         <v>306</v>
       </c>
       <c r="N429" t="n">
-        <v>1690.8700098184</v>
+        <v>1690.8700098765</v>
       </c>
       <c r="O429" t="n">
-        <v>517406.2230044304</v>
+        <v>517406.223022209</v>
       </c>
       <c r="P429" t="n">
         <v>3000</v>
@@ -19803,10 +19803,10 @@
         <v>3</v>
       </c>
       <c r="N431" t="n">
-        <v>2270.3215151515</v>
+        <v>2270.3217241379</v>
       </c>
       <c r="O431" t="n">
-        <v>6810.964545454501</v>
+        <v>6810.9651724137</v>
       </c>
       <c r="P431" t="n">
         <v>3900</v>
@@ -20401,10 +20401,10 @@
         <v>52</v>
       </c>
       <c r="N444" t="n">
-        <v>4032.3967801047</v>
+        <v>4032.3967716535</v>
       </c>
       <c r="O444" t="n">
-        <v>209684.6325654444</v>
+        <v>209684.632125982</v>
       </c>
       <c r="P444" t="n">
         <v>4200</v>
@@ -21278,10 +21278,10 @@
         <v>17742</v>
       </c>
       <c r="N463" t="n">
-        <v>703.7945831140599</v>
+        <v>703.79457726026</v>
       </c>
       <c r="O463" t="n">
-        <v>12486723.49360965</v>
+        <v>12486723.38975153</v>
       </c>
       <c r="P463" t="n">
         <v>900</v>
@@ -21419,10 +21419,10 @@
         <v>40</v>
       </c>
       <c r="N466" t="n">
-        <v>2501.3837931034</v>
+        <v>2501.3837572254</v>
       </c>
       <c r="O466" t="n">
-        <v>100055.351724136</v>
+        <v>100055.350289016</v>
       </c>
       <c r="P466" t="n">
         <v>4100</v>
@@ -22272,10 +22272,10 @@
         <v>18</v>
       </c>
       <c r="N484" t="n">
-        <v>2832.1961818182</v>
+        <v>2832.1965384615</v>
       </c>
       <c r="O484" t="n">
-        <v>50979.5312727276</v>
+        <v>50979.537692307</v>
       </c>
       <c r="P484" t="n">
         <v>12900</v>
@@ -22653,10 +22653,10 @@
         <v>40</v>
       </c>
       <c r="N492" t="n">
-        <v>12156.79</v>
+        <v>12709.371363636</v>
       </c>
       <c r="O492" t="n">
-        <v>486271.6</v>
+        <v>508374.8545454401</v>
       </c>
       <c r="P492" t="n">
         <v>12000</v>
@@ -22751,10 +22751,10 @@
         <v>7</v>
       </c>
       <c r="N494" t="n">
-        <v>16670.89</v>
+        <v>17351.334489796</v>
       </c>
       <c r="O494" t="n">
-        <v>116696.23</v>
+        <v>121459.341428572</v>
       </c>
       <c r="P494" t="n">
         <v>25500</v>
@@ -22846,10 +22846,10 @@
         <v>12</v>
       </c>
       <c r="N496" t="n">
-        <v>9746.8802105263</v>
+        <v>9746.880217391301</v>
       </c>
       <c r="O496" t="n">
-        <v>116962.5625263156</v>
+        <v>116962.5626086956</v>
       </c>
       <c r="P496" t="n">
         <v>18500</v>
@@ -23201,20 +23201,17 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>C7294</t>
-        </is>
-      </c>
-      <c r="B504" t="n">
-        <v>6895675680022</v>
+          <t>C73-IO</t>
+        </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>INFLABLE RANA C73</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -23223,7 +23220,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -23232,44 +23229,42 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="N504" t="n">
-        <v>4337.31</v>
+        <v>3000.33</v>
       </c>
       <c r="O504" t="n">
-        <v>286262.46</v>
+        <v>1962215.82</v>
       </c>
       <c r="P504" t="n">
-        <v>12900</v>
+        <v>2900</v>
       </c>
       <c r="Q504" t="n">
-        <v>851400</v>
+        <v>1896600</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>C73-IO</t>
-        </is>
+          <t>C731</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>6903728884218</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>INFLABLE RANA C73</t>
-        </is>
-      </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>ATARI CEL ANIMALES</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J505" t="n">
-        <v>654</v>
+        <v>3</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -23278,33 +23273,30 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>654</v>
+        <v>3</v>
       </c>
       <c r="N505" t="n">
-        <v>3000.33</v>
+        <v>19743.578983051</v>
       </c>
       <c r="O505" t="n">
-        <v>1962215.82</v>
+        <v>59230.736949153</v>
       </c>
       <c r="P505" t="n">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="Q505" t="n">
-        <v>1896600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>C731</t>
-        </is>
-      </c>
-      <c r="B506" t="n">
-        <v>6903728884218</v>
+          <t>C732</t>
+        </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>ATARI CEL ANIMALES</t>
+          <t>GLOBOS BOUQUET HROES</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -23313,7 +23305,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -23322,39 +23314,47 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="N506" t="n">
-        <v>19743.578983051</v>
+        <v>3414.5659584665</v>
       </c>
       <c r="O506" t="n">
-        <v>59230.736949153</v>
+        <v>1065344.579041548</v>
       </c>
       <c r="P506" t="n">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="Q506" t="n">
-        <v>8400</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>C732</t>
-        </is>
+          <t>C7325</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>6974555555022</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET HROES</t>
+          <t>PISTA EN BLISTER C7325</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J507" t="n">
-        <v>312</v>
+        <v>94</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23363,38 +23363,38 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>312</v>
+        <v>94</v>
       </c>
       <c r="N507" t="n">
-        <v>3414.5659584665</v>
+        <v>3067.0906360424</v>
       </c>
       <c r="O507" t="n">
-        <v>1065344.579041548</v>
+        <v>288306.5197879856</v>
       </c>
       <c r="P507" t="n">
-        <v>3500</v>
+        <v>7200</v>
       </c>
       <c r="Q507" t="n">
-        <v>1092000</v>
+        <v>676800</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>C7325</t>
+          <t>C7332</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>6974555555022</v>
+        <v>9092407809158</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>FICHAS DE ARMAR MUÑECO SOLDADO EN BOLSA C7332</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -23403,7 +23403,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23412,38 +23412,35 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="N508" t="n">
-        <v>3067.0906360424</v>
+        <v>507.37</v>
       </c>
       <c r="O508" t="n">
-        <v>288306.5197879856</v>
+        <v>12176.88</v>
       </c>
       <c r="P508" t="n">
-        <v>7200</v>
+        <v>2500</v>
       </c>
       <c r="Q508" t="n">
-        <v>676800</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>C7332</t>
-        </is>
-      </c>
-      <c r="B509" t="n">
-        <v>9092407809158</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR MUÑECO SOLDADO EN BOLSA C7332</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -23452,7 +23449,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -23461,35 +23458,38 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="N509" t="n">
-        <v>507.37</v>
+        <v>640</v>
       </c>
       <c r="O509" t="n">
-        <v>12176.88</v>
+        <v>32000</v>
       </c>
       <c r="P509" t="n">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="Q509" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -23498,7 +23498,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23507,33 +23507,33 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="N510" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O510" t="n">
-        <v>32000</v>
+        <v>657950.89</v>
       </c>
       <c r="P510" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q510" t="n">
-        <v>40000</v>
+        <v>926300</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -23547,7 +23547,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>157</v>
+        <v>335</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23556,33 +23556,33 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>157</v>
+        <v>335</v>
       </c>
       <c r="N511" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O511" t="n">
-        <v>657950.89</v>
+        <v>1172406.2</v>
       </c>
       <c r="P511" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q511" t="n">
-        <v>926300</v>
+        <v>2311500</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7367</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>6920240750098</v>
+        <v>6.9202407501356e+18</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>HELICPTERODIDACTICO EN BOLSA C7367</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -23596,7 +23596,7 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23605,33 +23605,33 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="N512" t="n">
-        <v>3499.72</v>
+        <v>5347.88</v>
       </c>
       <c r="O512" t="n">
-        <v>1172406.2</v>
+        <v>1684582.2</v>
       </c>
       <c r="P512" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="Q512" t="n">
-        <v>2311500</v>
+        <v>2488500</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>C7367</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>6.9202407501356e+18</v>
+        <v>6920240750159</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>HELICPTERODIDACTICO EN BOLSA C7367</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -23645,7 +23645,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -23654,38 +23654,35 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="N513" t="n">
-        <v>5347.88</v>
+        <v>4578.04</v>
       </c>
       <c r="O513" t="n">
-        <v>1684582.2</v>
+        <v>1258961</v>
       </c>
       <c r="P513" t="n">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="Q513" t="n">
-        <v>2488500</v>
+        <v>2062500</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B514" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -23694,7 +23691,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>275</v>
+        <v>2568</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -23703,35 +23700,38 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>275</v>
+        <v>2568</v>
       </c>
       <c r="N514" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O514" t="n">
-        <v>1258961</v>
+        <v>1232640</v>
       </c>
       <c r="P514" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q514" t="n">
-        <v>2062500</v>
+        <v>1540800</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7400</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>6920240228207</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>GALLINA PONE HUEVOS CON LUZ Y SONIDO C7400/2282</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -23740,7 +23740,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>2568</v>
+        <v>35</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23749,33 +23749,33 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>2568</v>
+        <v>35</v>
       </c>
       <c r="N515" t="n">
-        <v>480</v>
+        <v>10378.12</v>
       </c>
       <c r="O515" t="n">
-        <v>1232640</v>
+        <v>363234.2</v>
       </c>
       <c r="P515" t="n">
-        <v>600</v>
+        <v>13500</v>
       </c>
       <c r="Q515" t="n">
-        <v>1540800</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>C7400</t>
+          <t>C7401</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>6920240228207</v>
+        <v>6920601877884</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>GALLINA PONE HUEVOS CON LUZ Y SONIDO C7400/2282</t>
+          <t>SONAJERO PANDERETA Y TROMPETA EN BOLSA C7401</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -23789,7 +23789,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -23798,38 +23798,38 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="N516" t="n">
-        <v>10378.12</v>
+        <v>3828.03</v>
       </c>
       <c r="O516" t="n">
-        <v>363234.2</v>
+        <v>750293.88</v>
       </c>
       <c r="P516" t="n">
-        <v>13500</v>
+        <v>7500</v>
       </c>
       <c r="Q516" t="n">
-        <v>472500</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>C7401</t>
+          <t>C7409</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>6920601877884</v>
+        <v>6954446905013</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>SONAJERO PANDERETA Y TROMPETA EN BOLSA C7401</t>
+          <t>CARRO METALICO CAMARO 1/24 C7409</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -23838,7 +23838,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>196</v>
+        <v>16</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -23847,33 +23847,33 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>196</v>
+        <v>16</v>
       </c>
       <c r="N517" t="n">
-        <v>3828.03</v>
+        <v>23229.8</v>
       </c>
       <c r="O517" t="n">
-        <v>750293.88</v>
+        <v>371676.8</v>
       </c>
       <c r="P517" t="n">
-        <v>7500</v>
+        <v>56000</v>
       </c>
       <c r="Q517" t="n">
-        <v>1470000</v>
+        <v>896000</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>C7409</t>
+          <t>C7411</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>6954446905013</v>
+        <v>6954446905037</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>CARRO METALICO CAMARO 1/24 C7409</t>
+          <t>CARRO METALICO TOYOTA 1/24 C7411</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -23896,38 +23896,38 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="N518" t="n">
-        <v>23229.8</v>
+        <v>20983.74</v>
       </c>
       <c r="O518" t="n">
-        <v>371676.8</v>
+        <v>839349.6000000001</v>
       </c>
       <c r="P518" t="n">
-        <v>56000</v>
+        <v>65900</v>
       </c>
       <c r="Q518" t="n">
-        <v>896000</v>
+        <v>2636000</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>C7411</t>
+          <t>C7415</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>6954446905037</v>
+        <v>3400869890861</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>CARRO METALICO TOYOTA 1/24 C7411</t>
+          <t>JUEGO MOLDEABLE DINOSAURIO EN TARRO C7415</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -23945,47 +23945,42 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="N519" t="n">
-        <v>20983.74</v>
+        <v>2296.45</v>
       </c>
       <c r="O519" t="n">
-        <v>839349.6000000001</v>
+        <v>2296.45</v>
       </c>
       <c r="P519" t="n">
-        <v>65900</v>
+        <v>8900</v>
       </c>
       <c r="Q519" t="n">
-        <v>2636000</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>C7415</t>
+          <t>C743</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>3400869890861</v>
+        <v>8596162180329</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>JUEGO MOLDEABLE DINOSAURIO EN TARRO C7415</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO MENSAJE 10 STD</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J520" t="n">
-        <v>1</v>
+        <v>2950</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -23994,42 +23989,44 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>1</v>
+        <v>2950</v>
       </c>
       <c r="N520" t="n">
-        <v>2296.45</v>
+        <v>286.61335546613</v>
       </c>
       <c r="O520" t="n">
-        <v>2296.45</v>
+        <v>845509.3986250834</v>
       </c>
       <c r="P520" t="n">
-        <v>8900</v>
+        <v>350</v>
       </c>
       <c r="Q520" t="n">
-        <v>8900</v>
+        <v>1032500</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>C743</t>
-        </is>
-      </c>
-      <c r="B521" t="n">
-        <v>8596162180329</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE 10 STD</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J521" t="n">
-        <v>2950</v>
+        <v>155</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -24038,35 +24035,38 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>2950</v>
+        <v>155</v>
       </c>
       <c r="N521" t="n">
-        <v>286.61335546613</v>
+        <v>1554.12</v>
       </c>
       <c r="O521" t="n">
-        <v>845509.3986250834</v>
+        <v>240888.6</v>
       </c>
       <c r="P521" t="n">
-        <v>350</v>
+        <v>1900</v>
       </c>
       <c r="Q521" t="n">
-        <v>1032500</v>
+        <v>294500</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>C744-IO</t>
-        </is>
+          <t>C7443</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>6998799866621</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>COCINA EN CAJA LUZ Y SONIDO C7443</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -24075,7 +24075,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -24084,47 +24084,42 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="N522" t="n">
-        <v>1554.12</v>
+        <v>12229.63</v>
       </c>
       <c r="O522" t="n">
-        <v>240888.6</v>
+        <v>73377.78</v>
       </c>
       <c r="P522" t="n">
-        <v>1900</v>
+        <v>49900</v>
       </c>
       <c r="Q522" t="n">
-        <v>294500</v>
+        <v>299400</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>C7443</t>
+          <t>C745</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>6998799866621</v>
+        <v>8596162180343</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>COCINA EN CAJA LUZ Y SONIDO C7443</t>
-        </is>
-      </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J523" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -24133,42 +24128,44 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="N523" t="n">
-        <v>12229.63</v>
+        <v>3097.9492241379</v>
       </c>
       <c r="O523" t="n">
-        <v>73377.78</v>
+        <v>405831.3483620649</v>
       </c>
       <c r="P523" t="n">
-        <v>49900</v>
+        <v>2400</v>
       </c>
       <c r="Q523" t="n">
-        <v>299400</v>
+        <v>314400</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>C745</t>
-        </is>
-      </c>
-      <c r="B524" t="n">
-        <v>8596162180343</v>
+          <t>C7458</t>
+        </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
+          <t>COCINA EN CAJA C7458</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J524" t="n">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -24177,35 +24174,38 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="N524" t="n">
-        <v>3097.9492241379</v>
+        <v>36004.28</v>
       </c>
       <c r="O524" t="n">
-        <v>405831.3483620649</v>
+        <v>180021.4</v>
       </c>
       <c r="P524" t="n">
-        <v>2400</v>
+        <v>83500</v>
       </c>
       <c r="Q524" t="n">
-        <v>314400</v>
+        <v>417500</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>C7458</t>
-        </is>
+          <t>C7459</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>3790120020022</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>COCINA EN CAJA C7458</t>
+          <t>PIANO MUSICAL LEONCITO C7459</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="J525" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24223,38 +24223,35 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N525" t="n">
-        <v>36004.28</v>
+        <v>7742.4</v>
       </c>
       <c r="O525" t="n">
-        <v>180021.4</v>
+        <v>15484.8</v>
       </c>
       <c r="P525" t="n">
-        <v>83500</v>
+        <v>17500</v>
       </c>
       <c r="Q525" t="n">
-        <v>417500</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>C7459</t>
-        </is>
-      </c>
-      <c r="B526" t="n">
-        <v>3790120020022</v>
+          <t>C7462</t>
+        </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>PIANO MUSICAL LEONCITO C7459</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -24263,7 +24260,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24272,30 +24269,30 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N526" t="n">
-        <v>7742.4</v>
+        <v>14751.820392157</v>
       </c>
       <c r="O526" t="n">
-        <v>15484.8</v>
+        <v>132766.383529413</v>
       </c>
       <c r="P526" t="n">
-        <v>17500</v>
+        <v>37100</v>
       </c>
       <c r="Q526" t="n">
-        <v>35000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>C7462</t>
+          <t>C7463</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>DINOSAURIO C7463</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -24309,7 +24306,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24318,35 +24315,35 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N527" t="n">
-        <v>14751.820377358</v>
+        <v>9372</v>
       </c>
       <c r="O527" t="n">
-        <v>132766.383396222</v>
+        <v>112464</v>
       </c>
       <c r="P527" t="n">
-        <v>37100</v>
+        <v>17900</v>
       </c>
       <c r="Q527" t="n">
-        <v>333900</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>C7463</t>
+          <t>C7470</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>DINOSAURIO C7463</t>
+          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -24355,7 +24352,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24364,30 +24361,33 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N528" t="n">
-        <v>9372</v>
+        <v>14170.65</v>
       </c>
       <c r="O528" t="n">
-        <v>112464</v>
+        <v>340095.6</v>
       </c>
       <c r="P528" t="n">
-        <v>17900</v>
+        <v>49000</v>
       </c>
       <c r="Q528" t="n">
-        <v>214800</v>
+        <v>1176000</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>C7470</t>
-        </is>
+          <t>C7471</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>6973673170247</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
+          <t>CARRO METALICO COLECCION TOYOTA PRADO C7471</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -24401,7 +24401,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24410,33 +24410,33 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N529" t="n">
-        <v>14170.65</v>
+        <v>13168.16</v>
       </c>
       <c r="O529" t="n">
-        <v>340095.6</v>
+        <v>105345.28</v>
       </c>
       <c r="P529" t="n">
         <v>49000</v>
       </c>
       <c r="Q529" t="n">
-        <v>1176000</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>C7471</t>
+          <t>C7473</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>6973673170247</v>
+        <v>6896896988512500</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION TOYOTA PRADO C7471</t>
+          <t>CARRO METALICO COLECCIO TOYOTA MODEL C7473</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -24450,7 +24450,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24459,33 +24459,33 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="N530" t="n">
-        <v>13168.16</v>
+        <v>10504.37</v>
       </c>
       <c r="O530" t="n">
-        <v>105345.28</v>
+        <v>546227.24</v>
       </c>
       <c r="P530" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q530" t="n">
-        <v>392000</v>
+        <v>2340000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>C7473</t>
+          <t>C7474</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>6896896988512500</v>
+        <v>6896988512529</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCIO TOYOTA MODEL C7473</t>
+          <t>CARRO METALICO COLECCION CHELVI GT500 C7474</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -24499,7 +24499,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24508,33 +24508,33 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="N531" t="n">
-        <v>10504.37</v>
+        <v>9526.51</v>
       </c>
       <c r="O531" t="n">
-        <v>546227.24</v>
+        <v>304848.32</v>
       </c>
       <c r="P531" t="n">
         <v>45000</v>
       </c>
       <c r="Q531" t="n">
-        <v>2340000</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>C7474</t>
+          <t>C7475</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>6896988512529</v>
+        <v>6896988512536</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION CHELVI GT500 C7474</t>
+          <t>CARRO METALICO COLECCION BMW C7475</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -24548,7 +24548,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24557,33 +24557,30 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="N532" t="n">
-        <v>9526.51</v>
+        <v>10798.03</v>
       </c>
       <c r="O532" t="n">
-        <v>304848.32</v>
+        <v>431921.2</v>
       </c>
       <c r="P532" t="n">
         <v>45000</v>
       </c>
       <c r="Q532" t="n">
-        <v>1440000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>C7475</t>
-        </is>
-      </c>
-      <c r="B533" t="n">
-        <v>6896988512536</v>
+          <t>C7479</t>
+        </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7475</t>
+          <t>CARRO COLECCION METALICO MERCEDES C7479</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -24597,7 +24594,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24606,30 +24603,30 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="N533" t="n">
-        <v>10798.03</v>
+        <v>8473.91</v>
       </c>
       <c r="O533" t="n">
-        <v>431921.2</v>
+        <v>135582.56</v>
       </c>
       <c r="P533" t="n">
-        <v>45000</v>
+        <v>49000</v>
       </c>
       <c r="Q533" t="n">
-        <v>1800000</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>C7479</t>
+          <t>C7480</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCEDES C7479</t>
+          <t>CARRO METALICO COLECCION BMW C7480</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -24655,10 +24652,10 @@
         <v>16</v>
       </c>
       <c r="N534" t="n">
-        <v>8473.91</v>
+        <v>10541.34</v>
       </c>
       <c r="O534" t="n">
-        <v>135582.56</v>
+        <v>168661.44</v>
       </c>
       <c r="P534" t="n">
         <v>49000</v>
@@ -24670,12 +24667,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>C7480</t>
+          <t>C7481</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7480</t>
+          <t>CARRO COLECCION METALICO AUDI A7 C7481</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -24689,7 +24686,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24698,30 +24695,30 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N535" t="n">
-        <v>10541.34</v>
+        <v>6006.77</v>
       </c>
       <c r="O535" t="n">
-        <v>168661.44</v>
+        <v>216243.72</v>
       </c>
       <c r="P535" t="n">
         <v>49000</v>
       </c>
       <c r="Q535" t="n">
-        <v>784000</v>
+        <v>1764000</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>C7481</t>
+          <t>C7482</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO AUDI A7 C7481</t>
+          <t>CARRO METALICO COLECCION BMW C7482</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -24735,7 +24732,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24744,30 +24741,30 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="N536" t="n">
-        <v>6006.77</v>
+        <v>7205.37</v>
       </c>
       <c r="O536" t="n">
-        <v>216243.72</v>
+        <v>86464.44</v>
       </c>
       <c r="P536" t="n">
         <v>49000</v>
       </c>
       <c r="Q536" t="n">
-        <v>1764000</v>
+        <v>588000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>C7482</t>
+          <t>C7483</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7482</t>
+          <t>CARRO COLECCION METALICO TOYOTA C7483</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -24781,7 +24778,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24790,30 +24787,30 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N537" t="n">
-        <v>7205.37</v>
+        <v>9031.370000000001</v>
       </c>
       <c r="O537" t="n">
-        <v>86464.44</v>
+        <v>72250.96000000001</v>
       </c>
       <c r="P537" t="n">
         <v>49000</v>
       </c>
       <c r="Q537" t="n">
-        <v>588000</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>C7483</t>
+          <t>C7484</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO TOYOTA C7483</t>
+          <t>CARRO COLECCION METALICO MERCEDES AMG C7484</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -24827,7 +24824,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24836,30 +24833,30 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N538" t="n">
-        <v>9031.370000000001</v>
+        <v>7884.67</v>
       </c>
       <c r="O538" t="n">
-        <v>72250.96000000001</v>
+        <v>47308.02</v>
       </c>
       <c r="P538" t="n">
         <v>49000</v>
       </c>
       <c r="Q538" t="n">
-        <v>392000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>C7484</t>
+          <t>C7486</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCEDES AMG C7484</t>
+          <t>CARRO COLECCCION METALICO TESLA C7486</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -24873,7 +24870,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24882,35 +24879,38 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="N539" t="n">
-        <v>7884.67</v>
+        <v>6529.54</v>
       </c>
       <c r="O539" t="n">
-        <v>47308.02</v>
+        <v>261181.6</v>
       </c>
       <c r="P539" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q539" t="n">
-        <v>294000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>C7486</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>CARRO COLECCCION METALICO TESLA C7486</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24919,7 +24919,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24928,38 +24928,35 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N540" t="n">
-        <v>6529.54</v>
+        <v>8919.16</v>
       </c>
       <c r="O540" t="n">
-        <v>261181.6</v>
+        <v>552987.92</v>
       </c>
       <c r="P540" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="Q540" t="n">
-        <v>1800000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>C7488</t>
-        </is>
-      </c>
-      <c r="B541" t="n">
-        <v>6945158254520</v>
+          <t>C7503</t>
+        </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>BOLSO ALAS CON ACCESORIOS DE BELLEZA C7503</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24968,7 +24965,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24977,30 +24974,33 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="N541" t="n">
-        <v>8919.16</v>
+        <v>5216.9</v>
       </c>
       <c r="O541" t="n">
-        <v>552987.92</v>
+        <v>380833.7</v>
       </c>
       <c r="P541" t="n">
-        <v>10000</v>
+        <v>20500</v>
       </c>
       <c r="Q541" t="n">
-        <v>620000</v>
+        <v>1496500</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>C7503</t>
-        </is>
+          <t>C7513</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>6905698382824</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>BOLSO ALAS CON ACCESORIOS DE BELLEZA C7503</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -25014,7 +25014,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -25023,33 +25023,33 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="N542" t="n">
-        <v>5216.9</v>
+        <v>1024.29</v>
       </c>
       <c r="O542" t="n">
-        <v>380833.7</v>
+        <v>158764.95</v>
       </c>
       <c r="P542" t="n">
-        <v>20500</v>
+        <v>2900</v>
       </c>
       <c r="Q542" t="n">
-        <v>1496500</v>
+        <v>449500</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C7514</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>6905698382824</v>
+        <v>6905698386815</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
+          <t>SONAJERO LUZ BOLSA C7514</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -25063,7 +25063,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>155</v>
+        <v>664</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -25072,33 +25072,33 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>155</v>
+        <v>664</v>
       </c>
       <c r="N543" t="n">
-        <v>1024.29</v>
+        <v>711.48</v>
       </c>
       <c r="O543" t="n">
-        <v>158764.95</v>
+        <v>472422.72</v>
       </c>
       <c r="P543" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q543" t="n">
-        <v>449500</v>
+        <v>1660000</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>C7514</t>
+          <t>C7517</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>6905698386815</v>
+        <v>9872447770119</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ BOLSA C7514</t>
+          <t>SET HERRAMIENTA EN BOLSA C7517</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -25112,7 +25112,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -25121,47 +25121,42 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="N544" t="n">
-        <v>711.48</v>
+        <v>1278.27</v>
       </c>
       <c r="O544" t="n">
-        <v>472422.72</v>
+        <v>3834.81</v>
       </c>
       <c r="P544" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="Q544" t="n">
-        <v>1660000</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>C7517</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>9872447770119</v>
+        <v>8596162180497</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>SET HERRAMIENTA EN BOLSA C7517</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J545" t="n">
-        <v>3</v>
+        <v>619</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -25170,42 +25165,47 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>3</v>
+        <v>619</v>
       </c>
       <c r="N545" t="n">
-        <v>1278.27</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O545" t="n">
-        <v>3834.81</v>
+        <v>720358.0180402457</v>
       </c>
       <c r="P545" t="n">
-        <v>5900</v>
+        <v>1500</v>
       </c>
       <c r="Q545" t="n">
-        <v>17700</v>
+        <v>928500</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7524</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>8596162180497</v>
+        <v>6905454130201</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J546" t="n">
-        <v>619</v>
+        <v>300</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25214,38 +25214,38 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>619</v>
+        <v>300</v>
       </c>
       <c r="N546" t="n">
-        <v>1163.7447787403</v>
+        <v>1934.77</v>
       </c>
       <c r="O546" t="n">
-        <v>720358.0180402457</v>
+        <v>580431</v>
       </c>
       <c r="P546" t="n">
-        <v>1500</v>
+        <v>8900</v>
       </c>
       <c r="Q546" t="n">
-        <v>928500</v>
+        <v>2670000</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>C7524</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>6905454130201</v>
+        <v>6951241752002</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>CARRO BEBE TRUCK PQÑ X3 C7524</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25254,7 +25254,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>300</v>
+        <v>1085</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25263,38 +25263,35 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>300</v>
+        <v>1085</v>
       </c>
       <c r="N547" t="n">
-        <v>1934.77</v>
+        <v>7046.9398262758</v>
       </c>
       <c r="O547" t="n">
-        <v>580431</v>
+        <v>7645929.711509244</v>
       </c>
       <c r="P547" t="n">
-        <v>8900</v>
+        <v>9900</v>
       </c>
       <c r="Q547" t="n">
-        <v>2670000</v>
+        <v>10741500</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B548" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25303,7 +25300,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>1085</v>
+        <v>116</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25312,35 +25309,38 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>1085</v>
+        <v>116</v>
       </c>
       <c r="N548" t="n">
-        <v>7046.9398262758</v>
+        <v>24602.063537906</v>
       </c>
       <c r="O548" t="n">
-        <v>7645929.711509244</v>
+        <v>2853839.370397096</v>
       </c>
       <c r="P548" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q548" t="n">
-        <v>10741500</v>
+        <v>3236400</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C7555-B</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>6970635795388</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -25349,7 +25349,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25358,38 +25358,35 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="N549" t="n">
-        <v>24338.47</v>
+        <v>16146.498</v>
       </c>
       <c r="O549" t="n">
-        <v>2823262.52</v>
+        <v>16146.498</v>
       </c>
       <c r="P549" t="n">
-        <v>27900</v>
+        <v>26900</v>
       </c>
       <c r="Q549" t="n">
-        <v>3236400</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>C7555-B</t>
-        </is>
-      </c>
-      <c r="B550" t="n">
-        <v>6970635795388</v>
+          <t>C7561-AB</t>
+        </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
+          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -25398,7 +25395,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25407,35 +25404,38 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N550" t="n">
-        <v>16146.498181818</v>
+        <v>38508.28</v>
       </c>
       <c r="O550" t="n">
-        <v>16146.498181818</v>
+        <v>924198.72</v>
       </c>
       <c r="P550" t="n">
-        <v>26900</v>
+        <v>40000</v>
       </c>
       <c r="Q550" t="n">
-        <v>26900</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>C7561-AB</t>
-        </is>
+          <t>C7586</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>7808880075865</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
+          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -25444,7 +25444,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>24</v>
+        <v>648</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25453,33 +25453,33 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>24</v>
+        <v>648</v>
       </c>
       <c r="N551" t="n">
-        <v>38508.28</v>
+        <v>665.3240434332999</v>
       </c>
       <c r="O551" t="n">
-        <v>924198.72</v>
+        <v>431129.9801447784</v>
       </c>
       <c r="P551" t="n">
-        <v>40000</v>
+        <v>2900</v>
       </c>
       <c r="Q551" t="n">
-        <v>960000</v>
+        <v>1879200</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>C7586</t>
+          <t>C7587</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>7808880075865</v>
+        <v>7587228020247</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
+          <t>TROMPO LUCES DEPORTES C7587</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -25493,7 +25493,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>648</v>
+        <v>256</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25502,33 +25502,33 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>648</v>
+        <v>256</v>
       </c>
       <c r="N552" t="n">
-        <v>665.3240434332999</v>
+        <v>1080.18</v>
       </c>
       <c r="O552" t="n">
-        <v>431129.9801447784</v>
+        <v>276526.08</v>
       </c>
       <c r="P552" t="n">
-        <v>2900</v>
+        <v>4900</v>
       </c>
       <c r="Q552" t="n">
-        <v>1879200</v>
+        <v>1254400</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>C7587</t>
+          <t>C7588</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>7587228020247</v>
+        <v>7588228020244</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>TROMPO LUCES DEPORTES C7587</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -25542,7 +25542,7 @@
         </is>
       </c>
       <c r="J553" t="n">
-        <v>256</v>
+        <v>720</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25551,38 +25551,38 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>256</v>
+        <v>720</v>
       </c>
       <c r="N553" t="n">
-        <v>1080.18</v>
+        <v>641.78</v>
       </c>
       <c r="O553" t="n">
-        <v>276526.08</v>
+        <v>462081.6</v>
       </c>
       <c r="P553" t="n">
-        <v>4900</v>
+        <v>2500</v>
       </c>
       <c r="Q553" t="n">
-        <v>1254400</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -25591,7 +25591,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>720</v>
+        <v>550</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25600,33 +25600,33 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>720</v>
+        <v>550</v>
       </c>
       <c r="N554" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O554" t="n">
-        <v>462081.6</v>
+        <v>4296545</v>
       </c>
       <c r="P554" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q554" t="n">
-        <v>1800000</v>
+        <v>7645000</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA PATO C7614</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25649,25 +25649,25 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="N555" t="n">
-        <v>7811.9</v>
+        <v>4581.84</v>
       </c>
       <c r="O555" t="n">
-        <v>4296545</v>
+        <v>229092</v>
       </c>
       <c r="P555" t="n">
-        <v>13900</v>
+        <v>7900</v>
       </c>
       <c r="Q555" t="n">
-        <v>7645000</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>C7614</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -25675,12 +25675,12 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA PATO C7614</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -25689,7 +25689,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25698,38 +25698,35 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="N556" t="n">
-        <v>4581.84</v>
+        <v>3155</v>
       </c>
       <c r="O556" t="n">
-        <v>229092</v>
+        <v>558435</v>
       </c>
       <c r="P556" t="n">
-        <v>7900</v>
+        <v>5900</v>
       </c>
       <c r="Q556" t="n">
-        <v>395000</v>
+        <v>1044300</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>C7614-F</t>
-        </is>
-      </c>
-      <c r="B557" t="n">
-        <v>6999899236130</v>
+          <t>C7615</t>
+        </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
+          <t>CHALECO PISCINA ALITAS C7615</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -25738,7 +25735,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25747,30 +25744,33 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="N557" t="n">
-        <v>3155</v>
+        <v>1262.07</v>
       </c>
       <c r="O557" t="n">
-        <v>558435</v>
+        <v>277655.4</v>
       </c>
       <c r="P557" t="n">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="Q557" t="n">
-        <v>1044300</v>
+        <v>1958000</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>C7615</t>
-        </is>
+          <t>C7617</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>6999899236192</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>CHALECO PISCINA ALITAS C7615</t>
+          <t>BRAZITOS PISCINA #A 12PCS</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -25784,7 +25784,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25793,33 +25793,33 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="N558" t="n">
-        <v>1262.07</v>
+        <v>540.40123762376</v>
       </c>
       <c r="O558" t="n">
-        <v>277655.4</v>
+        <v>6484.81485148512</v>
       </c>
       <c r="P558" t="n">
-        <v>8900</v>
+        <v>2500</v>
       </c>
       <c r="Q558" t="n">
-        <v>1958000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>C7617</t>
+          <t>C7618</t>
         </is>
       </c>
       <c r="B559" t="n">
-        <v>6999899236192</v>
+        <v>6999899236208</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>BRAZITOS PISCINA #A 12PCS</t>
+          <t>BRAZITO PISCINA  27X17 C7618</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -25833,7 +25833,7 @@
         </is>
       </c>
       <c r="J559" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25842,33 +25842,33 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N559" t="n">
-        <v>540.40123762376</v>
+        <v>616.4</v>
       </c>
       <c r="O559" t="n">
-        <v>6484.81485148512</v>
+        <v>616.4</v>
       </c>
       <c r="P559" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q559" t="n">
-        <v>30000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>C7618</t>
+          <t>C7631</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>6999899236208</v>
+        <v>6999899236352</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>BRAZITO PISCINA  27X17 C7618</t>
+          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -25882,7 +25882,7 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
@@ -25891,47 +25891,39 @@
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="N560" t="n">
-        <v>616.4</v>
+        <v>315.02766929134</v>
       </c>
       <c r="O560" t="n">
-        <v>616.4</v>
+        <v>29927.6285826773</v>
       </c>
       <c r="P560" t="n">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="Q560" t="n">
-        <v>2900</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>C7631</t>
-        </is>
-      </c>
-      <c r="B561" t="n">
-        <v>6999899236352</v>
+          <t>C766</t>
+        </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DINOSAURIOS C7631</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>DOMIN PEQUEO</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J561" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25940,30 +25932,30 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="N561" t="n">
-        <v>315.02766929134</v>
+        <v>2752.52</v>
       </c>
       <c r="O561" t="n">
-        <v>29927.6285826773</v>
+        <v>38535.28</v>
       </c>
       <c r="P561" t="n">
-        <v>2200</v>
+        <v>4500</v>
       </c>
       <c r="Q561" t="n">
-        <v>209000</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>C766</t>
+          <t>C771</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>DOMIN PEQUEO</t>
+          <t>GLOBO LOVE YOU</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -25972,7 +25964,7 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
@@ -25981,30 +25973,33 @@
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="N562" t="n">
-        <v>2752.52</v>
+        <v>1244.5992565056</v>
       </c>
       <c r="O562" t="n">
-        <v>38535.28</v>
+        <v>88366.54721189759</v>
       </c>
       <c r="P562" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="Q562" t="n">
-        <v>63000</v>
+        <v>106500</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>C771</t>
-        </is>
+          <t>C773</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>2021071411128</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>GLOBO LOVE YOU</t>
+          <t>GLOBO HBD 32</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -26013,7 +26008,7 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -26022,42 +26017,47 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="N563" t="n">
-        <v>1244.5992565056</v>
+        <v>2703.2000014451</v>
       </c>
       <c r="O563" t="n">
-        <v>88366.54721189759</v>
+        <v>113534.4000606942</v>
       </c>
       <c r="P563" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="Q563" t="n">
-        <v>106500</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>C773</t>
+          <t>C80-IO</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>2021071411128</v>
+        <v>6524521011221</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>GLOBO HBD 32</t>
+          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J564" t="n">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -26066,47 +26066,39 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="N564" t="n">
-        <v>2703.2000014451</v>
+        <v>2235.19</v>
       </c>
       <c r="O564" t="n">
-        <v>113534.4000606942</v>
+        <v>695144.09</v>
       </c>
       <c r="P564" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="Q564" t="n">
-        <v>189000</v>
+        <v>933000</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>C80-IO</t>
-        </is>
-      </c>
-      <c r="B565" t="n">
-        <v>6524521011221</v>
+          <t>C815</t>
+        </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
-        </is>
-      </c>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J565" t="n">
-        <v>311</v>
+        <v>12</v>
       </c>
       <c r="K565" t="n">
         <v>0</v>
@@ -26115,30 +26107,33 @@
         <v>0</v>
       </c>
       <c r="M565" t="n">
-        <v>311</v>
+        <v>12</v>
       </c>
       <c r="N565" t="n">
-        <v>2235.19</v>
+        <v>110520.77</v>
       </c>
       <c r="O565" t="n">
-        <v>695144.09</v>
+        <v>1326249.24</v>
       </c>
       <c r="P565" t="n">
-        <v>3000</v>
+        <v>176900</v>
       </c>
       <c r="Q565" t="n">
-        <v>933000</v>
+        <v>2122800</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>C815</t>
-        </is>
+          <t>C819</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>2087202108190</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -26147,7 +26142,7 @@
         </is>
       </c>
       <c r="J566" t="n">
-        <v>12</v>
+        <v>600</v>
       </c>
       <c r="K566" t="n">
         <v>0</v>
@@ -26156,33 +26151,30 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>12</v>
+        <v>600</v>
       </c>
       <c r="N566" t="n">
-        <v>110520.77</v>
+        <v>6761.25</v>
       </c>
       <c r="O566" t="n">
-        <v>1326249.24</v>
+        <v>4056750</v>
       </c>
       <c r="P566" t="n">
-        <v>176900</v>
+        <v>5200</v>
       </c>
       <c r="Q566" t="n">
-        <v>2122800</v>
+        <v>3120000</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B567" t="n">
-        <v>2087202108190</v>
+          <t>C822</t>
+        </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -26191,7 +26183,7 @@
         </is>
       </c>
       <c r="J567" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="K567" t="n">
         <v>0</v>
@@ -26200,30 +26192,33 @@
         <v>0</v>
       </c>
       <c r="M567" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="N567" t="n">
-        <v>6761.25</v>
+        <v>5577.2680373832</v>
       </c>
       <c r="O567" t="n">
-        <v>4056750</v>
+        <v>167318.041121496</v>
       </c>
       <c r="P567" t="n">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="Q567" t="n">
-        <v>3120000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>C822</t>
-        </is>
+          <t>C828</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>6900159908285</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
+          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -26232,7 +26227,7 @@
         </is>
       </c>
       <c r="J568" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K568" t="n">
         <v>0</v>
@@ -26241,33 +26236,33 @@
         <v>0</v>
       </c>
       <c r="M568" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N568" t="n">
-        <v>5577.2680373832</v>
+        <v>6243.3531884058</v>
       </c>
       <c r="O568" t="n">
-        <v>167318.041121496</v>
+        <v>249734.127536232</v>
       </c>
       <c r="P568" t="n">
-        <v>6500</v>
+        <v>9900</v>
       </c>
       <c r="Q568" t="n">
-        <v>195000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>C828</t>
+          <t>C848</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>6900159908285</v>
+        <v>6900159908483</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
+          <t>BLOBO GRANDE SORPRESA NINONINA</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -26276,7 +26271,7 @@
         </is>
       </c>
       <c r="J569" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K569" t="n">
         <v>0</v>
@@ -26285,33 +26280,30 @@
         <v>0</v>
       </c>
       <c r="M569" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="N569" t="n">
-        <v>6243.3531884058</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O569" t="n">
-        <v>249734.127536232</v>
+        <v>224025.773659551</v>
       </c>
       <c r="P569" t="n">
-        <v>9900</v>
+        <v>3000</v>
       </c>
       <c r="Q569" t="n">
-        <v>396000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>C848</t>
-        </is>
-      </c>
-      <c r="B570" t="n">
-        <v>6900159908483</v>
+          <t>C855</t>
+        </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>BLOBO GRANDE SORPRESA NINONINA</t>
+          <t>GLOBOS BUQUET CERVEZA</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -26320,7 +26312,7 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K570" t="n">
         <v>0</v>
@@ -26329,30 +26321,30 @@
         <v>0</v>
       </c>
       <c r="M570" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="N570" t="n">
-        <v>2489.1752628839</v>
+        <v>2129.8331743119</v>
       </c>
       <c r="O570" t="n">
-        <v>224025.773659551</v>
+        <v>42596.663486238</v>
       </c>
       <c r="P570" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="Q570" t="n">
-        <v>270000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>C855</t>
+          <t>C863</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>GLOBOS BUQUET CERVEZA</t>
+          <t>GLOBOS BOUQUET FELIZ DIA</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -26361,7 +26353,7 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K571" t="n">
         <v>0</v>
@@ -26370,30 +26362,30 @@
         <v>0</v>
       </c>
       <c r="M571" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N571" t="n">
-        <v>2129.8331743119</v>
+        <v>5497.1752906977</v>
       </c>
       <c r="O571" t="n">
-        <v>42596.663486238</v>
+        <v>27485.8764534885</v>
       </c>
       <c r="P571" t="n">
-        <v>2700</v>
+        <v>6500</v>
       </c>
       <c r="Q571" t="n">
-        <v>54000</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>C863</t>
+          <t>C866</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET FELIZ DIA</t>
+          <t>YOYO SURTIDO</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -26402,7 +26394,7 @@
         </is>
       </c>
       <c r="J572" t="n">
-        <v>5</v>
+        <v>1178</v>
       </c>
       <c r="K572" t="n">
         <v>0</v>
@@ -26411,30 +26403,33 @@
         <v>0</v>
       </c>
       <c r="M572" t="n">
-        <v>5</v>
+        <v>1178</v>
       </c>
       <c r="N572" t="n">
-        <v>5497.1752906977</v>
+        <v>1176.57</v>
       </c>
       <c r="O572" t="n">
-        <v>27485.8764534885</v>
+        <v>1385999.46</v>
       </c>
       <c r="P572" t="n">
-        <v>6500</v>
+        <v>1900</v>
       </c>
       <c r="Q572" t="n">
-        <v>32500</v>
+        <v>2238200</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>C866</t>
-        </is>
+          <t>C887</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>6920210213929</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>YOYO SURTIDO</t>
+          <t>BALON FOOTBALL SURTIDO #2</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -26443,7 +26438,7 @@
         </is>
       </c>
       <c r="J573" t="n">
-        <v>1178</v>
+        <v>553</v>
       </c>
       <c r="K573" t="n">
         <v>0</v>
@@ -26452,33 +26447,30 @@
         <v>0</v>
       </c>
       <c r="M573" t="n">
-        <v>1178</v>
+        <v>553</v>
       </c>
       <c r="N573" t="n">
-        <v>1176.57</v>
+        <v>3181.9</v>
       </c>
       <c r="O573" t="n">
-        <v>1385999.46</v>
+        <v>1759590.7</v>
       </c>
       <c r="P573" t="n">
-        <v>1900</v>
+        <v>5100</v>
       </c>
       <c r="Q573" t="n">
-        <v>2238200</v>
+        <v>2820300</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>C887</t>
-        </is>
-      </c>
-      <c r="B574" t="n">
-        <v>6920210213929</v>
+          <t>C888</t>
+        </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>BALON FOOTBALL SURTIDO #2</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -26487,7 +26479,7 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>553</v>
+        <v>4</v>
       </c>
       <c r="K574" t="n">
         <v>0</v>
@@ -26496,30 +26488,33 @@
         <v>0</v>
       </c>
       <c r="M574" t="n">
-        <v>553</v>
+        <v>4</v>
       </c>
       <c r="N574" t="n">
-        <v>3181.9</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O574" t="n">
-        <v>1759590.7</v>
+        <v>4854.7285603112</v>
       </c>
       <c r="P574" t="n">
-        <v>5100</v>
+        <v>1500</v>
       </c>
       <c r="Q574" t="n">
-        <v>2820300</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>C888</t>
-        </is>
+          <t>C890</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>6913545113699</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>CORTINA FEST</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -26528,7 +26523,7 @@
         </is>
       </c>
       <c r="J575" t="n">
-        <v>4</v>
+        <v>450</v>
       </c>
       <c r="K575" t="n">
         <v>0</v>
@@ -26537,33 +26532,33 @@
         <v>0</v>
       </c>
       <c r="M575" t="n">
-        <v>4</v>
+        <v>450</v>
       </c>
       <c r="N575" t="n">
-        <v>1213.6821400778</v>
+        <v>1794.2879512478</v>
       </c>
       <c r="O575" t="n">
-        <v>4854.7285603112</v>
+        <v>807429.57806151</v>
       </c>
       <c r="P575" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="Q575" t="n">
-        <v>6000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>C890</t>
+          <t>C895</t>
         </is>
       </c>
       <c r="B576" t="n">
-        <v>6913545113699</v>
+        <v>6913545115815</v>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>CORTINA FEST</t>
+          <t>CORTINA FESTIN TORNASOL</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -26572,7 +26567,7 @@
         </is>
       </c>
       <c r="J576" t="n">
-        <v>450</v>
+        <v>44</v>
       </c>
       <c r="K576" t="n">
         <v>0</v>
@@ -26581,33 +26576,33 @@
         <v>0</v>
       </c>
       <c r="M576" t="n">
-        <v>450</v>
+        <v>44</v>
       </c>
       <c r="N576" t="n">
-        <v>1794.2879512478</v>
+        <v>2830.2252424242</v>
       </c>
       <c r="O576" t="n">
-        <v>807429.57806151</v>
+        <v>124529.9106666648</v>
       </c>
       <c r="P576" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="Q576" t="n">
-        <v>720000</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>C895</t>
+          <t>C899</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>6913545115815</v>
+        <v>6920202108998</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>CORTINA FESTIN TORNASOL</t>
+          <t>GLOBO BOUQUET ARCO GRANDE</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -26616,7 +26611,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -26625,33 +26620,33 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="N577" t="n">
-        <v>2830.2252424242</v>
+        <v>15219.155119048</v>
       </c>
       <c r="O577" t="n">
-        <v>124529.9106666648</v>
+        <v>426136.343333344</v>
       </c>
       <c r="P577" t="n">
-        <v>2400</v>
+        <v>16000</v>
       </c>
       <c r="Q577" t="n">
-        <v>105600</v>
+        <v>448000</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>C899</t>
+          <t>C91</t>
         </is>
       </c>
       <c r="B578" t="n">
-        <v>6920202108998</v>
+        <v>6803012120018</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET ARCO GRANDE</t>
+          <t>GLOBO BOUQUET SURTIDO</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -26660,7 +26655,7 @@
         </is>
       </c>
       <c r="J578" t="n">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="K578" t="n">
         <v>0</v>
@@ -26669,42 +26664,47 @@
         <v>0</v>
       </c>
       <c r="M578" t="n">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="N578" t="n">
-        <v>15219.155119048</v>
+        <v>2523.3377277904</v>
       </c>
       <c r="O578" t="n">
-        <v>426136.343333344</v>
+        <v>479434.168280176</v>
       </c>
       <c r="P578" t="n">
-        <v>16000</v>
+        <v>2800</v>
       </c>
       <c r="Q578" t="n">
-        <v>448000</v>
+        <v>532000</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>C91</t>
+          <t>C91-IO</t>
         </is>
       </c>
       <c r="B579" t="n">
-        <v>6803012120018</v>
+        <v>6524521011108</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET SURTIDO</t>
+          <t>GLOBO BOUQUET X 7 MAS BASE 2021-17</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J579" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="K579" t="n">
         <v>0</v>
@@ -26713,47 +26713,42 @@
         <v>0</v>
       </c>
       <c r="M579" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="N579" t="n">
-        <v>2523.3377277904</v>
+        <v>4648.51</v>
       </c>
       <c r="O579" t="n">
-        <v>479434.168280176</v>
+        <v>278910.6</v>
       </c>
       <c r="P579" t="n">
-        <v>2800</v>
+        <v>5500</v>
       </c>
       <c r="Q579" t="n">
-        <v>532000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>C91-IO</t>
+          <t>C913</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>6524521011108</v>
+        <v>6920210204279</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 7 MAS BASE 2021-17</t>
-        </is>
-      </c>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>BLISTER HERRAMIENTAS DINO</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J580" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
@@ -26762,42 +26757,44 @@
         <v>0</v>
       </c>
       <c r="M580" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N580" t="n">
-        <v>4648.51</v>
+        <v>8922.2155844156</v>
       </c>
       <c r="O580" t="n">
-        <v>278910.6</v>
+        <v>401499.701298702</v>
       </c>
       <c r="P580" t="n">
-        <v>5500</v>
+        <v>8200</v>
       </c>
       <c r="Q580" t="n">
-        <v>330000</v>
+        <v>369000</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>C913</t>
-        </is>
-      </c>
-      <c r="B581" t="n">
-        <v>6920210204279</v>
+          <t>C92-IO</t>
+        </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>BLISTER HERRAMIENTAS DINO</t>
+          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J581" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="K581" t="n">
         <v>0</v>
@@ -26806,44 +26803,42 @@
         <v>0</v>
       </c>
       <c r="M581" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="N581" t="n">
-        <v>8922.2155844156</v>
+        <v>1520</v>
       </c>
       <c r="O581" t="n">
-        <v>401499.701298702</v>
+        <v>167200</v>
       </c>
       <c r="P581" t="n">
-        <v>8200</v>
+        <v>1900</v>
       </c>
       <c r="Q581" t="n">
-        <v>369000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>C92-IO</t>
-        </is>
+          <t>C928</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>6920202109285</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO BOUQUET COLA SIRENA</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J582" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="K582" t="n">
         <v>0</v>
@@ -26852,33 +26847,33 @@
         <v>0</v>
       </c>
       <c r="M582" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="N582" t="n">
-        <v>1520</v>
+        <v>12251</v>
       </c>
       <c r="O582" t="n">
-        <v>167200</v>
+        <v>343028</v>
       </c>
       <c r="P582" t="n">
-        <v>1900</v>
+        <v>13000</v>
       </c>
       <c r="Q582" t="n">
-        <v>209000</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>C928</t>
+          <t>C935</t>
         </is>
       </c>
       <c r="B583" t="n">
-        <v>6920202109285</v>
+        <v>6920202109353</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET COLA SIRENA</t>
+          <t>GLOBO BOUQUET</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -26887,7 +26882,7 @@
         </is>
       </c>
       <c r="J583" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="K583" t="n">
         <v>0</v>
@@ -26896,33 +26891,35 @@
         <v>0</v>
       </c>
       <c r="M583" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="N583" t="n">
-        <v>12251</v>
+        <v>3683.6327464789</v>
       </c>
       <c r="O583" t="n">
-        <v>343028</v>
+        <v>368363.27464789</v>
       </c>
       <c r="P583" t="n">
-        <v>13000</v>
+        <v>3600</v>
       </c>
       <c r="Q583" t="n">
-        <v>364000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>C935</t>
-        </is>
-      </c>
-      <c r="B584" t="n">
-        <v>6920202109353</v>
+          <t>C943</t>
+        </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET</t>
+          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -26931,7 +26928,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -26940,35 +26937,35 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="N584" t="n">
-        <v>3683.6327464789</v>
+        <v>22951.704248927</v>
       </c>
       <c r="O584" t="n">
-        <v>368363.27464789</v>
+        <v>6426477.189699559</v>
       </c>
       <c r="P584" t="n">
-        <v>3600</v>
+        <v>37900</v>
       </c>
       <c r="Q584" t="n">
-        <v>360000</v>
+        <v>10612000</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>C943</t>
+          <t>C984</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>CG2016531</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
-        </is>
-      </c>
-      <c r="E585" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TANGRAM</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -26977,7 +26974,7 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>280</v>
+        <v>172</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
@@ -26986,35 +26983,30 @@
         <v>0</v>
       </c>
       <c r="M585" t="n">
-        <v>280</v>
+        <v>172</v>
       </c>
       <c r="N585" t="n">
-        <v>22951.704345992</v>
+        <v>705.52795348837</v>
       </c>
       <c r="O585" t="n">
-        <v>6426477.216877759</v>
+        <v>121350.8079999996</v>
       </c>
       <c r="P585" t="n">
-        <v>37900</v>
+        <v>1500</v>
       </c>
       <c r="Q585" t="n">
-        <v>10612000</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>C984</t>
-        </is>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>CG2016531</t>
+          <t>C99</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>TANGRAM</t>
+          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -27023,7 +27015,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -27032,39 +27024,49 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="N586" t="n">
-        <v>705.52795348837</v>
+        <v>4985.4088235294</v>
       </c>
       <c r="O586" t="n">
-        <v>121350.8079999996</v>
+        <v>189445.5352941172</v>
       </c>
       <c r="P586" t="n">
-        <v>1500</v>
+        <v>7900</v>
       </c>
       <c r="Q586" t="n">
-        <v>258000</v>
+        <v>300200</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>CA1673</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>CA11673</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
+          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J587" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="K587" t="n">
         <v>0</v>
@@ -27073,40 +27075,40 @@
         <v>0</v>
       </c>
       <c r="M587" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="N587" t="n">
-        <v>5058.1883211679</v>
+        <v>1547.8830909091</v>
       </c>
       <c r="O587" t="n">
-        <v>192211.1562043802</v>
+        <v>3095.7661818182</v>
       </c>
       <c r="P587" t="n">
-        <v>7900</v>
+        <v>5500</v>
       </c>
       <c r="Q587" t="n">
-        <v>300200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>CA1673</t>
+          <t>CA886</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>CA11673</t>
+          <t>CA886</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>JUGUETE GUITARRA MUSICAL DINO CA1673</t>
+          <t>ANIMAL TAMBOR  CERDITO CA886</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -27115,7 +27117,7 @@
         </is>
       </c>
       <c r="J588" t="n">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
@@ -27124,35 +27126,30 @@
         <v>0</v>
       </c>
       <c r="M588" t="n">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="N588" t="n">
-        <v>1547.8829824561</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O588" t="n">
-        <v>3095.7659649122</v>
+        <v>507865.6637163752</v>
       </c>
       <c r="P588" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="Q588" t="n">
-        <v>11000</v>
+        <v>578000</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CA886</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>CA886</t>
+          <t>CA891</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>ANIMAL TAMBOR  CERDITO CA886</t>
+          <t>MUÑECA TAMBOR CA891</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -27166,7 +27163,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -27175,35 +27172,35 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="N589" t="n">
-        <v>1757.3206356968</v>
+        <v>1561.33</v>
       </c>
       <c r="O589" t="n">
-        <v>507865.6637163752</v>
+        <v>518361.56</v>
       </c>
       <c r="P589" t="n">
         <v>2000</v>
       </c>
       <c r="Q589" t="n">
-        <v>578000</v>
+        <v>664000</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CA891</t>
+          <t>DPB087</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>MUÑECA TAMBOR CA891</t>
+          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -27212,7 +27209,7 @@
         </is>
       </c>
       <c r="J590" t="n">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="K590" t="n">
         <v>0</v>
@@ -27221,35 +27218,35 @@
         <v>0</v>
       </c>
       <c r="M590" t="n">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="N590" t="n">
-        <v>1561.33</v>
+        <v>13520</v>
       </c>
       <c r="O590" t="n">
-        <v>518361.56</v>
+        <v>135200</v>
       </c>
       <c r="P590" t="n">
-        <v>2000</v>
+        <v>16900</v>
       </c>
       <c r="Q590" t="n">
-        <v>664000</v>
+        <v>169000</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>DPB087</t>
+          <t>DV052</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>VIEJITOS CM25 VIEJITO/DPB087</t>
+          <t>PELOTA PISCINA DV052</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -27258,7 +27255,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>10</v>
+        <v>1700</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -27267,35 +27264,35 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>10</v>
+        <v>1700</v>
       </c>
       <c r="N591" t="n">
-        <v>13520</v>
+        <v>219.9969793366</v>
       </c>
       <c r="O591" t="n">
-        <v>135200</v>
+        <v>373994.86487222</v>
       </c>
       <c r="P591" t="n">
-        <v>16900</v>
+        <v>260</v>
       </c>
       <c r="Q591" t="n">
-        <v>169000</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>DV052</t>
+          <t>FG021</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DV052</t>
+          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -27304,7 +27301,7 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>1700</v>
+        <v>10</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
@@ -27313,35 +27310,35 @@
         <v>0</v>
       </c>
       <c r="M592" t="n">
-        <v>1700</v>
+        <v>10</v>
       </c>
       <c r="N592" t="n">
-        <v>219.9969793366</v>
+        <v>3504.16</v>
       </c>
       <c r="O592" t="n">
-        <v>373994.86487222</v>
+        <v>35041.6</v>
       </c>
       <c r="P592" t="n">
-        <v>260</v>
+        <v>3900</v>
       </c>
       <c r="Q592" t="n">
-        <v>442000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>FG021</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>CARRO LLANTON DINOSAURIO BOLSA 1967-1</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -27350,7 +27347,7 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
@@ -27359,30 +27356,30 @@
         <v>0</v>
       </c>
       <c r="M593" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="N593" t="n">
-        <v>3504.16</v>
+        <v>13493.858287462</v>
       </c>
       <c r="O593" t="n">
-        <v>35041.6</v>
+        <v>1025533.229847112</v>
       </c>
       <c r="P593" t="n">
-        <v>3900</v>
+        <v>16900</v>
       </c>
       <c r="Q593" t="n">
-        <v>39000</v>
+        <v>1284400</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -27396,7 +27393,7 @@
         </is>
       </c>
       <c r="J594" t="n">
-        <v>76</v>
+        <v>439</v>
       </c>
       <c r="K594" t="n">
         <v>0</v>
@@ -27405,35 +27402,35 @@
         <v>0</v>
       </c>
       <c r="M594" t="n">
-        <v>76</v>
+        <v>439</v>
       </c>
       <c r="N594" t="n">
-        <v>13493.858287462</v>
+        <v>2644.9</v>
       </c>
       <c r="O594" t="n">
-        <v>1025533.229847112</v>
+        <v>1161111.1</v>
       </c>
       <c r="P594" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q594" t="n">
-        <v>1284400</v>
+        <v>1712100</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG042</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>BURBUJERO PANDA BLISTER 43043</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -27442,7 +27439,7 @@
         </is>
       </c>
       <c r="J595" t="n">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="K595" t="n">
         <v>0</v>
@@ -27451,30 +27448,30 @@
         <v>0</v>
       </c>
       <c r="M595" t="n">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="N595" t="n">
-        <v>2644.9</v>
+        <v>14576.2</v>
       </c>
       <c r="O595" t="n">
-        <v>1161111.1</v>
+        <v>102033.4</v>
       </c>
       <c r="P595" t="n">
-        <v>3900</v>
+        <v>19000</v>
       </c>
       <c r="Q595" t="n">
-        <v>1712100</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>FG042</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>BURBUJERO PANDA BLISTER 43043</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -27488,7 +27485,7 @@
         </is>
       </c>
       <c r="J596" t="n">
-        <v>7</v>
+        <v>351</v>
       </c>
       <c r="K596" t="n">
         <v>0</v>
@@ -27497,35 +27494,35 @@
         <v>0</v>
       </c>
       <c r="M596" t="n">
-        <v>7</v>
+        <v>351</v>
       </c>
       <c r="N596" t="n">
-        <v>14576.2</v>
+        <v>1952.66</v>
       </c>
       <c r="O596" t="n">
-        <v>102033.4</v>
+        <v>685383.66</v>
       </c>
       <c r="P596" t="n">
-        <v>19000</v>
+        <v>3500</v>
       </c>
       <c r="Q596" t="n">
-        <v>133000</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG057</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>ABACO BOLSA 8022</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -27534,7 +27531,7 @@
         </is>
       </c>
       <c r="J597" t="n">
-        <v>351</v>
+        <v>232</v>
       </c>
       <c r="K597" t="n">
         <v>0</v>
@@ -27543,35 +27540,35 @@
         <v>0</v>
       </c>
       <c r="M597" t="n">
-        <v>351</v>
+        <v>232</v>
       </c>
       <c r="N597" t="n">
-        <v>1952.66</v>
+        <v>2293.26</v>
       </c>
       <c r="O597" t="n">
-        <v>685383.66</v>
+        <v>532036.3200000001</v>
       </c>
       <c r="P597" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="Q597" t="n">
-        <v>1228500</v>
+        <v>1113600</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>FG050</t>
+          <t>FG083</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
+          <t>SONAJERO BOLSA RANA XZM5XS</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -27580,7 +27577,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -27589,35 +27586,35 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="N598" t="n">
-        <v>9708.190000000001</v>
+        <v>1952.41</v>
       </c>
       <c r="O598" t="n">
-        <v>67957.33</v>
+        <v>310433.19</v>
       </c>
       <c r="P598" t="n">
-        <v>10200</v>
+        <v>2700</v>
       </c>
       <c r="Q598" t="n">
-        <v>71400</v>
+        <v>429300</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>FG057</t>
+          <t>FG092</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>ABACO BOLSA 8022</t>
+          <t>BLISTER  TETERA SJ377-1</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -27626,7 +27623,7 @@
         </is>
       </c>
       <c r="J599" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="K599" t="n">
         <v>0</v>
@@ -27635,35 +27632,35 @@
         <v>0</v>
       </c>
       <c r="M599" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="N599" t="n">
-        <v>2293.26</v>
+        <v>9855.037826087</v>
       </c>
       <c r="O599" t="n">
-        <v>532036.3200000001</v>
+        <v>9855.037826087</v>
       </c>
       <c r="P599" t="n">
-        <v>4800</v>
+        <v>15500</v>
       </c>
       <c r="Q599" t="n">
-        <v>1113600</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>FG083</t>
+          <t>FG097</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA RANA XZM5XS</t>
+          <t>MUÑECO ROBOT BLISTER 5090B</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -27672,7 +27669,7 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
@@ -27681,35 +27678,35 @@
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="N600" t="n">
-        <v>1952.41</v>
+        <v>17986.24</v>
       </c>
       <c r="O600" t="n">
-        <v>310433.19</v>
+        <v>1438899.2</v>
       </c>
       <c r="P600" t="n">
-        <v>2700</v>
+        <v>18500</v>
       </c>
       <c r="Q600" t="n">
-        <v>429300</v>
+        <v>1480000</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>FG092</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>BLISTER  TETERA SJ377-1</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -27718,7 +27715,7 @@
         </is>
       </c>
       <c r="J601" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K601" t="n">
         <v>0</v>
@@ -27727,35 +27724,35 @@
         <v>0</v>
       </c>
       <c r="M601" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="N601" t="n">
-        <v>9855.037826087</v>
+        <v>7480</v>
       </c>
       <c r="O601" t="n">
-        <v>9855.037826087</v>
+        <v>269280</v>
       </c>
       <c r="P601" t="n">
-        <v>15500</v>
+        <v>9500</v>
       </c>
       <c r="Q601" t="n">
-        <v>15500</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>FG097</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>MUÑECO ROBOT BLISTER 5090B</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -27764,7 +27761,7 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="K602" t="n">
         <v>0</v>
@@ -27773,30 +27770,30 @@
         <v>0</v>
       </c>
       <c r="M602" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="N602" t="n">
-        <v>17986.24</v>
+        <v>5280</v>
       </c>
       <c r="O602" t="n">
-        <v>1438899.2</v>
+        <v>174240</v>
       </c>
       <c r="P602" t="n">
-        <v>18500</v>
+        <v>6900</v>
       </c>
       <c r="Q602" t="n">
-        <v>1480000</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -27810,7 +27807,7 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
@@ -27819,30 +27816,33 @@
         <v>0</v>
       </c>
       <c r="M603" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="N603" t="n">
-        <v>7480</v>
+        <v>5280</v>
       </c>
       <c r="O603" t="n">
-        <v>269280</v>
+        <v>469920</v>
       </c>
       <c r="P603" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="Q603" t="n">
-        <v>342000</v>
+        <v>614100</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>J-1316</t>
-        </is>
+          <t>J-1386</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
+          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -27856,7 +27856,7 @@
         </is>
       </c>
       <c r="J604" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="K604" t="n">
         <v>0</v>
@@ -27865,30 +27865,30 @@
         <v>0</v>
       </c>
       <c r="M604" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="N604" t="n">
-        <v>5280</v>
+        <v>7920</v>
       </c>
       <c r="O604" t="n">
-        <v>174240</v>
+        <v>427680</v>
       </c>
       <c r="P604" t="n">
-        <v>6900</v>
+        <v>10500</v>
       </c>
       <c r="Q604" t="n">
-        <v>227700</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>J-1317</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -27902,7 +27902,7 @@
         </is>
       </c>
       <c r="J605" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="K605" t="n">
         <v>0</v>
@@ -27911,33 +27911,30 @@
         <v>0</v>
       </c>
       <c r="M605" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="N605" t="n">
-        <v>5280</v>
+        <v>4576</v>
       </c>
       <c r="O605" t="n">
-        <v>469920</v>
+        <v>329472</v>
       </c>
       <c r="P605" t="n">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="Q605" t="n">
-        <v>614100</v>
+        <v>424800</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>J-1386</t>
-        </is>
-      </c>
-      <c r="B606" t="n">
-        <v>7700154271143</v>
+          <t>J-719</t>
+        </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>VARA LUZ UNICORNIO 37cm J-1386</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -27951,7 +27948,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="K606" t="n">
         <v>0</v>
@@ -27960,30 +27957,30 @@
         <v>0</v>
       </c>
       <c r="M606" t="n">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="N606" t="n">
-        <v>7920</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O606" t="n">
-        <v>427680</v>
+        <v>1078177.036310099</v>
       </c>
       <c r="P606" t="n">
-        <v>10500</v>
+        <v>6900</v>
       </c>
       <c r="Q606" t="n">
-        <v>567000</v>
+        <v>1407600</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -27997,7 +27994,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="K607" t="n">
         <v>0</v>
@@ -28006,35 +28003,35 @@
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="N607" t="n">
-        <v>4591.2533333333</v>
+        <v>46491.75</v>
       </c>
       <c r="O607" t="n">
-        <v>330570.2399999976</v>
+        <v>2743013.25</v>
       </c>
       <c r="P607" t="n">
-        <v>5900</v>
+        <v>52900</v>
       </c>
       <c r="Q607" t="n">
-        <v>424800</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -28043,7 +28040,7 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
@@ -28052,35 +28049,35 @@
         <v>0</v>
       </c>
       <c r="M608" t="n">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="N608" t="n">
-        <v>5285.1815505397</v>
+        <v>910.85</v>
       </c>
       <c r="O608" t="n">
-        <v>1078177.036310099</v>
+        <v>22771.25</v>
       </c>
       <c r="P608" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="Q608" t="n">
-        <v>1407600</v>
+        <v>197500</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -28089,7 +28086,7 @@
         </is>
       </c>
       <c r="J609" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="K609" t="n">
         <v>0</v>
@@ -28098,30 +28095,30 @@
         <v>0</v>
       </c>
       <c r="M609" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="N609" t="n">
-        <v>46491.75</v>
+        <v>1129.14</v>
       </c>
       <c r="O609" t="n">
-        <v>2743013.25</v>
+        <v>13549.68</v>
       </c>
       <c r="P609" t="n">
-        <v>52900</v>
+        <v>6900</v>
       </c>
       <c r="Q609" t="n">
-        <v>3121100</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -28135,7 +28132,7 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
@@ -28144,35 +28141,40 @@
         <v>0</v>
       </c>
       <c r="M610" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="N610" t="n">
-        <v>910.85</v>
+        <v>11433.53</v>
       </c>
       <c r="O610" t="n">
-        <v>22771.25</v>
+        <v>68601.18000000001</v>
       </c>
       <c r="P610" t="n">
-        <v>7900</v>
+        <v>15000</v>
       </c>
       <c r="Q610" t="n">
-        <v>197500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -28181,7 +28183,7 @@
         </is>
       </c>
       <c r="J611" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K611" t="n">
         <v>0</v>
@@ -28190,35 +28192,35 @@
         <v>0</v>
       </c>
       <c r="M611" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N611" t="n">
-        <v>1129.14</v>
+        <v>15452.21</v>
       </c>
       <c r="O611" t="n">
-        <v>13549.68</v>
+        <v>46356.63</v>
       </c>
       <c r="P611" t="n">
-        <v>6900</v>
+        <v>36500</v>
       </c>
       <c r="Q611" t="n">
-        <v>82800</v>
+        <v>109500</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -28227,7 +28229,7 @@
         </is>
       </c>
       <c r="J612" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="K612" t="n">
         <v>0</v>
@@ -28236,40 +28238,40 @@
         <v>0</v>
       </c>
       <c r="M612" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="N612" t="n">
-        <v>11433.53</v>
+        <v>1319.3612448133</v>
       </c>
       <c r="O612" t="n">
-        <v>68601.18000000001</v>
+        <v>145129.736929463</v>
       </c>
       <c r="P612" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="Q612" t="n">
-        <v>90000</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -28278,7 +28280,7 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K613" t="n">
         <v>0</v>
@@ -28287,35 +28289,35 @@
         <v>0</v>
       </c>
       <c r="M613" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N613" t="n">
-        <v>15452.21</v>
+        <v>751.45</v>
       </c>
       <c r="O613" t="n">
-        <v>46356.63</v>
+        <v>751.45</v>
       </c>
       <c r="P613" t="n">
-        <v>36500</v>
+        <v>2500</v>
       </c>
       <c r="Q613" t="n">
-        <v>109500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -28324,7 +28326,7 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="K614" t="n">
         <v>0</v>
@@ -28333,40 +28335,35 @@
         <v>0</v>
       </c>
       <c r="M614" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="N614" t="n">
-        <v>1319.3611070111</v>
+        <v>571.87</v>
       </c>
       <c r="O614" t="n">
-        <v>184710.554981554</v>
+        <v>69196.27</v>
       </c>
       <c r="P614" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="Q614" t="n">
-        <v>490000</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -28375,7 +28372,7 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
@@ -28384,35 +28381,40 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="N615" t="n">
-        <v>751.45</v>
+        <v>227.41615210843</v>
       </c>
       <c r="O615" t="n">
-        <v>751.45</v>
+        <v>154642.9834337324</v>
       </c>
       <c r="P615" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q615" t="n">
-        <v>2500</v>
+        <v>816000</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -28421,7 +28423,7 @@
         </is>
       </c>
       <c r="J616" t="n">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="K616" t="n">
         <v>0</v>
@@ -28430,44 +28432,47 @@
         <v>0</v>
       </c>
       <c r="M616" t="n">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="N616" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O616" t="n">
-        <v>69196.27</v>
+        <v>208257.84</v>
       </c>
       <c r="P616" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q616" t="n">
-        <v>302500</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>MG40334</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J617" t="n">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="K617" t="n">
         <v>0</v>
@@ -28476,40 +28481,35 @@
         <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>680</v>
+        <v>158</v>
       </c>
       <c r="N617" t="n">
-        <v>227.41615210843</v>
+        <v>2539.5719098712</v>
       </c>
       <c r="O617" t="n">
-        <v>154642.9834337324</v>
+        <v>401252.3617596496</v>
       </c>
       <c r="P617" t="n">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="Q617" t="n">
-        <v>816000</v>
+        <v>458200</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -28518,7 +28518,7 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="K618" t="n">
         <v>0</v>
@@ -28527,47 +28527,44 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="N618" t="n">
-        <v>9917.040000000001</v>
+        <v>4171.6682164634</v>
       </c>
       <c r="O618" t="n">
-        <v>208257.84</v>
+        <v>396308.480564023</v>
       </c>
       <c r="P618" t="n">
-        <v>15900</v>
+        <v>5000</v>
       </c>
       <c r="Q618" t="n">
-        <v>333900</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B619" t="n">
-        <v>7700154271143</v>
+          <t>SEB010</t>
+        </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J619" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
@@ -28576,35 +28573,35 @@
         <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="N619" t="n">
-        <v>2539.5719098712</v>
+        <v>7600</v>
       </c>
       <c r="O619" t="n">
-        <v>401252.3617596496</v>
+        <v>364800</v>
       </c>
       <c r="P619" t="n">
-        <v>2900</v>
+        <v>9500</v>
       </c>
       <c r="Q619" t="n">
-        <v>458200</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -28625,32 +28622,32 @@
         <v>95</v>
       </c>
       <c r="N620" t="n">
-        <v>4171.6682164634</v>
+        <v>5520</v>
       </c>
       <c r="O620" t="n">
-        <v>396308.480564023</v>
+        <v>524400</v>
       </c>
       <c r="P620" t="n">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="Q620" t="n">
-        <v>475000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -28659,7 +28656,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
@@ -28668,30 +28665,30 @@
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="N621" t="n">
-        <v>7600</v>
+        <v>1600</v>
       </c>
       <c r="O621" t="n">
-        <v>364800</v>
+        <v>132800</v>
       </c>
       <c r="P621" t="n">
-        <v>9500</v>
+        <v>2000</v>
       </c>
       <c r="Q621" t="n">
-        <v>456000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -28705,7 +28702,7 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
@@ -28714,35 +28711,38 @@
         <v>0</v>
       </c>
       <c r="M622" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="N622" t="n">
-        <v>5520</v>
+        <v>4091.4</v>
       </c>
       <c r="O622" t="n">
-        <v>524400</v>
+        <v>4091.4</v>
       </c>
       <c r="P622" t="n">
-        <v>6900</v>
+        <v>10000</v>
       </c>
       <c r="Q622" t="n">
-        <v>655500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>SEB09</t>
-        </is>
+          <t>SLT3728</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -28760,35 +28760,38 @@
         <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="N623" t="n">
-        <v>1600</v>
+        <v>2465</v>
       </c>
       <c r="O623" t="n">
-        <v>132800</v>
+        <v>788800</v>
       </c>
       <c r="P623" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="Q623" t="n">
-        <v>166000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
-        </is>
+          <t>SLT4037</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -28797,7 +28800,7 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="K624" t="n">
         <v>0</v>
@@ -28806,33 +28809,30 @@
         <v>0</v>
       </c>
       <c r="M624" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="N624" t="n">
-        <v>4091.4</v>
+        <v>1700</v>
       </c>
       <c r="O624" t="n">
-        <v>4091.4</v>
+        <v>652800</v>
       </c>
       <c r="P624" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="Q624" t="n">
-        <v>10000</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>SLT3728</t>
-        </is>
-      </c>
-      <c r="B625" t="n">
-        <v>7700154271143</v>
+          <t>T040-LJ</t>
+        </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>SQUISHIE HUELLA BLANCA 60gr SLT3728</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -28846,7 +28846,7 @@
         </is>
       </c>
       <c r="J625" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="K625" t="n">
         <v>0</v>
@@ -28855,33 +28855,30 @@
         <v>0</v>
       </c>
       <c r="M625" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="N625" t="n">
-        <v>2465</v>
+        <v>3661.88</v>
       </c>
       <c r="O625" t="n">
-        <v>788800</v>
+        <v>10985.64</v>
       </c>
       <c r="P625" t="n">
-        <v>3000</v>
+        <v>38900</v>
       </c>
       <c r="Q625" t="n">
-        <v>960000</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>SLT4037</t>
-        </is>
-      </c>
-      <c r="B626" t="n">
-        <v>7700154271143</v>
+          <t>T041-LJ</t>
+        </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>SQUISHE PATICA GATO 40gr SLT4037</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -28895,7 +28892,7 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
@@ -28904,30 +28901,30 @@
         <v>0</v>
       </c>
       <c r="M626" t="n">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="N626" t="n">
-        <v>1700</v>
+        <v>2797.08</v>
       </c>
       <c r="O626" t="n">
-        <v>652800</v>
+        <v>13985.4</v>
       </c>
       <c r="P626" t="n">
-        <v>2000</v>
+        <v>30900</v>
       </c>
       <c r="Q626" t="n">
-        <v>768000</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -28941,7 +28938,7 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
@@ -28950,30 +28947,30 @@
         <v>0</v>
       </c>
       <c r="M627" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N627" t="n">
-        <v>3661.88</v>
+        <v>3462.255</v>
       </c>
       <c r="O627" t="n">
-        <v>10985.64</v>
+        <v>38084.805</v>
       </c>
       <c r="P627" t="n">
-        <v>38900</v>
+        <v>42000</v>
       </c>
       <c r="Q627" t="n">
-        <v>116700</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -28987,7 +28984,7 @@
         </is>
       </c>
       <c r="J628" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K628" t="n">
         <v>0</v>
@@ -28996,30 +28993,30 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="N628" t="n">
-        <v>2797.08</v>
+        <v>24882.58</v>
       </c>
       <c r="O628" t="n">
-        <v>13985.4</v>
+        <v>696712.24</v>
       </c>
       <c r="P628" t="n">
-        <v>30900</v>
+        <v>31500</v>
       </c>
       <c r="Q628" t="n">
-        <v>154500</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -29033,7 +29030,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -29042,35 +29039,35 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N629" t="n">
-        <v>3462.255</v>
+        <v>0.8</v>
       </c>
       <c r="O629" t="n">
-        <v>38084.805</v>
+        <v>15.2</v>
       </c>
       <c r="P629" t="n">
-        <v>42000</v>
+        <v>22900</v>
       </c>
       <c r="Q629" t="n">
-        <v>462000</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -29079,7 +29076,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -29088,35 +29085,35 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="N630" t="n">
-        <v>24882.58</v>
+        <v>5186.45</v>
       </c>
       <c r="O630" t="n">
-        <v>696712.24</v>
+        <v>82983.2</v>
       </c>
       <c r="P630" t="n">
-        <v>31500</v>
+        <v>7200</v>
       </c>
       <c r="Q630" t="n">
-        <v>882000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>TB028</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -29125,7 +29122,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -29134,30 +29131,30 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N631" t="n">
-        <v>0.8</v>
+        <v>47796.1625</v>
       </c>
       <c r="O631" t="n">
-        <v>15.2</v>
+        <v>95592.325</v>
       </c>
       <c r="P631" t="n">
-        <v>22900</v>
+        <v>54000</v>
       </c>
       <c r="Q631" t="n">
-        <v>435100</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>TB115</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -29171,7 +29168,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29180,30 +29177,30 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="N632" t="n">
-        <v>5186.45</v>
+        <v>8006.3731111111</v>
       </c>
       <c r="O632" t="n">
-        <v>82983.2</v>
+        <v>344274.0437777773</v>
       </c>
       <c r="P632" t="n">
-        <v>7200</v>
+        <v>10000</v>
       </c>
       <c r="Q632" t="n">
-        <v>115200</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>TB122</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -29217,7 +29214,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -29226,110 +29223,18 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N633" t="n">
-        <v>47796.1625</v>
+        <v>47920</v>
       </c>
       <c r="O633" t="n">
-        <v>95592.325</v>
+        <v>191680</v>
       </c>
       <c r="P633" t="n">
-        <v>54000</v>
+        <v>59900</v>
       </c>
       <c r="Q633" t="n">
-        <v>108000</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>TB115</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I634" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J634" t="n">
-        <v>43</v>
-      </c>
-      <c r="K634" t="n">
-        <v>0</v>
-      </c>
-      <c r="L634" t="n">
-        <v>0</v>
-      </c>
-      <c r="M634" t="n">
-        <v>43</v>
-      </c>
-      <c r="N634" t="n">
-        <v>8006.3731111111</v>
-      </c>
-      <c r="O634" t="n">
-        <v>344274.0437777773</v>
-      </c>
-      <c r="P634" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Q634" t="n">
-        <v>430000</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>TB122</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>PELUCHE DRAGON 50CM DRAG-50</t>
-        </is>
-      </c>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I635" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J635" t="n">
-        <v>4</v>
-      </c>
-      <c r="K635" t="n">
-        <v>0</v>
-      </c>
-      <c r="L635" t="n">
-        <v>0</v>
-      </c>
-      <c r="M635" t="n">
-        <v>4</v>
-      </c>
-      <c r="N635" t="n">
-        <v>47920</v>
-      </c>
-      <c r="O635" t="n">
-        <v>191680</v>
-      </c>
-      <c r="P635" t="n">
-        <v>59900</v>
-      </c>
-      <c r="Q635" t="n">
         <v>239600</v>
       </c>
     </row>
